--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>17.08.2026 09:28:02</t>
+    <t>17.08.2026 10:07:23</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -7733,25 +7733,25 @@
         <v>4</v>
       </c>
       <c r="E30" s="7">
-        <v>0.021724999999999998</v>
+        <v>0.02487</v>
       </c>
       <c r="F30" s="7">
-        <v>0.060046999999999996</v>
+        <v>0.06331</v>
       </c>
       <c r="G30" s="7">
-        <v>0.152836</v>
+        <v>0.156385</v>
       </c>
       <c r="H30" s="7">
-        <v>0.273254</v>
+        <v>0.27717400000000003</v>
       </c>
       <c r="I30" s="7">
-        <v>0.439672</v>
+        <v>0.44410400000000005</v>
       </c>
       <c r="J30" s="7">
-        <v>1.931103</v>
+        <v>1.940126</v>
       </c>
       <c r="K30" s="7">
-        <v>8.104554</v>
+        <v>8.132582</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -8504,16 +8504,16 @@
         <v>6</v>
       </c>
       <c r="E53" s="7">
-        <v>0.11410500000000001</v>
+        <v>0.114254</v>
       </c>
       <c r="F53" s="7">
-        <v>0.009500999999999999</v>
+        <v>0.009636</v>
       </c>
       <c r="G53" s="7">
-        <v>-0.056749</v>
+        <v>-0.056623</v>
       </c>
       <c r="H53" s="7">
-        <v>0.12061400000000001</v>
+        <v>0.120764</v>
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
@@ -8562,25 +8562,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.008419</v>
+        <v>0.007992</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.011766</v>
+        <v>-0.012183999999999999</v>
       </c>
       <c r="G55" s="7">
-        <v>-0.051269</v>
+        <v>-0.051670999999999995</v>
       </c>
       <c r="H55" s="7">
-        <v>0.165234</v>
+        <v>0.16474</v>
       </c>
       <c r="I55" s="7">
-        <v>0.21590299999999998</v>
+        <v>0.215387</v>
       </c>
       <c r="J55" s="7">
-        <v>0.849881</v>
+        <v>0.849098</v>
       </c>
       <c r="K55" s="7">
-        <v>6.475669</v>
+        <v>6.472500999999999</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -11216,22 +11216,22 @@
         <v>6</v>
       </c>
       <c r="E141" s="7">
-        <v>-0.018216</v>
+        <v>-0.018231999999999998</v>
       </c>
       <c r="F141" s="7">
-        <v>-0.024647000000000002</v>
+        <v>-0.024663</v>
       </c>
       <c r="G141" s="7">
-        <v>0.019644</v>
+        <v>0.019627</v>
       </c>
       <c r="H141" s="7">
-        <v>0.248839</v>
+        <v>0.24881799999999998</v>
       </c>
       <c r="I141" s="7">
-        <v>0.230875</v>
+        <v>0.230854</v>
       </c>
       <c r="J141" s="7">
-        <v>0.787563</v>
+        <v>0.7875329999999999</v>
       </c>
       <c r="K141" s="7"/>
     </row>
@@ -11445,16 +11445,16 @@
         <v>6</v>
       </c>
       <c r="E148" s="7">
-        <v>0.111395</v>
+        <v>0.11136900000000001</v>
       </c>
       <c r="F148" s="7">
-        <v>0.167948</v>
+        <v>0.16792</v>
       </c>
       <c r="G148" s="7">
-        <v>0.13619</v>
+        <v>0.136163</v>
       </c>
       <c r="H148" s="7">
-        <v>0.22150999999999998</v>
+        <v>0.22148099999999998</v>
       </c>
       <c r="I148" s="7"/>
       <c r="J148" s="7"/>
@@ -12418,19 +12418,19 @@
         <v>6</v>
       </c>
       <c r="E179" s="7">
-        <v>0.008326</v>
+        <v>0.008193</v>
       </c>
       <c r="F179" s="7">
-        <v>0.030402</v>
+        <v>0.030265</v>
       </c>
       <c r="G179" s="7">
-        <v>0.024194</v>
+        <v>0.024058000000000003</v>
       </c>
       <c r="H179" s="7">
-        <v>0.26537700000000003</v>
+        <v>0.26520900000000003</v>
       </c>
       <c r="I179" s="7">
-        <v>0.300954</v>
+        <v>0.300782</v>
       </c>
       <c r="J179" s="7"/>
       <c r="K179" s="7"/>
@@ -14277,22 +14277,22 @@
       </c>
       <c r="D238" s="6"/>
       <c r="E238" s="7">
-        <v>0.025501999999999997</v>
+        <v>0.025767</v>
       </c>
       <c r="F238" s="7">
-        <v>0.049291999999999996</v>
+        <v>0.049562999999999996</v>
       </c>
       <c r="G238" s="7">
-        <v>0.075869</v>
+        <v>0.076147</v>
       </c>
       <c r="H238" s="7">
-        <v>0.110291</v>
+        <v>0.11057700000000001</v>
       </c>
       <c r="I238" s="7">
-        <v>0.18209599999999998</v>
+        <v>0.182401</v>
       </c>
       <c r="J238" s="7">
-        <v>0.988061</v>
+        <v>0.988574</v>
       </c>
       <c r="K238" s="7"/>
     </row>
@@ -14956,22 +14956,22 @@
         <v>6</v>
       </c>
       <c r="E259" s="7">
-        <v>0.04848499999999999</v>
+        <v>0.050668</v>
       </c>
       <c r="F259" s="7">
-        <v>0.079137</v>
+        <v>0.081383</v>
       </c>
       <c r="G259" s="7">
-        <v>0.358275</v>
+        <v>0.361102</v>
       </c>
       <c r="H259" s="7">
-        <v>0.364211</v>
+        <v>0.367051</v>
       </c>
       <c r="I259" s="7">
-        <v>0.5523060000000001</v>
+        <v>0.555537</v>
       </c>
       <c r="J259" s="7">
-        <v>2.533017</v>
+        <v>2.540371</v>
       </c>
       <c r="K259" s="7"/>
     </row>
@@ -15315,22 +15315,22 @@
         <v>4</v>
       </c>
       <c r="E270" s="7">
-        <v>0.026844999999999997</v>
+        <v>0.028515000000000002</v>
       </c>
       <c r="F270" s="7">
-        <v>0.057504</v>
+        <v>0.059224</v>
       </c>
       <c r="G270" s="7">
-        <v>0.104136</v>
+        <v>0.105932</v>
       </c>
       <c r="H270" s="7">
-        <v>0.19324000000000002</v>
+        <v>0.195181</v>
       </c>
       <c r="I270" s="7">
-        <v>0.346902</v>
+        <v>0.34909300000000004</v>
       </c>
       <c r="J270" s="7">
-        <v>1.87418</v>
+        <v>1.8788550000000002</v>
       </c>
       <c r="K270" s="7"/>
     </row>
@@ -15523,25 +15523,25 @@
         <v>3</v>
       </c>
       <c r="E276" s="7">
-        <v>0</v>
+        <v>0.030651</v>
       </c>
       <c r="F276" s="7">
-        <v>0</v>
+        <v>0.074408</v>
       </c>
       <c r="G276" s="7">
-        <v>0</v>
+        <v>0.11505699999999999</v>
       </c>
       <c r="H276" s="7">
-        <v>0</v>
+        <v>0.220631</v>
       </c>
       <c r="I276" s="7">
-        <v>0</v>
+        <v>0.403136</v>
       </c>
       <c r="J276" s="7">
-        <v>0</v>
+        <v>2.229012</v>
       </c>
       <c r="K276" s="7">
-        <v>0</v>
+        <v>6.129993</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -15795,22 +15795,22 @@
         <v>6</v>
       </c>
       <c r="E284" s="7">
-        <v>0</v>
+        <v>0.024404</v>
       </c>
       <c r="F284" s="7">
-        <v>0</v>
+        <v>0.038795</v>
       </c>
       <c r="G284" s="7">
-        <v>0</v>
+        <v>0.30145</v>
       </c>
       <c r="H284" s="7">
-        <v>0</v>
+        <v>0.37626800000000005</v>
       </c>
       <c r="I284" s="7">
-        <v>0</v>
+        <v>0.605611</v>
       </c>
       <c r="J284" s="7">
-        <v>0</v>
+        <v>3.783596</v>
       </c>
       <c r="K284" s="7"/>
     </row>
@@ -15828,22 +15828,22 @@
         <v>6</v>
       </c>
       <c r="E285" s="7">
-        <v>0.057050000000000003</v>
+        <v>0.057295</v>
       </c>
       <c r="F285" s="7">
-        <v>-0.001675</v>
+        <v>-0.001444</v>
       </c>
       <c r="G285" s="7">
-        <v>0.162255</v>
+        <v>0.162525</v>
       </c>
       <c r="H285" s="7">
-        <v>0.256994</v>
+        <v>0.257285</v>
       </c>
       <c r="I285" s="7">
-        <v>0.505772</v>
+        <v>0.5061209999999999</v>
       </c>
       <c r="J285" s="7">
-        <v>1.5219649999999998</v>
+        <v>1.522549</v>
       </c>
       <c r="K285" s="7"/>
     </row>
@@ -15931,19 +15931,19 @@
         <v>5</v>
       </c>
       <c r="E288" s="7">
-        <v>0</v>
+        <v>-0.012492000000000001</v>
       </c>
       <c r="F288" s="7">
-        <v>0</v>
+        <v>-0.000766</v>
       </c>
       <c r="G288" s="7">
-        <v>0</v>
+        <v>-0.010805</v>
       </c>
       <c r="H288" s="7">
-        <v>0</v>
+        <v>0.14472200000000002</v>
       </c>
       <c r="I288" s="7">
-        <v>0</v>
+        <v>0.20927700000000002</v>
       </c>
       <c r="J288" s="7"/>
       <c r="K288" s="7"/>
@@ -16195,25 +16195,25 @@
         <v>6</v>
       </c>
       <c r="E296" s="7">
-        <v>0.015607</v>
+        <v>0.016242</v>
       </c>
       <c r="F296" s="7">
-        <v>0.024709</v>
+        <v>0.02535</v>
       </c>
       <c r="G296" s="7">
-        <v>-0.000123</v>
+        <v>0.0005020000000000001</v>
       </c>
       <c r="H296" s="7">
-        <v>0.249853</v>
+        <v>0.250634</v>
       </c>
       <c r="I296" s="7">
-        <v>0.386171</v>
+        <v>0.387038</v>
       </c>
       <c r="J296" s="7">
-        <v>1.625045</v>
+        <v>1.626685</v>
       </c>
       <c r="K296" s="7">
-        <v>13.264882</v>
+        <v>13.273798</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -16909,25 +16909,25 @@
         <v>2</v>
       </c>
       <c r="E318" s="7">
-        <v>0</v>
+        <v>0.030537</v>
       </c>
       <c r="F318" s="7">
-        <v>0</v>
+        <v>0.082134</v>
       </c>
       <c r="G318" s="7">
-        <v>0</v>
+        <v>0.141113</v>
       </c>
       <c r="H318" s="7">
-        <v>0</v>
+        <v>0.221173</v>
       </c>
       <c r="I318" s="7">
-        <v>0</v>
+        <v>0.391472</v>
       </c>
       <c r="J318" s="7">
-        <v>0</v>
+        <v>2.0763409999999998</v>
       </c>
       <c r="K318" s="7">
-        <v>0</v>
+        <v>3.82955</v>
       </c>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
@@ -16942,25 +16942,25 @@
       </c>
       <c r="D319" s="6"/>
       <c r="E319" s="7">
-        <v>0</v>
+        <v>0.022913000000000003</v>
       </c>
       <c r="F319" s="7">
-        <v>0</v>
+        <v>0.070068</v>
       </c>
       <c r="G319" s="7">
-        <v>0</v>
+        <v>0.100529</v>
       </c>
       <c r="H319" s="7">
-        <v>0</v>
+        <v>0.130235</v>
       </c>
       <c r="I319" s="7">
-        <v>0</v>
+        <v>0.23598400000000003</v>
       </c>
       <c r="J319" s="7">
-        <v>0</v>
+        <v>1.30846</v>
       </c>
       <c r="K319" s="7">
-        <v>0</v>
+        <v>6.136268</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
@@ -17047,25 +17047,25 @@
         <v>3</v>
       </c>
       <c r="E322" s="7">
-        <v>0</v>
+        <v>0.030899</v>
       </c>
       <c r="F322" s="7">
-        <v>0</v>
+        <v>0.07510900000000001</v>
       </c>
       <c r="G322" s="7">
-        <v>0</v>
+        <v>0.12256299999999999</v>
       </c>
       <c r="H322" s="7">
-        <v>0</v>
+        <v>0.229188</v>
       </c>
       <c r="I322" s="7">
-        <v>0</v>
+        <v>0.40958799999999995</v>
       </c>
       <c r="J322" s="7">
-        <v>0</v>
+        <v>2.192141</v>
       </c>
       <c r="K322" s="7">
-        <v>0</v>
+        <v>6.2930600000000005</v>
       </c>
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
@@ -17173,25 +17173,25 @@
         <v>4</v>
       </c>
       <c r="E326" s="7">
-        <v>0</v>
+        <v>0.029990000000000003</v>
       </c>
       <c r="F326" s="7">
-        <v>0</v>
+        <v>0.062794</v>
       </c>
       <c r="G326" s="7">
-        <v>0</v>
+        <v>0.085848</v>
       </c>
       <c r="H326" s="7">
-        <v>0</v>
+        <v>0.238737</v>
       </c>
       <c r="I326" s="7">
-        <v>0</v>
+        <v>0.415611</v>
       </c>
       <c r="J326" s="7">
-        <v>0</v>
+        <v>2.18361</v>
       </c>
       <c r="K326" s="7">
-        <v>0</v>
+        <v>7.082282</v>
       </c>
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
@@ -17505,25 +17505,25 @@
         <v>6</v>
       </c>
       <c r="E336" s="7">
-        <v>0</v>
+        <v>0.047958999999999995</v>
       </c>
       <c r="F336" s="7">
-        <v>0</v>
+        <v>0.10617800000000001</v>
       </c>
       <c r="G336" s="7">
-        <v>0</v>
+        <v>0.08402799999999999</v>
       </c>
       <c r="H336" s="7">
-        <v>0</v>
+        <v>0.227025</v>
       </c>
       <c r="I336" s="7">
-        <v>0</v>
+        <v>0.40463</v>
       </c>
       <c r="J336" s="7">
-        <v>0</v>
+        <v>1.753128</v>
       </c>
       <c r="K336" s="7">
-        <v>0</v>
+        <v>4.871635</v>
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
@@ -17540,25 +17540,25 @@
         <v>7</v>
       </c>
       <c r="E337" s="7">
-        <v>0</v>
+        <v>0.168959</v>
       </c>
       <c r="F337" s="7">
-        <v>0</v>
+        <v>-0.122186</v>
       </c>
       <c r="G337" s="7">
-        <v>0</v>
+        <v>-0.096972</v>
       </c>
       <c r="H337" s="7">
-        <v>0</v>
+        <v>-0.040212000000000005</v>
       </c>
       <c r="I337" s="7">
-        <v>0</v>
+        <v>0.856693</v>
       </c>
       <c r="J337" s="7">
-        <v>0</v>
+        <v>3.535763</v>
       </c>
       <c r="K337" s="7">
-        <v>0</v>
+        <v>10.737421999999999</v>
       </c>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
@@ -17629,25 +17629,25 @@
         <v>6</v>
       </c>
       <c r="E340" s="7">
-        <v>0</v>
+        <v>0.056315</v>
       </c>
       <c r="F340" s="7">
-        <v>0</v>
+        <v>0.125957</v>
       </c>
       <c r="G340" s="7">
-        <v>0</v>
+        <v>0.48324</v>
       </c>
       <c r="H340" s="7">
-        <v>0</v>
+        <v>0.483592</v>
       </c>
       <c r="I340" s="7">
-        <v>0</v>
+        <v>0.828684</v>
       </c>
       <c r="J340" s="7">
-        <v>0</v>
+        <v>2.737409</v>
       </c>
       <c r="K340" s="7">
-        <v>0</v>
+        <v>8.734704</v>
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
@@ -17664,16 +17664,16 @@
         <v>7</v>
       </c>
       <c r="E341" s="7">
-        <v>0</v>
+        <v>0.15987600000000002</v>
       </c>
       <c r="F341" s="7">
-        <v>0</v>
+        <v>-0.12667799999999999</v>
       </c>
       <c r="G341" s="7">
-        <v>0</v>
+        <v>-0.09838</v>
       </c>
       <c r="H341" s="7">
-        <v>0</v>
+        <v>-0.064844</v>
       </c>
       <c r="I341" s="7"/>
       <c r="J341" s="7"/>
@@ -17759,22 +17759,22 @@
         <v>6</v>
       </c>
       <c r="E344" s="7">
-        <v>0</v>
+        <v>0.0057799999999999995</v>
       </c>
       <c r="F344" s="7">
-        <v>0</v>
+        <v>-0.050197000000000006</v>
       </c>
       <c r="G344" s="7">
-        <v>0</v>
+        <v>0.090364</v>
       </c>
       <c r="H344" s="7">
-        <v>0</v>
+        <v>0.203685</v>
       </c>
       <c r="I344" s="7">
-        <v>0</v>
+        <v>0.414436</v>
       </c>
       <c r="J344" s="7">
-        <v>0</v>
+        <v>1.276357</v>
       </c>
       <c r="K344" s="7"/>
     </row>
@@ -17792,22 +17792,22 @@
         <v>5</v>
       </c>
       <c r="E345" s="7">
-        <v>0</v>
+        <v>0.021116000000000003</v>
       </c>
       <c r="F345" s="7">
-        <v>0</v>
+        <v>0.026705999999999997</v>
       </c>
       <c r="G345" s="7">
-        <v>0</v>
+        <v>-0.00045</v>
       </c>
       <c r="H345" s="7">
-        <v>0</v>
+        <v>0.168852</v>
       </c>
       <c r="I345" s="7">
-        <v>0</v>
+        <v>0.304578</v>
       </c>
       <c r="J345" s="7">
-        <v>0</v>
+        <v>1.672878</v>
       </c>
       <c r="K345" s="7"/>
     </row>
@@ -17860,22 +17860,22 @@
         <v>6</v>
       </c>
       <c r="E347" s="7">
-        <v>0</v>
+        <v>0.064107</v>
       </c>
       <c r="F347" s="7">
-        <v>0</v>
+        <v>-0.003614</v>
       </c>
       <c r="G347" s="7">
-        <v>0</v>
+        <v>0.165628</v>
       </c>
       <c r="H347" s="7">
-        <v>0</v>
+        <v>0.221878</v>
       </c>
       <c r="I347" s="7">
-        <v>0</v>
+        <v>0.553499</v>
       </c>
       <c r="J347" s="7">
-        <v>0</v>
+        <v>1.4900829999999998</v>
       </c>
       <c r="K347" s="7"/>
     </row>
@@ -17893,22 +17893,22 @@
         <v>6</v>
       </c>
       <c r="E348" s="7">
-        <v>0</v>
+        <v>0.028768</v>
       </c>
       <c r="F348" s="7">
-        <v>0</v>
+        <v>0.181756</v>
       </c>
       <c r="G348" s="7">
-        <v>0</v>
+        <v>0.261232</v>
       </c>
       <c r="H348" s="7">
-        <v>0</v>
+        <v>0.314767</v>
       </c>
       <c r="I348" s="7">
-        <v>0</v>
+        <v>0.538717</v>
       </c>
       <c r="J348" s="7">
-        <v>0</v>
+        <v>1.353882</v>
       </c>
       <c r="K348" s="7"/>
     </row>
@@ -17926,25 +17926,25 @@
         <v>5</v>
       </c>
       <c r="E349" s="7">
-        <v>0</v>
+        <v>0.019811000000000002</v>
       </c>
       <c r="F349" s="7">
-        <v>0</v>
+        <v>-0.032295</v>
       </c>
       <c r="G349" s="7">
-        <v>0</v>
+        <v>0.063776</v>
       </c>
       <c r="H349" s="7">
-        <v>0</v>
+        <v>0.279484</v>
       </c>
       <c r="I349" s="7">
-        <v>0</v>
+        <v>0.551612</v>
       </c>
       <c r="J349" s="7">
-        <v>0</v>
+        <v>0.883588</v>
       </c>
       <c r="K349" s="7">
-        <v>0</v>
+        <v>4.3928769999999995</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
@@ -17996,22 +17996,22 @@
         <v>5</v>
       </c>
       <c r="E351" s="7">
-        <v>0</v>
+        <v>0.009762999999999999</v>
       </c>
       <c r="F351" s="7">
-        <v>0</v>
+        <v>0.04128999999999999</v>
       </c>
       <c r="G351" s="7">
-        <v>0</v>
+        <v>0.092014</v>
       </c>
       <c r="H351" s="7">
-        <v>0</v>
+        <v>0.34027500000000005</v>
       </c>
       <c r="I351" s="7">
-        <v>0</v>
+        <v>0.415701</v>
       </c>
       <c r="J351" s="7">
-        <v>0</v>
+        <v>0.8559019999999999</v>
       </c>
       <c r="K351" s="7"/>
     </row>
@@ -18099,25 +18099,25 @@
         <v>3</v>
       </c>
       <c r="E354" s="7">
-        <v>0</v>
+        <v>0.029112</v>
       </c>
       <c r="F354" s="7">
-        <v>0</v>
+        <v>0.06988699999999999</v>
       </c>
       <c r="G354" s="7">
-        <v>0</v>
+        <v>0.123897</v>
       </c>
       <c r="H354" s="7">
-        <v>0</v>
+        <v>0.21962800000000002</v>
       </c>
       <c r="I354" s="7">
-        <v>0</v>
+        <v>0.39563699999999996</v>
       </c>
       <c r="J354" s="7">
-        <v>0</v>
+        <v>2.18669</v>
       </c>
       <c r="K354" s="7">
-        <v>0</v>
+        <v>6.032916</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -18169,25 +18169,25 @@
         <v>5</v>
       </c>
       <c r="E356" s="7">
-        <v>0</v>
+        <v>0.044286000000000006</v>
       </c>
       <c r="F356" s="7">
-        <v>0</v>
+        <v>0.075754</v>
       </c>
       <c r="G356" s="7">
-        <v>0</v>
+        <v>0.140184</v>
       </c>
       <c r="H356" s="7">
-        <v>0</v>
+        <v>0.252043</v>
       </c>
       <c r="I356" s="7">
-        <v>0</v>
+        <v>0.38433100000000003</v>
       </c>
       <c r="J356" s="7">
-        <v>0</v>
+        <v>1.471258</v>
       </c>
       <c r="K356" s="7">
-        <v>0</v>
+        <v>6.33789</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
@@ -18204,22 +18204,22 @@
         <v>6</v>
       </c>
       <c r="E357" s="7">
-        <v>0</v>
+        <v>0.022336</v>
       </c>
       <c r="F357" s="7">
-        <v>0</v>
+        <v>0.159911</v>
       </c>
       <c r="G357" s="7">
-        <v>0</v>
+        <v>0.063545</v>
       </c>
       <c r="H357" s="7">
-        <v>0</v>
+        <v>0.142993</v>
       </c>
       <c r="I357" s="7">
-        <v>0</v>
+        <v>0.195999</v>
       </c>
       <c r="J357" s="7">
-        <v>0</v>
+        <v>1.397564</v>
       </c>
       <c r="K357" s="7"/>
     </row>
@@ -18324,16 +18324,16 @@
         <v>7</v>
       </c>
       <c r="E361" s="7">
-        <v>0.08069699999999999</v>
+        <v>0.074113</v>
       </c>
       <c r="F361" s="7">
-        <v>-0.001933</v>
+        <v>-0.008012</v>
       </c>
       <c r="G361" s="7">
-        <v>0.032546</v>
+        <v>0.026255999999999998</v>
       </c>
       <c r="H361" s="7">
-        <v>0.22157</v>
+        <v>0.214129</v>
       </c>
       <c r="I361" s="7"/>
       <c r="J361" s="7"/>
@@ -18415,22 +18415,22 @@
       </c>
       <c r="D364" s="6"/>
       <c r="E364" s="7">
-        <v>0</v>
+        <v>0.025605000000000003</v>
       </c>
       <c r="F364" s="7">
-        <v>0</v>
+        <v>0.050205</v>
       </c>
       <c r="G364" s="7">
-        <v>0</v>
+        <v>0.077834</v>
       </c>
       <c r="H364" s="7">
-        <v>0</v>
+        <v>0.211704</v>
       </c>
       <c r="I364" s="7">
-        <v>0</v>
+        <v>0.31156300000000003</v>
       </c>
       <c r="J364" s="7">
-        <v>0</v>
+        <v>1.54739</v>
       </c>
       <c r="K364" s="7"/>
     </row>
@@ -19337,25 +19337,25 @@
       </c>
       <c r="D394" s="6"/>
       <c r="E394" s="7">
-        <v>0.040541</v>
+        <v>0.040443</v>
       </c>
       <c r="F394" s="7">
-        <v>0.090037</v>
+        <v>0.089933</v>
       </c>
       <c r="G394" s="7">
-        <v>0.167225</v>
+        <v>0.167114</v>
       </c>
       <c r="H394" s="7">
-        <v>0.236854</v>
+        <v>0.236736</v>
       </c>
       <c r="I394" s="7">
-        <v>0.367128</v>
+        <v>0.36699800000000005</v>
       </c>
       <c r="J394" s="7">
-        <v>1.543692</v>
+        <v>1.5434510000000001</v>
       </c>
       <c r="K394" s="7">
-        <v>6.4565719999999995</v>
+        <v>6.455865</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
@@ -19721,7 +19721,7 @@
         <v>6</v>
       </c>
       <c r="E406" s="7">
-        <v>0.10462300000000001</v>
+        <v>0.106452</v>
       </c>
       <c r="F406" s="7"/>
       <c r="G406" s="7"/>
@@ -20198,22 +20198,22 @@
         <v>3</v>
       </c>
       <c r="E421" s="7">
-        <v>0.019168</v>
+        <v>0.026225000000000002</v>
       </c>
       <c r="F421" s="7">
-        <v>0.07415</v>
+        <v>0.08158699999999999</v>
       </c>
       <c r="G421" s="7">
-        <v>0.17082999999999998</v>
+        <v>0.17893599999999998</v>
       </c>
       <c r="H421" s="7">
-        <v>0.21113900000000002</v>
+        <v>0.219524</v>
       </c>
       <c r="I421" s="7">
-        <v>0.376903</v>
+        <v>0.386436</v>
       </c>
       <c r="J421" s="7">
-        <v>1.8855410000000001</v>
+        <v>1.905519</v>
       </c>
       <c r="K421" s="7"/>
     </row>
@@ -22120,16 +22120,16 @@
         <v>2</v>
       </c>
       <c r="E479" s="7">
-        <v>0</v>
+        <v>0.030533</v>
       </c>
       <c r="F479" s="7">
-        <v>0</v>
+        <v>0.097964</v>
       </c>
       <c r="G479" s="7">
-        <v>0</v>
+        <v>0.248163</v>
       </c>
       <c r="H479" s="7">
-        <v>0</v>
+        <v>0.294714</v>
       </c>
       <c r="I479" s="7"/>
       <c r="J479" s="7"/>
@@ -22793,22 +22793,22 @@
       </c>
       <c r="D500" s="6"/>
       <c r="E500" s="7">
-        <v>0</v>
+        <v>0.02469</v>
       </c>
       <c r="F500" s="7">
-        <v>0</v>
+        <v>0.046659</v>
       </c>
       <c r="G500" s="7">
-        <v>0</v>
+        <v>0.07029099999999999</v>
       </c>
       <c r="H500" s="7">
-        <v>0</v>
+        <v>0.10333</v>
       </c>
       <c r="I500" s="7">
-        <v>0</v>
+        <v>0.170367</v>
       </c>
       <c r="J500" s="7">
-        <v>0</v>
+        <v>0.92931</v>
       </c>
       <c r="K500" s="7"/>
     </row>
@@ -22880,22 +22880,22 @@
         <v>2</v>
       </c>
       <c r="E503" s="7">
-        <v>0</v>
+        <v>0.022391</v>
       </c>
       <c r="F503" s="7">
-        <v>0</v>
+        <v>0.057137</v>
       </c>
       <c r="G503" s="7">
-        <v>0</v>
+        <v>0.208182</v>
       </c>
       <c r="H503" s="7">
-        <v>0</v>
+        <v>0.32634500000000005</v>
       </c>
       <c r="I503" s="7">
-        <v>0</v>
+        <v>0.543988</v>
       </c>
       <c r="J503" s="7">
-        <v>0</v>
+        <v>2.348846</v>
       </c>
       <c r="K503" s="7"/>
     </row>
@@ -22913,19 +22913,19 @@
         <v>3</v>
       </c>
       <c r="E504" s="7">
-        <v>0</v>
+        <v>0.02778</v>
       </c>
       <c r="F504" s="7">
-        <v>0</v>
+        <v>0.09692</v>
       </c>
       <c r="G504" s="7">
-        <v>0</v>
+        <v>0.23759899999999998</v>
       </c>
       <c r="H504" s="7">
-        <v>0</v>
+        <v>0.38978</v>
       </c>
       <c r="I504" s="7">
-        <v>0</v>
+        <v>0.563374</v>
       </c>
       <c r="J504" s="7"/>
       <c r="K504" s="7"/>
@@ -22942,22 +22942,22 @@
       </c>
       <c r="D505" s="6"/>
       <c r="E505" s="7">
-        <v>0</v>
+        <v>0.01775</v>
       </c>
       <c r="F505" s="7">
-        <v>0</v>
+        <v>0.056554</v>
       </c>
       <c r="G505" s="7">
-        <v>0</v>
+        <v>0.103992</v>
       </c>
       <c r="H505" s="7">
-        <v>0</v>
+        <v>0.127018</v>
       </c>
       <c r="I505" s="7">
-        <v>0</v>
+        <v>0.193828</v>
       </c>
       <c r="J505" s="7">
-        <v>0</v>
+        <v>0.884877</v>
       </c>
       <c r="K505" s="7"/>
     </row>
@@ -23031,19 +23031,19 @@
         <v>6</v>
       </c>
       <c r="E508" s="7">
-        <v>0</v>
+        <v>0.166486</v>
       </c>
       <c r="F508" s="7">
-        <v>0</v>
+        <v>-0.104735</v>
       </c>
       <c r="G508" s="7">
-        <v>0</v>
+        <v>-0.062319000000000006</v>
       </c>
       <c r="H508" s="7">
-        <v>0</v>
+        <v>-0.017601</v>
       </c>
       <c r="I508" s="7">
-        <v>0</v>
+        <v>0.913208</v>
       </c>
       <c r="J508" s="7"/>
       <c r="K508" s="7"/>
@@ -23378,16 +23378,16 @@
         <v>6</v>
       </c>
       <c r="E519" s="7">
-        <v>0</v>
+        <v>0.038381</v>
       </c>
       <c r="F519" s="7">
-        <v>0</v>
+        <v>0.037334</v>
       </c>
       <c r="G519" s="7">
-        <v>0</v>
+        <v>0.16159199999999999</v>
       </c>
       <c r="H519" s="7">
-        <v>0</v>
+        <v>0.338239</v>
       </c>
       <c r="I519" s="7"/>
       <c r="J519" s="7"/>
@@ -23508,19 +23508,19 @@
         <v>2</v>
       </c>
       <c r="E523" s="7">
-        <v>0.03748</v>
+        <v>0.037482</v>
       </c>
       <c r="F523" s="7">
-        <v>0.11570399999999999</v>
+        <v>0.115706</v>
       </c>
       <c r="G523" s="7">
-        <v>0.244629</v>
+        <v>0.24463200000000002</v>
       </c>
       <c r="H523" s="7">
-        <v>0.317684</v>
+        <v>0.317687</v>
       </c>
       <c r="I523" s="7">
-        <v>0.5457500000000001</v>
+        <v>0.5457529999999999</v>
       </c>
       <c r="J523" s="7"/>
       <c r="K523" s="7"/>
@@ -23630,25 +23630,25 @@
         <v>1</v>
       </c>
       <c r="E527" s="7">
-        <v>0</v>
+        <v>0.032379</v>
       </c>
       <c r="F527" s="7">
-        <v>0</v>
+        <v>0.100024</v>
       </c>
       <c r="G527" s="7">
-        <v>0</v>
+        <v>0.204879</v>
       </c>
       <c r="H527" s="7">
-        <v>0</v>
+        <v>0.258229</v>
       </c>
       <c r="I527" s="7">
-        <v>0</v>
+        <v>0.439743</v>
       </c>
       <c r="J527" s="7">
-        <v>0</v>
+        <v>2.159426</v>
       </c>
       <c r="K527" s="7">
-        <v>0</v>
+        <v>3.5380700000000003</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.25">
@@ -23665,19 +23665,19 @@
         <v>2</v>
       </c>
       <c r="E528" s="7">
-        <v>0</v>
+        <v>0.0032300000000000002</v>
       </c>
       <c r="F528" s="7">
-        <v>0</v>
+        <v>0.03878</v>
       </c>
       <c r="G528" s="7">
-        <v>0</v>
+        <v>0.139615</v>
       </c>
       <c r="H528" s="7">
-        <v>0</v>
+        <v>0.235175</v>
       </c>
       <c r="I528" s="7">
-        <v>0</v>
+        <v>0.42292799999999997</v>
       </c>
       <c r="J528" s="7"/>
       <c r="K528" s="7"/>
@@ -23783,19 +23783,19 @@
         <v>5</v>
       </c>
       <c r="E532" s="7">
-        <v>0</v>
+        <v>0.073956</v>
       </c>
       <c r="F532" s="7">
-        <v>0</v>
+        <v>0.064092</v>
       </c>
       <c r="G532" s="7">
-        <v>0</v>
+        <v>0.216388</v>
       </c>
       <c r="H532" s="7">
-        <v>0</v>
+        <v>0.45345599999999997</v>
       </c>
       <c r="I532" s="7">
-        <v>0</v>
+        <v>0.6613939999999999</v>
       </c>
       <c r="J532" s="7"/>
       <c r="K532" s="7"/>
@@ -23901,19 +23901,19 @@
         <v>6</v>
       </c>
       <c r="E536" s="7">
-        <v>0</v>
+        <v>0.00105</v>
       </c>
       <c r="F536" s="7">
-        <v>0</v>
+        <v>0.066417</v>
       </c>
       <c r="G536" s="7">
-        <v>0</v>
+        <v>0.1942</v>
       </c>
       <c r="H536" s="7">
-        <v>0</v>
+        <v>0.40332999999999997</v>
       </c>
       <c r="I536" s="7">
-        <v>0</v>
+        <v>0.417468</v>
       </c>
       <c r="J536" s="7"/>
       <c r="K536" s="7"/>
@@ -23932,25 +23932,25 @@
         <v>6</v>
       </c>
       <c r="E537" s="7">
-        <v>0</v>
+        <v>0.013552999999999999</v>
       </c>
       <c r="F537" s="7">
-        <v>0</v>
+        <v>0.008341</v>
       </c>
       <c r="G537" s="7">
-        <v>0</v>
+        <v>0.147017</v>
       </c>
       <c r="H537" s="7">
-        <v>0</v>
+        <v>0.40482799999999997</v>
       </c>
       <c r="I537" s="7">
-        <v>0</v>
+        <v>0.49879199999999996</v>
       </c>
       <c r="J537" s="7">
-        <v>0</v>
+        <v>1.691105</v>
       </c>
       <c r="K537" s="7">
-        <v>0</v>
+        <v>13.714726</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.25">
@@ -23965,19 +23965,19 @@
       </c>
       <c r="D538" s="6"/>
       <c r="E538" s="7">
-        <v>0</v>
+        <v>0.016982</v>
       </c>
       <c r="F538" s="7">
-        <v>0</v>
+        <v>0.049977999999999995</v>
       </c>
       <c r="G538" s="7">
-        <v>0</v>
+        <v>0.072625</v>
       </c>
       <c r="H538" s="7">
-        <v>0</v>
+        <v>0.094118</v>
       </c>
       <c r="I538" s="7">
-        <v>0</v>
+        <v>0.17386</v>
       </c>
       <c r="J538" s="7"/>
       <c r="K538" s="7"/>
@@ -24120,22 +24120,22 @@
         <v>6</v>
       </c>
       <c r="E543" s="7">
-        <v>0</v>
+        <v>-0.007199</v>
       </c>
       <c r="F543" s="7">
-        <v>0</v>
+        <v>-0.001621</v>
       </c>
       <c r="G543" s="7">
-        <v>0</v>
+        <v>0.11238</v>
       </c>
       <c r="H543" s="7">
-        <v>0</v>
+        <v>0.370884</v>
       </c>
       <c r="I543" s="7">
-        <v>0</v>
+        <v>0.42653399999999997</v>
       </c>
       <c r="J543" s="7">
-        <v>0</v>
+        <v>1.293333</v>
       </c>
       <c r="K543" s="7"/>
     </row>
@@ -24382,22 +24382,22 @@
         <v>5</v>
       </c>
       <c r="E551" s="7">
-        <v>0</v>
+        <v>0.050831</v>
       </c>
       <c r="F551" s="7">
-        <v>0</v>
+        <v>0.063543</v>
       </c>
       <c r="G551" s="7">
-        <v>0</v>
+        <v>0.18157199999999998</v>
       </c>
       <c r="H551" s="7">
-        <v>0</v>
+        <v>0.298492</v>
       </c>
       <c r="I551" s="7">
-        <v>0</v>
+        <v>0.46076700000000004</v>
       </c>
       <c r="J551" s="7">
-        <v>0</v>
+        <v>1.496292</v>
       </c>
       <c r="K551" s="7"/>
     </row>
@@ -24446,25 +24446,25 @@
         <v>1</v>
       </c>
       <c r="E553" s="7">
-        <v>0</v>
+        <v>0.030248</v>
       </c>
       <c r="F553" s="7">
-        <v>0</v>
+        <v>0.09397399999999999</v>
       </c>
       <c r="G553" s="7">
-        <v>0</v>
+        <v>0.19067499999999998</v>
       </c>
       <c r="H553" s="7">
-        <v>0</v>
+        <v>0.24156300000000003</v>
       </c>
       <c r="I553" s="7">
-        <v>0</v>
+        <v>0.419745</v>
       </c>
       <c r="J553" s="7">
-        <v>0</v>
+        <v>2.200864</v>
       </c>
       <c r="K553" s="7">
-        <v>0</v>
+        <v>3.746124</v>
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.25">
@@ -24512,19 +24512,19 @@
         <v>6</v>
       </c>
       <c r="E555" s="7">
-        <v>0</v>
+        <v>0.066341</v>
       </c>
       <c r="F555" s="7">
-        <v>0</v>
+        <v>0.147137</v>
       </c>
       <c r="G555" s="7">
-        <v>0</v>
+        <v>0.430533</v>
       </c>
       <c r="H555" s="7">
-        <v>0</v>
+        <v>0.537111</v>
       </c>
       <c r="I555" s="7">
-        <v>0</v>
+        <v>0.7484869999999999</v>
       </c>
       <c r="J555" s="7"/>
       <c r="K555" s="7"/>
@@ -24543,25 +24543,25 @@
         <v>3</v>
       </c>
       <c r="E556" s="7">
-        <v>0</v>
+        <v>0.024515</v>
       </c>
       <c r="F556" s="7">
-        <v>0</v>
+        <v>0.06920899999999999</v>
       </c>
       <c r="G556" s="7">
-        <v>0</v>
+        <v>0.175244</v>
       </c>
       <c r="H556" s="7">
-        <v>0</v>
+        <v>0.29735</v>
       </c>
       <c r="I556" s="7">
-        <v>0</v>
+        <v>0.450955</v>
       </c>
       <c r="J556" s="7">
-        <v>0</v>
+        <v>2.0092920000000003</v>
       </c>
       <c r="K556" s="7">
-        <v>0</v>
+        <v>8.092917</v>
       </c>
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.25">
@@ -24578,25 +24578,25 @@
         <v>2</v>
       </c>
       <c r="E557" s="7">
-        <v>0</v>
+        <v>0.027023000000000002</v>
       </c>
       <c r="F557" s="7">
-        <v>0</v>
+        <v>0.06465900000000001</v>
       </c>
       <c r="G557" s="7">
-        <v>0</v>
+        <v>0.142102</v>
       </c>
       <c r="H557" s="7">
-        <v>0</v>
+        <v>0.205824</v>
       </c>
       <c r="I557" s="7">
-        <v>0</v>
+        <v>0.377924</v>
       </c>
       <c r="J557" s="7">
-        <v>0</v>
+        <v>1.645458</v>
       </c>
       <c r="K557" s="7">
-        <v>0</v>
+        <v>3.057566</v>
       </c>
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.25">
@@ -24613,25 +24613,25 @@
         <v>1</v>
       </c>
       <c r="E558" s="7">
-        <v>0</v>
+        <v>0.030328</v>
       </c>
       <c r="F558" s="7">
-        <v>0</v>
+        <v>0.094696</v>
       </c>
       <c r="G558" s="7">
-        <v>0</v>
+        <v>0.194152</v>
       </c>
       <c r="H558" s="7">
-        <v>0</v>
+        <v>0.248084</v>
       </c>
       <c r="I558" s="7">
-        <v>0</v>
+        <v>0.43471</v>
       </c>
       <c r="J558" s="7">
-        <v>0</v>
+        <v>2.301504</v>
       </c>
       <c r="K558" s="7">
-        <v>0</v>
+        <v>4.0443</v>
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.25">
@@ -24648,25 +24648,25 @@
         <v>5</v>
       </c>
       <c r="E559" s="7">
-        <v>0</v>
+        <v>-0.000137</v>
       </c>
       <c r="F559" s="7">
-        <v>0</v>
+        <v>0.0438</v>
       </c>
       <c r="G559" s="7">
-        <v>0</v>
+        <v>0.143333</v>
       </c>
       <c r="H559" s="7">
-        <v>0</v>
+        <v>0.44533</v>
       </c>
       <c r="I559" s="7">
-        <v>0</v>
+        <v>0.460921</v>
       </c>
       <c r="J559" s="7">
-        <v>0</v>
+        <v>1.624981</v>
       </c>
       <c r="K559" s="7">
-        <v>0</v>
+        <v>7.00831</v>
       </c>
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.25">
@@ -24681,25 +24681,25 @@
       </c>
       <c r="D560" s="6"/>
       <c r="E560" s="7">
-        <v>0</v>
+        <v>0.020402999999999998</v>
       </c>
       <c r="F560" s="7">
-        <v>0</v>
+        <v>0.062176</v>
       </c>
       <c r="G560" s="7">
-        <v>0</v>
+        <v>0.107544</v>
       </c>
       <c r="H560" s="7">
-        <v>0</v>
+        <v>0.133583</v>
       </c>
       <c r="I560" s="7">
-        <v>0</v>
+        <v>0.234054</v>
       </c>
       <c r="J560" s="7">
-        <v>0</v>
+        <v>1.1747159999999999</v>
       </c>
       <c r="K560" s="7">
-        <v>0</v>
+        <v>6.1998500000000005</v>
       </c>
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.25">
@@ -24716,25 +24716,25 @@
         <v>1</v>
       </c>
       <c r="E561" s="7">
-        <v>0</v>
+        <v>0.031346</v>
       </c>
       <c r="F561" s="7">
-        <v>0</v>
+        <v>0.093415</v>
       </c>
       <c r="G561" s="7">
-        <v>0</v>
+        <v>0.188699</v>
       </c>
       <c r="H561" s="7">
-        <v>0</v>
+        <v>0.242502</v>
       </c>
       <c r="I561" s="7">
-        <v>0</v>
+        <v>0.426381</v>
       </c>
       <c r="J561" s="7">
-        <v>0</v>
+        <v>2.0852850000000003</v>
       </c>
       <c r="K561" s="7">
-        <v>0</v>
+        <v>3.466755</v>
       </c>
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.25">
@@ -24751,10 +24751,10 @@
         <v>5</v>
       </c>
       <c r="E562" s="7">
-        <v>0</v>
+        <v>0.021758000000000003</v>
       </c>
       <c r="F562" s="7">
-        <v>0</v>
+        <v>0.073878</v>
       </c>
       <c r="G562" s="7"/>
       <c r="H562" s="7"/>
@@ -24776,19 +24776,19 @@
         <v>5</v>
       </c>
       <c r="E563" s="7">
-        <v>0</v>
+        <v>-0.012555</v>
       </c>
       <c r="F563" s="7">
-        <v>0</v>
+        <v>-0.025949</v>
       </c>
       <c r="G563" s="7">
-        <v>0</v>
+        <v>0.004921</v>
       </c>
       <c r="H563" s="7">
-        <v>0</v>
+        <v>0.191724</v>
       </c>
       <c r="I563" s="7">
-        <v>0</v>
+        <v>0.218944</v>
       </c>
       <c r="J563" s="7"/>
       <c r="K563" s="7"/>
@@ -24842,19 +24842,19 @@
         <v>3</v>
       </c>
       <c r="E565" s="7">
-        <v>0</v>
+        <v>0.042052</v>
       </c>
       <c r="F565" s="7">
-        <v>0</v>
+        <v>0.08722200000000001</v>
       </c>
       <c r="G565" s="7">
-        <v>0</v>
+        <v>0.22653099999999998</v>
       </c>
       <c r="H565" s="7">
-        <v>0</v>
+        <v>0.40139899999999995</v>
       </c>
       <c r="I565" s="7">
-        <v>0</v>
+        <v>0.538656</v>
       </c>
       <c r="J565" s="7"/>
       <c r="K565" s="7"/>
@@ -24873,22 +24873,22 @@
         <v>6</v>
       </c>
       <c r="E566" s="7">
-        <v>0</v>
+        <v>0.105813</v>
       </c>
       <c r="F566" s="7">
-        <v>0</v>
+        <v>-0.053516</v>
       </c>
       <c r="G566" s="7">
-        <v>0</v>
+        <v>-0.082483</v>
       </c>
       <c r="H566" s="7">
-        <v>0</v>
+        <v>0.053128</v>
       </c>
       <c r="I566" s="7">
-        <v>0</v>
+        <v>0.690403</v>
       </c>
       <c r="J566" s="7">
-        <v>0</v>
+        <v>3.0856380000000003</v>
       </c>
       <c r="K566" s="7"/>
     </row>
@@ -25090,25 +25090,25 @@
       </c>
       <c r="D573" s="6"/>
       <c r="E573" s="7">
-        <v>0</v>
+        <v>0.09382099999999999</v>
       </c>
       <c r="F573" s="7">
-        <v>0</v>
+        <v>-0.010682</v>
       </c>
       <c r="G573" s="7">
-        <v>0</v>
+        <v>-0.085575</v>
       </c>
       <c r="H573" s="7">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="I573" s="7">
-        <v>0</v>
+        <v>0.528969</v>
       </c>
       <c r="J573" s="7">
-        <v>0</v>
+        <v>3.0589210000000002</v>
       </c>
       <c r="K573" s="7">
-        <v>0</v>
+        <v>13.343983000000001</v>
       </c>
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.25">
@@ -25125,19 +25125,19 @@
         <v>6</v>
       </c>
       <c r="E574" s="7">
-        <v>0</v>
+        <v>0.097508</v>
       </c>
       <c r="F574" s="7">
-        <v>0</v>
+        <v>-0.002742</v>
       </c>
       <c r="G574" s="7">
-        <v>0</v>
+        <v>-0.079979</v>
       </c>
       <c r="H574" s="7">
-        <v>0</v>
+        <v>0.052687</v>
       </c>
       <c r="I574" s="7">
-        <v>0</v>
+        <v>0.447224</v>
       </c>
       <c r="J574" s="7"/>
       <c r="K574" s="7"/>
@@ -25559,16 +25559,16 @@
         <v>6</v>
       </c>
       <c r="E588" s="7">
-        <v>0.05114</v>
+        <v>0.049042</v>
       </c>
       <c r="F588" s="7">
-        <v>-0.015385</v>
+        <v>-0.01735</v>
       </c>
       <c r="G588" s="7">
-        <v>0.07163</v>
+        <v>0.069491</v>
       </c>
       <c r="H588" s="7">
-        <v>0.120946</v>
+        <v>0.118708</v>
       </c>
       <c r="I588" s="7"/>
       <c r="J588" s="7"/>
@@ -25588,22 +25588,22 @@
         <v>6</v>
       </c>
       <c r="E589" s="7">
-        <v>0</v>
+        <v>0.022631000000000002</v>
       </c>
       <c r="F589" s="7">
-        <v>0</v>
+        <v>0.062693</v>
       </c>
       <c r="G589" s="7">
-        <v>0</v>
+        <v>0.272498</v>
       </c>
       <c r="H589" s="7">
-        <v>0</v>
+        <v>0.301043</v>
       </c>
       <c r="I589" s="7">
-        <v>0</v>
+        <v>0.460053</v>
       </c>
       <c r="J589" s="7">
-        <v>0</v>
+        <v>2.5320400000000003</v>
       </c>
       <c r="K589" s="7"/>
     </row>
@@ -26269,19 +26269,19 @@
       </c>
       <c r="D610" s="6"/>
       <c r="E610" s="7">
-        <v>0.025299000000000002</v>
+        <v>-0.000297</v>
       </c>
       <c r="F610" s="7">
-        <v>0.014049</v>
+        <v>-0.011267000000000001</v>
       </c>
       <c r="G610" s="7">
-        <v>-0.018949</v>
+        <v>-0.043441</v>
       </c>
       <c r="H610" s="7">
-        <v>0.064149</v>
+        <v>0.037582</v>
       </c>
       <c r="I610" s="7">
-        <v>0.095968</v>
+        <v>0.068607</v>
       </c>
       <c r="J610" s="7"/>
       <c r="K610" s="7"/>
@@ -26544,22 +26544,22 @@
         <v>6</v>
       </c>
       <c r="E619" s="7">
-        <v>0.057133</v>
+        <v>0.057159</v>
       </c>
       <c r="F619" s="7">
-        <v>0.067953</v>
+        <v>0.067979</v>
       </c>
       <c r="G619" s="7">
-        <v>0.308989</v>
+        <v>0.309021</v>
       </c>
       <c r="H619" s="7">
-        <v>0.298155</v>
+        <v>0.298186</v>
       </c>
       <c r="I619" s="7">
-        <v>0.41031399999999996</v>
+        <v>0.410349</v>
       </c>
       <c r="J619" s="7">
-        <v>2.1541900000000003</v>
+        <v>2.154267</v>
       </c>
       <c r="K619" s="7"/>
     </row>
@@ -28310,25 +28310,25 @@
         <v>4</v>
       </c>
       <c r="E675" s="7">
-        <v>0</v>
+        <v>0.044496</v>
       </c>
       <c r="F675" s="7">
-        <v>0</v>
+        <v>0.042221</v>
       </c>
       <c r="G675" s="7">
-        <v>0</v>
+        <v>0.090178</v>
       </c>
       <c r="H675" s="7">
-        <v>0</v>
+        <v>0.17907900000000002</v>
       </c>
       <c r="I675" s="7">
-        <v>0</v>
+        <v>0.358977</v>
       </c>
       <c r="J675" s="7">
-        <v>0</v>
+        <v>1.7337420000000001</v>
       </c>
       <c r="K675" s="7">
-        <v>0</v>
+        <v>6.458903</v>
       </c>
     </row>
     <row r="676" spans="1:11" x14ac:dyDescent="0.25">
@@ -28580,25 +28580,25 @@
         <v>6</v>
       </c>
       <c r="E683" s="7">
-        <v>0.072617</v>
+        <v>0.072851</v>
       </c>
       <c r="F683" s="7">
-        <v>0.104632</v>
+        <v>0.104873</v>
       </c>
       <c r="G683" s="7">
-        <v>0.405819</v>
+        <v>0.406126</v>
       </c>
       <c r="H683" s="7">
-        <v>0.439343</v>
+        <v>0.439658</v>
       </c>
       <c r="I683" s="7">
-        <v>0.625401</v>
+        <v>0.625756</v>
       </c>
       <c r="J683" s="7">
-        <v>2.8687389999999997</v>
+        <v>2.8695850000000003</v>
       </c>
       <c r="K683" s="7">
-        <v>11.052508</v>
+        <v>11.055142</v>
       </c>
     </row>
     <row r="684" spans="1:11" x14ac:dyDescent="0.25">
@@ -29077,25 +29077,25 @@
         <v>6</v>
       </c>
       <c r="E698" s="7">
-        <v>-0.015584</v>
+        <v>-0.001482</v>
       </c>
       <c r="F698" s="7">
-        <v>-0.011986000000000002</v>
+        <v>0.002168</v>
       </c>
       <c r="G698" s="7">
-        <v>0.009624</v>
+        <v>0.024087</v>
       </c>
       <c r="H698" s="7">
-        <v>0.24499700000000002</v>
+        <v>0.262833</v>
       </c>
       <c r="I698" s="7">
-        <v>0.322254</v>
+        <v>0.34119700000000003</v>
       </c>
       <c r="J698" s="7">
-        <v>0.9316530000000001</v>
+        <v>0.9593259999999999</v>
       </c>
       <c r="K698" s="7">
-        <v>10.532613</v>
+        <v>10.697827</v>
       </c>
     </row>
     <row r="699" spans="1:11" x14ac:dyDescent="0.25">
@@ -29248,25 +29248,25 @@
         <v>2</v>
       </c>
       <c r="E703" s="7">
-        <v>0.030517</v>
+        <v>0.03376</v>
       </c>
       <c r="F703" s="7">
-        <v>0.09643499999999999</v>
+        <v>0.099886</v>
       </c>
       <c r="G703" s="7">
-        <v>0.19956</v>
+        <v>0.20333500000000002</v>
       </c>
       <c r="H703" s="7">
-        <v>0.25776299999999996</v>
+        <v>0.261722</v>
       </c>
       <c r="I703" s="7">
-        <v>0.46206200000000003</v>
+        <v>0.466664</v>
       </c>
       <c r="J703" s="7">
-        <v>2.332974</v>
+        <v>2.343465</v>
       </c>
       <c r="K703" s="7">
-        <v>3.843486</v>
+        <v>3.85873</v>
       </c>
     </row>
     <row r="704" spans="1:11" x14ac:dyDescent="0.25">
@@ -29283,22 +29283,22 @@
         <v>6</v>
       </c>
       <c r="E704" s="7">
-        <v>0</v>
+        <v>0.113239</v>
       </c>
       <c r="F704" s="7">
-        <v>0</v>
+        <v>-0.051100000000000007</v>
       </c>
       <c r="G704" s="7">
-        <v>0</v>
+        <v>-0.061199</v>
       </c>
       <c r="H704" s="7">
-        <v>0</v>
+        <v>0.025666</v>
       </c>
       <c r="I704" s="7">
-        <v>0</v>
+        <v>0.66079</v>
       </c>
       <c r="J704" s="7">
-        <v>0</v>
+        <v>2.73604</v>
       </c>
       <c r="K704" s="7"/>
     </row>
@@ -31044,19 +31044,19 @@
         <v>2</v>
       </c>
       <c r="E761" s="7">
-        <v>0.034554</v>
+        <v>0.034047999999999995</v>
       </c>
       <c r="F761" s="7">
-        <v>0.10211600000000001</v>
+        <v>0.101578</v>
       </c>
       <c r="G761" s="7">
-        <v>0.211803</v>
+        <v>0.21121099999999998</v>
       </c>
       <c r="H761" s="7">
-        <v>0.269006</v>
+        <v>0.268386</v>
       </c>
       <c r="I761" s="7">
-        <v>0.471305</v>
+        <v>0.470586</v>
       </c>
       <c r="J761" s="7"/>
       <c r="K761" s="7"/>
@@ -33523,19 +33523,19 @@
         <v>6</v>
       </c>
       <c r="E840" s="7">
-        <v>0</v>
+        <v>-0.04273</v>
       </c>
       <c r="F840" s="7">
-        <v>0</v>
+        <v>-0.027446</v>
       </c>
       <c r="G840" s="7">
-        <v>0</v>
+        <v>0.046499</v>
       </c>
       <c r="H840" s="7">
-        <v>0</v>
+        <v>0.24046199999999998</v>
       </c>
       <c r="I840" s="7">
-        <v>0</v>
+        <v>0.501239</v>
       </c>
       <c r="J840" s="7"/>
       <c r="K840" s="7"/>
@@ -33575,16 +33575,16 @@
         <v>5</v>
       </c>
       <c r="E842" s="7">
-        <v>0.01836</v>
+        <v>0.02116</v>
       </c>
       <c r="F842" s="7">
-        <v>0.036219</v>
+        <v>0.039068</v>
       </c>
       <c r="G842" s="7">
-        <v>0.107765</v>
+        <v>0.11080999999999999</v>
       </c>
       <c r="H842" s="7">
-        <v>0.262494</v>
+        <v>0.265965</v>
       </c>
       <c r="I842" s="7"/>
       <c r="J842" s="7"/>
@@ -33625,19 +33625,19 @@
         <v>5</v>
       </c>
       <c r="E844" s="7">
-        <v>0</v>
+        <v>0.080742</v>
       </c>
       <c r="F844" s="7">
-        <v>0</v>
+        <v>0.248498</v>
       </c>
       <c r="G844" s="7">
-        <v>0</v>
+        <v>0.443786</v>
       </c>
       <c r="H844" s="7">
-        <v>0</v>
+        <v>0.499628</v>
       </c>
       <c r="I844" s="7">
-        <v>0</v>
+        <v>0.605187</v>
       </c>
       <c r="J844" s="7"/>
       <c r="K844" s="7"/>
@@ -33710,16 +33710,16 @@
         <v>6</v>
       </c>
       <c r="E847" s="7">
-        <v>0</v>
+        <v>-0.001889</v>
       </c>
       <c r="F847" s="7">
-        <v>0</v>
+        <v>0.016375999999999998</v>
       </c>
       <c r="G847" s="7">
-        <v>0</v>
+        <v>0.066385</v>
       </c>
       <c r="H847" s="7">
-        <v>0</v>
+        <v>0.422512</v>
       </c>
       <c r="I847" s="7"/>
       <c r="J847" s="7"/>
@@ -34082,19 +34082,19 @@
         <v>5</v>
       </c>
       <c r="E859" s="7">
-        <v>0.042488</v>
+        <v>0.042521</v>
       </c>
       <c r="F859" s="7">
-        <v>0.153453</v>
+        <v>0.15348900000000001</v>
       </c>
       <c r="G859" s="7">
-        <v>0.144518</v>
+        <v>0.144554</v>
       </c>
       <c r="H859" s="7">
-        <v>0.221778</v>
+        <v>0.221817</v>
       </c>
       <c r="I859" s="7">
-        <v>0.44493499999999997</v>
+        <v>0.444981</v>
       </c>
       <c r="J859" s="7"/>
       <c r="K859" s="7"/>
@@ -34177,19 +34177,19 @@
         <v>6</v>
       </c>
       <c r="E862" s="7">
-        <v>0.047659</v>
+        <v>0.048731</v>
       </c>
       <c r="F862" s="7">
-        <v>0.018192</v>
+        <v>0.019234</v>
       </c>
       <c r="G862" s="7">
-        <v>0.12596</v>
+        <v>0.127113</v>
       </c>
       <c r="H862" s="7">
-        <v>0.258693</v>
+        <v>0.259981</v>
       </c>
       <c r="I862" s="7">
-        <v>0.07595299999999999</v>
+        <v>0.077054</v>
       </c>
       <c r="J862" s="7"/>
       <c r="K862" s="7"/>
@@ -34208,25 +34208,25 @@
         <v>3</v>
       </c>
       <c r="E863" s="7">
-        <v>0.034916</v>
+        <v>0.034684</v>
       </c>
       <c r="F863" s="7">
-        <v>0.09051500000000001</v>
+        <v>0.09026999999999999</v>
       </c>
       <c r="G863" s="7">
-        <v>0.17952400000000002</v>
+        <v>0.17925899999999997</v>
       </c>
       <c r="H863" s="7">
-        <v>0.23567799999999997</v>
+        <v>0.235401</v>
       </c>
       <c r="I863" s="7">
-        <v>0.509194</v>
+        <v>0.508856</v>
       </c>
       <c r="J863" s="7">
-        <v>2.439835</v>
+        <v>2.439064</v>
       </c>
       <c r="K863" s="7">
-        <v>6.483291</v>
+        <v>6.481612999999999</v>
       </c>
     </row>
     <row r="864" spans="1:11" x14ac:dyDescent="0.25">
@@ -34820,19 +34820,19 @@
         <v>6</v>
       </c>
       <c r="E881" s="7">
-        <v>0.08783099999999999</v>
+        <v>0.088157</v>
       </c>
       <c r="F881" s="7">
-        <v>0.136442</v>
+        <v>0.136783</v>
       </c>
       <c r="G881" s="7">
-        <v>0.433113</v>
+        <v>0.433543</v>
       </c>
       <c r="H881" s="7">
-        <v>0.501274</v>
+        <v>0.501725</v>
       </c>
       <c r="I881" s="7">
-        <v>0.711769</v>
+        <v>0.712282</v>
       </c>
       <c r="J881" s="7"/>
       <c r="K881" s="7"/>
@@ -35666,10 +35666,10 @@
         <v>6.8493949999999995</v>
       </c>
       <c r="J906" s="7">
-        <v>678.5750350000001</v>
+        <v>678.5749920000001</v>
       </c>
       <c r="K906" s="7">
-        <v>5898.910793</v>
+        <v>5898.910422</v>
       </c>
     </row>
     <row r="907" spans="1:11" x14ac:dyDescent="0.25">
@@ -35822,16 +35822,16 @@
         <v>2</v>
       </c>
       <c r="E911" s="7">
-        <v>0.023976</v>
+        <v>0.027218</v>
       </c>
       <c r="F911" s="7">
-        <v>0.067163</v>
+        <v>0.070542</v>
       </c>
       <c r="G911" s="7">
-        <v>0.156315</v>
+        <v>0.159976</v>
       </c>
       <c r="H911" s="7">
-        <v>0.240393</v>
+        <v>0.24431999999999998</v>
       </c>
       <c r="I911" s="7"/>
       <c r="J911" s="7"/>
@@ -36513,22 +36513,22 @@
         <v>6</v>
       </c>
       <c r="E932" s="7">
-        <v>0.044911000000000006</v>
+        <v>0.044954</v>
       </c>
       <c r="F932" s="7">
-        <v>0.13096</v>
+        <v>0.131006</v>
       </c>
       <c r="G932" s="7">
-        <v>0.20958300000000002</v>
+        <v>0.209632</v>
       </c>
       <c r="H932" s="7">
-        <v>0.297444</v>
+        <v>0.297497</v>
       </c>
       <c r="I932" s="7">
-        <v>0.539274</v>
+        <v>0.5393370000000001</v>
       </c>
       <c r="J932" s="7">
-        <v>1.779016</v>
+        <v>1.77913</v>
       </c>
       <c r="K932" s="7"/>
     </row>
@@ -36917,25 +36917,25 @@
         <v>6</v>
       </c>
       <c r="E944" s="7">
-        <v>0.032451</v>
+        <v>0.032109</v>
       </c>
       <c r="F944" s="7">
-        <v>0.083911</v>
+        <v>0.083553</v>
       </c>
       <c r="G944" s="7">
-        <v>0.153835</v>
+        <v>0.153453</v>
       </c>
       <c r="H944" s="7">
-        <v>0.197939</v>
+        <v>0.197543</v>
       </c>
       <c r="I944" s="7">
-        <v>0.528002</v>
+        <v>0.527496</v>
       </c>
       <c r="J944" s="7">
-        <v>1.6096940000000002</v>
+        <v>1.6088310000000001</v>
       </c>
       <c r="K944" s="7">
-        <v>9.523299</v>
+        <v>9.519817</v>
       </c>
     </row>
     <row r="945" spans="1:11" x14ac:dyDescent="0.25">
@@ -37051,7 +37051,7 @@
         <v>6</v>
       </c>
       <c r="E948" s="7">
-        <v>0</v>
+        <v>0.08534900000000001</v>
       </c>
       <c r="F948" s="7"/>
       <c r="G948" s="7"/>
@@ -37336,25 +37336,25 @@
         <v>5</v>
       </c>
       <c r="E959" s="7">
-        <v>0</v>
+        <v>0.045006000000000004</v>
       </c>
       <c r="F959" s="7">
-        <v>0</v>
+        <v>0.043749</v>
       </c>
       <c r="G959" s="7">
-        <v>0</v>
+        <v>0.064722</v>
       </c>
       <c r="H959" s="7">
-        <v>0</v>
+        <v>0.17330600000000002</v>
       </c>
       <c r="I959" s="7">
-        <v>0</v>
+        <v>0.33009900000000003</v>
       </c>
       <c r="J959" s="7">
-        <v>0</v>
+        <v>1.4228200000000002</v>
       </c>
       <c r="K959" s="7">
-        <v>0</v>
+        <v>5.888541</v>
       </c>
     </row>
     <row r="960" spans="1:11" x14ac:dyDescent="0.25">
@@ -37431,25 +37431,25 @@
         <v>4</v>
       </c>
       <c r="E962" s="7">
-        <v>0</v>
+        <v>0.031485</v>
       </c>
       <c r="F962" s="7">
-        <v>0</v>
+        <v>0.084747</v>
       </c>
       <c r="G962" s="7">
-        <v>0</v>
+        <v>0.12606799999999999</v>
       </c>
       <c r="H962" s="7">
-        <v>0</v>
+        <v>0.212893</v>
       </c>
       <c r="I962" s="7">
-        <v>0</v>
+        <v>0.35213099999999997</v>
       </c>
       <c r="J962" s="7">
-        <v>0</v>
+        <v>1.243754</v>
       </c>
       <c r="K962" s="7">
-        <v>0</v>
+        <v>4.785571</v>
       </c>
     </row>
     <row r="963" spans="1:11" x14ac:dyDescent="0.25">
@@ -38198,19 +38198,19 @@
         <v>6</v>
       </c>
       <c r="E985" s="7">
-        <v>0</v>
+        <v>0.027967</v>
       </c>
       <c r="F985" s="7">
-        <v>0</v>
+        <v>0.071785</v>
       </c>
       <c r="G985" s="7">
-        <v>0</v>
+        <v>0.46420900000000004</v>
       </c>
       <c r="H985" s="7">
-        <v>0</v>
+        <v>0.722089</v>
       </c>
       <c r="I985" s="7">
-        <v>0</v>
+        <v>1.142076</v>
       </c>
       <c r="J985" s="7"/>
       <c r="K985" s="7"/>
@@ -38262,22 +38262,22 @@
         <v>5</v>
       </c>
       <c r="E987" s="7">
-        <v>0</v>
+        <v>0.06884</v>
       </c>
       <c r="F987" s="7">
-        <v>0</v>
+        <v>0.102168</v>
       </c>
       <c r="G987" s="7">
-        <v>0</v>
+        <v>0.39411999999999997</v>
       </c>
       <c r="H987" s="7">
-        <v>0</v>
+        <v>0.522381</v>
       </c>
       <c r="I987" s="7">
-        <v>0</v>
+        <v>0.7668470000000001</v>
       </c>
       <c r="J987" s="7">
-        <v>0</v>
+        <v>2.454052</v>
       </c>
       <c r="K987" s="7"/>
     </row>
@@ -38885,25 +38885,25 @@
         <v>5</v>
       </c>
       <c r="E1006" s="7">
-        <v>0</v>
+        <v>0.046679000000000005</v>
       </c>
       <c r="F1006" s="7">
-        <v>0</v>
+        <v>0.024184999999999998</v>
       </c>
       <c r="G1006" s="7">
-        <v>0</v>
+        <v>0.037437</v>
       </c>
       <c r="H1006" s="7">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="I1006" s="7">
-        <v>0</v>
+        <v>0.25632699999999997</v>
       </c>
       <c r="J1006" s="7">
-        <v>0</v>
+        <v>1.13664</v>
       </c>
       <c r="K1006" s="7">
-        <v>0</v>
+        <v>4.601253</v>
       </c>
     </row>
     <row r="1007" spans="1:11" x14ac:dyDescent="0.25">
@@ -39067,25 +39067,25 @@
         <v>6</v>
       </c>
       <c r="E1012" s="7">
-        <v>0</v>
+        <v>0.06963599999999999</v>
       </c>
       <c r="F1012" s="7">
-        <v>0</v>
+        <v>0.12122899999999999</v>
       </c>
       <c r="G1012" s="7">
-        <v>0</v>
+        <v>0.24237999999999998</v>
       </c>
       <c r="H1012" s="7">
-        <v>0</v>
+        <v>0.23362300000000003</v>
       </c>
       <c r="I1012" s="7">
-        <v>0</v>
+        <v>0.464405</v>
       </c>
       <c r="J1012" s="7">
-        <v>0</v>
+        <v>2.142631</v>
       </c>
       <c r="K1012" s="7">
-        <v>0</v>
+        <v>8.256817999999999</v>
       </c>
     </row>
     <row r="1013" spans="1:11" x14ac:dyDescent="0.25">
@@ -39323,25 +39323,25 @@
         <v>7</v>
       </c>
       <c r="E1020" s="7">
-        <v>0</v>
+        <v>0.164556</v>
       </c>
       <c r="F1020" s="7">
-        <v>0</v>
+        <v>-0.121626</v>
       </c>
       <c r="G1020" s="7">
-        <v>0</v>
+        <v>-0.10411799999999999</v>
       </c>
       <c r="H1020" s="7">
-        <v>0</v>
+        <v>-0.025764</v>
       </c>
       <c r="I1020" s="7">
-        <v>0</v>
+        <v>0.90836</v>
       </c>
       <c r="J1020" s="7">
-        <v>0</v>
+        <v>3.6201139999999996</v>
       </c>
       <c r="K1020" s="7">
-        <v>0</v>
+        <v>11.650300999999999</v>
       </c>
     </row>
     <row r="1021" spans="1:11" x14ac:dyDescent="0.25">

--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>20.08.2026 10:47:42</t>
+    <t>20.08.2026 11:28:00</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -7394,25 +7394,25 @@
         <v>7</v>
       </c>
       <c r="E19" s="7">
-        <v>0</v>
+        <v>0.075839</v>
       </c>
       <c r="F19" s="7">
-        <v>0</v>
+        <v>-0.016712</v>
       </c>
       <c r="G19" s="7">
-        <v>0</v>
+        <v>0.629652</v>
       </c>
       <c r="H19" s="7">
-        <v>0</v>
+        <v>0.8861950000000001</v>
       </c>
       <c r="I19" s="7">
-        <v>0</v>
+        <v>0.894012</v>
       </c>
       <c r="J19" s="7">
-        <v>0</v>
+        <v>1.571344</v>
       </c>
       <c r="K19" s="7">
-        <v>0</v>
+        <v>10.786424</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -8276,25 +8276,25 @@
         <v>6</v>
       </c>
       <c r="E45" s="7">
-        <v>0</v>
+        <v>0.041004</v>
       </c>
       <c r="F45" s="7">
-        <v>0</v>
+        <v>0.013815</v>
       </c>
       <c r="G45" s="7">
-        <v>0</v>
+        <v>-0.0066549999999999995</v>
       </c>
       <c r="H45" s="7">
-        <v>0</v>
+        <v>0.185561</v>
       </c>
       <c r="I45" s="7">
-        <v>0</v>
+        <v>0.239293</v>
       </c>
       <c r="J45" s="7">
-        <v>0</v>
+        <v>1.0953279999999999</v>
       </c>
       <c r="K45" s="7">
-        <v>0</v>
+        <v>2.995025</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -8379,25 +8379,25 @@
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="7">
-        <v>0</v>
+        <v>0.031134</v>
       </c>
       <c r="F48" s="7">
-        <v>0</v>
+        <v>0.049915</v>
       </c>
       <c r="G48" s="7">
-        <v>0</v>
+        <v>0.10315300000000001</v>
       </c>
       <c r="H48" s="7">
-        <v>0</v>
+        <v>0.20228200000000002</v>
       </c>
       <c r="I48" s="7">
-        <v>0</v>
+        <v>0.35519100000000003</v>
       </c>
       <c r="J48" s="7">
-        <v>0</v>
+        <v>2.004654</v>
       </c>
       <c r="K48" s="7">
-        <v>0</v>
+        <v>5.402311999999999</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -8412,25 +8412,25 @@
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7">
-        <v>0</v>
+        <v>0.030728</v>
       </c>
       <c r="F49" s="7">
-        <v>0</v>
+        <v>0.02628</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>0.052396000000000005</v>
       </c>
       <c r="H49" s="7">
-        <v>0</v>
+        <v>0.17707699999999998</v>
       </c>
       <c r="I49" s="7">
-        <v>0</v>
+        <v>0.32333199999999995</v>
       </c>
       <c r="J49" s="7">
-        <v>0</v>
+        <v>1.821745</v>
       </c>
       <c r="K49" s="7">
-        <v>0</v>
+        <v>5.966201</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -8447,19 +8447,19 @@
         <v>5</v>
       </c>
       <c r="E50" s="7">
-        <v>0.015024</v>
+        <v>0.015019</v>
       </c>
       <c r="F50" s="7">
-        <v>0.01012</v>
+        <v>0.010115</v>
       </c>
       <c r="G50" s="7">
-        <v>0.017399</v>
+        <v>0.017393000000000002</v>
       </c>
       <c r="H50" s="7">
-        <v>0.015988</v>
+        <v>0.015983</v>
       </c>
       <c r="I50" s="7">
-        <v>0.059644</v>
+        <v>0.059639</v>
       </c>
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
@@ -10215,10 +10215,10 @@
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>0.029354</v>
+        <v>0.034566</v>
       </c>
       <c r="F108" s="7">
-        <v>0.19112200000000001</v>
+        <v>0.197153</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
@@ -11116,25 +11116,25 @@
         <v>2</v>
       </c>
       <c r="E137" s="7">
-        <v>0.033023</v>
+        <v>0.032965</v>
       </c>
       <c r="F137" s="7">
-        <v>0.10124599999999999</v>
+        <v>0.101183</v>
       </c>
       <c r="G137" s="7">
-        <v>0.207427</v>
+        <v>0.20735900000000002</v>
       </c>
       <c r="H137" s="7">
-        <v>0.268208</v>
+        <v>0.268135</v>
       </c>
       <c r="I137" s="7">
-        <v>0.465062</v>
+        <v>0.464978</v>
       </c>
       <c r="J137" s="7">
-        <v>2.406267</v>
+        <v>2.406073</v>
       </c>
       <c r="K137" s="7">
-        <v>3.949921</v>
+        <v>3.9496390000000003</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -12413,25 +12413,25 @@
         <v>3</v>
       </c>
       <c r="E178" s="7">
-        <v>0.039765999999999996</v>
+        <v>0.039767000000000004</v>
       </c>
       <c r="F178" s="7">
         <v>0.08025299999999999</v>
       </c>
       <c r="G178" s="7">
-        <v>0.131491</v>
+        <v>0.131492</v>
       </c>
       <c r="H178" s="7">
-        <v>0.210837</v>
+        <v>0.210838</v>
       </c>
       <c r="I178" s="7">
-        <v>0.401633</v>
+        <v>0.40163400000000005</v>
       </c>
       <c r="J178" s="7">
-        <v>1.819085</v>
+        <v>1.8190870000000001</v>
       </c>
       <c r="K178" s="7">
-        <v>6.62322</v>
+        <v>6.623226</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -13732,19 +13732,19 @@
         <v>3</v>
       </c>
       <c r="E221" s="7">
-        <v>0.057495000000000004</v>
+        <v>0.066154</v>
       </c>
       <c r="F221" s="7">
-        <v>0.05931</v>
+        <v>0.067984</v>
       </c>
       <c r="G221" s="7">
-        <v>0.12603999999999999</v>
+        <v>0.13526</v>
       </c>
       <c r="H221" s="7">
-        <v>0.253413</v>
+        <v>0.263677</v>
       </c>
       <c r="I221" s="7">
-        <v>0.517171</v>
+        <v>0.529594</v>
       </c>
       <c r="J221" s="7"/>
       <c r="K221" s="7"/>
@@ -16141,25 +16141,25 @@
         <v>5</v>
       </c>
       <c r="E294" s="7">
-        <v>0.024297</v>
+        <v>0.031074</v>
       </c>
       <c r="F294" s="7">
-        <v>0.008631999999999999</v>
+        <v>0.015305</v>
       </c>
       <c r="G294" s="7">
-        <v>0.071387</v>
+        <v>0.078476</v>
       </c>
       <c r="H294" s="7">
-        <v>0.21334499999999998</v>
+        <v>0.221373</v>
       </c>
       <c r="I294" s="7">
-        <v>0.500901</v>
+        <v>0.510832</v>
       </c>
       <c r="J294" s="7">
-        <v>1.831275</v>
+        <v>1.8500079999999999</v>
       </c>
       <c r="K294" s="7">
-        <v>9.207258000000001</v>
+        <v>9.274792999999999</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -16343,22 +16343,22 @@
         <v>5</v>
       </c>
       <c r="E300" s="7">
-        <v>0.041384</v>
+        <v>0.049690000000000005</v>
       </c>
       <c r="F300" s="7">
-        <v>0.024014</v>
+        <v>0.032183</v>
       </c>
       <c r="G300" s="7">
-        <v>0.035496</v>
+        <v>0.043756</v>
       </c>
       <c r="H300" s="7">
-        <v>0.073946</v>
+        <v>0.082513</v>
       </c>
       <c r="I300" s="7">
-        <v>0.20203600000000002</v>
+        <v>0.211624</v>
       </c>
       <c r="J300" s="7">
-        <v>1.531931</v>
+        <v>1.552128</v>
       </c>
       <c r="K300" s="7"/>
     </row>
@@ -16500,22 +16500,22 @@
         <v>7</v>
       </c>
       <c r="E305" s="7">
-        <v>0</v>
+        <v>0.19943100000000002</v>
       </c>
       <c r="F305" s="7">
-        <v>0</v>
+        <v>-0.13478199999999999</v>
       </c>
       <c r="G305" s="7">
-        <v>0</v>
+        <v>-0.11810499999999999</v>
       </c>
       <c r="H305" s="7">
-        <v>0</v>
+        <v>-0.049242999999999995</v>
       </c>
       <c r="I305" s="7">
-        <v>0</v>
+        <v>0.899833</v>
       </c>
       <c r="J305" s="7">
-        <v>0</v>
+        <v>3.472633</v>
       </c>
       <c r="K305" s="7"/>
     </row>
@@ -17827,25 +17827,25 @@
         <v>7</v>
       </c>
       <c r="E346" s="7">
-        <v>0</v>
+        <v>0.18398</v>
       </c>
       <c r="F346" s="7">
-        <v>0</v>
+        <v>-0.12258100000000001</v>
       </c>
       <c r="G346" s="7">
-        <v>0</v>
+        <v>-0.107698</v>
       </c>
       <c r="H346" s="7">
-        <v>0</v>
+        <v>-0.025282</v>
       </c>
       <c r="I346" s="7">
-        <v>0</v>
+        <v>0.895935</v>
       </c>
       <c r="J346" s="7">
-        <v>0</v>
+        <v>3.4192590000000003</v>
       </c>
       <c r="K346" s="7">
-        <v>0</v>
+        <v>11.437071000000001</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
@@ -21609,25 +21609,25 @@
         <v>3</v>
       </c>
       <c r="E464" s="7">
-        <v>0</v>
+        <v>0.032925</v>
       </c>
       <c r="F464" s="7">
-        <v>0</v>
+        <v>0.06793199999999999</v>
       </c>
       <c r="G464" s="7">
-        <v>0</v>
+        <v>0.129563</v>
       </c>
       <c r="H464" s="7">
-        <v>0</v>
+        <v>0.203137</v>
       </c>
       <c r="I464" s="7">
-        <v>0</v>
+        <v>0.342943</v>
       </c>
       <c r="J464" s="7">
-        <v>0</v>
+        <v>2.086343</v>
       </c>
       <c r="K464" s="7">
-        <v>0</v>
+        <v>6.019272999999999</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
@@ -22316,22 +22316,22 @@
         <v>3</v>
       </c>
       <c r="E485" s="7">
-        <v>0</v>
+        <v>0.038134</v>
       </c>
       <c r="F485" s="7">
-        <v>0</v>
+        <v>0.140396</v>
       </c>
       <c r="G485" s="7">
-        <v>0</v>
+        <v>0.253674</v>
       </c>
       <c r="H485" s="7">
-        <v>0</v>
+        <v>0.346678</v>
       </c>
       <c r="I485" s="7">
-        <v>0</v>
+        <v>0.605386</v>
       </c>
       <c r="J485" s="7">
-        <v>0</v>
+        <v>2.469078</v>
       </c>
       <c r="K485" s="7"/>
     </row>
@@ -22607,22 +22607,22 @@
         <v>5</v>
       </c>
       <c r="E494" s="7">
-        <v>0.059847000000000004</v>
+        <v>0.057725</v>
       </c>
       <c r="F494" s="7">
-        <v>0.099384</v>
+        <v>0.09718299999999999</v>
       </c>
       <c r="G494" s="7">
-        <v>0.359633</v>
+        <v>0.356911</v>
       </c>
       <c r="H494" s="7">
-        <v>0.42633000000000004</v>
+        <v>0.423474</v>
       </c>
       <c r="I494" s="7">
-        <v>0.601757</v>
+        <v>0.5985499999999999</v>
       </c>
       <c r="J494" s="7">
-        <v>2.383007</v>
+        <v>2.376234</v>
       </c>
       <c r="K494" s="7"/>
     </row>
@@ -22832,22 +22832,22 @@
         <v>5</v>
       </c>
       <c r="E501" s="7">
-        <v>0.039682</v>
+        <v>0.042475</v>
       </c>
       <c r="F501" s="7">
-        <v>0.160669</v>
+        <v>0.163786</v>
       </c>
       <c r="G501" s="7">
-        <v>0.311046</v>
+        <v>0.31456700000000004</v>
       </c>
       <c r="H501" s="7">
-        <v>0.39848999999999996</v>
+        <v>0.40224600000000005</v>
       </c>
       <c r="I501" s="7">
-        <v>0.491049</v>
+        <v>0.49505299999999997</v>
       </c>
       <c r="J501" s="7">
-        <v>1.8519040000000002</v>
+        <v>1.859564</v>
       </c>
       <c r="K501" s="7"/>
     </row>
@@ -23766,19 +23766,19 @@
         <v>6</v>
       </c>
       <c r="E531" s="7">
-        <v>0.010714</v>
+        <v>0.010513</v>
       </c>
       <c r="F531" s="7">
-        <v>0.013170999999999999</v>
+        <v>0.012969</v>
       </c>
       <c r="G531" s="7">
-        <v>-0.000136</v>
+        <v>-0.000336</v>
       </c>
       <c r="H531" s="7">
-        <v>-0.007696</v>
+        <v>-0.007894</v>
       </c>
       <c r="I531" s="7">
-        <v>0.027849</v>
+        <v>0.027645</v>
       </c>
       <c r="J531" s="7"/>
       <c r="K531" s="7"/>
@@ -25881,22 +25881,22 @@
         <v>6</v>
       </c>
       <c r="E598" s="7">
-        <v>0.05137800000000001</v>
+        <v>0.058112000000000004</v>
       </c>
       <c r="F598" s="7">
-        <v>0.04771</v>
+        <v>0.05442</v>
       </c>
       <c r="G598" s="7">
-        <v>0.139967</v>
+        <v>0.14726699999999998</v>
       </c>
       <c r="H598" s="7">
-        <v>0.288151</v>
+        <v>0.296401</v>
       </c>
       <c r="I598" s="7">
-        <v>0.41295099999999996</v>
+        <v>0.42200000000000004</v>
       </c>
       <c r="J598" s="7">
-        <v>1.80843</v>
+        <v>1.826417</v>
       </c>
       <c r="K598" s="7"/>
     </row>
@@ -25914,25 +25914,25 @@
         <v>7</v>
       </c>
       <c r="E599" s="7">
-        <v>0.171541</v>
+        <v>0.16625800000000002</v>
       </c>
       <c r="F599" s="7">
-        <v>-0.105057</v>
+        <v>-0.109093</v>
       </c>
       <c r="G599" s="7">
-        <v>-0.08773199999999999</v>
+        <v>-0.091846</v>
       </c>
       <c r="H599" s="7">
-        <v>-0.03932</v>
+        <v>-0.043651999999999996</v>
       </c>
       <c r="I599" s="7">
-        <v>0.8632569999999999</v>
+        <v>0.854854</v>
       </c>
       <c r="J599" s="7">
-        <v>3.616575</v>
+        <v>3.5957549999999996</v>
       </c>
       <c r="K599" s="7">
-        <v>11.957661</v>
+        <v>11.899223999999998</v>
       </c>
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.25">
@@ -26678,22 +26678,22 @@
         <v>5</v>
       </c>
       <c r="E623" s="7">
-        <v>0.01601</v>
+        <v>0.018638</v>
       </c>
       <c r="F623" s="7">
-        <v>0.009598</v>
+        <v>0.012209000000000001</v>
       </c>
       <c r="G623" s="7">
-        <v>0.053308999999999995</v>
+        <v>0.056033</v>
       </c>
       <c r="H623" s="7">
-        <v>0.160153</v>
+        <v>0.163154</v>
       </c>
       <c r="I623" s="7">
-        <v>0.24398499999999998</v>
+        <v>0.24720199999999998</v>
       </c>
       <c r="J623" s="7">
-        <v>1.056545</v>
+        <v>1.061865</v>
       </c>
       <c r="K623" s="7"/>
     </row>
@@ -26996,19 +26996,19 @@
         <v>5</v>
       </c>
       <c r="E633" s="7">
-        <v>0</v>
+        <v>0.031838000000000005</v>
       </c>
       <c r="F633" s="7">
-        <v>0</v>
+        <v>0.09012</v>
       </c>
       <c r="G633" s="7">
-        <v>0</v>
+        <v>0.161535</v>
       </c>
       <c r="H633" s="7">
-        <v>0</v>
+        <v>0.027256999999999997</v>
       </c>
       <c r="I633" s="7">
-        <v>0</v>
+        <v>0.105799</v>
       </c>
       <c r="J633" s="7"/>
       <c r="K633" s="7"/>
@@ -27027,22 +27027,22 @@
         <v>3</v>
       </c>
       <c r="E634" s="7">
-        <v>0</v>
+        <v>-0.013354</v>
       </c>
       <c r="F634" s="7">
-        <v>0</v>
+        <v>0.033815</v>
       </c>
       <c r="G634" s="7">
-        <v>0</v>
+        <v>0.124438</v>
       </c>
       <c r="H634" s="7">
-        <v>0</v>
+        <v>0.15691</v>
       </c>
       <c r="I634" s="7">
-        <v>0</v>
+        <v>0.34756</v>
       </c>
       <c r="J634" s="7">
-        <v>0</v>
+        <v>1.726764</v>
       </c>
       <c r="K634" s="7"/>
     </row>
@@ -28413,25 +28413,25 @@
         <v>5</v>
       </c>
       <c r="E678" s="7">
-        <v>0</v>
+        <v>0.032108</v>
       </c>
       <c r="F678" s="7">
-        <v>0</v>
+        <v>-0.002964</v>
       </c>
       <c r="G678" s="7">
-        <v>0</v>
+        <v>0.000604</v>
       </c>
       <c r="H678" s="7">
-        <v>0</v>
+        <v>0.144178</v>
       </c>
       <c r="I678" s="7">
-        <v>0</v>
+        <v>0.271609</v>
       </c>
       <c r="J678" s="7">
-        <v>0</v>
+        <v>1.606157</v>
       </c>
       <c r="K678" s="7">
-        <v>0</v>
+        <v>6.595646</v>
       </c>
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.25">
@@ -28617,22 +28617,22 @@
         <v>6</v>
       </c>
       <c r="E684" s="7">
-        <v>0.11869199999999999</v>
+        <v>0.11412800000000001</v>
       </c>
       <c r="F684" s="7">
-        <v>0.019796</v>
+        <v>0.015635</v>
       </c>
       <c r="G684" s="7">
-        <v>-0.018259</v>
+        <v>-0.022264</v>
       </c>
       <c r="H684" s="7">
-        <v>0.138463</v>
+        <v>0.133818</v>
       </c>
       <c r="I684" s="7">
-        <v>0.1845</v>
+        <v>0.179667</v>
       </c>
       <c r="J684" s="7">
-        <v>0.812458</v>
+        <v>0.805063</v>
       </c>
       <c r="K684" s="7"/>
     </row>
@@ -28650,22 +28650,22 @@
         <v>3</v>
       </c>
       <c r="E685" s="7">
-        <v>0.036953</v>
+        <v>0.040683</v>
       </c>
       <c r="F685" s="7">
-        <v>0.068737</v>
+        <v>0.07258099999999999</v>
       </c>
       <c r="G685" s="7">
-        <v>0.12591</v>
+        <v>0.12995900000000002</v>
       </c>
       <c r="H685" s="7">
-        <v>0.229212</v>
+        <v>0.23363299999999998</v>
       </c>
       <c r="I685" s="7">
-        <v>0.438665</v>
+        <v>0.443839</v>
       </c>
       <c r="J685" s="7">
-        <v>2.22501</v>
+        <v>2.236609</v>
       </c>
       <c r="K685" s="7"/>
     </row>
@@ -28953,22 +28953,22 @@
         <v>2</v>
       </c>
       <c r="E694" s="7">
-        <v>0.032857</v>
+        <v>0.033972</v>
       </c>
       <c r="F694" s="7">
-        <v>0.10299799999999999</v>
+        <v>0.10418799999999999</v>
       </c>
       <c r="G694" s="7">
-        <v>0.217656</v>
+        <v>0.21897099999999997</v>
       </c>
       <c r="H694" s="7">
-        <v>0.281849</v>
+        <v>0.283232</v>
       </c>
       <c r="I694" s="7">
-        <v>0.486366</v>
+        <v>0.487971</v>
       </c>
       <c r="J694" s="7">
-        <v>2.496137</v>
+        <v>2.499911</v>
       </c>
       <c r="K694" s="7"/>
     </row>
@@ -29246,25 +29246,25 @@
         <v>6</v>
       </c>
       <c r="E703" s="7">
-        <v>0.030713</v>
+        <v>0.030269</v>
       </c>
       <c r="F703" s="7">
-        <v>0.05524</v>
+        <v>0.054786</v>
       </c>
       <c r="G703" s="7">
-        <v>0.098541</v>
+        <v>0.098068</v>
       </c>
       <c r="H703" s="7">
-        <v>0.29291</v>
+        <v>0.292353</v>
       </c>
       <c r="I703" s="7">
-        <v>0.38033900000000004</v>
+        <v>0.379744</v>
       </c>
       <c r="J703" s="7">
-        <v>1.0445579999999999</v>
+        <v>1.043677</v>
       </c>
       <c r="K703" s="7">
-        <v>11.111266</v>
+        <v>11.106048000000001</v>
       </c>
     </row>
     <row r="704" spans="1:11" x14ac:dyDescent="0.25">
@@ -29281,25 +29281,25 @@
         <v>6</v>
       </c>
       <c r="E704" s="7">
-        <v>0.021804999999999998</v>
+        <v>0.019818</v>
       </c>
       <c r="F704" s="7">
-        <v>-0.018938</v>
+        <v>-0.020846</v>
       </c>
       <c r="G704" s="7">
-        <v>-0.000833</v>
+        <v>-0.002777</v>
       </c>
       <c r="H704" s="7">
-        <v>0.191491</v>
+        <v>0.189174</v>
       </c>
       <c r="I704" s="7">
-        <v>0.253379</v>
+        <v>0.250941</v>
       </c>
       <c r="J704" s="7">
-        <v>0.903183</v>
+        <v>0.899481</v>
       </c>
       <c r="K704" s="7">
-        <v>10.062404</v>
+        <v>10.040885</v>
       </c>
     </row>
     <row r="705" spans="1:11" x14ac:dyDescent="0.25">
@@ -29791,19 +29791,19 @@
         <v>4</v>
       </c>
       <c r="E720" s="7">
-        <v>0.053569000000000006</v>
+        <v>0.061848</v>
       </c>
       <c r="F720" s="7">
-        <v>0.106068</v>
+        <v>0.114759</v>
       </c>
       <c r="G720" s="7">
-        <v>0.250507</v>
+        <v>0.260333</v>
       </c>
       <c r="H720" s="7">
-        <v>0.42396500000000004</v>
+        <v>0.435155</v>
       </c>
       <c r="I720" s="7">
-        <v>0.597478</v>
+        <v>0.610031</v>
       </c>
       <c r="J720" s="7"/>
       <c r="K720" s="7"/>
@@ -29888,19 +29888,19 @@
         <v>6</v>
       </c>
       <c r="E723" s="7">
-        <v>0</v>
+        <v>-0.033778</v>
       </c>
       <c r="F723" s="7">
-        <v>0</v>
+        <v>0.311386</v>
       </c>
       <c r="G723" s="7">
-        <v>0</v>
+        <v>0.808395</v>
       </c>
       <c r="H723" s="7">
-        <v>0</v>
+        <v>1.383416</v>
       </c>
       <c r="I723" s="7">
-        <v>0</v>
+        <v>1.902895</v>
       </c>
       <c r="J723" s="7"/>
       <c r="K723" s="7"/>
@@ -30177,19 +30177,19 @@
         <v>6</v>
       </c>
       <c r="E732" s="7">
-        <v>0</v>
+        <v>0.042088</v>
       </c>
       <c r="F732" s="7">
-        <v>0</v>
+        <v>0.399105</v>
       </c>
       <c r="G732" s="7">
-        <v>0</v>
+        <v>0.9154810000000001</v>
       </c>
       <c r="H732" s="7">
-        <v>0</v>
+        <v>1.797183</v>
       </c>
       <c r="I732" s="7">
-        <v>0</v>
+        <v>2.364081</v>
       </c>
       <c r="J732" s="7"/>
       <c r="K732" s="7"/>
@@ -30301,22 +30301,22 @@
         <v>6</v>
       </c>
       <c r="E736" s="7">
-        <v>0.06831000000000001</v>
+        <v>0.066872</v>
       </c>
       <c r="F736" s="7">
-        <v>-0.038083</v>
+        <v>-0.039378</v>
       </c>
       <c r="G736" s="7">
-        <v>0.09735900000000001</v>
+        <v>0.09588200000000001</v>
       </c>
       <c r="H736" s="7">
-        <v>0.272742</v>
+        <v>0.271029</v>
       </c>
       <c r="I736" s="7">
-        <v>0.751345</v>
+        <v>0.7489870000000001</v>
       </c>
       <c r="J736" s="7">
-        <v>2.172646</v>
+        <v>2.168375</v>
       </c>
       <c r="K736" s="7"/>
     </row>
@@ -32531,7 +32531,7 @@
         <v>6</v>
       </c>
       <c r="E808" s="7">
-        <v>0.087786</v>
+        <v>0.088165</v>
       </c>
       <c r="F808" s="7"/>
       <c r="G808" s="7"/>
@@ -33796,19 +33796,19 @@
         <v>5</v>
       </c>
       <c r="E849" s="7">
-        <v>0</v>
+        <v>0.052093</v>
       </c>
       <c r="F849" s="7">
-        <v>0</v>
+        <v>0.19733699999999998</v>
       </c>
       <c r="G849" s="7">
-        <v>0</v>
+        <v>0.43095500000000003</v>
       </c>
       <c r="H849" s="7">
-        <v>0</v>
+        <v>0.44974899999999995</v>
       </c>
       <c r="I849" s="7">
-        <v>0</v>
+        <v>0.535046</v>
       </c>
       <c r="J849" s="7"/>
       <c r="K849" s="7"/>
@@ -34191,19 +34191,19 @@
         <v>4</v>
       </c>
       <c r="E862" s="7">
-        <v>0.053879</v>
+        <v>0.06362</v>
       </c>
       <c r="F862" s="7">
-        <v>0.066432</v>
+        <v>0.076289</v>
       </c>
       <c r="G862" s="7">
-        <v>0.141491</v>
+        <v>0.152042</v>
       </c>
       <c r="H862" s="7">
-        <v>0.257989</v>
+        <v>0.269616</v>
       </c>
       <c r="I862" s="7">
-        <v>0.532023</v>
+        <v>0.546183</v>
       </c>
       <c r="J862" s="7"/>
       <c r="K862" s="7"/>
@@ -34855,22 +34855,22 @@
         <v>3</v>
       </c>
       <c r="E882" s="7">
-        <v>0</v>
+        <v>0.033858</v>
       </c>
       <c r="F882" s="7">
-        <v>0</v>
+        <v>0.093667</v>
       </c>
       <c r="G882" s="7">
-        <v>0</v>
+        <v>0.19206499999999999</v>
       </c>
       <c r="H882" s="7">
-        <v>0</v>
+        <v>0.263702</v>
       </c>
       <c r="I882" s="7">
-        <v>0</v>
+        <v>0.45982599999999996</v>
       </c>
       <c r="J882" s="7">
-        <v>0</v>
+        <v>2.313097</v>
       </c>
       <c r="K882" s="7"/>
     </row>
@@ -35558,25 +35558,25 @@
         <v>6</v>
       </c>
       <c r="E903" s="7">
-        <v>0</v>
+        <v>0.027361</v>
       </c>
       <c r="F903" s="7">
-        <v>0</v>
+        <v>0.019975</v>
       </c>
       <c r="G903" s="7">
-        <v>0</v>
+        <v>0.084749</v>
       </c>
       <c r="H903" s="7">
-        <v>0</v>
+        <v>0.23490100000000003</v>
       </c>
       <c r="I903" s="7">
-        <v>0</v>
+        <v>0.30889099999999997</v>
       </c>
       <c r="J903" s="7">
-        <v>0</v>
+        <v>1.2078470000000001</v>
       </c>
       <c r="K903" s="7">
-        <v>0</v>
+        <v>4.486803</v>
       </c>
     </row>
     <row r="904" spans="1:11" x14ac:dyDescent="0.25">
@@ -35593,22 +35593,22 @@
         <v>4</v>
       </c>
       <c r="E904" s="7">
-        <v>0</v>
+        <v>0.055220000000000005</v>
       </c>
       <c r="F904" s="7">
-        <v>0</v>
+        <v>0.04638</v>
       </c>
       <c r="G904" s="7">
-        <v>0</v>
+        <v>0.087523</v>
       </c>
       <c r="H904" s="7">
-        <v>0</v>
+        <v>0.219772</v>
       </c>
       <c r="I904" s="7">
-        <v>0</v>
+        <v>0.413526</v>
       </c>
       <c r="J904" s="7">
-        <v>0</v>
+        <v>1.738567</v>
       </c>
       <c r="K904" s="7"/>
     </row>
@@ -36150,25 +36150,25 @@
         <v>6</v>
       </c>
       <c r="E921" s="7">
-        <v>0</v>
+        <v>0.126824</v>
       </c>
       <c r="F921" s="7">
-        <v>0</v>
+        <v>-0.030427</v>
       </c>
       <c r="G921" s="7">
-        <v>0</v>
+        <v>-0.05163</v>
       </c>
       <c r="H921" s="7">
-        <v>0</v>
+        <v>0.05025</v>
       </c>
       <c r="I921" s="7">
-        <v>0</v>
+        <v>0.44656199999999996</v>
       </c>
       <c r="J921" s="7">
-        <v>0</v>
+        <v>1.8093469999999998</v>
       </c>
       <c r="K921" s="7">
-        <v>0</v>
+        <v>6.262225</v>
       </c>
     </row>
     <row r="922" spans="1:11" x14ac:dyDescent="0.25">
@@ -37903,22 +37903,22 @@
         <v>2</v>
       </c>
       <c r="E976" s="7">
-        <v>0</v>
+        <v>0.034495</v>
       </c>
       <c r="F976" s="7">
-        <v>0</v>
+        <v>0.091045</v>
       </c>
       <c r="G976" s="7">
-        <v>0</v>
+        <v>0.18922799999999998</v>
       </c>
       <c r="H976" s="7">
-        <v>0</v>
+        <v>0.25810099999999997</v>
       </c>
       <c r="I976" s="7">
-        <v>0</v>
+        <v>0.43737499999999996</v>
       </c>
       <c r="J976" s="7">
-        <v>0</v>
+        <v>1.79216</v>
       </c>
       <c r="K976" s="7"/>
     </row>

--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>21.08.2026 11:36:57</t>
+    <t>21.08.2026 22:24:47</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -15224,16 +15224,16 @@
         <v>6</v>
       </c>
       <c r="E267" s="7">
-        <v>0.09766400000000001</v>
+        <v>0.097663</v>
       </c>
       <c r="F267" s="7">
         <v>0.027719999999999998</v>
       </c>
       <c r="G267" s="7">
-        <v>0.123175</v>
+        <v>0.12317399999999999</v>
       </c>
       <c r="H267" s="7">
-        <v>0.278594</v>
+        <v>0.27859300000000004</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
@@ -21124,22 +21124,22 @@
       </c>
       <c r="D449" s="6"/>
       <c r="E449" s="7">
-        <v>0.030602</v>
+        <v>0.030653</v>
       </c>
       <c r="F449" s="7">
-        <v>0.082248</v>
+        <v>0.082302</v>
       </c>
       <c r="G449" s="7">
-        <v>0.140341</v>
+        <v>0.140397</v>
       </c>
       <c r="H449" s="7">
-        <v>0.18634799999999999</v>
+        <v>0.186406</v>
       </c>
       <c r="I449" s="7">
-        <v>0.33793500000000004</v>
+        <v>0.338001</v>
       </c>
       <c r="J449" s="7">
-        <v>1.2978530000000001</v>
+        <v>1.2979660000000002</v>
       </c>
       <c r="K449" s="7"/>
     </row>
@@ -22830,22 +22830,22 @@
         <v>5</v>
       </c>
       <c r="E501" s="7">
-        <v>0.037915000000000004</v>
+        <v>0.041621</v>
       </c>
       <c r="F501" s="7">
-        <v>0.165881</v>
+        <v>0.170044</v>
       </c>
       <c r="G501" s="7">
-        <v>0.305141</v>
+        <v>0.309801</v>
       </c>
       <c r="H501" s="7">
-        <v>0.40219299999999997</v>
+        <v>0.40719900000000003</v>
       </c>
       <c r="I501" s="7">
-        <v>0.48214599999999996</v>
+        <v>0.487438</v>
       </c>
       <c r="J501" s="7">
-        <v>1.859455</v>
+        <v>1.869665</v>
       </c>
       <c r="K501" s="7"/>
     </row>
@@ -37057,19 +37057,19 @@
         <v>6</v>
       </c>
       <c r="E948" s="7">
-        <v>0.045347</v>
+        <v>0.087287</v>
       </c>
       <c r="F948" s="7">
-        <v>-0.046388</v>
+        <v>-0.008128999999999999</v>
       </c>
       <c r="G948" s="7">
-        <v>-0.007088</v>
+        <v>0.032748</v>
       </c>
       <c r="H948" s="7">
-        <v>0.193165</v>
+        <v>0.241035</v>
       </c>
       <c r="I948" s="7">
-        <v>0.515239</v>
+        <v>0.576031</v>
       </c>
       <c r="J948" s="7"/>
       <c r="K948" s="7"/>

--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>24.08.2026 09:28:22</t>
+    <t>24.08.2026 11:51:54</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -7394,25 +7394,25 @@
         <v>7</v>
       </c>
       <c r="E19" s="7">
-        <v>0</v>
+        <v>0.015485</v>
       </c>
       <c r="F19" s="7">
-        <v>0</v>
+        <v>0.022303000000000003</v>
       </c>
       <c r="G19" s="7">
-        <v>0</v>
+        <v>0.644164</v>
       </c>
       <c r="H19" s="7">
-        <v>0</v>
+        <v>0.923056</v>
       </c>
       <c r="I19" s="7">
-        <v>0</v>
+        <v>0.882357</v>
       </c>
       <c r="J19" s="7">
-        <v>0</v>
+        <v>1.661957</v>
       </c>
       <c r="K19" s="7">
-        <v>0</v>
+        <v>10.802105</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -7497,25 +7497,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0</v>
+        <v>0.131029</v>
       </c>
       <c r="F22" s="7">
-        <v>0</v>
+        <v>0.058034</v>
       </c>
       <c r="G22" s="7">
-        <v>0</v>
+        <v>-0.069573</v>
       </c>
       <c r="H22" s="7">
-        <v>0</v>
+        <v>0.132853</v>
       </c>
       <c r="I22" s="7">
-        <v>0</v>
+        <v>0.556907</v>
       </c>
       <c r="J22" s="7">
-        <v>0</v>
+        <v>2.782925</v>
       </c>
       <c r="K22" s="7">
-        <v>0</v>
+        <v>11.900352</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -7775,25 +7775,25 @@
         <v>4</v>
       </c>
       <c r="E30" s="7">
-        <v>0.027071</v>
+        <v>0.034110999999999995</v>
       </c>
       <c r="F30" s="7">
-        <v>0.073972</v>
+        <v>0.081334</v>
       </c>
       <c r="G30" s="7">
-        <v>0.159484</v>
+        <v>0.16743200000000003</v>
       </c>
       <c r="H30" s="7">
-        <v>0.286637</v>
+        <v>0.295456</v>
       </c>
       <c r="I30" s="7">
-        <v>0.441257</v>
+        <v>0.451136</v>
       </c>
       <c r="J30" s="7">
-        <v>1.9022640000000002</v>
+        <v>1.922158</v>
       </c>
       <c r="K30" s="7">
-        <v>8.215135</v>
+        <v>8.278303</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -8245,19 +8245,19 @@
         <v>3</v>
       </c>
       <c r="E44" s="7">
-        <v>0.030175999999999998</v>
+        <v>0.029967</v>
       </c>
       <c r="F44" s="7">
-        <v>0.103748</v>
+        <v>0.10352399999999999</v>
       </c>
       <c r="G44" s="7">
-        <v>0.23328700000000002</v>
+        <v>0.233036</v>
       </c>
       <c r="H44" s="7">
-        <v>0.289934</v>
+        <v>0.289671</v>
       </c>
       <c r="I44" s="7">
-        <v>0.477729</v>
+        <v>0.477429</v>
       </c>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
@@ -8276,25 +8276,25 @@
         <v>6</v>
       </c>
       <c r="E45" s="7">
-        <v>0</v>
+        <v>0.036696</v>
       </c>
       <c r="F45" s="7">
-        <v>0</v>
+        <v>0.043261</v>
       </c>
       <c r="G45" s="7">
-        <v>0</v>
+        <v>-0.020552</v>
       </c>
       <c r="H45" s="7">
-        <v>0</v>
+        <v>0.194217</v>
       </c>
       <c r="I45" s="7">
-        <v>0</v>
+        <v>0.211921</v>
       </c>
       <c r="J45" s="7">
-        <v>0</v>
+        <v>1.094252</v>
       </c>
       <c r="K45" s="7">
-        <v>0</v>
+        <v>3.014373</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -8379,25 +8379,25 @@
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="7">
-        <v>0</v>
+        <v>0.031902</v>
       </c>
       <c r="F48" s="7">
-        <v>0</v>
+        <v>0.062636</v>
       </c>
       <c r="G48" s="7">
-        <v>0</v>
+        <v>0.098223</v>
       </c>
       <c r="H48" s="7">
-        <v>0</v>
+        <v>0.208781</v>
       </c>
       <c r="I48" s="7">
-        <v>0</v>
+        <v>0.34789499999999995</v>
       </c>
       <c r="J48" s="7">
-        <v>0</v>
+        <v>1.997692</v>
       </c>
       <c r="K48" s="7">
-        <v>0</v>
+        <v>5.418520999999999</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -8412,25 +8412,25 @@
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7">
-        <v>0</v>
+        <v>0.030784</v>
       </c>
       <c r="F49" s="7">
-        <v>0</v>
+        <v>0.046421000000000004</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>0.042996999999999994</v>
       </c>
       <c r="H49" s="7">
-        <v>0</v>
+        <v>0.18387599999999998</v>
       </c>
       <c r="I49" s="7">
-        <v>0</v>
+        <v>0.310975</v>
       </c>
       <c r="J49" s="7">
-        <v>0</v>
+        <v>1.81321</v>
       </c>
       <c r="K49" s="7">
-        <v>0</v>
+        <v>5.9832410000000005</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -8999,19 +8999,19 @@
         <v>5</v>
       </c>
       <c r="E68" s="7">
-        <v>0.011498</v>
+        <v>0.016131</v>
       </c>
       <c r="F68" s="7">
-        <v>0.054661</v>
+        <v>0.059492</v>
       </c>
       <c r="G68" s="7">
-        <v>0.044871999999999995</v>
+        <v>0.049658</v>
       </c>
       <c r="H68" s="7">
-        <v>0.143423</v>
+        <v>0.14866</v>
       </c>
       <c r="I68" s="7">
-        <v>0.30889500000000003</v>
+        <v>0.31489</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
@@ -9361,19 +9361,19 @@
         <v>6</v>
       </c>
       <c r="E80" s="7">
-        <v>0.047464000000000006</v>
+        <v>0.047367</v>
       </c>
       <c r="F80" s="7">
-        <v>0.179877</v>
+        <v>0.179767</v>
       </c>
       <c r="G80" s="7">
-        <v>0.214805</v>
+        <v>0.214692</v>
       </c>
       <c r="H80" s="7">
-        <v>0.40765999999999997</v>
+        <v>0.407529</v>
       </c>
       <c r="I80" s="7">
-        <v>0.9084780000000001</v>
+        <v>0.9083</v>
       </c>
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
@@ -9878,19 +9878,19 @@
         <v>5</v>
       </c>
       <c r="E97" s="7">
-        <v>0.036169</v>
+        <v>0.039188</v>
       </c>
       <c r="F97" s="7">
-        <v>0.055918999999999996</v>
+        <v>0.058995</v>
       </c>
       <c r="G97" s="7">
-        <v>0.12305999999999999</v>
+        <v>0.126332</v>
       </c>
       <c r="H97" s="7">
-        <v>0.306992</v>
+        <v>0.31079999999999997</v>
       </c>
       <c r="I97" s="7">
-        <v>0.46726599999999996</v>
+        <v>0.471541</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
@@ -10058,16 +10058,16 @@
         <v>7</v>
       </c>
       <c r="E103" s="7">
-        <v>0.046479</v>
+        <v>0.046474</v>
       </c>
       <c r="F103" s="7">
-        <v>0.157864</v>
+        <v>0.15786</v>
       </c>
       <c r="G103" s="7">
-        <v>0.387711</v>
+        <v>0.387706</v>
       </c>
       <c r="H103" s="7">
-        <v>0.535945</v>
+        <v>0.5359389999999999</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
@@ -10244,10 +10244,10 @@
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>0</v>
+        <v>0.029251999999999997</v>
       </c>
       <c r="F109" s="7">
-        <v>0</v>
+        <v>0.21943400000000002</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
@@ -10544,16 +10544,16 @@
         <v>6</v>
       </c>
       <c r="E119" s="7">
-        <v>0</v>
+        <v>-0.042824999999999995</v>
       </c>
       <c r="F119" s="7">
-        <v>0</v>
+        <v>-0.07206</v>
       </c>
       <c r="G119" s="7">
-        <v>0</v>
+        <v>-0.01856</v>
       </c>
       <c r="H119" s="7">
-        <v>0</v>
+        <v>0.24369700000000002</v>
       </c>
       <c r="I119" s="7"/>
       <c r="J119" s="7"/>
@@ -11531,22 +11531,22 @@
         <v>6</v>
       </c>
       <c r="E150" s="7">
-        <v>0.031225999999999997</v>
+        <v>0.035445000000000004</v>
       </c>
       <c r="F150" s="7">
-        <v>0.032859</v>
+        <v>0.037085</v>
       </c>
       <c r="G150" s="7">
-        <v>0.058257</v>
+        <v>0.062587</v>
       </c>
       <c r="H150" s="7">
-        <v>0.215358</v>
+        <v>0.22033000000000003</v>
       </c>
       <c r="I150" s="7">
-        <v>0.24762499999999998</v>
+        <v>0.25273</v>
       </c>
       <c r="J150" s="7">
-        <v>1.4110740000000002</v>
+        <v>1.420939</v>
       </c>
       <c r="K150" s="7"/>
     </row>
@@ -11564,16 +11564,16 @@
         <v>6</v>
       </c>
       <c r="E151" s="7">
-        <v>0.062913</v>
+        <v>0.062515</v>
       </c>
       <c r="F151" s="7">
-        <v>0.12296599999999999</v>
+        <v>0.122545</v>
       </c>
       <c r="G151" s="7">
-        <v>0.09050000000000001</v>
+        <v>0.090091</v>
       </c>
       <c r="H151" s="7">
-        <v>0.187589</v>
+        <v>0.187144</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="7"/>
@@ -11744,19 +11744,19 @@
         <v>3</v>
       </c>
       <c r="E157" s="7">
-        <v>0</v>
+        <v>0.020249000000000003</v>
       </c>
       <c r="F157" s="7">
-        <v>0</v>
+        <v>0.063242</v>
       </c>
       <c r="G157" s="7">
-        <v>0</v>
+        <v>0.104569</v>
       </c>
       <c r="H157" s="7">
-        <v>0</v>
+        <v>0.135991</v>
       </c>
       <c r="I157" s="7">
-        <v>0</v>
+        <v>0.213625</v>
       </c>
       <c r="J157" s="7"/>
       <c r="K157" s="7"/>
@@ -11936,22 +11936,22 @@
         <v>7</v>
       </c>
       <c r="E163" s="7">
-        <v>0.208418</v>
+        <v>0.21047999999999997</v>
       </c>
       <c r="F163" s="7">
-        <v>-0.043467000000000006</v>
+        <v>-0.041835000000000004</v>
       </c>
       <c r="G163" s="7">
-        <v>-0.119805</v>
+        <v>-0.11830299999999999</v>
       </c>
       <c r="H163" s="7">
-        <v>0.052569</v>
+        <v>0.054365</v>
       </c>
       <c r="I163" s="7">
-        <v>1.02948</v>
+        <v>1.0329430000000002</v>
       </c>
       <c r="J163" s="7">
-        <v>3.6127100000000003</v>
+        <v>3.620581</v>
       </c>
       <c r="K163" s="7"/>
     </row>
@@ -11969,16 +11969,16 @@
         <v>4</v>
       </c>
       <c r="E164" s="7">
-        <v>0.073664</v>
+        <v>0.076918</v>
       </c>
       <c r="F164" s="7">
-        <v>0.09728300000000001</v>
+        <v>0.100608</v>
       </c>
       <c r="G164" s="7">
-        <v>0.12827</v>
+        <v>0.131689</v>
       </c>
       <c r="H164" s="7">
-        <v>0.262268</v>
+        <v>0.266093</v>
       </c>
       <c r="I164" s="7"/>
       <c r="J164" s="7"/>
@@ -12056,19 +12056,19 @@
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="7">
-        <v>0.051536</v>
+        <v>0.059371</v>
       </c>
       <c r="F167" s="7">
-        <v>0.089478</v>
+        <v>0.097596</v>
       </c>
       <c r="G167" s="7">
-        <v>0.100239</v>
+        <v>0.108437</v>
       </c>
       <c r="H167" s="7">
-        <v>0.131471</v>
+        <v>0.139902</v>
       </c>
       <c r="I167" s="7">
-        <v>0.266051</v>
+        <v>0.275485</v>
       </c>
       <c r="J167" s="7"/>
       <c r="K167" s="7"/>
@@ -12442,25 +12442,25 @@
         <v>3</v>
       </c>
       <c r="E179" s="7">
-        <v>0.037738999999999995</v>
+        <v>0.042026</v>
       </c>
       <c r="F179" s="7">
-        <v>0.08422299999999999</v>
+        <v>0.088702</v>
       </c>
       <c r="G179" s="7">
-        <v>0.125666</v>
+        <v>0.130316</v>
       </c>
       <c r="H179" s="7">
-        <v>0.214808</v>
+        <v>0.21982700000000002</v>
       </c>
       <c r="I179" s="7">
-        <v>0.396901</v>
+        <v>0.402671</v>
       </c>
       <c r="J179" s="7">
-        <v>1.79489</v>
+        <v>1.8064349999999998</v>
       </c>
       <c r="K179" s="7">
-        <v>6.62938</v>
+        <v>6.660896</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -12634,19 +12634,19 @@
         <v>6</v>
       </c>
       <c r="E185" s="7">
-        <v>0</v>
+        <v>0.139704</v>
       </c>
       <c r="F185" s="7">
-        <v>0</v>
+        <v>0.375681</v>
       </c>
       <c r="G185" s="7">
-        <v>0</v>
+        <v>0.152951</v>
       </c>
       <c r="H185" s="7">
-        <v>0</v>
+        <v>0.084726</v>
       </c>
       <c r="I185" s="7">
-        <v>0</v>
+        <v>0.11939999999999999</v>
       </c>
       <c r="J185" s="7"/>
       <c r="K185" s="7"/>
@@ -12925,16 +12925,16 @@
       </c>
       <c r="D194" s="6"/>
       <c r="E194" s="7">
-        <v>0.047048</v>
+        <v>0.047145</v>
       </c>
       <c r="F194" s="7">
-        <v>0.07876</v>
+        <v>0.07886</v>
       </c>
       <c r="G194" s="7">
-        <v>0.086203</v>
+        <v>0.086303</v>
       </c>
       <c r="H194" s="7">
-        <v>0.127993</v>
+        <v>0.128097</v>
       </c>
       <c r="I194" s="7"/>
       <c r="J194" s="7"/>
@@ -12952,16 +12952,16 @@
       </c>
       <c r="D195" s="6"/>
       <c r="E195" s="7">
-        <v>0.024786000000000002</v>
+        <v>0.023559</v>
       </c>
       <c r="F195" s="7">
-        <v>0.070578</v>
+        <v>0.069297</v>
       </c>
       <c r="G195" s="7">
-        <v>0.110938</v>
+        <v>0.10960900000000001</v>
       </c>
       <c r="H195" s="7">
-        <v>0.143765</v>
+        <v>0.142396</v>
       </c>
       <c r="I195" s="7"/>
       <c r="J195" s="7"/>
@@ -13161,7 +13161,7 @@
         <v>6</v>
       </c>
       <c r="E202" s="7">
-        <v>0.061671</v>
+        <v>0.061678</v>
       </c>
       <c r="F202" s="7"/>
       <c r="G202" s="7"/>
@@ -13498,16 +13498,16 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>0.157164</v>
+        <v>0.158182</v>
       </c>
       <c r="F213" s="7">
-        <v>0.00358</v>
+        <v>0.004463</v>
       </c>
       <c r="G213" s="7">
-        <v>-0.109433</v>
+        <v>-0.10865</v>
       </c>
       <c r="H213" s="7">
-        <v>0.09494</v>
+        <v>0.09590299999999999</v>
       </c>
       <c r="I213" s="7"/>
       <c r="J213" s="7"/>
@@ -13765,19 +13765,19 @@
         <v>3</v>
       </c>
       <c r="E222" s="7">
-        <v>0.054245999999999996</v>
+        <v>0.062301999999999996</v>
       </c>
       <c r="F222" s="7">
-        <v>0.062904</v>
+        <v>0.07102699999999999</v>
       </c>
       <c r="G222" s="7">
-        <v>0.12475</v>
+        <v>0.133345</v>
       </c>
       <c r="H222" s="7">
-        <v>0.266934</v>
+        <v>0.276615</v>
       </c>
       <c r="I222" s="7">
-        <v>0.510501</v>
+        <v>0.522044</v>
       </c>
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
@@ -13951,25 +13951,25 @@
         <v>6</v>
       </c>
       <c r="E228" s="7">
-        <v>0.065869</v>
+        <v>0.065868</v>
       </c>
       <c r="F228" s="7">
-        <v>0.039114</v>
+        <v>0.039113</v>
       </c>
       <c r="G228" s="7">
-        <v>0.28981999999999997</v>
+        <v>0.289818</v>
       </c>
       <c r="H228" s="7">
-        <v>0.281739</v>
+        <v>0.281737</v>
       </c>
       <c r="I228" s="7">
-        <v>0.492064</v>
+        <v>0.492063</v>
       </c>
       <c r="J228" s="7">
-        <v>1.784358</v>
+        <v>1.784355</v>
       </c>
       <c r="K228" s="7">
-        <v>3.2235050000000003</v>
+        <v>3.223501</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -14147,25 +14147,25 @@
         <v>4</v>
       </c>
       <c r="E234" s="7">
-        <v>0.04785300000000001</v>
+        <v>0.056536</v>
       </c>
       <c r="F234" s="7">
-        <v>0.06177</v>
+        <v>0.070568</v>
       </c>
       <c r="G234" s="7">
-        <v>0.06502100000000001</v>
+        <v>0.073846</v>
       </c>
       <c r="H234" s="7">
-        <v>0.16157900000000003</v>
+        <v>0.171205</v>
       </c>
       <c r="I234" s="7">
-        <v>0.390201</v>
+        <v>0.401721</v>
       </c>
       <c r="J234" s="7">
-        <v>1.892808</v>
+        <v>1.916779</v>
       </c>
       <c r="K234" s="7">
-        <v>5.7530660000000005</v>
+        <v>5.809026</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -14576,25 +14576,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.057709</v>
+        <v>0.060871</v>
       </c>
       <c r="F247" s="7">
-        <v>0.10160399999999999</v>
+        <v>0.10489699999999999</v>
       </c>
       <c r="G247" s="7">
-        <v>0.092797</v>
+        <v>0.09606400000000001</v>
       </c>
       <c r="H247" s="7">
-        <v>0.18179099999999998</v>
+        <v>0.185324</v>
       </c>
       <c r="I247" s="7">
-        <v>0.38791800000000004</v>
+        <v>0.392067</v>
       </c>
       <c r="J247" s="7">
-        <v>1.9467189999999999</v>
+        <v>1.9555289999999999</v>
       </c>
       <c r="K247" s="7">
-        <v>6.363107</v>
+        <v>6.38512</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -14611,19 +14611,19 @@
         <v>6</v>
       </c>
       <c r="E248" s="7">
-        <v>0</v>
+        <v>0.070713</v>
       </c>
       <c r="F248" s="7">
-        <v>0</v>
+        <v>0.185745</v>
       </c>
       <c r="G248" s="7">
-        <v>0</v>
+        <v>0.135823</v>
       </c>
       <c r="H248" s="7">
-        <v>0</v>
+        <v>0.423963</v>
       </c>
       <c r="I248" s="7">
-        <v>0</v>
+        <v>0.340529</v>
       </c>
       <c r="J248" s="7"/>
       <c r="K248" s="7"/>
@@ -14803,25 +14803,25 @@
         <v>1</v>
       </c>
       <c r="E254" s="7">
-        <v>-0.011496</v>
+        <v>0.034865</v>
       </c>
       <c r="F254" s="7">
-        <v>0.048880999999999994</v>
+        <v>0.098074</v>
       </c>
       <c r="G254" s="7">
-        <v>0.130133</v>
+        <v>0.18313600000000002</v>
       </c>
       <c r="H254" s="7">
-        <v>0.19281199999999998</v>
+        <v>0.24875499999999998</v>
       </c>
       <c r="I254" s="7">
-        <v>0.369158</v>
+        <v>0.43337200000000003</v>
       </c>
       <c r="J254" s="7">
-        <v>2.101759</v>
+        <v>2.247233</v>
       </c>
       <c r="K254" s="7">
-        <v>3.472379</v>
+        <v>3.682136</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -15102,22 +15102,22 @@
         <v>6</v>
       </c>
       <c r="E263" s="7">
-        <v>0.035725</v>
+        <v>0.037554</v>
       </c>
       <c r="F263" s="7">
-        <v>0.037014</v>
+        <v>0.038846</v>
       </c>
       <c r="G263" s="7">
-        <v>0.33134399999999997</v>
+        <v>0.333695</v>
       </c>
       <c r="H263" s="7">
-        <v>0.338337</v>
+        <v>0.340701</v>
       </c>
       <c r="I263" s="7">
-        <v>0.532471</v>
+        <v>0.535178</v>
       </c>
       <c r="J263" s="7">
-        <v>2.438205</v>
+        <v>2.444279</v>
       </c>
       <c r="K263" s="7"/>
     </row>
@@ -15228,16 +15228,16 @@
         <v>6</v>
       </c>
       <c r="E267" s="7">
-        <v>0</v>
+        <v>0.084944</v>
       </c>
       <c r="F267" s="7">
-        <v>0</v>
+        <v>0.056882</v>
       </c>
       <c r="G267" s="7">
-        <v>0</v>
+        <v>0.126363</v>
       </c>
       <c r="H267" s="7">
-        <v>0</v>
+        <v>0.29412099999999997</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
@@ -15461,22 +15461,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.031772</v>
+        <v>0.038323</v>
       </c>
       <c r="F274" s="7">
-        <v>0.073352</v>
+        <v>0.080168</v>
       </c>
       <c r="G274" s="7">
-        <v>0.117208</v>
+        <v>0.124302</v>
       </c>
       <c r="H274" s="7">
-        <v>0.20501000000000003</v>
+        <v>0.21266100000000002</v>
       </c>
       <c r="I274" s="7">
-        <v>0.34780700000000003</v>
+        <v>0.356365</v>
       </c>
       <c r="J274" s="7">
-        <v>1.873057</v>
+        <v>1.8912989999999998</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -15669,25 +15669,25 @@
         <v>3</v>
       </c>
       <c r="E280" s="7">
-        <v>0</v>
+        <v>0.033908</v>
       </c>
       <c r="F280" s="7">
-        <v>0</v>
+        <v>0.09310399999999999</v>
       </c>
       <c r="G280" s="7">
-        <v>0</v>
+        <v>0.120233</v>
       </c>
       <c r="H280" s="7">
-        <v>0</v>
+        <v>0.230748</v>
       </c>
       <c r="I280" s="7">
-        <v>0</v>
+        <v>0.393554</v>
       </c>
       <c r="J280" s="7">
-        <v>0</v>
+        <v>2.247403</v>
       </c>
       <c r="K280" s="7">
-        <v>0</v>
+        <v>6.184353</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -15941,22 +15941,22 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0</v>
+        <v>-0.0006419999999999999</v>
       </c>
       <c r="F288" s="7">
-        <v>0</v>
+        <v>0.028863</v>
       </c>
       <c r="G288" s="7">
-        <v>0</v>
+        <v>0.307775</v>
       </c>
       <c r="H288" s="7">
-        <v>0</v>
+        <v>0.378832</v>
       </c>
       <c r="I288" s="7">
-        <v>0</v>
+        <v>0.597276</v>
       </c>
       <c r="J288" s="7">
-        <v>0</v>
+        <v>3.849065</v>
       </c>
       <c r="K288" s="7"/>
     </row>
@@ -15974,22 +15974,22 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.071208</v>
+        <v>0.071394</v>
       </c>
       <c r="F289" s="7">
-        <v>0.033285999999999996</v>
+        <v>0.033464999999999995</v>
       </c>
       <c r="G289" s="7">
-        <v>0.161949</v>
+        <v>0.16215</v>
       </c>
       <c r="H289" s="7">
-        <v>0.29994</v>
+        <v>0.300166</v>
       </c>
       <c r="I289" s="7">
-        <v>0.5273129999999999</v>
+        <v>0.527578</v>
       </c>
       <c r="J289" s="7">
-        <v>1.591493</v>
+        <v>1.591942</v>
       </c>
       <c r="K289" s="7"/>
     </row>
@@ -16077,19 +16077,19 @@
         <v>5</v>
       </c>
       <c r="E292" s="7">
-        <v>0</v>
+        <v>0.021120999999999997</v>
       </c>
       <c r="F292" s="7">
-        <v>0</v>
+        <v>0.055576999999999994</v>
       </c>
       <c r="G292" s="7">
-        <v>0</v>
+        <v>0.040923</v>
       </c>
       <c r="H292" s="7">
-        <v>0</v>
+        <v>0.17937</v>
       </c>
       <c r="I292" s="7">
-        <v>0</v>
+        <v>0.235104</v>
       </c>
       <c r="J292" s="7"/>
       <c r="K292" s="7"/>
@@ -16174,25 +16174,25 @@
         <v>5</v>
       </c>
       <c r="E295" s="7">
-        <v>0.026425999999999998</v>
+        <v>0.033946000000000004</v>
       </c>
       <c r="F295" s="7">
-        <v>0.014514</v>
+        <v>0.021948</v>
       </c>
       <c r="G295" s="7">
-        <v>0.067936</v>
+        <v>0.07576100000000001</v>
       </c>
       <c r="H295" s="7">
-        <v>0.223189</v>
+        <v>0.232152</v>
       </c>
       <c r="I295" s="7">
-        <v>0.486976</v>
+        <v>0.497872</v>
       </c>
       <c r="J295" s="7">
-        <v>1.771747</v>
+        <v>1.792056</v>
       </c>
       <c r="K295" s="7">
-        <v>9.178882999999999</v>
+        <v>9.253466</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -16376,22 +16376,22 @@
         <v>5</v>
       </c>
       <c r="E301" s="7">
-        <v>0.049665999999999995</v>
+        <v>0.0594</v>
       </c>
       <c r="F301" s="7">
-        <v>0.046725</v>
+        <v>0.056430999999999995</v>
       </c>
       <c r="G301" s="7">
-        <v>0.043781999999999995</v>
+        <v>0.053461</v>
       </c>
       <c r="H301" s="7">
-        <v>0.088224</v>
+        <v>0.098314</v>
       </c>
       <c r="I301" s="7">
-        <v>0.212377</v>
+        <v>0.22361899999999998</v>
       </c>
       <c r="J301" s="7">
-        <v>1.52726</v>
+        <v>1.550694</v>
       </c>
       <c r="K301" s="7"/>
     </row>
@@ -16533,22 +16533,22 @@
         <v>7</v>
       </c>
       <c r="E306" s="7">
-        <v>0</v>
+        <v>0.227624</v>
       </c>
       <c r="F306" s="7">
-        <v>0</v>
+        <v>-0.056741</v>
       </c>
       <c r="G306" s="7">
-        <v>0</v>
+        <v>-0.161223</v>
       </c>
       <c r="H306" s="7">
-        <v>0</v>
+        <v>0.018989</v>
       </c>
       <c r="I306" s="7">
-        <v>0</v>
+        <v>1.008979</v>
       </c>
       <c r="J306" s="7">
-        <v>0</v>
+        <v>3.535251</v>
       </c>
       <c r="K306" s="7"/>
     </row>
@@ -16566,22 +16566,22 @@
         <v>5</v>
       </c>
       <c r="E307" s="7">
-        <v>0.016169</v>
+        <v>0.016209</v>
       </c>
       <c r="F307" s="7">
-        <v>0.064524</v>
+        <v>0.064567</v>
       </c>
       <c r="G307" s="7">
-        <v>0.150611</v>
+        <v>0.15065699999999999</v>
       </c>
       <c r="H307" s="7">
-        <v>0.20658200000000002</v>
+        <v>0.20663</v>
       </c>
       <c r="I307" s="7">
-        <v>0.19888899999999998</v>
+        <v>0.198937</v>
       </c>
       <c r="J307" s="7">
-        <v>0.401952</v>
+        <v>0.40200899999999995</v>
       </c>
       <c r="K307" s="7"/>
     </row>
@@ -16754,22 +16754,22 @@
         <v>3</v>
       </c>
       <c r="E313" s="7">
-        <v>0.044516</v>
+        <v>0.045824</v>
       </c>
       <c r="F313" s="7">
-        <v>0.11224600000000001</v>
+        <v>0.11363899999999999</v>
       </c>
       <c r="G313" s="7">
-        <v>0.17858000000000002</v>
+        <v>0.18005600000000002</v>
       </c>
       <c r="H313" s="7">
-        <v>0.310688</v>
+        <v>0.31233</v>
       </c>
       <c r="I313" s="7">
-        <v>0.5309579999999999</v>
+        <v>0.532876</v>
       </c>
       <c r="J313" s="7">
-        <v>2.7895549999999996</v>
+        <v>2.794301</v>
       </c>
       <c r="K313" s="7"/>
     </row>
@@ -16787,22 +16787,22 @@
         <v>3</v>
       </c>
       <c r="E314" s="7">
-        <v>0.022414999999999997</v>
+        <v>0.024939</v>
       </c>
       <c r="F314" s="7">
-        <v>0.057767</v>
+        <v>0.060377</v>
       </c>
       <c r="G314" s="7">
-        <v>0.135022</v>
+        <v>0.137824</v>
       </c>
       <c r="H314" s="7">
-        <v>0.253496</v>
+        <v>0.256589</v>
       </c>
       <c r="I314" s="7">
-        <v>0.46231099999999997</v>
+        <v>0.46592</v>
       </c>
       <c r="J314" s="7">
-        <v>2.283925</v>
+        <v>2.292029</v>
       </c>
       <c r="K314" s="7"/>
     </row>
@@ -16820,22 +16820,22 @@
         <v>5</v>
       </c>
       <c r="E315" s="7">
-        <v>0.044182</v>
+        <v>0.043993000000000004</v>
       </c>
       <c r="F315" s="7">
-        <v>0.054147999999999995</v>
+        <v>0.053957</v>
       </c>
       <c r="G315" s="7">
-        <v>0.048788</v>
+        <v>0.048598</v>
       </c>
       <c r="H315" s="7">
-        <v>0.24013600000000002</v>
+        <v>0.23991099999999999</v>
       </c>
       <c r="I315" s="7">
-        <v>0.40474699999999997</v>
+        <v>0.40449199999999996</v>
       </c>
       <c r="J315" s="7">
-        <v>1.9411269999999998</v>
+        <v>1.9405940000000002</v>
       </c>
       <c r="K315" s="7"/>
     </row>
@@ -16853,22 +16853,22 @@
         <v>5</v>
       </c>
       <c r="E316" s="7">
-        <v>0.04619500000000001</v>
+        <v>0.046366</v>
       </c>
       <c r="F316" s="7">
-        <v>0.062016</v>
+        <v>0.062188999999999994</v>
       </c>
       <c r="G316" s="7">
-        <v>0.036285</v>
+        <v>0.036455</v>
       </c>
       <c r="H316" s="7">
-        <v>0.224691</v>
+        <v>0.224892</v>
       </c>
       <c r="I316" s="7">
-        <v>0.404008</v>
+        <v>0.404238</v>
       </c>
       <c r="J316" s="7">
-        <v>1.9359110000000002</v>
+        <v>1.936392</v>
       </c>
       <c r="K316" s="7"/>
     </row>
@@ -17016,10 +17016,10 @@
         <v>1</v>
       </c>
       <c r="E321" s="7">
-        <v>0</v>
+        <v>0.034780000000000005</v>
       </c>
       <c r="F321" s="7">
-        <v>0</v>
+        <v>0.10606600000000001</v>
       </c>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
@@ -17076,25 +17076,25 @@
         <v>2</v>
       </c>
       <c r="E323" s="7">
-        <v>0</v>
+        <v>0.036002</v>
       </c>
       <c r="F323" s="7">
-        <v>0</v>
+        <v>0.098468</v>
       </c>
       <c r="G323" s="7">
-        <v>0</v>
+        <v>0.14801</v>
       </c>
       <c r="H323" s="7">
-        <v>0</v>
+        <v>0.23506799999999997</v>
       </c>
       <c r="I323" s="7">
-        <v>0</v>
+        <v>0.394561</v>
       </c>
       <c r="J323" s="7">
-        <v>0</v>
+        <v>2.091406</v>
       </c>
       <c r="K323" s="7">
-        <v>0</v>
+        <v>3.881767</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
@@ -17109,25 +17109,25 @@
       </c>
       <c r="D324" s="6"/>
       <c r="E324" s="7">
-        <v>0</v>
+        <v>0.027368</v>
       </c>
       <c r="F324" s="7">
-        <v>0</v>
+        <v>0.074435</v>
       </c>
       <c r="G324" s="7">
-        <v>0</v>
+        <v>0.099555</v>
       </c>
       <c r="H324" s="7">
-        <v>0</v>
+        <v>0.13286699999999999</v>
       </c>
       <c r="I324" s="7">
-        <v>0</v>
+        <v>0.233368</v>
       </c>
       <c r="J324" s="7">
-        <v>0</v>
+        <v>1.299607</v>
       </c>
       <c r="K324" s="7">
-        <v>0</v>
+        <v>6.168712</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
@@ -17214,25 +17214,25 @@
         <v>3</v>
       </c>
       <c r="E327" s="7">
-        <v>0</v>
+        <v>0.035282</v>
       </c>
       <c r="F327" s="7">
-        <v>0</v>
+        <v>0.093484</v>
       </c>
       <c r="G327" s="7">
-        <v>0</v>
+        <v>0.128773</v>
       </c>
       <c r="H327" s="7">
-        <v>0</v>
+        <v>0.239952</v>
       </c>
       <c r="I327" s="7">
-        <v>0</v>
+        <v>0.401633</v>
       </c>
       <c r="J327" s="7">
-        <v>0</v>
+        <v>2.2099320000000002</v>
       </c>
       <c r="K327" s="7">
-        <v>0</v>
+        <v>6.350701</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -17340,25 +17340,25 @@
         <v>4</v>
       </c>
       <c r="E331" s="7">
-        <v>0</v>
+        <v>0.037937</v>
       </c>
       <c r="F331" s="7">
-        <v>0</v>
+        <v>0.088314</v>
       </c>
       <c r="G331" s="7">
-        <v>0</v>
+        <v>0.09318</v>
       </c>
       <c r="H331" s="7">
-        <v>0</v>
+        <v>0.251907</v>
       </c>
       <c r="I331" s="7">
-        <v>0</v>
+        <v>0.400749</v>
       </c>
       <c r="J331" s="7">
-        <v>0</v>
+        <v>2.209413</v>
       </c>
       <c r="K331" s="7">
-        <v>0</v>
+        <v>7.176081</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
@@ -17410,19 +17410,19 @@
         <v>5</v>
       </c>
       <c r="E333" s="7">
-        <v>0.076126</v>
+        <v>0.085461</v>
       </c>
       <c r="F333" s="7">
-        <v>0.071658</v>
+        <v>0.080955</v>
       </c>
       <c r="G333" s="7">
-        <v>0.08783200000000001</v>
+        <v>0.09726900000000001</v>
       </c>
       <c r="H333" s="7">
-        <v>0.227422</v>
+        <v>0.23806999999999998</v>
       </c>
       <c r="I333" s="7">
-        <v>0.382096</v>
+        <v>0.39408499999999996</v>
       </c>
       <c r="J333" s="7"/>
       <c r="K333" s="7"/>
@@ -17672,25 +17672,25 @@
         <v>6</v>
       </c>
       <c r="E341" s="7">
-        <v>0</v>
+        <v>0.052558</v>
       </c>
       <c r="F341" s="7">
-        <v>0</v>
+        <v>0.11931599999999999</v>
       </c>
       <c r="G341" s="7">
-        <v>0</v>
+        <v>0.08720900000000001</v>
       </c>
       <c r="H341" s="7">
-        <v>0</v>
+        <v>0.22849799999999998</v>
       </c>
       <c r="I341" s="7">
-        <v>0</v>
+        <v>0.379872</v>
       </c>
       <c r="J341" s="7">
-        <v>0</v>
+        <v>1.7136740000000001</v>
       </c>
       <c r="K341" s="7">
-        <v>0</v>
+        <v>4.917176</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
@@ -17707,25 +17707,25 @@
         <v>7</v>
       </c>
       <c r="E342" s="7">
-        <v>0</v>
+        <v>0.210011</v>
       </c>
       <c r="F342" s="7">
-        <v>0</v>
+        <v>-0.047626</v>
       </c>
       <c r="G342" s="7">
-        <v>0</v>
+        <v>-0.148689</v>
       </c>
       <c r="H342" s="7">
-        <v>0</v>
+        <v>0.027482000000000003</v>
       </c>
       <c r="I342" s="7">
-        <v>0</v>
+        <v>0.952119</v>
       </c>
       <c r="J342" s="7">
-        <v>0</v>
+        <v>3.581696</v>
       </c>
       <c r="K342" s="7">
-        <v>0</v>
+        <v>11.673532</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
@@ -17773,10 +17773,10 @@
         <v>7</v>
       </c>
       <c r="E344" s="7">
-        <v>0.19525099999999998</v>
+        <v>0.199218</v>
       </c>
       <c r="F344" s="7">
-        <v>-0.040208</v>
+        <v>-0.037023</v>
       </c>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
@@ -17798,25 +17798,25 @@
         <v>6</v>
       </c>
       <c r="E345" s="7">
-        <v>0</v>
+        <v>0.015146</v>
       </c>
       <c r="F345" s="7">
-        <v>0</v>
+        <v>0.063032</v>
       </c>
       <c r="G345" s="7">
-        <v>0</v>
+        <v>0.422371</v>
       </c>
       <c r="H345" s="7">
-        <v>0</v>
+        <v>0.433253</v>
       </c>
       <c r="I345" s="7">
-        <v>0</v>
+        <v>0.80265</v>
       </c>
       <c r="J345" s="7">
-        <v>0</v>
+        <v>2.5840410000000005</v>
       </c>
       <c r="K345" s="7">
-        <v>0</v>
+        <v>8.304746999999999</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -17833,16 +17833,16 @@
         <v>7</v>
       </c>
       <c r="E346" s="7">
-        <v>0</v>
+        <v>0.204859</v>
       </c>
       <c r="F346" s="7">
-        <v>0</v>
+        <v>-0.055869999999999996</v>
       </c>
       <c r="G346" s="7">
-        <v>0</v>
+        <v>-0.156243</v>
       </c>
       <c r="H346" s="7">
-        <v>0</v>
+        <v>-0.00037600000000000003</v>
       </c>
       <c r="I346" s="7"/>
       <c r="J346" s="7"/>
@@ -17862,25 +17862,25 @@
         <v>7</v>
       </c>
       <c r="E347" s="7">
-        <v>0</v>
+        <v>0.214813</v>
       </c>
       <c r="F347" s="7">
-        <v>0</v>
+        <v>-0.046836</v>
       </c>
       <c r="G347" s="7">
-        <v>0</v>
+        <v>-0.141719</v>
       </c>
       <c r="H347" s="7">
-        <v>0</v>
+        <v>0.042663</v>
       </c>
       <c r="I347" s="7">
-        <v>0</v>
+        <v>0.997599</v>
       </c>
       <c r="J347" s="7">
-        <v>0</v>
+        <v>3.4798880000000003</v>
       </c>
       <c r="K347" s="7">
-        <v>0</v>
+        <v>12.225678</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
@@ -17928,22 +17928,22 @@
         <v>6</v>
       </c>
       <c r="E349" s="7">
-        <v>0</v>
+        <v>0.011677</v>
       </c>
       <c r="F349" s="7">
-        <v>0</v>
+        <v>-0.057877</v>
       </c>
       <c r="G349" s="7">
-        <v>0</v>
+        <v>0.080393</v>
       </c>
       <c r="H349" s="7">
-        <v>0</v>
+        <v>0.19406099999999998</v>
       </c>
       <c r="I349" s="7">
-        <v>0</v>
+        <v>0.380215</v>
       </c>
       <c r="J349" s="7">
-        <v>0</v>
+        <v>1.24733</v>
       </c>
       <c r="K349" s="7"/>
     </row>
@@ -17961,22 +17961,22 @@
         <v>5</v>
       </c>
       <c r="E350" s="7">
-        <v>0</v>
+        <v>0.033372</v>
       </c>
       <c r="F350" s="7">
-        <v>0</v>
+        <v>0.064816</v>
       </c>
       <c r="G350" s="7">
-        <v>0</v>
+        <v>0.014536</v>
       </c>
       <c r="H350" s="7">
-        <v>0</v>
+        <v>0.181674</v>
       </c>
       <c r="I350" s="7">
-        <v>0</v>
+        <v>0.29090699999999997</v>
       </c>
       <c r="J350" s="7">
-        <v>0</v>
+        <v>1.6793559999999998</v>
       </c>
       <c r="K350" s="7"/>
     </row>
@@ -18029,25 +18029,25 @@
         <v>6</v>
       </c>
       <c r="E352" s="7">
-        <v>0</v>
+        <v>0.059864</v>
       </c>
       <c r="F352" s="7">
-        <v>0</v>
+        <v>0.047724</v>
       </c>
       <c r="G352" s="7">
-        <v>0</v>
+        <v>0.17468</v>
       </c>
       <c r="H352" s="7">
-        <v>0</v>
+        <v>0.265604</v>
       </c>
       <c r="I352" s="7">
-        <v>0</v>
+        <v>0.5935320000000001</v>
       </c>
       <c r="J352" s="7">
-        <v>0</v>
+        <v>1.551059</v>
       </c>
       <c r="K352" s="7">
-        <v>0</v>
+        <v>6.976998999999999</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
@@ -18064,22 +18064,22 @@
         <v>6</v>
       </c>
       <c r="E353" s="7">
-        <v>0</v>
+        <v>0.08123200000000001</v>
       </c>
       <c r="F353" s="7">
-        <v>0</v>
+        <v>0.23029699999999997</v>
       </c>
       <c r="G353" s="7">
-        <v>0</v>
+        <v>0.315913</v>
       </c>
       <c r="H353" s="7">
-        <v>0</v>
+        <v>0.374365</v>
       </c>
       <c r="I353" s="7">
-        <v>0</v>
+        <v>0.575205</v>
       </c>
       <c r="J353" s="7">
-        <v>0</v>
+        <v>1.4053069999999999</v>
       </c>
       <c r="K353" s="7"/>
     </row>
@@ -18097,25 +18097,25 @@
         <v>5</v>
       </c>
       <c r="E354" s="7">
-        <v>0</v>
+        <v>0.000517</v>
       </c>
       <c r="F354" s="7">
-        <v>0</v>
+        <v>-0.053030999999999995</v>
       </c>
       <c r="G354" s="7">
-        <v>0</v>
+        <v>0.038112</v>
       </c>
       <c r="H354" s="7">
-        <v>0</v>
+        <v>0.25512799999999997</v>
       </c>
       <c r="I354" s="7">
-        <v>0</v>
+        <v>0.428036</v>
       </c>
       <c r="J354" s="7">
-        <v>0</v>
+        <v>0.882004</v>
       </c>
       <c r="K354" s="7">
-        <v>0</v>
+        <v>4.287020999999999</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -18132,25 +18132,25 @@
         <v>4</v>
       </c>
       <c r="E355" s="7">
-        <v>0</v>
+        <v>0.032147999999999996</v>
       </c>
       <c r="F355" s="7">
-        <v>0</v>
+        <v>0.07603</v>
       </c>
       <c r="G355" s="7">
-        <v>0</v>
+        <v>0.06312000000000001</v>
       </c>
       <c r="H355" s="7">
-        <v>0</v>
+        <v>0.20341599999999999</v>
       </c>
       <c r="I355" s="7">
-        <v>0</v>
+        <v>0.337087</v>
       </c>
       <c r="J355" s="7">
-        <v>0</v>
+        <v>1.992899</v>
       </c>
       <c r="K355" s="7">
-        <v>0</v>
+        <v>6.967876</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
@@ -18167,22 +18167,22 @@
         <v>5</v>
       </c>
       <c r="E356" s="7">
-        <v>0</v>
+        <v>0.010702</v>
       </c>
       <c r="F356" s="7">
-        <v>0</v>
+        <v>0.08677699999999999</v>
       </c>
       <c r="G356" s="7">
-        <v>0</v>
+        <v>0.131798</v>
       </c>
       <c r="H356" s="7">
-        <v>0</v>
+        <v>0.369625</v>
       </c>
       <c r="I356" s="7">
-        <v>0</v>
+        <v>0.419376</v>
       </c>
       <c r="J356" s="7">
-        <v>0</v>
+        <v>0.88684</v>
       </c>
       <c r="K356" s="7"/>
     </row>
@@ -18270,25 +18270,25 @@
         <v>3</v>
       </c>
       <c r="E359" s="7">
-        <v>0</v>
+        <v>0.033552</v>
       </c>
       <c r="F359" s="7">
-        <v>0</v>
+        <v>0.08646699999999999</v>
       </c>
       <c r="G359" s="7">
-        <v>0</v>
+        <v>0.128605</v>
       </c>
       <c r="H359" s="7">
-        <v>0</v>
+        <v>0.23034500000000002</v>
       </c>
       <c r="I359" s="7">
-        <v>0</v>
+        <v>0.38868600000000003</v>
       </c>
       <c r="J359" s="7">
-        <v>0</v>
+        <v>2.190867</v>
       </c>
       <c r="K359" s="7">
-        <v>0</v>
+        <v>6.067442</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
@@ -18340,25 +18340,25 @@
         <v>5</v>
       </c>
       <c r="E361" s="7">
-        <v>0</v>
+        <v>0.042974</v>
       </c>
       <c r="F361" s="7">
-        <v>0</v>
+        <v>0.063332</v>
       </c>
       <c r="G361" s="7">
-        <v>0</v>
+        <v>0.131214</v>
       </c>
       <c r="H361" s="7">
-        <v>0</v>
+        <v>0.24286100000000002</v>
       </c>
       <c r="I361" s="7">
-        <v>0</v>
+        <v>0.35973900000000003</v>
       </c>
       <c r="J361" s="7">
-        <v>0</v>
+        <v>1.463517</v>
       </c>
       <c r="K361" s="7">
-        <v>0</v>
+        <v>6.277313</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
@@ -18375,22 +18375,22 @@
         <v>6</v>
       </c>
       <c r="E362" s="7">
-        <v>0</v>
+        <v>0.038749</v>
       </c>
       <c r="F362" s="7">
-        <v>0</v>
+        <v>0.117141</v>
       </c>
       <c r="G362" s="7">
-        <v>0</v>
+        <v>0.06117</v>
       </c>
       <c r="H362" s="7">
-        <v>0</v>
+        <v>0.115814</v>
       </c>
       <c r="I362" s="7">
-        <v>0</v>
+        <v>0.146025</v>
       </c>
       <c r="J362" s="7">
-        <v>0</v>
+        <v>1.394203</v>
       </c>
       <c r="K362" s="7"/>
     </row>
@@ -18408,22 +18408,22 @@
         <v>5</v>
       </c>
       <c r="E363" s="7">
-        <v>0</v>
+        <v>0.054592999999999996</v>
       </c>
       <c r="F363" s="7">
-        <v>0</v>
+        <v>0.107266</v>
       </c>
       <c r="G363" s="7">
-        <v>0</v>
+        <v>0.047161</v>
       </c>
       <c r="H363" s="7">
-        <v>0</v>
+        <v>0.090678</v>
       </c>
       <c r="I363" s="7">
-        <v>0</v>
+        <v>0.183262</v>
       </c>
       <c r="J363" s="7">
-        <v>0</v>
+        <v>1.727774</v>
       </c>
       <c r="K363" s="7"/>
     </row>
@@ -18464,19 +18464,19 @@
         <v>6</v>
       </c>
       <c r="E365" s="7">
-        <v>0</v>
+        <v>0.12933999999999998</v>
       </c>
       <c r="F365" s="7">
-        <v>0</v>
+        <v>0.055805999999999994</v>
       </c>
       <c r="G365" s="7">
-        <v>0</v>
+        <v>-0.051449999999999996</v>
       </c>
       <c r="H365" s="7">
-        <v>0</v>
+        <v>0.153345</v>
       </c>
       <c r="I365" s="7">
-        <v>0</v>
+        <v>0.6553319999999999</v>
       </c>
       <c r="J365" s="7"/>
       <c r="K365" s="7"/>
@@ -18524,19 +18524,19 @@
         <v>2</v>
       </c>
       <c r="E367" s="7">
-        <v>0</v>
+        <v>0.004482</v>
       </c>
       <c r="F367" s="7">
-        <v>0</v>
+        <v>0.023629999999999998</v>
       </c>
       <c r="G367" s="7">
-        <v>0</v>
+        <v>0.084593</v>
       </c>
       <c r="H367" s="7">
-        <v>0</v>
+        <v>0.124238</v>
       </c>
       <c r="I367" s="7">
-        <v>0</v>
+        <v>0.254336</v>
       </c>
       <c r="J367" s="7"/>
       <c r="K367" s="7"/>
@@ -18586,22 +18586,22 @@
       </c>
       <c r="D369" s="6"/>
       <c r="E369" s="7">
-        <v>0</v>
+        <v>0.030848</v>
       </c>
       <c r="F369" s="7">
-        <v>0</v>
+        <v>0.062508</v>
       </c>
       <c r="G369" s="7">
-        <v>0</v>
+        <v>0.10021200000000001</v>
       </c>
       <c r="H369" s="7">
-        <v>0</v>
+        <v>0.22225799999999998</v>
       </c>
       <c r="I369" s="7">
-        <v>0</v>
+        <v>0.297502</v>
       </c>
       <c r="J369" s="7">
-        <v>0</v>
+        <v>1.572326</v>
       </c>
       <c r="K369" s="7"/>
     </row>
@@ -18652,10 +18652,10 @@
         <v>5</v>
       </c>
       <c r="E371" s="7">
-        <v>0</v>
+        <v>0.184056</v>
       </c>
       <c r="F371" s="7">
-        <v>0</v>
+        <v>-0.017203</v>
       </c>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
@@ -18677,19 +18677,19 @@
         <v>2</v>
       </c>
       <c r="E372" s="7">
-        <v>0</v>
+        <v>0.020062000000000003</v>
       </c>
       <c r="F372" s="7">
-        <v>0</v>
+        <v>0.068994</v>
       </c>
       <c r="G372" s="7">
-        <v>0</v>
+        <v>0.165134</v>
       </c>
       <c r="H372" s="7">
-        <v>0</v>
+        <v>0.213632</v>
       </c>
       <c r="I372" s="7">
-        <v>0</v>
+        <v>0.36861</v>
       </c>
       <c r="J372" s="7"/>
       <c r="K372" s="7"/>
@@ -18731,22 +18731,22 @@
         <v>2</v>
       </c>
       <c r="E374" s="7">
-        <v>0</v>
+        <v>0.018607</v>
       </c>
       <c r="F374" s="7">
-        <v>0</v>
+        <v>0.05246000000000001</v>
       </c>
       <c r="G374" s="7">
-        <v>0</v>
+        <v>0.113786</v>
       </c>
       <c r="H374" s="7">
-        <v>0</v>
+        <v>0.163018</v>
       </c>
       <c r="I374" s="7">
-        <v>0</v>
+        <v>0.273052</v>
       </c>
       <c r="J374" s="7">
-        <v>0</v>
+        <v>1.86768</v>
       </c>
       <c r="K374" s="7"/>
     </row>
@@ -18764,22 +18764,22 @@
         <v>3</v>
       </c>
       <c r="E375" s="7">
-        <v>0</v>
+        <v>0.021123</v>
       </c>
       <c r="F375" s="7">
-        <v>0</v>
+        <v>0.08362</v>
       </c>
       <c r="G375" s="7">
-        <v>0</v>
+        <v>0.190734</v>
       </c>
       <c r="H375" s="7">
-        <v>0</v>
+        <v>0.239293</v>
       </c>
       <c r="I375" s="7">
-        <v>0</v>
+        <v>0.397299</v>
       </c>
       <c r="J375" s="7">
-        <v>0</v>
+        <v>2.704523</v>
       </c>
       <c r="K375" s="7"/>
     </row>
@@ -18797,19 +18797,19 @@
         <v>6</v>
       </c>
       <c r="E376" s="7">
-        <v>0</v>
+        <v>0.04077600000000001</v>
       </c>
       <c r="F376" s="7">
-        <v>0</v>
+        <v>0.093946</v>
       </c>
       <c r="G376" s="7">
-        <v>0</v>
+        <v>0.253693</v>
       </c>
       <c r="H376" s="7">
-        <v>0</v>
+        <v>0.451662</v>
       </c>
       <c r="I376" s="7">
-        <v>0</v>
+        <v>0.325178</v>
       </c>
       <c r="J376" s="7"/>
       <c r="K376" s="7"/>
@@ -18880,22 +18880,22 @@
         <v>6</v>
       </c>
       <c r="E379" s="7">
-        <v>0</v>
+        <v>0.044179</v>
       </c>
       <c r="F379" s="7">
-        <v>0</v>
+        <v>0.061455</v>
       </c>
       <c r="G379" s="7">
-        <v>0</v>
+        <v>0.153882</v>
       </c>
       <c r="H379" s="7">
-        <v>0</v>
+        <v>0.499902</v>
       </c>
       <c r="I379" s="7">
-        <v>0</v>
+        <v>0.43460099999999996</v>
       </c>
       <c r="J379" s="7">
-        <v>0</v>
+        <v>1.773614</v>
       </c>
       <c r="K379" s="7"/>
     </row>
@@ -18913,16 +18913,16 @@
         <v>5</v>
       </c>
       <c r="E380" s="7">
-        <v>0</v>
+        <v>0.038355</v>
       </c>
       <c r="F380" s="7">
-        <v>0</v>
+        <v>0.066575</v>
       </c>
       <c r="G380" s="7">
-        <v>0</v>
+        <v>0.16423300000000002</v>
       </c>
       <c r="H380" s="7">
-        <v>0</v>
+        <v>0.30811900000000003</v>
       </c>
       <c r="I380" s="7"/>
       <c r="J380" s="7"/>
@@ -18942,22 +18942,22 @@
         <v>7</v>
       </c>
       <c r="E381" s="7">
-        <v>0</v>
+        <v>-0.01595</v>
       </c>
       <c r="F381" s="7">
-        <v>0</v>
+        <v>-0.017089</v>
       </c>
       <c r="G381" s="7">
-        <v>0</v>
+        <v>-0.042739</v>
       </c>
       <c r="H381" s="7">
-        <v>0</v>
+        <v>0.092674</v>
       </c>
       <c r="I381" s="7">
-        <v>0</v>
+        <v>-0.08302199999999998</v>
       </c>
       <c r="J381" s="7">
-        <v>0</v>
+        <v>1.476191</v>
       </c>
       <c r="K381" s="7"/>
     </row>
@@ -18975,19 +18975,19 @@
         <v>3</v>
       </c>
       <c r="E382" s="7">
-        <v>0</v>
+        <v>0.026823</v>
       </c>
       <c r="F382" s="7">
-        <v>0</v>
+        <v>0.089955</v>
       </c>
       <c r="G382" s="7">
-        <v>0</v>
+        <v>0.196233</v>
       </c>
       <c r="H382" s="7">
-        <v>0</v>
+        <v>0.26289999999999997</v>
       </c>
       <c r="I382" s="7">
-        <v>0</v>
+        <v>0.46891</v>
       </c>
       <c r="J382" s="7"/>
       <c r="K382" s="7"/>
@@ -19006,16 +19006,16 @@
         <v>6</v>
       </c>
       <c r="E383" s="7">
-        <v>0</v>
+        <v>0.028037</v>
       </c>
       <c r="F383" s="7">
-        <v>0</v>
+        <v>-0.064556</v>
       </c>
       <c r="G383" s="7">
-        <v>0</v>
+        <v>-0.35155200000000003</v>
       </c>
       <c r="H383" s="7">
-        <v>0</v>
+        <v>-0.338695</v>
       </c>
       <c r="I383" s="7"/>
       <c r="J383" s="7"/>
@@ -19066,22 +19066,22 @@
         <v>2</v>
       </c>
       <c r="E385" s="7">
-        <v>0</v>
+        <v>0.023291</v>
       </c>
       <c r="F385" s="7">
-        <v>0</v>
+        <v>0.07768</v>
       </c>
       <c r="G385" s="7">
-        <v>0</v>
+        <v>0.180689</v>
       </c>
       <c r="H385" s="7">
-        <v>0</v>
+        <v>0.230898</v>
       </c>
       <c r="I385" s="7">
-        <v>0</v>
+        <v>0.386537</v>
       </c>
       <c r="J385" s="7">
-        <v>0</v>
+        <v>2.593723</v>
       </c>
       <c r="K385" s="7"/>
     </row>
@@ -19130,22 +19130,22 @@
         <v>6</v>
       </c>
       <c r="E387" s="7">
-        <v>0</v>
+        <v>0.046109</v>
       </c>
       <c r="F387" s="7">
-        <v>0</v>
+        <v>0.121599</v>
       </c>
       <c r="G387" s="7">
-        <v>0</v>
+        <v>0.08706699999999999</v>
       </c>
       <c r="H387" s="7">
-        <v>0</v>
+        <v>0.33771799999999996</v>
       </c>
       <c r="I387" s="7">
-        <v>0</v>
+        <v>0.439506</v>
       </c>
       <c r="J387" s="7">
-        <v>0</v>
+        <v>1.97835</v>
       </c>
       <c r="K387" s="7"/>
     </row>
@@ -19194,22 +19194,22 @@
         <v>6</v>
       </c>
       <c r="E389" s="7">
-        <v>0</v>
+        <v>0.016375</v>
       </c>
       <c r="F389" s="7">
-        <v>0</v>
+        <v>0.023132</v>
       </c>
       <c r="G389" s="7">
-        <v>0</v>
+        <v>-0.0021479999999999997</v>
       </c>
       <c r="H389" s="7">
-        <v>0</v>
+        <v>0.110404</v>
       </c>
       <c r="I389" s="7">
-        <v>0</v>
+        <v>0.09228</v>
       </c>
       <c r="J389" s="7">
-        <v>0</v>
+        <v>0.9936889999999999</v>
       </c>
       <c r="K389" s="7"/>
     </row>
@@ -19227,16 +19227,16 @@
         <v>1</v>
       </c>
       <c r="E390" s="7">
-        <v>0</v>
+        <v>0.038601</v>
       </c>
       <c r="F390" s="7">
-        <v>0</v>
+        <v>0.114549</v>
       </c>
       <c r="G390" s="7">
-        <v>0</v>
+        <v>0.239326</v>
       </c>
       <c r="H390" s="7">
-        <v>0</v>
+        <v>0.32179699999999994</v>
       </c>
       <c r="I390" s="7"/>
       <c r="J390" s="7"/>
@@ -19256,22 +19256,22 @@
         <v>7</v>
       </c>
       <c r="E391" s="7">
-        <v>0</v>
+        <v>-0.027320999999999998</v>
       </c>
       <c r="F391" s="7">
-        <v>0</v>
+        <v>-0.094298</v>
       </c>
       <c r="G391" s="7">
-        <v>0</v>
+        <v>0.09818199999999999</v>
       </c>
       <c r="H391" s="7">
-        <v>0</v>
+        <v>-0.027504</v>
       </c>
       <c r="I391" s="7">
-        <v>0</v>
+        <v>-0.040159</v>
       </c>
       <c r="J391" s="7">
-        <v>0</v>
+        <v>0.7229819999999999</v>
       </c>
       <c r="K391" s="7"/>
     </row>
@@ -19320,22 +19320,22 @@
         <v>5</v>
       </c>
       <c r="E393" s="7">
-        <v>0</v>
+        <v>0.040053</v>
       </c>
       <c r="F393" s="7">
-        <v>0</v>
+        <v>0.132986</v>
       </c>
       <c r="G393" s="7">
-        <v>0</v>
+        <v>0.06933099999999999</v>
       </c>
       <c r="H393" s="7">
-        <v>0</v>
+        <v>0.10676999999999999</v>
       </c>
       <c r="I393" s="7">
-        <v>0</v>
+        <v>0.15281599999999998</v>
       </c>
       <c r="J393" s="7">
-        <v>0</v>
+        <v>0.927061</v>
       </c>
       <c r="K393" s="7"/>
     </row>
@@ -19384,19 +19384,19 @@
       </c>
       <c r="D395" s="6"/>
       <c r="E395" s="7">
-        <v>0</v>
+        <v>0.008767</v>
       </c>
       <c r="F395" s="7">
-        <v>0</v>
+        <v>0.027034</v>
       </c>
       <c r="G395" s="7">
-        <v>0</v>
+        <v>0.054144</v>
       </c>
       <c r="H395" s="7">
-        <v>0</v>
+        <v>0.078509</v>
       </c>
       <c r="I395" s="7">
-        <v>0</v>
+        <v>0.143709</v>
       </c>
       <c r="J395" s="7"/>
       <c r="K395" s="7"/>
@@ -19444,25 +19444,25 @@
       </c>
       <c r="D397" s="6"/>
       <c r="E397" s="7">
-        <v>0.04429</v>
+        <v>0.04471</v>
       </c>
       <c r="F397" s="7">
-        <v>0.035151</v>
+        <v>0.035568</v>
       </c>
       <c r="G397" s="7">
-        <v>0.23556999999999997</v>
+        <v>0.236068</v>
       </c>
       <c r="H397" s="7">
-        <v>0.288004</v>
+        <v>0.288522</v>
       </c>
       <c r="I397" s="7">
-        <v>0.46732100000000004</v>
+        <v>0.46791200000000005</v>
       </c>
       <c r="J397" s="7">
-        <v>2.6408319999999996</v>
+        <v>2.6422969999999997</v>
       </c>
       <c r="K397" s="7">
-        <v>8.023042</v>
+        <v>8.026672999999999</v>
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
@@ -19477,25 +19477,25 @@
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="7">
-        <v>0.035157</v>
+        <v>0.035434</v>
       </c>
       <c r="F398" s="7">
-        <v>0.064153</v>
+        <v>0.06443800000000001</v>
       </c>
       <c r="G398" s="7">
-        <v>0.146057</v>
+        <v>0.146364</v>
       </c>
       <c r="H398" s="7">
-        <v>0.22760000000000002</v>
+        <v>0.227928</v>
       </c>
       <c r="I398" s="7">
-        <v>0.352604</v>
+        <v>0.352966</v>
       </c>
       <c r="J398" s="7">
-        <v>1.518202</v>
+        <v>1.518876</v>
       </c>
       <c r="K398" s="7">
-        <v>6.453211</v>
+        <v>6.4552059999999996</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
@@ -19510,22 +19510,22 @@
       </c>
       <c r="D399" s="6"/>
       <c r="E399" s="7">
-        <v>0</v>
+        <v>0.020323</v>
       </c>
       <c r="F399" s="7">
-        <v>0</v>
+        <v>0.06563</v>
       </c>
       <c r="G399" s="7">
-        <v>0</v>
+        <v>0.12343799999999999</v>
       </c>
       <c r="H399" s="7">
-        <v>0</v>
+        <v>0.14566800000000002</v>
       </c>
       <c r="I399" s="7">
-        <v>0</v>
+        <v>0.199283</v>
       </c>
       <c r="J399" s="7">
-        <v>0</v>
+        <v>1.12014</v>
       </c>
       <c r="K399" s="7"/>
     </row>
@@ -19576,19 +19576,19 @@
         <v>1</v>
       </c>
       <c r="E401" s="7">
-        <v>0</v>
+        <v>0.027306</v>
       </c>
       <c r="F401" s="7">
-        <v>0</v>
+        <v>0.095713</v>
       </c>
       <c r="G401" s="7">
-        <v>0</v>
+        <v>0.20492100000000002</v>
       </c>
       <c r="H401" s="7">
-        <v>0</v>
+        <v>0.269576</v>
       </c>
       <c r="I401" s="7">
-        <v>0</v>
+        <v>0.455403</v>
       </c>
       <c r="J401" s="7"/>
       <c r="K401" s="7"/>
@@ -19702,25 +19702,25 @@
       </c>
       <c r="D405" s="6"/>
       <c r="E405" s="7">
-        <v>0.026524000000000002</v>
+        <v>0.026526</v>
       </c>
       <c r="F405" s="7">
-        <v>0.047331000000000005</v>
+        <v>0.047333</v>
       </c>
       <c r="G405" s="7">
-        <v>0.089425</v>
+        <v>0.089427</v>
       </c>
       <c r="H405" s="7">
-        <v>0.233171</v>
+        <v>0.233173</v>
       </c>
       <c r="I405" s="7">
-        <v>0.229004</v>
+        <v>0.22900500000000001</v>
       </c>
       <c r="J405" s="7">
-        <v>1.298698</v>
+        <v>1.298702</v>
       </c>
       <c r="K405" s="7">
-        <v>9.504883</v>
+        <v>9.5049</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
@@ -19830,19 +19830,19 @@
         <v>4</v>
       </c>
       <c r="E409" s="7">
-        <v>0</v>
+        <v>0.079193</v>
       </c>
       <c r="F409" s="7">
-        <v>0</v>
+        <v>0.068594</v>
       </c>
       <c r="G409" s="7">
-        <v>0</v>
+        <v>0.301102</v>
       </c>
       <c r="H409" s="7">
-        <v>0</v>
+        <v>0.302562</v>
       </c>
       <c r="I409" s="7">
-        <v>0</v>
+        <v>0.435648</v>
       </c>
       <c r="J409" s="7"/>
       <c r="K409" s="7"/>
@@ -19861,7 +19861,7 @@
         <v>6</v>
       </c>
       <c r="E410" s="7">
-        <v>0.035579</v>
+        <v>0.034401</v>
       </c>
       <c r="F410" s="7"/>
       <c r="G410" s="7"/>
@@ -19882,19 +19882,19 @@
       </c>
       <c r="D411" s="6"/>
       <c r="E411" s="7">
-        <v>0</v>
+        <v>0.046426999999999996</v>
       </c>
       <c r="F411" s="7">
-        <v>0</v>
+        <v>0.061528</v>
       </c>
       <c r="G411" s="7">
-        <v>0</v>
+        <v>0.24311</v>
       </c>
       <c r="H411" s="7">
-        <v>0</v>
+        <v>0.24936499999999998</v>
       </c>
       <c r="I411" s="7">
-        <v>0</v>
+        <v>0.381999</v>
       </c>
       <c r="J411" s="7"/>
       <c r="K411" s="7"/>
@@ -19942,22 +19942,22 @@
         <v>2</v>
       </c>
       <c r="E413" s="7">
-        <v>0</v>
+        <v>-0.047176</v>
       </c>
       <c r="F413" s="7">
-        <v>0</v>
+        <v>0.020798999999999998</v>
       </c>
       <c r="G413" s="7">
-        <v>0</v>
+        <v>0.12443199999999999</v>
       </c>
       <c r="H413" s="7">
-        <v>0</v>
+        <v>0.189987</v>
       </c>
       <c r="I413" s="7">
-        <v>0</v>
+        <v>0.375924</v>
       </c>
       <c r="J413" s="7">
-        <v>0</v>
+        <v>2.438275</v>
       </c>
       <c r="K413" s="7"/>
     </row>
@@ -20171,25 +20171,25 @@
         <v>1</v>
       </c>
       <c r="E420" s="7">
-        <v>0</v>
+        <v>0.03401</v>
       </c>
       <c r="F420" s="7">
-        <v>0</v>
+        <v>0.10220000000000001</v>
       </c>
       <c r="G420" s="7">
-        <v>0</v>
+        <v>0.208735</v>
       </c>
       <c r="H420" s="7">
-        <v>0</v>
+        <v>0.275229</v>
       </c>
       <c r="I420" s="7">
-        <v>0</v>
+        <v>0.476074</v>
       </c>
       <c r="J420" s="7">
-        <v>0</v>
+        <v>2.6566289999999997</v>
       </c>
       <c r="K420" s="7">
-        <v>0</v>
+        <v>4.761646</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.25">
@@ -20237,19 +20237,19 @@
         <v>5</v>
       </c>
       <c r="E422" s="7">
-        <v>0.046460999999999995</v>
+        <v>0.048226000000000005</v>
       </c>
       <c r="F422" s="7">
-        <v>0.040143000000000005</v>
+        <v>0.041897000000000004</v>
       </c>
       <c r="G422" s="7">
-        <v>0.051722000000000004</v>
+        <v>0.053495999999999995</v>
       </c>
       <c r="H422" s="7">
-        <v>0.184853</v>
+        <v>0.186852</v>
       </c>
       <c r="I422" s="7">
-        <v>0.337764</v>
+        <v>0.34002000000000004</v>
       </c>
       <c r="J422" s="7"/>
       <c r="K422" s="7"/>
@@ -20944,25 +20944,25 @@
         <v>4</v>
       </c>
       <c r="E443" s="7">
-        <v>0</v>
+        <v>0.031265999999999995</v>
       </c>
       <c r="F443" s="7">
-        <v>0</v>
+        <v>0.08132500000000001</v>
       </c>
       <c r="G443" s="7">
-        <v>0</v>
+        <v>0.161343</v>
       </c>
       <c r="H443" s="7">
-        <v>0</v>
+        <v>0.302682</v>
       </c>
       <c r="I443" s="7">
-        <v>0</v>
+        <v>0.506699</v>
       </c>
       <c r="J443" s="7">
-        <v>0</v>
+        <v>2.4046719999999997</v>
       </c>
       <c r="K443" s="7">
-        <v>0</v>
+        <v>6.082652</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.25">
@@ -21613,25 +21613,25 @@
         <v>3</v>
       </c>
       <c r="E464" s="7">
-        <v>0</v>
+        <v>0.033887</v>
       </c>
       <c r="F464" s="7">
-        <v>0</v>
+        <v>0.0766</v>
       </c>
       <c r="G464" s="7">
-        <v>0</v>
+        <v>0.125402</v>
       </c>
       <c r="H464" s="7">
-        <v>0</v>
+        <v>0.210592</v>
       </c>
       <c r="I464" s="7">
-        <v>0</v>
+        <v>0.33854100000000004</v>
       </c>
       <c r="J464" s="7">
-        <v>0</v>
+        <v>2.040177</v>
       </c>
       <c r="K464" s="7">
-        <v>0</v>
+        <v>6.0557680000000005</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
@@ -21953,25 +21953,25 @@
         <v>2</v>
       </c>
       <c r="E474" s="7">
-        <v>0.025891</v>
+        <v>0.029045</v>
       </c>
       <c r="F474" s="7">
-        <v>0.080662</v>
+        <v>0.083984</v>
       </c>
       <c r="G474" s="7">
-        <v>0.09640399999999999</v>
+        <v>0.09977399999999999</v>
       </c>
       <c r="H474" s="7">
-        <v>0.136741</v>
+        <v>0.140235</v>
       </c>
       <c r="I474" s="7">
-        <v>0.37175199999999997</v>
+        <v>0.375968</v>
       </c>
       <c r="J474" s="7">
-        <v>2.158528</v>
+        <v>2.168237</v>
       </c>
       <c r="K474" s="7">
-        <v>6.634684999999999</v>
+        <v>6.6581529999999995</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.25">
@@ -22188,25 +22188,25 @@
         <v>5</v>
       </c>
       <c r="E481" s="7">
-        <v>0.023712</v>
+        <v>0.027466</v>
       </c>
       <c r="F481" s="7">
-        <v>0.067766</v>
+        <v>0.071682</v>
       </c>
       <c r="G481" s="7">
-        <v>0.054021</v>
+        <v>0.057887</v>
       </c>
       <c r="H481" s="7">
-        <v>0.138787</v>
+        <v>0.142964</v>
       </c>
       <c r="I481" s="7">
-        <v>0.304428</v>
+        <v>0.309212</v>
       </c>
       <c r="J481" s="7">
-        <v>1.5660239999999999</v>
+        <v>1.575435</v>
       </c>
       <c r="K481" s="7">
-        <v>4.877573</v>
+        <v>4.899131</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.25">
@@ -22320,22 +22320,22 @@
         <v>3</v>
       </c>
       <c r="E485" s="7">
-        <v>0</v>
+        <v>0.033152</v>
       </c>
       <c r="F485" s="7">
-        <v>0</v>
+        <v>0.145932</v>
       </c>
       <c r="G485" s="7">
-        <v>0</v>
+        <v>0.251153</v>
       </c>
       <c r="H485" s="7">
-        <v>0</v>
+        <v>0.355908</v>
       </c>
       <c r="I485" s="7">
-        <v>0</v>
+        <v>0.6009920000000001</v>
       </c>
       <c r="J485" s="7">
-        <v>0</v>
+        <v>2.408339</v>
       </c>
       <c r="K485" s="7"/>
     </row>
@@ -22611,22 +22611,22 @@
         <v>5</v>
       </c>
       <c r="E494" s="7">
-        <v>0.037339000000000004</v>
+        <v>0.039946</v>
       </c>
       <c r="F494" s="7">
-        <v>0.079011</v>
+        <v>0.081722</v>
       </c>
       <c r="G494" s="7">
-        <v>0.348358</v>
+        <v>0.35174500000000003</v>
       </c>
       <c r="H494" s="7">
-        <v>0.422165</v>
+        <v>0.425738</v>
       </c>
       <c r="I494" s="7">
-        <v>0.5927089999999999</v>
+        <v>0.59671</v>
       </c>
       <c r="J494" s="7">
-        <v>2.280062</v>
+        <v>2.288303</v>
       </c>
       <c r="K494" s="7"/>
     </row>
@@ -22642,22 +22642,22 @@
       </c>
       <c r="D495" s="6"/>
       <c r="E495" s="7">
-        <v>0</v>
+        <v>0.024982999999999998</v>
       </c>
       <c r="F495" s="7">
-        <v>0</v>
+        <v>0.081701</v>
       </c>
       <c r="G495" s="7">
-        <v>0</v>
+        <v>0.09919</v>
       </c>
       <c r="H495" s="7">
-        <v>0</v>
+        <v>0.14594200000000002</v>
       </c>
       <c r="I495" s="7">
-        <v>0</v>
+        <v>0.251604</v>
       </c>
       <c r="J495" s="7">
-        <v>0</v>
+        <v>1.337205</v>
       </c>
       <c r="K495" s="7"/>
     </row>
@@ -22772,25 +22772,25 @@
         <v>4</v>
       </c>
       <c r="E499" s="7">
-        <v>0.026806999999999997</v>
+        <v>0.02681</v>
       </c>
       <c r="F499" s="7">
-        <v>0.037087</v>
+        <v>0.037091</v>
       </c>
       <c r="G499" s="7">
-        <v>0.10751300000000001</v>
+        <v>0.107517</v>
       </c>
       <c r="H499" s="7">
-        <v>0.252503</v>
+        <v>0.252508</v>
       </c>
       <c r="I499" s="7">
-        <v>0.41551000000000005</v>
+        <v>0.41551499999999997</v>
       </c>
       <c r="J499" s="7">
-        <v>1.948898</v>
+        <v>1.9489089999999998</v>
       </c>
       <c r="K499" s="7">
-        <v>6.181674</v>
+        <v>6.181699</v>
       </c>
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.25">
@@ -22964,22 +22964,22 @@
       </c>
       <c r="D505" s="6"/>
       <c r="E505" s="7">
-        <v>0</v>
+        <v>0.041926</v>
       </c>
       <c r="F505" s="7">
-        <v>0</v>
+        <v>0.062296</v>
       </c>
       <c r="G505" s="7">
-        <v>0</v>
+        <v>0.089637</v>
       </c>
       <c r="H505" s="7">
-        <v>0</v>
+        <v>0.12106299999999999</v>
       </c>
       <c r="I505" s="7">
-        <v>0</v>
+        <v>0.19428</v>
       </c>
       <c r="J505" s="7">
-        <v>0</v>
+        <v>0.96719</v>
       </c>
       <c r="K505" s="7"/>
     </row>
@@ -22997,19 +22997,19 @@
         <v>6</v>
       </c>
       <c r="E506" s="7">
-        <v>0</v>
+        <v>0.037686000000000004</v>
       </c>
       <c r="F506" s="7">
-        <v>0</v>
+        <v>0.075501</v>
       </c>
       <c r="G506" s="7">
-        <v>0</v>
+        <v>0.11967499999999999</v>
       </c>
       <c r="H506" s="7">
-        <v>0</v>
+        <v>0.293489</v>
       </c>
       <c r="I506" s="7">
-        <v>0</v>
+        <v>0.455079</v>
       </c>
       <c r="J506" s="7"/>
       <c r="K506" s="7"/>
@@ -23051,22 +23051,22 @@
         <v>2</v>
       </c>
       <c r="E508" s="7">
-        <v>0</v>
+        <v>0.039173</v>
       </c>
       <c r="F508" s="7">
-        <v>0</v>
+        <v>0.080946</v>
       </c>
       <c r="G508" s="7">
-        <v>0</v>
+        <v>0.22181</v>
       </c>
       <c r="H508" s="7">
-        <v>0</v>
+        <v>0.347118</v>
       </c>
       <c r="I508" s="7">
-        <v>0</v>
+        <v>0.552487</v>
       </c>
       <c r="J508" s="7">
-        <v>0</v>
+        <v>2.391352</v>
       </c>
       <c r="K508" s="7"/>
     </row>
@@ -23084,19 +23084,19 @@
         <v>3</v>
       </c>
       <c r="E509" s="7">
-        <v>0</v>
+        <v>0.047377</v>
       </c>
       <c r="F509" s="7">
-        <v>0</v>
+        <v>0.12197100000000001</v>
       </c>
       <c r="G509" s="7">
-        <v>0</v>
+        <v>0.261805</v>
       </c>
       <c r="H509" s="7">
-        <v>0</v>
+        <v>0.41076999999999997</v>
       </c>
       <c r="I509" s="7">
-        <v>0</v>
+        <v>0.5609810000000001</v>
       </c>
       <c r="J509" s="7"/>
       <c r="K509" s="7"/>
@@ -23113,22 +23113,22 @@
       </c>
       <c r="D510" s="6"/>
       <c r="E510" s="7">
-        <v>0</v>
+        <v>0.01726</v>
       </c>
       <c r="F510" s="7">
-        <v>0</v>
+        <v>0.056253000000000004</v>
       </c>
       <c r="G510" s="7">
-        <v>0</v>
+        <v>0.104746</v>
       </c>
       <c r="H510" s="7">
-        <v>0</v>
+        <v>0.13120900000000002</v>
       </c>
       <c r="I510" s="7">
-        <v>0</v>
+        <v>0.194332</v>
       </c>
       <c r="J510" s="7">
-        <v>0</v>
+        <v>0.8805289999999999</v>
       </c>
       <c r="K510" s="7"/>
     </row>
@@ -23202,19 +23202,19 @@
         <v>6</v>
       </c>
       <c r="E513" s="7">
-        <v>0</v>
+        <v>0.209753</v>
       </c>
       <c r="F513" s="7">
-        <v>0</v>
+        <v>-0.031117</v>
       </c>
       <c r="G513" s="7">
-        <v>0</v>
+        <v>-0.107493</v>
       </c>
       <c r="H513" s="7">
-        <v>0</v>
+        <v>0.052382</v>
       </c>
       <c r="I513" s="7">
-        <v>0</v>
+        <v>1.002902</v>
       </c>
       <c r="J513" s="7"/>
       <c r="K513" s="7"/>
@@ -23293,19 +23293,19 @@
         <v>7</v>
       </c>
       <c r="E516" s="7">
-        <v>0</v>
+        <v>-0.019703</v>
       </c>
       <c r="F516" s="7">
-        <v>0</v>
+        <v>0.149903</v>
       </c>
       <c r="G516" s="7">
-        <v>0</v>
+        <v>0.14004899999999998</v>
       </c>
       <c r="H516" s="7">
-        <v>0</v>
+        <v>0.350987</v>
       </c>
       <c r="I516" s="7">
-        <v>0</v>
+        <v>0.30383099999999996</v>
       </c>
       <c r="J516" s="7"/>
       <c r="K516" s="7"/>
@@ -23452,22 +23452,22 @@
         <v>6</v>
       </c>
       <c r="E521" s="7">
-        <v>0.048202999999999996</v>
+        <v>0.049090999999999996</v>
       </c>
       <c r="F521" s="7">
-        <v>0.063151</v>
+        <v>0.064052</v>
       </c>
       <c r="G521" s="7">
-        <v>0.131163</v>
+        <v>0.132121</v>
       </c>
       <c r="H521" s="7">
-        <v>0.195299</v>
+        <v>0.196312</v>
       </c>
       <c r="I521" s="7">
-        <v>0.28091</v>
+        <v>0.281996</v>
       </c>
       <c r="J521" s="7">
-        <v>1.616806</v>
+        <v>1.619024</v>
       </c>
       <c r="K521" s="7"/>
     </row>
@@ -23485,22 +23485,22 @@
         <v>1</v>
       </c>
       <c r="E522" s="7">
-        <v>0.038838</v>
+        <v>0.038845</v>
       </c>
       <c r="F522" s="7">
-        <v>0.11209899999999999</v>
+        <v>0.112107</v>
       </c>
       <c r="G522" s="7">
-        <v>0.222544</v>
+        <v>0.22255199999999997</v>
       </c>
       <c r="H522" s="7">
-        <v>0.266229</v>
+        <v>0.266238</v>
       </c>
       <c r="I522" s="7">
-        <v>0.456811</v>
+        <v>0.456821</v>
       </c>
       <c r="J522" s="7">
-        <v>2.5704219999999998</v>
+        <v>2.5704469999999997</v>
       </c>
       <c r="K522" s="7"/>
     </row>
@@ -23518,19 +23518,19 @@
         <v>2</v>
       </c>
       <c r="E523" s="7">
-        <v>0</v>
+        <v>0.029323000000000002</v>
       </c>
       <c r="F523" s="7">
-        <v>0</v>
+        <v>0.089771</v>
       </c>
       <c r="G523" s="7">
-        <v>0</v>
+        <v>0.184138</v>
       </c>
       <c r="H523" s="7">
-        <v>0</v>
+        <v>0.22894899999999999</v>
       </c>
       <c r="I523" s="7">
-        <v>0</v>
+        <v>0.33775599999999995</v>
       </c>
       <c r="J523" s="7"/>
       <c r="K523" s="7"/>
@@ -23549,19 +23549,19 @@
         <v>6</v>
       </c>
       <c r="E524" s="7">
-        <v>0</v>
+        <v>0.016557</v>
       </c>
       <c r="F524" s="7">
-        <v>0</v>
+        <v>0.032893</v>
       </c>
       <c r="G524" s="7">
-        <v>0</v>
+        <v>0.14729599999999998</v>
       </c>
       <c r="H524" s="7">
-        <v>0</v>
+        <v>0.319517</v>
       </c>
       <c r="I524" s="7">
-        <v>0</v>
+        <v>0.446222</v>
       </c>
       <c r="J524" s="7"/>
       <c r="K524" s="7"/>
@@ -23615,19 +23615,19 @@
         <v>4</v>
       </c>
       <c r="E526" s="7">
-        <v>0</v>
+        <v>0.042759</v>
       </c>
       <c r="F526" s="7">
-        <v>0</v>
+        <v>0.064706</v>
       </c>
       <c r="G526" s="7">
-        <v>0</v>
+        <v>0.09510400000000001</v>
       </c>
       <c r="H526" s="7">
-        <v>0</v>
+        <v>0.128735</v>
       </c>
       <c r="I526" s="7">
-        <v>0</v>
+        <v>0.21164000000000002</v>
       </c>
       <c r="J526" s="7"/>
       <c r="K526" s="7"/>
@@ -23646,25 +23646,25 @@
         <v>4</v>
       </c>
       <c r="E527" s="7">
-        <v>0.021095000000000003</v>
+        <v>0.023527</v>
       </c>
       <c r="F527" s="7">
-        <v>0.06568</v>
+        <v>0.068218</v>
       </c>
       <c r="G527" s="7">
-        <v>0.081718</v>
+        <v>0.084294</v>
       </c>
       <c r="H527" s="7">
-        <v>0.12189299999999999</v>
+        <v>0.124565</v>
       </c>
       <c r="I527" s="7">
-        <v>0.35912799999999995</v>
+        <v>0.362365</v>
       </c>
       <c r="J527" s="7">
-        <v>1.742192</v>
+        <v>1.748724</v>
       </c>
       <c r="K527" s="7">
-        <v>4.9057010000000005</v>
+        <v>4.919766</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.25">
@@ -23803,25 +23803,25 @@
         <v>1</v>
       </c>
       <c r="E532" s="7">
-        <v>0</v>
+        <v>0.032302</v>
       </c>
       <c r="F532" s="7">
-        <v>0</v>
+        <v>0.099801</v>
       </c>
       <c r="G532" s="7">
-        <v>0</v>
+        <v>0.205574</v>
       </c>
       <c r="H532" s="7">
-        <v>0</v>
+        <v>0.267276</v>
       </c>
       <c r="I532" s="7">
-        <v>0</v>
+        <v>0.439331</v>
       </c>
       <c r="J532" s="7">
-        <v>0</v>
+        <v>2.166105</v>
       </c>
       <c r="K532" s="7">
-        <v>0</v>
+        <v>3.555301</v>
       </c>
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.25">
@@ -23838,19 +23838,19 @@
         <v>2</v>
       </c>
       <c r="E533" s="7">
-        <v>0</v>
+        <v>0.018811</v>
       </c>
       <c r="F533" s="7">
-        <v>0</v>
+        <v>0.058544</v>
       </c>
       <c r="G533" s="7">
-        <v>0</v>
+        <v>0.154682</v>
       </c>
       <c r="H533" s="7">
-        <v>0</v>
+        <v>0.258455</v>
       </c>
       <c r="I533" s="7">
-        <v>0</v>
+        <v>0.434449</v>
       </c>
       <c r="J533" s="7"/>
       <c r="K533" s="7"/>
@@ -23956,19 +23956,19 @@
         <v>5</v>
       </c>
       <c r="E537" s="7">
-        <v>0</v>
+        <v>0.072156</v>
       </c>
       <c r="F537" s="7">
-        <v>0</v>
+        <v>0.099161</v>
       </c>
       <c r="G537" s="7">
-        <v>0</v>
+        <v>0.241636</v>
       </c>
       <c r="H537" s="7">
-        <v>0</v>
+        <v>0.502441</v>
       </c>
       <c r="I537" s="7">
-        <v>0</v>
+        <v>0.6774760000000001</v>
       </c>
       <c r="J537" s="7"/>
       <c r="K537" s="7"/>
@@ -24043,19 +24043,19 @@
         <v>6</v>
       </c>
       <c r="E540" s="7">
-        <v>0</v>
+        <v>0.038996</v>
       </c>
       <c r="F540" s="7">
-        <v>0</v>
+        <v>0.054501</v>
       </c>
       <c r="G540" s="7">
-        <v>0</v>
+        <v>0.07288800000000001</v>
       </c>
       <c r="H540" s="7">
-        <v>0</v>
+        <v>0.088849</v>
       </c>
       <c r="I540" s="7">
-        <v>0</v>
+        <v>0.13398</v>
       </c>
       <c r="J540" s="7"/>
       <c r="K540" s="7"/>
@@ -24074,19 +24074,19 @@
         <v>6</v>
       </c>
       <c r="E541" s="7">
-        <v>0</v>
+        <v>0.048516000000000004</v>
       </c>
       <c r="F541" s="7">
-        <v>0</v>
+        <v>0.157356</v>
       </c>
       <c r="G541" s="7">
-        <v>0</v>
+        <v>0.286953</v>
       </c>
       <c r="H541" s="7">
-        <v>0</v>
+        <v>0.468688</v>
       </c>
       <c r="I541" s="7">
-        <v>0</v>
+        <v>0.443801</v>
       </c>
       <c r="J541" s="7"/>
       <c r="K541" s="7"/>
@@ -24105,25 +24105,25 @@
         <v>6</v>
       </c>
       <c r="E542" s="7">
-        <v>0</v>
+        <v>0.052806</v>
       </c>
       <c r="F542" s="7">
-        <v>0</v>
+        <v>0.08975300000000001</v>
       </c>
       <c r="G542" s="7">
-        <v>0</v>
+        <v>0.23079</v>
       </c>
       <c r="H542" s="7">
-        <v>0</v>
+        <v>0.460526</v>
       </c>
       <c r="I542" s="7">
-        <v>0</v>
+        <v>0.511439</v>
       </c>
       <c r="J542" s="7">
-        <v>0</v>
+        <v>1.7661529999999999</v>
       </c>
       <c r="K542" s="7">
-        <v>0</v>
+        <v>14.302204</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.25">
@@ -24138,19 +24138,19 @@
       </c>
       <c r="D543" s="6"/>
       <c r="E543" s="7">
-        <v>0</v>
+        <v>0.018541000000000002</v>
       </c>
       <c r="F543" s="7">
-        <v>0</v>
+        <v>0.053953</v>
       </c>
       <c r="G543" s="7">
-        <v>0</v>
+        <v>0.071707</v>
       </c>
       <c r="H543" s="7">
-        <v>0</v>
+        <v>0.096853</v>
       </c>
       <c r="I543" s="7">
-        <v>0</v>
+        <v>0.170346</v>
       </c>
       <c r="J543" s="7"/>
       <c r="K543" s="7"/>
@@ -24262,19 +24262,19 @@
         <v>1</v>
       </c>
       <c r="E547" s="7">
-        <v>0</v>
+        <v>0.034437</v>
       </c>
       <c r="F547" s="7">
-        <v>0</v>
+        <v>0.103914</v>
       </c>
       <c r="G547" s="7">
-        <v>0</v>
+        <v>0.215093</v>
       </c>
       <c r="H547" s="7">
-        <v>0</v>
+        <v>0.28328</v>
       </c>
       <c r="I547" s="7">
-        <v>0</v>
+        <v>0.478255</v>
       </c>
       <c r="J547" s="7"/>
       <c r="K547" s="7"/>
@@ -24293,22 +24293,22 @@
         <v>6</v>
       </c>
       <c r="E548" s="7">
-        <v>0</v>
+        <v>0.029945</v>
       </c>
       <c r="F548" s="7">
-        <v>0</v>
+        <v>0.062845</v>
       </c>
       <c r="G548" s="7">
-        <v>0</v>
+        <v>0.186386</v>
       </c>
       <c r="H548" s="7">
-        <v>0</v>
+        <v>0.41781399999999996</v>
       </c>
       <c r="I548" s="7">
-        <v>0</v>
+        <v>0.445472</v>
       </c>
       <c r="J548" s="7">
-        <v>0</v>
+        <v>1.3397640000000002</v>
       </c>
       <c r="K548" s="7"/>
     </row>
@@ -24326,25 +24326,25 @@
         <v>2</v>
       </c>
       <c r="E549" s="7">
-        <v>0</v>
+        <v>0.039667</v>
       </c>
       <c r="F549" s="7">
-        <v>0</v>
+        <v>0.10681800000000001</v>
       </c>
       <c r="G549" s="7">
-        <v>0</v>
+        <v>0.120731</v>
       </c>
       <c r="H549" s="7">
-        <v>0</v>
+        <v>0.17092500000000002</v>
       </c>
       <c r="I549" s="7">
-        <v>0</v>
+        <v>0.35557099999999997</v>
       </c>
       <c r="J549" s="7">
-        <v>0</v>
+        <v>2.066833</v>
       </c>
       <c r="K549" s="7">
-        <v>0</v>
+        <v>3.686395</v>
       </c>
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.25">
@@ -24361,25 +24361,25 @@
         <v>5</v>
       </c>
       <c r="E550" s="7">
-        <v>0</v>
+        <v>0.049584</v>
       </c>
       <c r="F550" s="7">
-        <v>0</v>
+        <v>0.09844900000000001</v>
       </c>
       <c r="G550" s="7">
-        <v>0</v>
+        <v>0.108908</v>
       </c>
       <c r="H550" s="7">
-        <v>0</v>
+        <v>0.259133</v>
       </c>
       <c r="I550" s="7">
-        <v>0</v>
+        <v>0.377751</v>
       </c>
       <c r="J550" s="7">
-        <v>0</v>
+        <v>2.211833</v>
       </c>
       <c r="K550" s="7">
-        <v>0</v>
+        <v>10.445022</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.25">
@@ -24421,25 +24421,25 @@
         <v>5</v>
       </c>
       <c r="E552" s="7">
-        <v>0</v>
+        <v>0.044672</v>
       </c>
       <c r="F552" s="7">
-        <v>0</v>
+        <v>0.055978</v>
       </c>
       <c r="G552" s="7">
-        <v>0</v>
+        <v>0.07195599999999999</v>
       </c>
       <c r="H552" s="7">
-        <v>0</v>
+        <v>0.146002</v>
       </c>
       <c r="I552" s="7">
-        <v>0</v>
+        <v>0.25837299999999996</v>
       </c>
       <c r="J552" s="7">
-        <v>0</v>
+        <v>1.278302</v>
       </c>
       <c r="K552" s="7">
-        <v>0</v>
+        <v>5.680794</v>
       </c>
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.25">
@@ -24456,25 +24456,25 @@
         <v>3</v>
       </c>
       <c r="E553" s="7">
-        <v>0</v>
+        <v>0.020905</v>
       </c>
       <c r="F553" s="7">
-        <v>0</v>
+        <v>0.065292</v>
       </c>
       <c r="G553" s="7">
-        <v>0</v>
+        <v>0.108873</v>
       </c>
       <c r="H553" s="7">
-        <v>0</v>
+        <v>0.146009</v>
       </c>
       <c r="I553" s="7">
-        <v>0</v>
+        <v>0.224674</v>
       </c>
       <c r="J553" s="7">
-        <v>0</v>
+        <v>1.1336190000000002</v>
       </c>
       <c r="K553" s="7">
-        <v>0</v>
+        <v>6.332986</v>
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.25">
@@ -24491,22 +24491,22 @@
         <v>2</v>
       </c>
       <c r="E554" s="7">
-        <v>0</v>
+        <v>0.03646</v>
       </c>
       <c r="F554" s="7">
-        <v>0</v>
+        <v>0.109912</v>
       </c>
       <c r="G554" s="7">
-        <v>0</v>
+        <v>0.227063</v>
       </c>
       <c r="H554" s="7">
-        <v>0</v>
+        <v>0.300831</v>
       </c>
       <c r="I554" s="7">
-        <v>0</v>
+        <v>0.513227</v>
       </c>
       <c r="J554" s="7">
-        <v>0</v>
+        <v>2.838037</v>
       </c>
       <c r="K554" s="7"/>
     </row>
@@ -24555,22 +24555,22 @@
         <v>5</v>
       </c>
       <c r="E556" s="7">
-        <v>0</v>
+        <v>0.048496</v>
       </c>
       <c r="F556" s="7">
-        <v>0</v>
+        <v>0.080351</v>
       </c>
       <c r="G556" s="7">
-        <v>0</v>
+        <v>0.18431699999999998</v>
       </c>
       <c r="H556" s="7">
-        <v>0</v>
+        <v>0.302519</v>
       </c>
       <c r="I556" s="7">
-        <v>0</v>
+        <v>0.448992</v>
       </c>
       <c r="J556" s="7">
-        <v>0</v>
+        <v>1.506797</v>
       </c>
       <c r="K556" s="7"/>
     </row>
@@ -24619,25 +24619,25 @@
         <v>1</v>
       </c>
       <c r="E558" s="7">
-        <v>0</v>
+        <v>0.030307</v>
       </c>
       <c r="F558" s="7">
-        <v>0</v>
+        <v>0.093124</v>
       </c>
       <c r="G558" s="7">
-        <v>0</v>
+        <v>0.191297</v>
       </c>
       <c r="H558" s="7">
-        <v>0</v>
+        <v>0.250017</v>
       </c>
       <c r="I558" s="7">
-        <v>0</v>
+        <v>0.418823</v>
       </c>
       <c r="J558" s="7">
-        <v>0</v>
+        <v>2.206028</v>
       </c>
       <c r="K558" s="7">
-        <v>0</v>
+        <v>3.7621499999999997</v>
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.25">
@@ -24685,19 +24685,19 @@
         <v>6</v>
       </c>
       <c r="E560" s="7">
-        <v>0</v>
+        <v>0.026457</v>
       </c>
       <c r="F560" s="7">
-        <v>0</v>
+        <v>0.100627</v>
       </c>
       <c r="G560" s="7">
-        <v>0</v>
+        <v>0.394509</v>
       </c>
       <c r="H560" s="7">
-        <v>0</v>
+        <v>0.49932899999999997</v>
       </c>
       <c r="I560" s="7">
-        <v>0</v>
+        <v>0.7036549999999999</v>
       </c>
       <c r="J560" s="7"/>
       <c r="K560" s="7"/>
@@ -24716,25 +24716,25 @@
         <v>3</v>
       </c>
       <c r="E561" s="7">
-        <v>0</v>
+        <v>0.039943</v>
       </c>
       <c r="F561" s="7">
-        <v>0</v>
+        <v>0.091664</v>
       </c>
       <c r="G561" s="7">
-        <v>0</v>
+        <v>0.207582</v>
       </c>
       <c r="H561" s="7">
-        <v>0</v>
+        <v>0.32356999999999997</v>
       </c>
       <c r="I561" s="7">
-        <v>0</v>
+        <v>0.453856</v>
       </c>
       <c r="J561" s="7">
-        <v>0</v>
+        <v>2.044998</v>
       </c>
       <c r="K561" s="7">
-        <v>0</v>
+        <v>8.28008</v>
       </c>
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.25">
@@ -24751,25 +24751,25 @@
         <v>2</v>
       </c>
       <c r="E562" s="7">
-        <v>0</v>
+        <v>0.026695000000000003</v>
       </c>
       <c r="F562" s="7">
-        <v>0</v>
+        <v>0.064841</v>
       </c>
       <c r="G562" s="7">
-        <v>0</v>
+        <v>0.14529899999999998</v>
       </c>
       <c r="H562" s="7">
-        <v>0</v>
+        <v>0.213054</v>
       </c>
       <c r="I562" s="7">
-        <v>0</v>
+        <v>0.37662999999999996</v>
       </c>
       <c r="J562" s="7">
-        <v>0</v>
+        <v>1.648991</v>
       </c>
       <c r="K562" s="7">
-        <v>0</v>
+        <v>3.070732</v>
       </c>
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.25">
@@ -24786,25 +24786,25 @@
         <v>1</v>
       </c>
       <c r="E563" s="7">
-        <v>0</v>
+        <v>0.030106</v>
       </c>
       <c r="F563" s="7">
-        <v>0</v>
+        <v>0.093407</v>
       </c>
       <c r="G563" s="7">
-        <v>0</v>
+        <v>0.194314</v>
       </c>
       <c r="H563" s="7">
-        <v>0</v>
+        <v>0.256541</v>
       </c>
       <c r="I563" s="7">
-        <v>0</v>
+        <v>0.433431</v>
       </c>
       <c r="J563" s="7">
-        <v>0</v>
+        <v>2.304775</v>
       </c>
       <c r="K563" s="7">
-        <v>0</v>
+        <v>4.061019</v>
       </c>
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.25">
@@ -24821,25 +24821,25 @@
         <v>5</v>
       </c>
       <c r="E564" s="7">
-        <v>0</v>
+        <v>0.05872</v>
       </c>
       <c r="F564" s="7">
-        <v>0</v>
+        <v>0.14413700000000002</v>
       </c>
       <c r="G564" s="7">
-        <v>0</v>
+        <v>0.238615</v>
       </c>
       <c r="H564" s="7">
-        <v>0</v>
+        <v>0.513534</v>
       </c>
       <c r="I564" s="7">
-        <v>0</v>
+        <v>0.498504</v>
       </c>
       <c r="J564" s="7">
-        <v>0</v>
+        <v>1.734551</v>
       </c>
       <c r="K564" s="7">
-        <v>0</v>
+        <v>7.3774</v>
       </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.25">
@@ -24854,25 +24854,25 @@
       </c>
       <c r="D565" s="6"/>
       <c r="E565" s="7">
-        <v>0</v>
+        <v>0.02155</v>
       </c>
       <c r="F565" s="7">
-        <v>0</v>
+        <v>0.066147</v>
       </c>
       <c r="G565" s="7">
-        <v>0</v>
+        <v>0.10807</v>
       </c>
       <c r="H565" s="7">
-        <v>0</v>
+        <v>0.137926</v>
       </c>
       <c r="I565" s="7">
-        <v>0</v>
+        <v>0.231691</v>
       </c>
       <c r="J565" s="7">
-        <v>0</v>
+        <v>1.168712</v>
       </c>
       <c r="K565" s="7">
-        <v>0</v>
+        <v>6.232641999999999</v>
       </c>
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.25">
@@ -24889,25 +24889,25 @@
         <v>1</v>
       </c>
       <c r="E566" s="7">
-        <v>0</v>
+        <v>0.031623</v>
       </c>
       <c r="F566" s="7">
-        <v>0</v>
+        <v>0.093527</v>
       </c>
       <c r="G566" s="7">
-        <v>0</v>
+        <v>0.189938</v>
       </c>
       <c r="H566" s="7">
-        <v>0</v>
+        <v>0.251213</v>
       </c>
       <c r="I566" s="7">
-        <v>0</v>
+        <v>0.42586199999999996</v>
       </c>
       <c r="J566" s="7">
-        <v>0</v>
+        <v>2.0910230000000003</v>
       </c>
       <c r="K566" s="7">
-        <v>0</v>
+        <v>3.483538</v>
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.25">
@@ -24924,10 +24924,10 @@
         <v>5</v>
       </c>
       <c r="E567" s="7">
-        <v>0</v>
+        <v>0.028689</v>
       </c>
       <c r="F567" s="7">
-        <v>0</v>
+        <v>0.101569</v>
       </c>
       <c r="G567" s="7"/>
       <c r="H567" s="7"/>
@@ -24949,19 +24949,19 @@
         <v>5</v>
       </c>
       <c r="E568" s="7">
-        <v>0</v>
+        <v>0.012285999999999998</v>
       </c>
       <c r="F568" s="7">
-        <v>0</v>
+        <v>0.020371</v>
       </c>
       <c r="G568" s="7">
-        <v>0</v>
+        <v>0.064461</v>
       </c>
       <c r="H568" s="7">
-        <v>0</v>
+        <v>0.21262599999999998</v>
       </c>
       <c r="I568" s="7">
-        <v>0</v>
+        <v>0.21874300000000002</v>
       </c>
       <c r="J568" s="7"/>
       <c r="K568" s="7"/>
@@ -24980,25 +24980,25 @@
         <v>6</v>
       </c>
       <c r="E569" s="7">
-        <v>0</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="F569" s="7">
-        <v>0</v>
+        <v>0.058757000000000004</v>
       </c>
       <c r="G569" s="7">
-        <v>0</v>
+        <v>0.096334</v>
       </c>
       <c r="H569" s="7">
-        <v>0</v>
+        <v>0.12226000000000001</v>
       </c>
       <c r="I569" s="7">
-        <v>0</v>
+        <v>0.21260400000000002</v>
       </c>
       <c r="J569" s="7">
-        <v>0</v>
+        <v>1.484281</v>
       </c>
       <c r="K569" s="7">
-        <v>0</v>
+        <v>6.741753</v>
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.25">
@@ -25015,19 +25015,19 @@
         <v>3</v>
       </c>
       <c r="E570" s="7">
-        <v>0</v>
+        <v>0.05279</v>
       </c>
       <c r="F570" s="7">
-        <v>0</v>
+        <v>0.10839700000000001</v>
       </c>
       <c r="G570" s="7">
-        <v>0</v>
+        <v>0.255586</v>
       </c>
       <c r="H570" s="7">
-        <v>0</v>
+        <v>0.42902999999999997</v>
       </c>
       <c r="I570" s="7">
-        <v>0</v>
+        <v>0.531941</v>
       </c>
       <c r="J570" s="7"/>
       <c r="K570" s="7"/>
@@ -25046,22 +25046,22 @@
         <v>6</v>
       </c>
       <c r="E571" s="7">
-        <v>0</v>
+        <v>0.149196</v>
       </c>
       <c r="F571" s="7">
-        <v>0</v>
+        <v>0.018259</v>
       </c>
       <c r="G571" s="7">
-        <v>0</v>
+        <v>-0.079825</v>
       </c>
       <c r="H571" s="7">
-        <v>0</v>
+        <v>0.117109</v>
       </c>
       <c r="I571" s="7">
-        <v>0</v>
+        <v>0.77667</v>
       </c>
       <c r="J571" s="7">
-        <v>0</v>
+        <v>3.2652010000000002</v>
       </c>
       <c r="K571" s="7"/>
     </row>
@@ -25079,16 +25079,16 @@
         <v>2</v>
       </c>
       <c r="E572" s="7">
-        <v>0</v>
+        <v>0.02582</v>
       </c>
       <c r="F572" s="7">
-        <v>0</v>
+        <v>0.084866</v>
       </c>
       <c r="G572" s="7">
-        <v>0</v>
+        <v>0.17687799999999998</v>
       </c>
       <c r="H572" s="7">
-        <v>0</v>
+        <v>0.22841899999999998</v>
       </c>
       <c r="I572" s="7"/>
       <c r="J572" s="7"/>
@@ -25199,25 +25199,25 @@
         <v>6</v>
       </c>
       <c r="E576" s="7">
-        <v>0</v>
+        <v>0.010369</v>
       </c>
       <c r="F576" s="7">
-        <v>0</v>
+        <v>0.043390000000000005</v>
       </c>
       <c r="G576" s="7">
-        <v>0</v>
+        <v>-0.067362</v>
       </c>
       <c r="H576" s="7">
-        <v>0</v>
+        <v>0.140704</v>
       </c>
       <c r="I576" s="7">
-        <v>0</v>
+        <v>0.14353</v>
       </c>
       <c r="J576" s="7">
-        <v>0</v>
+        <v>1.274205</v>
       </c>
       <c r="K576" s="7">
-        <v>0</v>
+        <v>12.641164000000002</v>
       </c>
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.25">
@@ -25234,19 +25234,19 @@
         <v>3</v>
       </c>
       <c r="E577" s="7">
-        <v>0</v>
+        <v>0.01199</v>
       </c>
       <c r="F577" s="7">
-        <v>0</v>
+        <v>0.083251</v>
       </c>
       <c r="G577" s="7">
-        <v>0</v>
+        <v>0.115954</v>
       </c>
       <c r="H577" s="7">
-        <v>0</v>
+        <v>0.16733599999999998</v>
       </c>
       <c r="I577" s="7">
-        <v>0</v>
+        <v>0.27967600000000004</v>
       </c>
       <c r="J577" s="7"/>
       <c r="K577" s="7"/>
@@ -25263,25 +25263,25 @@
       </c>
       <c r="D578" s="6"/>
       <c r="E578" s="7">
-        <v>0</v>
+        <v>0.1329</v>
       </c>
       <c r="F578" s="7">
-        <v>0</v>
+        <v>0.064711</v>
       </c>
       <c r="G578" s="7">
-        <v>0</v>
+        <v>-0.058560999999999995</v>
       </c>
       <c r="H578" s="7">
-        <v>0</v>
+        <v>0.15473599999999998</v>
       </c>
       <c r="I578" s="7">
-        <v>0</v>
+        <v>0.609657</v>
       </c>
       <c r="J578" s="7">
-        <v>0</v>
+        <v>3.246655</v>
       </c>
       <c r="K578" s="7">
-        <v>0</v>
+        <v>14.069697000000001</v>
       </c>
     </row>
     <row r="579" spans="1:11" x14ac:dyDescent="0.25">
@@ -25298,19 +25298,19 @@
         <v>6</v>
       </c>
       <c r="E579" s="7">
-        <v>0</v>
+        <v>0.12923199999999999</v>
       </c>
       <c r="F579" s="7">
-        <v>0</v>
+        <v>0.069731</v>
       </c>
       <c r="G579" s="7">
-        <v>0</v>
+        <v>-0.057396</v>
       </c>
       <c r="H579" s="7">
-        <v>0</v>
+        <v>0.10580099999999999</v>
       </c>
       <c r="I579" s="7">
-        <v>0</v>
+        <v>0.518252</v>
       </c>
       <c r="J579" s="7"/>
       <c r="K579" s="7"/>
@@ -25732,16 +25732,16 @@
         <v>6</v>
       </c>
       <c r="E593" s="7">
-        <v>0.057945</v>
+        <v>0.061315999999999996</v>
       </c>
       <c r="F593" s="7">
-        <v>0.022044</v>
+        <v>0.0253</v>
       </c>
       <c r="G593" s="7">
-        <v>0.089718</v>
+        <v>0.09319000000000001</v>
       </c>
       <c r="H593" s="7">
-        <v>0.16871099999999997</v>
+        <v>0.172434</v>
       </c>
       <c r="I593" s="7"/>
       <c r="J593" s="7"/>
@@ -25761,22 +25761,22 @@
         <v>6</v>
       </c>
       <c r="E594" s="7">
-        <v>0</v>
+        <v>0.019235</v>
       </c>
       <c r="F594" s="7">
-        <v>0</v>
+        <v>0.032481</v>
       </c>
       <c r="G594" s="7">
-        <v>0</v>
+        <v>0.235754</v>
       </c>
       <c r="H594" s="7">
-        <v>0</v>
+        <v>0.26542</v>
       </c>
       <c r="I594" s="7">
-        <v>0</v>
+        <v>0.42172</v>
       </c>
       <c r="J594" s="7">
-        <v>0</v>
+        <v>2.417214</v>
       </c>
       <c r="K594" s="7"/>
     </row>
@@ -25825,19 +25825,19 @@
         <v>2</v>
       </c>
       <c r="E596" s="7">
-        <v>0</v>
+        <v>0.039706</v>
       </c>
       <c r="F596" s="7">
-        <v>0</v>
+        <v>0.08990500000000001</v>
       </c>
       <c r="G596" s="7">
-        <v>0</v>
+        <v>0.148569</v>
       </c>
       <c r="H596" s="7">
-        <v>0</v>
+        <v>0.18509</v>
       </c>
       <c r="I596" s="7">
-        <v>0</v>
+        <v>0.348196</v>
       </c>
       <c r="J596" s="7"/>
       <c r="K596" s="7"/>
@@ -25887,22 +25887,22 @@
         <v>6</v>
       </c>
       <c r="E598" s="7">
-        <v>0.029795</v>
+        <v>0.043796</v>
       </c>
       <c r="F598" s="7">
-        <v>0.045875000000000006</v>
+        <v>0.060095</v>
       </c>
       <c r="G598" s="7">
-        <v>0.12886799999999998</v>
+        <v>0.14421699999999998</v>
       </c>
       <c r="H598" s="7">
-        <v>0.298169</v>
+        <v>0.315819</v>
       </c>
       <c r="I598" s="7">
-        <v>0.400251</v>
+        <v>0.41928899999999997</v>
       </c>
       <c r="J598" s="7">
-        <v>1.7735740000000002</v>
+        <v>1.811284</v>
       </c>
       <c r="K598" s="7"/>
     </row>
@@ -25920,25 +25920,25 @@
         <v>7</v>
       </c>
       <c r="E599" s="7">
-        <v>0.154148</v>
+        <v>0.194002</v>
       </c>
       <c r="F599" s="7">
-        <v>-0.065854</v>
+        <v>-0.033597999999999996</v>
       </c>
       <c r="G599" s="7">
-        <v>-0.161862</v>
+        <v>-0.13292</v>
       </c>
       <c r="H599" s="7">
-        <v>-0.009334</v>
+        <v>0.024874</v>
       </c>
       <c r="I599" s="7">
-        <v>0.87163</v>
+        <v>0.936258</v>
       </c>
       <c r="J599" s="7">
-        <v>3.482831</v>
+        <v>3.637626</v>
       </c>
       <c r="K599" s="7">
-        <v>12.285547999999999</v>
+        <v>12.744306</v>
       </c>
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.25">
@@ -25955,25 +25955,25 @@
         <v>6</v>
       </c>
       <c r="E600" s="7">
-        <v>-0.055616000000000006</v>
+        <v>-0.061900000000000004</v>
       </c>
       <c r="F600" s="7">
-        <v>-0.007857</v>
+        <v>-0.014459</v>
       </c>
       <c r="G600" s="7">
-        <v>-0.11554</v>
+        <v>-0.12142599999999999</v>
       </c>
       <c r="H600" s="7">
-        <v>-0.115317</v>
+        <v>-0.121203</v>
       </c>
       <c r="I600" s="7">
-        <v>-0.12376899999999999</v>
+        <v>-0.12960000000000002</v>
       </c>
       <c r="J600" s="7">
-        <v>0.399217</v>
+        <v>0.38990600000000003</v>
       </c>
       <c r="K600" s="7">
-        <v>2.960643</v>
+        <v>2.9342880000000005</v>
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.25">
@@ -26136,7 +26136,7 @@
         <v>1.402323</v>
       </c>
       <c r="K605" s="7">
-        <v>12.474054</v>
+        <v>12.474055</v>
       </c>
     </row>
     <row r="606" spans="1:11" x14ac:dyDescent="0.25">
@@ -26442,19 +26442,19 @@
       </c>
       <c r="D615" s="6"/>
       <c r="E615" s="7">
-        <v>0</v>
+        <v>0.011873</v>
       </c>
       <c r="F615" s="7">
-        <v>0</v>
+        <v>0.036181</v>
       </c>
       <c r="G615" s="7">
-        <v>0</v>
+        <v>-0.03543</v>
       </c>
       <c r="H615" s="7">
-        <v>0</v>
+        <v>0.052855</v>
       </c>
       <c r="I615" s="7">
-        <v>0</v>
+        <v>0.072436</v>
       </c>
       <c r="J615" s="7"/>
       <c r="K615" s="7"/>
@@ -26531,16 +26531,16 @@
         <v>5</v>
       </c>
       <c r="E618" s="7">
-        <v>0.109094</v>
+        <v>0.109355</v>
       </c>
       <c r="F618" s="7">
-        <v>0.023062</v>
+        <v>0.023302</v>
       </c>
       <c r="G618" s="7">
-        <v>0.127332</v>
+        <v>0.12759700000000002</v>
       </c>
       <c r="H618" s="7">
-        <v>0.27481500000000003</v>
+        <v>0.275115</v>
       </c>
       <c r="I618" s="7"/>
       <c r="J618" s="7"/>
@@ -26560,19 +26560,19 @@
         <v>7</v>
       </c>
       <c r="E619" s="7">
-        <v>0.026848999999999998</v>
+        <v>0.026846000000000002</v>
       </c>
       <c r="F619" s="7">
-        <v>0.07514</v>
+        <v>0.075137</v>
       </c>
       <c r="G619" s="7">
-        <v>0.173214</v>
+        <v>0.17321</v>
       </c>
       <c r="H619" s="7">
-        <v>0.215211</v>
+        <v>0.215208</v>
       </c>
       <c r="I619" s="7">
-        <v>0.330173</v>
+        <v>0.330169</v>
       </c>
       <c r="J619" s="7"/>
       <c r="K619" s="7"/>
@@ -26684,22 +26684,22 @@
         <v>5</v>
       </c>
       <c r="E623" s="7">
-        <v>0.0088</v>
+        <v>0.01677</v>
       </c>
       <c r="F623" s="7">
-        <v>0.025698</v>
+        <v>0.033802</v>
       </c>
       <c r="G623" s="7">
-        <v>0.055227000000000005</v>
+        <v>0.063564</v>
       </c>
       <c r="H623" s="7">
-        <v>0.16889700000000002</v>
+        <v>0.17813199999999998</v>
       </c>
       <c r="I623" s="7">
-        <v>0.238726</v>
+        <v>0.24851199999999998</v>
       </c>
       <c r="J623" s="7">
-        <v>1.056509</v>
+        <v>1.072757</v>
       </c>
       <c r="K623" s="7"/>
     </row>
@@ -26750,22 +26750,22 @@
         <v>6</v>
       </c>
       <c r="E625" s="7">
-        <v>0</v>
+        <v>0.014023</v>
       </c>
       <c r="F625" s="7">
-        <v>0</v>
+        <v>0.007718</v>
       </c>
       <c r="G625" s="7">
-        <v>0</v>
+        <v>0.224527</v>
       </c>
       <c r="H625" s="7">
-        <v>0</v>
+        <v>0.16352699999999998</v>
       </c>
       <c r="I625" s="7">
-        <v>0</v>
+        <v>0.30653199999999997</v>
       </c>
       <c r="J625" s="7">
-        <v>0</v>
+        <v>2.007411</v>
       </c>
       <c r="K625" s="7"/>
     </row>
@@ -26907,16 +26907,16 @@
         <v>5</v>
       </c>
       <c r="E630" s="7">
-        <v>0</v>
+        <v>0.035569</v>
       </c>
       <c r="F630" s="7">
-        <v>0</v>
+        <v>0.106491</v>
       </c>
       <c r="G630" s="7">
-        <v>0</v>
+        <v>0.22499199999999997</v>
       </c>
       <c r="H630" s="7">
-        <v>0</v>
+        <v>0.310612</v>
       </c>
       <c r="I630" s="7"/>
       <c r="J630" s="7"/>
@@ -26936,25 +26936,25 @@
         <v>6</v>
       </c>
       <c r="E631" s="7">
-        <v>0.018032</v>
+        <v>0.017973</v>
       </c>
       <c r="F631" s="7">
-        <v>0.058784</v>
+        <v>0.058722</v>
       </c>
       <c r="G631" s="7">
-        <v>0.11409599999999999</v>
+        <v>0.11403</v>
       </c>
       <c r="H631" s="7">
-        <v>0.14404899999999998</v>
+        <v>0.143982</v>
       </c>
       <c r="I631" s="7">
-        <v>0.22499300000000003</v>
+        <v>0.224922</v>
       </c>
       <c r="J631" s="7">
-        <v>0.9911490000000001</v>
+        <v>0.991033</v>
       </c>
       <c r="K631" s="7">
-        <v>6.151158000000001</v>
+        <v>6.15074</v>
       </c>
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.25">
@@ -26969,22 +26969,22 @@
       </c>
       <c r="D632" s="6"/>
       <c r="E632" s="7">
-        <v>0.019793</v>
+        <v>0.019849000000000002</v>
       </c>
       <c r="F632" s="7">
-        <v>0.063457</v>
+        <v>0.063516</v>
       </c>
       <c r="G632" s="7">
-        <v>0.120372</v>
+        <v>0.120435</v>
       </c>
       <c r="H632" s="7">
-        <v>0.152119</v>
+        <v>0.15218299999999998</v>
       </c>
       <c r="I632" s="7">
-        <v>0.22948899999999997</v>
+        <v>0.229557</v>
       </c>
       <c r="J632" s="7">
-        <v>1.1214279999999999</v>
+        <v>1.121546</v>
       </c>
       <c r="K632" s="7"/>
     </row>
@@ -27002,19 +27002,19 @@
         <v>5</v>
       </c>
       <c r="E633" s="7">
-        <v>0</v>
+        <v>0.031972</v>
       </c>
       <c r="F633" s="7">
-        <v>0</v>
+        <v>0.09117900000000001</v>
       </c>
       <c r="G633" s="7">
-        <v>0</v>
+        <v>0.173889</v>
       </c>
       <c r="H633" s="7">
-        <v>0</v>
+        <v>0.03236</v>
       </c>
       <c r="I633" s="7">
-        <v>0</v>
+        <v>0.09527799999999999</v>
       </c>
       <c r="J633" s="7"/>
       <c r="K633" s="7"/>
@@ -27033,22 +27033,22 @@
         <v>3</v>
       </c>
       <c r="E634" s="7">
-        <v>0</v>
+        <v>-0.000456</v>
       </c>
       <c r="F634" s="7">
-        <v>0</v>
+        <v>0.040416999999999995</v>
       </c>
       <c r="G634" s="7">
-        <v>0</v>
+        <v>0.122979</v>
       </c>
       <c r="H634" s="7">
-        <v>0</v>
+        <v>0.16403800000000002</v>
       </c>
       <c r="I634" s="7">
-        <v>0</v>
+        <v>0.343786</v>
       </c>
       <c r="J634" s="7">
-        <v>0</v>
+        <v>1.725468</v>
       </c>
       <c r="K634" s="7"/>
     </row>
@@ -27467,25 +27467,25 @@
         <v>6</v>
       </c>
       <c r="E648" s="7">
-        <v>0</v>
+        <v>0.004123</v>
       </c>
       <c r="F648" s="7">
-        <v>0</v>
+        <v>0.076293</v>
       </c>
       <c r="G648" s="7">
-        <v>0</v>
+        <v>-0.030293</v>
       </c>
       <c r="H648" s="7">
-        <v>0</v>
+        <v>0.153198</v>
       </c>
       <c r="I648" s="7">
-        <v>0</v>
+        <v>0.08947100000000001</v>
       </c>
       <c r="J648" s="7">
-        <v>0</v>
+        <v>1.126706</v>
       </c>
       <c r="K648" s="7">
-        <v>0</v>
+        <v>14.018793</v>
       </c>
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.25">
@@ -28002,22 +28002,22 @@
         <v>6</v>
       </c>
       <c r="E665" s="7">
-        <v>0.107736</v>
+        <v>0.10663500000000001</v>
       </c>
       <c r="F665" s="7">
-        <v>-0.169365</v>
+        <v>-0.170191</v>
       </c>
       <c r="G665" s="7">
-        <v>-0.104452</v>
+        <v>-0.105342</v>
       </c>
       <c r="H665" s="7">
-        <v>-0.028925</v>
+        <v>-0.02989</v>
       </c>
       <c r="I665" s="7">
-        <v>0.136775</v>
+        <v>0.13564500000000002</v>
       </c>
       <c r="J665" s="7">
-        <v>1.230654</v>
+        <v>1.2284359999999999</v>
       </c>
       <c r="K665" s="7"/>
     </row>
@@ -28419,25 +28419,25 @@
         <v>5</v>
       </c>
       <c r="E678" s="7">
-        <v>0</v>
+        <v>0.030432</v>
       </c>
       <c r="F678" s="7">
-        <v>0</v>
+        <v>0.023041999999999997</v>
       </c>
       <c r="G678" s="7">
-        <v>0</v>
+        <v>-0.013826</v>
       </c>
       <c r="H678" s="7">
-        <v>0</v>
+        <v>0.15043499999999999</v>
       </c>
       <c r="I678" s="7">
-        <v>0</v>
+        <v>0.253745</v>
       </c>
       <c r="J678" s="7">
-        <v>0</v>
+        <v>1.5910149999999998</v>
       </c>
       <c r="K678" s="7">
-        <v>0</v>
+        <v>6.594424</v>
       </c>
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.25">
@@ -28452,22 +28452,22 @@
       </c>
       <c r="D679" s="6"/>
       <c r="E679" s="7">
-        <v>0.051109999999999996</v>
+        <v>0.051151999999999996</v>
       </c>
       <c r="F679" s="7">
-        <v>0.063807</v>
+        <v>0.06385</v>
       </c>
       <c r="G679" s="7">
-        <v>0.11650100000000001</v>
+        <v>0.116546</v>
       </c>
       <c r="H679" s="7">
-        <v>0.213487</v>
+        <v>0.213536</v>
       </c>
       <c r="I679" s="7">
-        <v>0.345505</v>
+        <v>0.345559</v>
       </c>
       <c r="J679" s="7">
-        <v>1.407354</v>
+        <v>1.40745</v>
       </c>
       <c r="K679" s="7"/>
     </row>
@@ -28485,25 +28485,25 @@
         <v>4</v>
       </c>
       <c r="E680" s="7">
-        <v>0</v>
+        <v>0.054039000000000004</v>
       </c>
       <c r="F680" s="7">
-        <v>0</v>
+        <v>0.069416</v>
       </c>
       <c r="G680" s="7">
-        <v>0</v>
+        <v>0.09299099999999999</v>
       </c>
       <c r="H680" s="7">
-        <v>0</v>
+        <v>0.19838999999999998</v>
       </c>
       <c r="I680" s="7">
-        <v>0</v>
+        <v>0.36012</v>
       </c>
       <c r="J680" s="7">
-        <v>0</v>
+        <v>1.763023</v>
       </c>
       <c r="K680" s="7">
-        <v>0</v>
+        <v>6.513630000000001</v>
       </c>
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.25">
@@ -28623,22 +28623,22 @@
         <v>6</v>
       </c>
       <c r="E684" s="7">
-        <v>0.116531</v>
+        <v>0.13492200000000001</v>
       </c>
       <c r="F684" s="7">
-        <v>0.046882</v>
+        <v>0.064127</v>
       </c>
       <c r="G684" s="7">
-        <v>-0.012242999999999999</v>
+        <v>0.004028</v>
       </c>
       <c r="H684" s="7">
-        <v>0.16265999999999997</v>
+        <v>0.181812</v>
       </c>
       <c r="I684" s="7">
-        <v>0.17302</v>
+        <v>0.192342</v>
       </c>
       <c r="J684" s="7">
-        <v>0.8162959999999999</v>
+        <v>0.8462139999999999</v>
       </c>
       <c r="K684" s="7"/>
     </row>
@@ -28656,22 +28656,22 @@
         <v>3</v>
       </c>
       <c r="E685" s="7">
-        <v>0.033437999999999996</v>
+        <v>0.040711000000000004</v>
       </c>
       <c r="F685" s="7">
-        <v>0.074806</v>
+        <v>0.08237</v>
       </c>
       <c r="G685" s="7">
-        <v>0.12225899999999999</v>
+        <v>0.130157</v>
       </c>
       <c r="H685" s="7">
-        <v>0.236256</v>
+        <v>0.244956</v>
       </c>
       <c r="I685" s="7">
-        <v>0.435626</v>
+        <v>0.445729</v>
       </c>
       <c r="J685" s="7">
-        <v>2.225234</v>
+        <v>2.247931</v>
       </c>
       <c r="K685" s="7"/>
     </row>
@@ -28755,25 +28755,25 @@
         <v>6</v>
       </c>
       <c r="E688" s="7">
-        <v>0.036615</v>
+        <v>0.036049000000000005</v>
       </c>
       <c r="F688" s="7">
-        <v>0.056764</v>
+        <v>0.056186999999999994</v>
       </c>
       <c r="G688" s="7">
-        <v>0.36620600000000003</v>
+        <v>0.36545900000000003</v>
       </c>
       <c r="H688" s="7">
-        <v>0.403314</v>
+        <v>0.402547</v>
       </c>
       <c r="I688" s="7">
-        <v>0.584558</v>
+        <v>0.583692</v>
       </c>
       <c r="J688" s="7">
-        <v>2.746463</v>
+        <v>2.7444159999999997</v>
       </c>
       <c r="K688" s="7">
-        <v>10.581508</v>
+        <v>10.57518</v>
       </c>
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.25">
@@ -28959,22 +28959,22 @@
         <v>2</v>
       </c>
       <c r="E694" s="7">
-        <v>0.030891000000000002</v>
+        <v>0.034306</v>
       </c>
       <c r="F694" s="7">
-        <v>0.10002599999999999</v>
+        <v>0.10367000000000001</v>
       </c>
       <c r="G694" s="7">
-        <v>0.215515</v>
+        <v>0.21954100000000001</v>
       </c>
       <c r="H694" s="7">
-        <v>0.284838</v>
+        <v>0.289094</v>
       </c>
       <c r="I694" s="7">
-        <v>0.48105200000000004</v>
+        <v>0.48595799999999995</v>
       </c>
       <c r="J694" s="7">
-        <v>2.496648</v>
+        <v>2.50823</v>
       </c>
       <c r="K694" s="7"/>
     </row>
@@ -29061,13 +29061,13 @@
         <v>0.096859</v>
       </c>
       <c r="H697" s="7">
-        <v>0.13058999999999998</v>
+        <v>0.130591</v>
       </c>
       <c r="I697" s="7">
-        <v>0.209341</v>
+        <v>0.209342</v>
       </c>
       <c r="J697" s="7">
-        <v>1.067159</v>
+        <v>1.0671599999999999</v>
       </c>
       <c r="K697" s="7"/>
     </row>
@@ -29118,22 +29118,22 @@
       </c>
       <c r="D699" s="6"/>
       <c r="E699" s="7">
-        <v>0</v>
+        <v>0.01915</v>
       </c>
       <c r="F699" s="7">
-        <v>0</v>
+        <v>0.061211</v>
       </c>
       <c r="G699" s="7">
-        <v>0</v>
+        <v>0.11399</v>
       </c>
       <c r="H699" s="7">
-        <v>0</v>
+        <v>0.143325</v>
       </c>
       <c r="I699" s="7">
-        <v>0</v>
+        <v>0.21533100000000002</v>
       </c>
       <c r="J699" s="7">
-        <v>0</v>
+        <v>0.967522</v>
       </c>
       <c r="K699" s="7"/>
     </row>
@@ -29458,22 +29458,22 @@
         <v>6</v>
       </c>
       <c r="E709" s="7">
-        <v>0</v>
+        <v>0.153079</v>
       </c>
       <c r="F709" s="7">
-        <v>0</v>
+        <v>0.008421</v>
       </c>
       <c r="G709" s="7">
-        <v>0</v>
+        <v>-0.087108</v>
       </c>
       <c r="H709" s="7">
-        <v>0</v>
+        <v>0.075986</v>
       </c>
       <c r="I709" s="7">
-        <v>0</v>
+        <v>0.713454</v>
       </c>
       <c r="J709" s="7">
-        <v>0</v>
+        <v>2.7657350000000003</v>
       </c>
       <c r="K709" s="7"/>
     </row>
@@ -29588,22 +29588,22 @@
         <v>6</v>
       </c>
       <c r="E713" s="7">
-        <v>0.058053999999999994</v>
+        <v>0.058803999999999995</v>
       </c>
       <c r="F713" s="7">
-        <v>0.057911000000000004</v>
+        <v>0.05866</v>
       </c>
       <c r="G713" s="7">
-        <v>0.207606</v>
+        <v>0.208461</v>
       </c>
       <c r="H713" s="7">
-        <v>0.339632</v>
+        <v>0.340581</v>
       </c>
       <c r="I713" s="7">
-        <v>0.616095</v>
+        <v>0.61724</v>
       </c>
       <c r="J713" s="7">
-        <v>1.558693</v>
+        <v>1.560506</v>
       </c>
       <c r="K713" s="7"/>
     </row>
@@ -29650,7 +29650,7 @@
         <v>6</v>
       </c>
       <c r="E715" s="7">
-        <v>0</v>
+        <v>0.11240399999999999</v>
       </c>
       <c r="F715" s="7"/>
       <c r="G715" s="7"/>
@@ -29797,19 +29797,19 @@
         <v>4</v>
       </c>
       <c r="E720" s="7">
-        <v>0.046268000000000004</v>
+        <v>0.053350999999999996</v>
       </c>
       <c r="F720" s="7">
-        <v>0.13117499999999999</v>
+        <v>0.138834</v>
       </c>
       <c r="G720" s="7">
-        <v>0.239799</v>
+        <v>0.248193</v>
       </c>
       <c r="H720" s="7">
-        <v>0.44136600000000004</v>
+        <v>0.451124</v>
       </c>
       <c r="I720" s="7">
-        <v>0.600364</v>
+        <v>0.611199</v>
       </c>
       <c r="J720" s="7"/>
       <c r="K720" s="7"/>
@@ -29894,19 +29894,19 @@
         <v>6</v>
       </c>
       <c r="E723" s="7">
-        <v>0</v>
+        <v>-0.075431</v>
       </c>
       <c r="F723" s="7">
-        <v>0</v>
+        <v>0.296253</v>
       </c>
       <c r="G723" s="7">
-        <v>0</v>
+        <v>0.71631</v>
       </c>
       <c r="H723" s="7">
-        <v>0</v>
+        <v>1.3179480000000001</v>
       </c>
       <c r="I723" s="7">
-        <v>0</v>
+        <v>1.712164</v>
       </c>
       <c r="J723" s="7"/>
       <c r="K723" s="7"/>
@@ -30057,19 +30057,19 @@
         <v>4</v>
       </c>
       <c r="E728" s="7">
-        <v>0.023315000000000002</v>
+        <v>0.029178000000000003</v>
       </c>
       <c r="F728" s="7">
-        <v>0.05313</v>
+        <v>0.059164</v>
       </c>
       <c r="G728" s="7">
-        <v>0.022712</v>
+        <v>0.028572</v>
       </c>
       <c r="H728" s="7">
-        <v>0.18853</v>
+        <v>0.19533899999999998</v>
       </c>
       <c r="I728" s="7">
-        <v>0.307879</v>
+        <v>0.31537299999999996</v>
       </c>
       <c r="J728" s="7"/>
       <c r="K728" s="7"/>
@@ -30088,22 +30088,22 @@
         <v>4</v>
       </c>
       <c r="E729" s="7">
-        <v>0.036388</v>
+        <v>0.039676</v>
       </c>
       <c r="F729" s="7">
-        <v>0.07778299999999999</v>
+        <v>0.08120200000000001</v>
       </c>
       <c r="G729" s="7">
-        <v>0.141863</v>
+        <v>0.145486</v>
       </c>
       <c r="H729" s="7">
-        <v>0.264392</v>
+        <v>0.268403</v>
       </c>
       <c r="I729" s="7">
-        <v>0.476875</v>
+        <v>0.48156</v>
       </c>
       <c r="J729" s="7">
-        <v>1.983451</v>
+        <v>1.992916</v>
       </c>
       <c r="K729" s="7"/>
     </row>
@@ -30183,19 +30183,19 @@
         <v>6</v>
       </c>
       <c r="E732" s="7">
-        <v>0</v>
+        <v>0.029613999999999998</v>
       </c>
       <c r="F732" s="7">
-        <v>0</v>
+        <v>0.435491</v>
       </c>
       <c r="G732" s="7">
-        <v>0</v>
+        <v>0.8268460000000001</v>
       </c>
       <c r="H732" s="7">
-        <v>0</v>
+        <v>1.8054910000000002</v>
       </c>
       <c r="I732" s="7">
-        <v>0</v>
+        <v>2.202297</v>
       </c>
       <c r="J732" s="7"/>
       <c r="K732" s="7"/>
@@ -30307,22 +30307,22 @@
         <v>6</v>
       </c>
       <c r="E736" s="7">
-        <v>0.054627999999999996</v>
+        <v>0.055374999999999994</v>
       </c>
       <c r="F736" s="7">
-        <v>-0.056086</v>
+        <v>-0.055418</v>
       </c>
       <c r="G736" s="7">
-        <v>0.085493</v>
+        <v>0.086262</v>
       </c>
       <c r="H736" s="7">
-        <v>0.282744</v>
+        <v>0.283652</v>
       </c>
       <c r="I736" s="7">
-        <v>0.753595</v>
+        <v>0.754837</v>
       </c>
       <c r="J736" s="7">
-        <v>2.101611</v>
+        <v>2.1038069999999998</v>
       </c>
       <c r="K736" s="7"/>
     </row>
@@ -30516,19 +30516,19 @@
         <v>6</v>
       </c>
       <c r="E743" s="7">
-        <v>0</v>
+        <v>0.104003</v>
       </c>
       <c r="F743" s="7">
-        <v>0</v>
+        <v>0.13095299999999999</v>
       </c>
       <c r="G743" s="7">
-        <v>0</v>
+        <v>0.16606200000000002</v>
       </c>
       <c r="H743" s="7">
-        <v>0</v>
+        <v>0.186851</v>
       </c>
       <c r="I743" s="7">
-        <v>0</v>
+        <v>0.197026</v>
       </c>
       <c r="J743" s="7"/>
       <c r="K743" s="7"/>
@@ -30580,7 +30580,7 @@
         <v>1</v>
       </c>
       <c r="E745" s="7">
-        <v>0</v>
+        <v>0.033551000000000004</v>
       </c>
       <c r="F745" s="7"/>
       <c r="G745" s="7"/>
@@ -30785,10 +30785,10 @@
         <v>2</v>
       </c>
       <c r="E752" s="7">
-        <v>0</v>
+        <v>0.041951999999999996</v>
       </c>
       <c r="F752" s="7">
-        <v>0</v>
+        <v>0.126479</v>
       </c>
       <c r="G752" s="7"/>
       <c r="H752" s="7"/>
@@ -31529,19 +31529,19 @@
         <v>2</v>
       </c>
       <c r="E776" s="7">
-        <v>0</v>
+        <v>0.041588</v>
       </c>
       <c r="F776" s="7">
-        <v>0</v>
+        <v>0.12531499999999998</v>
       </c>
       <c r="G776" s="7">
-        <v>0</v>
+        <v>0.261614</v>
       </c>
       <c r="H776" s="7">
-        <v>0</v>
+        <v>0.349954</v>
       </c>
       <c r="I776" s="7">
-        <v>0</v>
+        <v>0.595993</v>
       </c>
       <c r="J776" s="7"/>
       <c r="K776" s="7"/>
@@ -31895,10 +31895,10 @@
         <v>5</v>
       </c>
       <c r="E788" s="7">
-        <v>0</v>
+        <v>0.062513</v>
       </c>
       <c r="F788" s="7">
-        <v>0</v>
+        <v>0.23971399999999998</v>
       </c>
       <c r="G788" s="7"/>
       <c r="H788" s="7"/>
@@ -32537,7 +32537,7 @@
         <v>6</v>
       </c>
       <c r="E808" s="7">
-        <v>0.065095</v>
+        <v>0.065964</v>
       </c>
       <c r="F808" s="7"/>
       <c r="G808" s="7"/>
@@ -33700,19 +33700,19 @@
         <v>6</v>
       </c>
       <c r="E845" s="7">
-        <v>0</v>
+        <v>-0.010738000000000001</v>
       </c>
       <c r="F845" s="7">
-        <v>0</v>
+        <v>0.039088</v>
       </c>
       <c r="G845" s="7">
-        <v>0</v>
+        <v>0.018303</v>
       </c>
       <c r="H845" s="7">
-        <v>0</v>
+        <v>0.245064</v>
       </c>
       <c r="I845" s="7">
-        <v>0</v>
+        <v>0.444503</v>
       </c>
       <c r="J845" s="7"/>
       <c r="K845" s="7"/>
@@ -33731,7 +33731,7 @@
         <v>5</v>
       </c>
       <c r="E846" s="7">
-        <v>0</v>
+        <v>0.046375</v>
       </c>
       <c r="F846" s="7"/>
       <c r="G846" s="7"/>
@@ -33754,19 +33754,19 @@
         <v>5</v>
       </c>
       <c r="E847" s="7">
-        <v>0.025756</v>
+        <v>0.034647000000000004</v>
       </c>
       <c r="F847" s="7">
-        <v>0.055244999999999995</v>
+        <v>0.064391</v>
       </c>
       <c r="G847" s="7">
-        <v>0.12118000000000001</v>
+        <v>0.13089800000000001</v>
       </c>
       <c r="H847" s="7">
-        <v>0.27631</v>
+        <v>0.287372</v>
       </c>
       <c r="I847" s="7">
-        <v>0.405996</v>
+        <v>0.418182</v>
       </c>
       <c r="J847" s="7"/>
       <c r="K847" s="7"/>
@@ -33806,19 +33806,19 @@
         <v>5</v>
       </c>
       <c r="E849" s="7">
-        <v>0</v>
+        <v>0.058258000000000004</v>
       </c>
       <c r="F849" s="7">
-        <v>0</v>
+        <v>0.15048</v>
       </c>
       <c r="G849" s="7">
-        <v>0</v>
+        <v>0.455927</v>
       </c>
       <c r="H849" s="7">
-        <v>0</v>
+        <v>0.43208599999999997</v>
       </c>
       <c r="I849" s="7">
-        <v>0</v>
+        <v>0.50489</v>
       </c>
       <c r="J849" s="7"/>
       <c r="K849" s="7"/>
@@ -33860,22 +33860,22 @@
         <v>6</v>
       </c>
       <c r="E851" s="7">
-        <v>0</v>
+        <v>0.018766</v>
       </c>
       <c r="F851" s="7">
-        <v>0</v>
+        <v>0.032938999999999996</v>
       </c>
       <c r="G851" s="7">
-        <v>0</v>
+        <v>-0.012235000000000001</v>
       </c>
       <c r="H851" s="7">
-        <v>0</v>
+        <v>0.162726</v>
       </c>
       <c r="I851" s="7">
-        <v>0</v>
+        <v>0.162056</v>
       </c>
       <c r="J851" s="7">
-        <v>0</v>
+        <v>1.4340629999999999</v>
       </c>
       <c r="K851" s="7"/>
     </row>
@@ -33893,16 +33893,16 @@
         <v>6</v>
       </c>
       <c r="E852" s="7">
-        <v>0</v>
+        <v>0.040834999999999996</v>
       </c>
       <c r="F852" s="7">
-        <v>0</v>
+        <v>0.115207</v>
       </c>
       <c r="G852" s="7">
-        <v>0</v>
+        <v>0.021204999999999998</v>
       </c>
       <c r="H852" s="7">
-        <v>0</v>
+        <v>0.458167</v>
       </c>
       <c r="I852" s="7"/>
       <c r="J852" s="7"/>
@@ -34042,19 +34042,19 @@
         <v>3</v>
       </c>
       <c r="E857" s="7">
-        <v>0</v>
+        <v>0.141364</v>
       </c>
       <c r="F857" s="7">
-        <v>0</v>
+        <v>0.25006</v>
       </c>
       <c r="G857" s="7">
-        <v>0</v>
+        <v>0.263932</v>
       </c>
       <c r="H857" s="7">
-        <v>0</v>
+        <v>0.392475</v>
       </c>
       <c r="I857" s="7">
-        <v>0</v>
+        <v>0.469932</v>
       </c>
       <c r="J857" s="7"/>
       <c r="K857" s="7"/>
@@ -34203,19 +34203,19 @@
         <v>4</v>
       </c>
       <c r="E862" s="7">
-        <v>0.051319</v>
+        <v>0.059517</v>
       </c>
       <c r="F862" s="7">
-        <v>0.072158</v>
+        <v>0.080519</v>
       </c>
       <c r="G862" s="7">
-        <v>0.143569</v>
+        <v>0.152486</v>
       </c>
       <c r="H862" s="7">
-        <v>0.273034</v>
+        <v>0.282961</v>
       </c>
       <c r="I862" s="7">
-        <v>0.53229</v>
+        <v>0.544238</v>
       </c>
       <c r="J862" s="7"/>
       <c r="K862" s="7"/>
@@ -34265,19 +34265,19 @@
         <v>5</v>
       </c>
       <c r="E864" s="7">
-        <v>0.080053</v>
+        <v>0.08010099999999999</v>
       </c>
       <c r="F864" s="7">
-        <v>0.16765</v>
+        <v>0.167703</v>
       </c>
       <c r="G864" s="7">
-        <v>0.18618500000000002</v>
+        <v>0.186239</v>
       </c>
       <c r="H864" s="7">
-        <v>0.257109</v>
+        <v>0.257166</v>
       </c>
       <c r="I864" s="7">
-        <v>0.45535</v>
+        <v>0.455415</v>
       </c>
       <c r="J864" s="7"/>
       <c r="K864" s="7"/>
@@ -34360,19 +34360,19 @@
         <v>6</v>
       </c>
       <c r="E867" s="7">
-        <v>0.060629</v>
+        <v>0.061433</v>
       </c>
       <c r="F867" s="7">
-        <v>0.026171000000000003</v>
+        <v>0.026948</v>
       </c>
       <c r="G867" s="7">
-        <v>0.12400800000000001</v>
+        <v>0.12486000000000001</v>
       </c>
       <c r="H867" s="7">
-        <v>0.261021</v>
+        <v>0.261977</v>
       </c>
       <c r="I867" s="7">
-        <v>0.057712000000000006</v>
+        <v>0.058514</v>
       </c>
       <c r="J867" s="7"/>
       <c r="K867" s="7"/>
@@ -34867,22 +34867,22 @@
         <v>3</v>
       </c>
       <c r="E882" s="7">
-        <v>0</v>
+        <v>0.035643</v>
       </c>
       <c r="F882" s="7">
-        <v>0</v>
+        <v>0.09592200000000001</v>
       </c>
       <c r="G882" s="7">
-        <v>0</v>
+        <v>0.192929</v>
       </c>
       <c r="H882" s="7">
-        <v>0</v>
+        <v>0.270617</v>
       </c>
       <c r="I882" s="7">
-        <v>0</v>
+        <v>0.45972700000000005</v>
       </c>
       <c r="J882" s="7">
-        <v>0</v>
+        <v>2.316229</v>
       </c>
       <c r="K882" s="7"/>
     </row>
@@ -34933,25 +34933,25 @@
         <v>4</v>
       </c>
       <c r="E884" s="7">
-        <v>0</v>
+        <v>0.053429000000000004</v>
       </c>
       <c r="F884" s="7">
-        <v>0</v>
+        <v>0.077593</v>
       </c>
       <c r="G884" s="7">
-        <v>0</v>
+        <v>0.13020400000000001</v>
       </c>
       <c r="H884" s="7">
-        <v>0</v>
+        <v>0.322204</v>
       </c>
       <c r="I884" s="7">
-        <v>0</v>
+        <v>0.5099819999999999</v>
       </c>
       <c r="J884" s="7">
-        <v>0</v>
+        <v>2.385164</v>
       </c>
       <c r="K884" s="7">
-        <v>0</v>
+        <v>5.538827</v>
       </c>
     </row>
     <row r="885" spans="1:11" x14ac:dyDescent="0.25">
@@ -34968,25 +34968,25 @@
         <v>3</v>
       </c>
       <c r="E885" s="7">
-        <v>0</v>
+        <v>0.035733</v>
       </c>
       <c r="F885" s="7">
-        <v>0</v>
+        <v>0.097091</v>
       </c>
       <c r="G885" s="7">
-        <v>0</v>
+        <v>0.19823000000000002</v>
       </c>
       <c r="H885" s="7">
-        <v>0</v>
+        <v>0.277746</v>
       </c>
       <c r="I885" s="7">
-        <v>0</v>
+        <v>0.483483</v>
       </c>
       <c r="J885" s="7">
-        <v>0</v>
+        <v>1.893707</v>
       </c>
       <c r="K885" s="7">
-        <v>0</v>
+        <v>4.997901</v>
       </c>
     </row>
     <row r="886" spans="1:11" x14ac:dyDescent="0.25">
@@ -35003,19 +35003,19 @@
         <v>6</v>
       </c>
       <c r="E886" s="7">
-        <v>0.045864</v>
+        <v>0.045964</v>
       </c>
       <c r="F886" s="7">
-        <v>0.082614</v>
+        <v>0.08271699999999998</v>
       </c>
       <c r="G886" s="7">
-        <v>0.387262</v>
+        <v>0.387394</v>
       </c>
       <c r="H886" s="7">
-        <v>0.466011</v>
+        <v>0.466151</v>
       </c>
       <c r="I886" s="7">
-        <v>0.6857899999999999</v>
+        <v>0.685951</v>
       </c>
       <c r="J886" s="7"/>
       <c r="K886" s="7"/>
@@ -35034,25 +35034,25 @@
         <v>6</v>
       </c>
       <c r="E887" s="7">
-        <v>0</v>
+        <v>0.041392</v>
       </c>
       <c r="F887" s="7">
-        <v>0</v>
+        <v>0.066452</v>
       </c>
       <c r="G887" s="7">
-        <v>0</v>
+        <v>0.377288</v>
       </c>
       <c r="H887" s="7">
-        <v>0</v>
+        <v>0.353661</v>
       </c>
       <c r="I887" s="7">
-        <v>0</v>
+        <v>0.5239309999999999</v>
       </c>
       <c r="J887" s="7">
-        <v>0</v>
+        <v>2.205507</v>
       </c>
       <c r="K887" s="7">
-        <v>0</v>
+        <v>7.829164</v>
       </c>
     </row>
     <row r="888" spans="1:11" x14ac:dyDescent="0.25">
@@ -35296,25 +35296,25 @@
         <v>7</v>
       </c>
       <c r="E895" s="7">
-        <v>0</v>
+        <v>-0.209301</v>
       </c>
       <c r="F895" s="7">
-        <v>0</v>
+        <v>-0.34739</v>
       </c>
       <c r="G895" s="7">
-        <v>0</v>
+        <v>-0.826682</v>
       </c>
       <c r="H895" s="7">
-        <v>0</v>
+        <v>-0.7760469999999999</v>
       </c>
       <c r="I895" s="7">
-        <v>0</v>
+        <v>1.8516599999999999</v>
       </c>
       <c r="J895" s="7">
-        <v>0</v>
+        <v>2.748132</v>
       </c>
       <c r="K895" s="7">
-        <v>0</v>
+        <v>17.439985</v>
       </c>
     </row>
     <row r="896" spans="1:11" x14ac:dyDescent="0.25">
@@ -35570,25 +35570,25 @@
         <v>6</v>
       </c>
       <c r="E903" s="7">
-        <v>0</v>
+        <v>0.018603</v>
       </c>
       <c r="F903" s="7">
-        <v>0</v>
+        <v>0.021901999999999998</v>
       </c>
       <c r="G903" s="7">
-        <v>0</v>
+        <v>0.076308</v>
       </c>
       <c r="H903" s="7">
-        <v>0</v>
+        <v>0.239863</v>
       </c>
       <c r="I903" s="7">
-        <v>0</v>
+        <v>0.294009</v>
       </c>
       <c r="J903" s="7">
-        <v>0</v>
+        <v>1.193082</v>
       </c>
       <c r="K903" s="7">
-        <v>0</v>
+        <v>4.454465</v>
       </c>
     </row>
     <row r="904" spans="1:11" x14ac:dyDescent="0.25">
@@ -35605,22 +35605,22 @@
         <v>4</v>
       </c>
       <c r="E904" s="7">
-        <v>0</v>
+        <v>0.052917</v>
       </c>
       <c r="F904" s="7">
-        <v>0</v>
+        <v>0.06423899999999999</v>
       </c>
       <c r="G904" s="7">
-        <v>0</v>
+        <v>0.079543</v>
       </c>
       <c r="H904" s="7">
-        <v>0</v>
+        <v>0.23569800000000002</v>
       </c>
       <c r="I904" s="7">
-        <v>0</v>
+        <v>0.40996000000000005</v>
       </c>
       <c r="J904" s="7">
-        <v>0</v>
+        <v>1.7552269999999999</v>
       </c>
       <c r="K904" s="7"/>
     </row>
@@ -35636,22 +35636,22 @@
       </c>
       <c r="D905" s="6"/>
       <c r="E905" s="7">
-        <v>0</v>
+        <v>0.046013</v>
       </c>
       <c r="F905" s="7">
-        <v>0</v>
+        <v>0.08006500000000001</v>
       </c>
       <c r="G905" s="7">
-        <v>0</v>
+        <v>0.088895</v>
       </c>
       <c r="H905" s="7">
-        <v>0</v>
+        <v>0.132013</v>
       </c>
       <c r="I905" s="7">
-        <v>0</v>
+        <v>0.23508099999999998</v>
       </c>
       <c r="J905" s="7">
-        <v>0</v>
+        <v>1.2859710000000002</v>
       </c>
       <c r="K905" s="7"/>
     </row>
@@ -35805,16 +35805,16 @@
         <v>1</v>
       </c>
       <c r="E910" s="7">
-        <v>0.034745</v>
+        <v>0.034742999999999996</v>
       </c>
       <c r="F910" s="7">
-        <v>0.10284599999999999</v>
+        <v>0.10284399999999999</v>
       </c>
       <c r="G910" s="7">
-        <v>0.225906</v>
+        <v>0.225904</v>
       </c>
       <c r="H910" s="7">
-        <v>0.30252</v>
+        <v>0.302518</v>
       </c>
       <c r="I910" s="7"/>
       <c r="J910" s="7"/>
@@ -35869,25 +35869,25 @@
         <v>6</v>
       </c>
       <c r="E912" s="7">
-        <v>0.048948</v>
+        <v>0.048947000000000004</v>
       </c>
       <c r="F912" s="7">
-        <v>0.074373</v>
+        <v>0.074372</v>
       </c>
       <c r="G912" s="7">
-        <v>0.207904</v>
+        <v>0.20790299999999998</v>
       </c>
       <c r="H912" s="7">
         <v>0.42186300000000004</v>
       </c>
       <c r="I912" s="7">
-        <v>0.49213</v>
+        <v>0.492129</v>
       </c>
       <c r="J912" s="7">
-        <v>1.17024</v>
+        <v>1.170239</v>
       </c>
       <c r="K912" s="7">
-        <v>12.712285999999999</v>
+        <v>12.71228</v>
       </c>
     </row>
     <row r="913" spans="1:11" x14ac:dyDescent="0.25">
@@ -36005,19 +36005,19 @@
         <v>2</v>
       </c>
       <c r="E916" s="7">
-        <v>0.026996000000000003</v>
+        <v>0.031179000000000002</v>
       </c>
       <c r="F916" s="7">
-        <v>0.07367499999999999</v>
+        <v>0.078047</v>
       </c>
       <c r="G916" s="7">
-        <v>0.157142</v>
+        <v>0.161855</v>
       </c>
       <c r="H916" s="7">
-        <v>0.250475</v>
+        <v>0.255567</v>
       </c>
       <c r="I916" s="7">
-        <v>0.420685</v>
+        <v>0.42647100000000004</v>
       </c>
       <c r="J916" s="7"/>
       <c r="K916" s="7"/>
@@ -36036,19 +36036,19 @@
         <v>5</v>
       </c>
       <c r="E917" s="7">
-        <v>0.016982999999999998</v>
+        <v>0.020592000000000003</v>
       </c>
       <c r="F917" s="7">
-        <v>0.055666</v>
+        <v>0.059412</v>
       </c>
       <c r="G917" s="7">
-        <v>0.149782</v>
+        <v>0.153862</v>
       </c>
       <c r="H917" s="7">
-        <v>0.233008</v>
+        <v>0.23738499999999998</v>
       </c>
       <c r="I917" s="7">
-        <v>0.31737</v>
+        <v>0.322046</v>
       </c>
       <c r="J917" s="7"/>
       <c r="K917" s="7"/>
@@ -36133,19 +36133,19 @@
         <v>2</v>
       </c>
       <c r="E920" s="7">
-        <v>0</v>
+        <v>0.041235999999999995</v>
       </c>
       <c r="F920" s="7">
-        <v>0</v>
+        <v>0.12430899999999999</v>
       </c>
       <c r="G920" s="7">
-        <v>0</v>
+        <v>0.260683</v>
       </c>
       <c r="H920" s="7">
-        <v>0</v>
+        <v>0.35013399999999995</v>
       </c>
       <c r="I920" s="7">
-        <v>0</v>
+        <v>0.60162</v>
       </c>
       <c r="J920" s="7"/>
       <c r="K920" s="7"/>
@@ -36164,25 +36164,25 @@
         <v>6</v>
       </c>
       <c r="E921" s="7">
-        <v>0</v>
+        <v>0.14907199999999998</v>
       </c>
       <c r="F921" s="7">
-        <v>0</v>
+        <v>0.028724</v>
       </c>
       <c r="G921" s="7">
-        <v>0</v>
+        <v>-0.061078</v>
       </c>
       <c r="H921" s="7">
-        <v>0</v>
+        <v>0.09955</v>
       </c>
       <c r="I921" s="7">
-        <v>0</v>
+        <v>0.505554</v>
       </c>
       <c r="J921" s="7">
-        <v>0</v>
+        <v>1.902584</v>
       </c>
       <c r="K921" s="7">
-        <v>0</v>
+        <v>6.603369</v>
       </c>
     </row>
     <row r="922" spans="1:11" x14ac:dyDescent="0.25">
@@ -36232,25 +36232,25 @@
       </c>
       <c r="D923" s="6"/>
       <c r="E923" s="7">
-        <v>0</v>
+        <v>0.024604</v>
       </c>
       <c r="F923" s="7">
-        <v>0</v>
+        <v>0.07579799999999999</v>
       </c>
       <c r="G923" s="7">
-        <v>0</v>
+        <v>0.110351</v>
       </c>
       <c r="H923" s="7">
-        <v>0</v>
+        <v>0.13994099999999998</v>
       </c>
       <c r="I923" s="7">
-        <v>0</v>
+        <v>0.242487</v>
       </c>
       <c r="J923" s="7">
-        <v>0</v>
+        <v>1.234251</v>
       </c>
       <c r="K923" s="7">
-        <v>0</v>
+        <v>6.505706</v>
       </c>
     </row>
     <row r="924" spans="1:11" x14ac:dyDescent="0.25">
@@ -36267,25 +36267,25 @@
         <v>6</v>
       </c>
       <c r="E924" s="7">
-        <v>0</v>
+        <v>0.027086000000000002</v>
       </c>
       <c r="F924" s="7">
-        <v>0</v>
+        <v>0.070132</v>
       </c>
       <c r="G924" s="7">
-        <v>0</v>
+        <v>0.09568199999999999</v>
       </c>
       <c r="H924" s="7">
-        <v>0</v>
+        <v>0.12072699999999999</v>
       </c>
       <c r="I924" s="7">
-        <v>0</v>
+        <v>0.212449</v>
       </c>
       <c r="J924" s="7">
-        <v>0</v>
+        <v>1.127003</v>
       </c>
       <c r="K924" s="7">
-        <v>0</v>
+        <v>5.836266</v>
       </c>
     </row>
     <row r="925" spans="1:11" x14ac:dyDescent="0.25">
@@ -36300,25 +36300,25 @@
       </c>
       <c r="D925" s="6"/>
       <c r="E925" s="7">
-        <v>0</v>
+        <v>0.05223900000000001</v>
       </c>
       <c r="F925" s="7">
-        <v>0</v>
+        <v>0.131064</v>
       </c>
       <c r="G925" s="7">
-        <v>0</v>
+        <v>0.225522</v>
       </c>
       <c r="H925" s="7">
-        <v>0</v>
+        <v>0.317821</v>
       </c>
       <c r="I925" s="7">
-        <v>0</v>
+        <v>0.676923</v>
       </c>
       <c r="J925" s="7">
-        <v>0</v>
+        <v>2.707001</v>
       </c>
       <c r="K925" s="7">
-        <v>0</v>
+        <v>20.317597</v>
       </c>
     </row>
     <row r="926" spans="1:11" x14ac:dyDescent="0.25">
@@ -36370,25 +36370,25 @@
         <v>6</v>
       </c>
       <c r="E927" s="7">
-        <v>0</v>
+        <v>0.021880999999999998</v>
       </c>
       <c r="F927" s="7">
-        <v>0</v>
+        <v>0.066927</v>
       </c>
       <c r="G927" s="7">
-        <v>0</v>
+        <v>0.118605</v>
       </c>
       <c r="H927" s="7">
-        <v>0</v>
+        <v>0.15176399999999998</v>
       </c>
       <c r="I927" s="7">
-        <v>0</v>
+        <v>0.248626</v>
       </c>
       <c r="J927" s="7">
-        <v>0</v>
+        <v>1.258086</v>
       </c>
       <c r="K927" s="7">
-        <v>0</v>
+        <v>6.8052589999999995</v>
       </c>
     </row>
     <row r="928" spans="1:11" x14ac:dyDescent="0.25">
@@ -36634,25 +36634,25 @@
         <v>6</v>
       </c>
       <c r="E935" s="7">
-        <v>0.13165100000000002</v>
+        <v>0.132304</v>
       </c>
       <c r="F935" s="7">
-        <v>0.057173</v>
+        <v>0.057784</v>
       </c>
       <c r="G935" s="7">
-        <v>-0.065733</v>
+        <v>-0.065193</v>
       </c>
       <c r="H935" s="7">
-        <v>0.129047</v>
+        <v>0.129699</v>
       </c>
       <c r="I935" s="7">
-        <v>0.543227</v>
+        <v>0.544118</v>
       </c>
       <c r="J935" s="7">
-        <v>3.0123309999999996</v>
+        <v>3.014649</v>
       </c>
       <c r="K935" s="7">
-        <v>12.412645</v>
+        <v>12.420392999999999</v>
       </c>
     </row>
     <row r="936" spans="1:11" x14ac:dyDescent="0.25">
@@ -36698,22 +36698,22 @@
         <v>6</v>
       </c>
       <c r="E937" s="7">
-        <v>0.04155300000000001</v>
+        <v>0.048415999999999994</v>
       </c>
       <c r="F937" s="7">
-        <v>0.15900999999999998</v>
+        <v>0.166646</v>
       </c>
       <c r="G937" s="7">
-        <v>0.21682600000000002</v>
+        <v>0.22484400000000002</v>
       </c>
       <c r="H937" s="7">
-        <v>0.318281</v>
+        <v>0.326967</v>
       </c>
       <c r="I937" s="7">
-        <v>0.555585</v>
+        <v>0.565835</v>
       </c>
       <c r="J937" s="7">
-        <v>1.824622</v>
+        <v>1.843233</v>
       </c>
       <c r="K937" s="7"/>
     </row>
@@ -37071,19 +37071,19 @@
         <v>6</v>
       </c>
       <c r="E948" s="7">
-        <v>0.07483</v>
+        <v>0.076626</v>
       </c>
       <c r="F948" s="7">
-        <v>0.011009</v>
+        <v>0.012697</v>
       </c>
       <c r="G948" s="7">
-        <v>0.057312</v>
+        <v>0.059078</v>
       </c>
       <c r="H948" s="7">
-        <v>0.274115</v>
+        <v>0.276243</v>
       </c>
       <c r="I948" s="7">
-        <v>0.510835</v>
+        <v>0.513359</v>
       </c>
       <c r="J948" s="7"/>
       <c r="K948" s="7"/>
@@ -37236,7 +37236,7 @@
         <v>6</v>
       </c>
       <c r="E953" s="7">
-        <v>0</v>
+        <v>0.125466</v>
       </c>
       <c r="F953" s="7"/>
       <c r="G953" s="7"/>
@@ -37351,19 +37351,19 @@
         <v>2</v>
       </c>
       <c r="E958" s="7">
-        <v>0</v>
+        <v>0.033046</v>
       </c>
       <c r="F958" s="7">
-        <v>0</v>
+        <v>0.102922</v>
       </c>
       <c r="G958" s="7">
-        <v>0</v>
+        <v>0.20935199999999998</v>
       </c>
       <c r="H958" s="7">
-        <v>0</v>
+        <v>0.28079899999999997</v>
       </c>
       <c r="I958" s="7">
-        <v>0</v>
+        <v>0.475562</v>
       </c>
       <c r="J958" s="7"/>
       <c r="K958" s="7"/>
@@ -37382,19 +37382,19 @@
         <v>3</v>
       </c>
       <c r="E959" s="7">
-        <v>0</v>
+        <v>0.035865</v>
       </c>
       <c r="F959" s="7">
-        <v>0</v>
+        <v>0.04534099999999999</v>
       </c>
       <c r="G959" s="7">
-        <v>0</v>
+        <v>0.07549800000000001</v>
       </c>
       <c r="H959" s="7">
-        <v>0</v>
+        <v>0.177482</v>
       </c>
       <c r="I959" s="7">
-        <v>0</v>
+        <v>0.41564300000000004</v>
       </c>
       <c r="J959" s="7"/>
       <c r="K959" s="7"/>
@@ -37438,13 +37438,13 @@
         <v>6</v>
       </c>
       <c r="E961" s="7">
-        <v>0</v>
+        <v>0.034639</v>
       </c>
       <c r="F961" s="7">
-        <v>0</v>
+        <v>0.097674</v>
       </c>
       <c r="G961" s="7">
-        <v>0</v>
+        <v>0.18087</v>
       </c>
       <c r="H961" s="7"/>
       <c r="I961" s="7"/>
@@ -37465,13 +37465,13 @@
         <v>6</v>
       </c>
       <c r="E962" s="7">
-        <v>0</v>
+        <v>-0.17363199999999998</v>
       </c>
       <c r="F962" s="7">
-        <v>0</v>
+        <v>-0.334146</v>
       </c>
       <c r="G962" s="7">
-        <v>0</v>
+        <v>-0.268561</v>
       </c>
       <c r="H962" s="7"/>
       <c r="I962" s="7"/>
@@ -37521,25 +37521,25 @@
         <v>5</v>
       </c>
       <c r="E964" s="7">
-        <v>0</v>
+        <v>0.051628</v>
       </c>
       <c r="F964" s="7">
-        <v>0</v>
+        <v>0.073689</v>
       </c>
       <c r="G964" s="7">
-        <v>0</v>
+        <v>0.077474</v>
       </c>
       <c r="H964" s="7">
-        <v>0</v>
+        <v>0.19239499999999998</v>
       </c>
       <c r="I964" s="7">
-        <v>0</v>
+        <v>0.33834200000000003</v>
       </c>
       <c r="J964" s="7">
-        <v>0</v>
+        <v>1.450863</v>
       </c>
       <c r="K964" s="7">
-        <v>0</v>
+        <v>5.9964070000000005</v>
       </c>
     </row>
     <row r="965" spans="1:11" x14ac:dyDescent="0.25">
@@ -37616,25 +37616,25 @@
         <v>4</v>
       </c>
       <c r="E967" s="7">
-        <v>0</v>
+        <v>0.035255999999999996</v>
       </c>
       <c r="F967" s="7">
-        <v>0</v>
+        <v>0.09779</v>
       </c>
       <c r="G967" s="7">
-        <v>0</v>
+        <v>0.137687</v>
       </c>
       <c r="H967" s="7">
-        <v>0</v>
+        <v>0.22375699999999998</v>
       </c>
       <c r="I967" s="7">
-        <v>0</v>
+        <v>0.347297</v>
       </c>
       <c r="J967" s="7">
-        <v>0</v>
+        <v>1.250415</v>
       </c>
       <c r="K967" s="7">
-        <v>0</v>
+        <v>4.837814</v>
       </c>
     </row>
     <row r="968" spans="1:11" x14ac:dyDescent="0.25">
@@ -37783,19 +37783,19 @@
       </c>
       <c r="D972" s="6"/>
       <c r="E972" s="7">
-        <v>0</v>
+        <v>0.026049000000000003</v>
       </c>
       <c r="F972" s="7">
-        <v>0</v>
+        <v>0.08679600000000001</v>
       </c>
       <c r="G972" s="7">
-        <v>0</v>
+        <v>0.102413</v>
       </c>
       <c r="H972" s="7">
-        <v>0</v>
+        <v>0.152336</v>
       </c>
       <c r="I972" s="7">
-        <v>0</v>
+        <v>0.264557</v>
       </c>
       <c r="J972" s="7"/>
       <c r="K972" s="7"/>
@@ -37917,22 +37917,22 @@
         <v>2</v>
       </c>
       <c r="E976" s="7">
-        <v>0</v>
+        <v>0.034314</v>
       </c>
       <c r="F976" s="7">
-        <v>0</v>
+        <v>0.092275</v>
       </c>
       <c r="G976" s="7">
-        <v>0</v>
+        <v>0.190502</v>
       </c>
       <c r="H976" s="7">
-        <v>0</v>
+        <v>0.264182</v>
       </c>
       <c r="I976" s="7">
-        <v>0</v>
+        <v>0.43688499999999997</v>
       </c>
       <c r="J976" s="7">
-        <v>0</v>
+        <v>1.79886</v>
       </c>
       <c r="K976" s="7"/>
     </row>
@@ -38383,19 +38383,19 @@
         <v>6</v>
       </c>
       <c r="E990" s="7">
-        <v>0</v>
+        <v>-0.024794</v>
       </c>
       <c r="F990" s="7">
-        <v>0</v>
+        <v>0.008981</v>
       </c>
       <c r="G990" s="7">
-        <v>0</v>
+        <v>0.400171</v>
       </c>
       <c r="H990" s="7">
-        <v>0</v>
+        <v>0.669145</v>
       </c>
       <c r="I990" s="7">
-        <v>0</v>
+        <v>1.04637</v>
       </c>
       <c r="J990" s="7"/>
       <c r="K990" s="7"/>
@@ -38447,22 +38447,22 @@
         <v>5</v>
       </c>
       <c r="E992" s="7">
-        <v>0</v>
+        <v>0.029380000000000003</v>
       </c>
       <c r="F992" s="7">
-        <v>0</v>
+        <v>0.042023000000000005</v>
       </c>
       <c r="G992" s="7">
-        <v>0</v>
+        <v>0.335881</v>
       </c>
       <c r="H992" s="7">
-        <v>0</v>
+        <v>0.474441</v>
       </c>
       <c r="I992" s="7">
-        <v>0</v>
+        <v>0.7072740000000001</v>
       </c>
       <c r="J992" s="7">
-        <v>0</v>
+        <v>2.308599</v>
       </c>
       <c r="K992" s="7"/>
     </row>
@@ -39070,25 +39070,25 @@
         <v>5</v>
       </c>
       <c r="E1011" s="7">
-        <v>0</v>
+        <v>0.056736</v>
       </c>
       <c r="F1011" s="7">
-        <v>0</v>
+        <v>0.064075</v>
       </c>
       <c r="G1011" s="7">
-        <v>0</v>
+        <v>0.055971</v>
       </c>
       <c r="H1011" s="7">
-        <v>0</v>
+        <v>0.19715800000000003</v>
       </c>
       <c r="I1011" s="7">
-        <v>0</v>
+        <v>0.260465</v>
       </c>
       <c r="J1011" s="7">
-        <v>0</v>
+        <v>1.196332</v>
       </c>
       <c r="K1011" s="7">
-        <v>0</v>
+        <v>4.711767</v>
       </c>
     </row>
     <row r="1012" spans="1:11" x14ac:dyDescent="0.25">
@@ -39252,25 +39252,25 @@
         <v>6</v>
       </c>
       <c r="E1017" s="7">
-        <v>0</v>
+        <v>0.07019</v>
       </c>
       <c r="F1017" s="7">
-        <v>0</v>
+        <v>0.08473499999999999</v>
       </c>
       <c r="G1017" s="7">
-        <v>0</v>
+        <v>0.20996099999999998</v>
       </c>
       <c r="H1017" s="7">
-        <v>0</v>
+        <v>0.22040700000000002</v>
       </c>
       <c r="I1017" s="7">
-        <v>0</v>
+        <v>0.46151699999999996</v>
       </c>
       <c r="J1017" s="7">
-        <v>0</v>
+        <v>2.085531</v>
       </c>
       <c r="K1017" s="7">
-        <v>0</v>
+        <v>8.247075</v>
       </c>
     </row>
     <row r="1018" spans="1:11" x14ac:dyDescent="0.25">
@@ -39539,25 +39539,25 @@
         <v>7</v>
       </c>
       <c r="E1026" s="7">
-        <v>0</v>
+        <v>0.207241</v>
       </c>
       <c r="F1026" s="7">
-        <v>0</v>
+        <v>-0.04884</v>
       </c>
       <c r="G1026" s="7">
-        <v>0</v>
+        <v>-0.152642</v>
       </c>
       <c r="H1026" s="7">
-        <v>0</v>
+        <v>0.042933000000000006</v>
       </c>
       <c r="I1026" s="7">
-        <v>0</v>
+        <v>1.008759</v>
       </c>
       <c r="J1026" s="7">
-        <v>0</v>
+        <v>3.630397</v>
       </c>
       <c r="K1026" s="7">
-        <v>0</v>
+        <v>12.681556</v>
       </c>
     </row>
     <row r="1027" spans="1:11" x14ac:dyDescent="0.25">
@@ -39863,22 +39863,22 @@
         <v>6</v>
       </c>
       <c r="E1036" s="7">
-        <v>0.06673</v>
+        <v>0.070282</v>
       </c>
       <c r="F1036" s="7">
-        <v>0.037703</v>
+        <v>0.041158</v>
       </c>
       <c r="G1036" s="7">
-        <v>0.122693</v>
+        <v>0.12643100000000002</v>
       </c>
       <c r="H1036" s="7">
-        <v>0.242886</v>
+        <v>0.247025</v>
       </c>
       <c r="I1036" s="7">
-        <v>0.520561</v>
+        <v>0.525625</v>
       </c>
       <c r="J1036" s="7">
-        <v>1.747527</v>
+        <v>1.756676</v>
       </c>
       <c r="K1036" s="7"/>
     </row>
@@ -40420,25 +40420,25 @@
         <v>5</v>
       </c>
       <c r="E1053" s="7">
-        <v>0.038356</v>
+        <v>0.038423</v>
       </c>
       <c r="F1053" s="7">
-        <v>0.075879</v>
+        <v>0.075948</v>
       </c>
       <c r="G1053" s="7">
-        <v>0.065977</v>
+        <v>0.06604499999999999</v>
       </c>
       <c r="H1053" s="7">
-        <v>0.16337800000000002</v>
+        <v>0.163452</v>
       </c>
       <c r="I1053" s="7">
-        <v>0.229743</v>
+        <v>0.229822</v>
       </c>
       <c r="J1053" s="7">
-        <v>1.273152</v>
+        <v>1.273298</v>
       </c>
       <c r="K1053" s="7">
-        <v>7.184446</v>
+        <v>7.184971000000001</v>
       </c>
     </row>
     <row r="1054" spans="1:11" x14ac:dyDescent="0.25">
@@ -40645,22 +40645,22 @@
         <v>6</v>
       </c>
       <c r="E1060" s="7">
-        <v>0.022566000000000003</v>
+        <v>0.024146</v>
       </c>
       <c r="F1060" s="7">
-        <v>0.019244</v>
+        <v>0.020819</v>
       </c>
       <c r="G1060" s="7">
-        <v>0.10087</v>
+        <v>0.102571</v>
       </c>
       <c r="H1060" s="7">
-        <v>0.24546099999999998</v>
+        <v>0.247385</v>
       </c>
       <c r="I1060" s="7">
-        <v>0.35556600000000005</v>
+        <v>0.35766</v>
       </c>
       <c r="J1060" s="7">
-        <v>1.4956120000000002</v>
+        <v>1.4994669999999999</v>
       </c>
       <c r="K1060" s="7"/>
     </row>
@@ -40678,19 +40678,19 @@
         <v>5</v>
       </c>
       <c r="E1061" s="7">
-        <v>0.017172</v>
+        <v>0.020633</v>
       </c>
       <c r="F1061" s="7">
-        <v>0.11328300000000001</v>
+        <v>0.11707100000000001</v>
       </c>
       <c r="G1061" s="7">
-        <v>0.16808599999999999</v>
+        <v>0.17206</v>
       </c>
       <c r="H1061" s="7">
-        <v>0.258612</v>
+        <v>0.262893</v>
       </c>
       <c r="I1061" s="7">
-        <v>0.295869</v>
+        <v>0.300277</v>
       </c>
       <c r="J1061" s="7"/>
       <c r="K1061" s="7"/>

--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>28.08.2026 09:29:02</t>
+    <t>28.08.2026 13:12:32</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -7262,25 +7262,25 @@
         <v>5</v>
       </c>
       <c r="E15" s="7">
-        <v>0.0215</v>
+        <v>0.021194</v>
       </c>
       <c r="F15" s="7">
-        <v>0.065176</v>
+        <v>0.064857</v>
       </c>
       <c r="G15" s="7">
-        <v>0.123268</v>
+        <v>0.12293100000000001</v>
       </c>
       <c r="H15" s="7">
-        <v>0.157295</v>
+        <v>0.156948</v>
       </c>
       <c r="I15" s="7">
-        <v>0.244679</v>
+        <v>0.244306</v>
       </c>
       <c r="J15" s="7">
-        <v>1.137874</v>
+        <v>1.137233</v>
       </c>
       <c r="K15" s="7">
-        <v>4.509147</v>
+        <v>4.507496</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -7400,25 +7400,25 @@
         <v>7</v>
       </c>
       <c r="E19" s="7">
-        <v>0</v>
+        <v>0.029754999999999997</v>
       </c>
       <c r="F19" s="7">
-        <v>0</v>
+        <v>-0.017151</v>
       </c>
       <c r="G19" s="7">
-        <v>0</v>
+        <v>0.571085</v>
       </c>
       <c r="H19" s="7">
-        <v>0</v>
+        <v>0.851985</v>
       </c>
       <c r="I19" s="7">
-        <v>0</v>
+        <v>0.8115730000000001</v>
       </c>
       <c r="J19" s="7">
-        <v>0</v>
+        <v>1.59083</v>
       </c>
       <c r="K19" s="7">
-        <v>0</v>
+        <v>9.880726</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -7781,25 +7781,25 @@
         <v>4</v>
       </c>
       <c r="E30" s="7">
-        <v>0.041090999999999996</v>
+        <v>0.04199</v>
       </c>
       <c r="F30" s="7">
-        <v>0.08007500000000001</v>
+        <v>0.081008</v>
       </c>
       <c r="G30" s="7">
-        <v>0.172643</v>
+        <v>0.173656</v>
       </c>
       <c r="H30" s="7">
-        <v>0.298946</v>
+        <v>0.300067</v>
       </c>
       <c r="I30" s="7">
-        <v>0.450806</v>
+        <v>0.452059</v>
       </c>
       <c r="J30" s="7">
-        <v>1.94464</v>
+        <v>1.947184</v>
       </c>
       <c r="K30" s="7">
-        <v>8.280173999999999</v>
+        <v>8.288189</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -8282,25 +8282,25 @@
         <v>6</v>
       </c>
       <c r="E45" s="7">
-        <v>0</v>
+        <v>0.059167</v>
       </c>
       <c r="F45" s="7">
-        <v>0</v>
+        <v>0.054513</v>
       </c>
       <c r="G45" s="7">
-        <v>0</v>
+        <v>0.000863</v>
       </c>
       <c r="H45" s="7">
-        <v>0</v>
+        <v>0.197794</v>
       </c>
       <c r="I45" s="7">
-        <v>0</v>
+        <v>0.22003399999999998</v>
       </c>
       <c r="J45" s="7">
-        <v>0</v>
+        <v>1.069793</v>
       </c>
       <c r="K45" s="7">
-        <v>0</v>
+        <v>3.0125279999999997</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -8385,25 +8385,25 @@
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="7">
-        <v>0</v>
+        <v>0.032286999999999996</v>
       </c>
       <c r="F48" s="7">
-        <v>0</v>
+        <v>0.057254</v>
       </c>
       <c r="G48" s="7">
-        <v>0</v>
+        <v>0.101721</v>
       </c>
       <c r="H48" s="7">
-        <v>0</v>
+        <v>0.21245</v>
       </c>
       <c r="I48" s="7">
-        <v>0</v>
+        <v>0.347928</v>
       </c>
       <c r="J48" s="7">
-        <v>0</v>
+        <v>2.0476240000000003</v>
       </c>
       <c r="K48" s="7">
-        <v>0</v>
+        <v>5.4163440000000005</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -8418,25 +8418,25 @@
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7">
-        <v>0</v>
+        <v>0.033089</v>
       </c>
       <c r="F49" s="7">
-        <v>0</v>
+        <v>0.041788</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>0.051075</v>
       </c>
       <c r="H49" s="7">
-        <v>0</v>
+        <v>0.186918</v>
       </c>
       <c r="I49" s="7">
-        <v>0</v>
+        <v>0.312099</v>
       </c>
       <c r="J49" s="7">
-        <v>0</v>
+        <v>1.8602459999999998</v>
       </c>
       <c r="K49" s="7">
-        <v>0</v>
+        <v>5.977524</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -8823,19 +8823,19 @@
         <v>6</v>
       </c>
       <c r="E62" s="7">
-        <v>0.072019</v>
+        <v>0.071976</v>
       </c>
       <c r="F62" s="7">
-        <v>0.053965</v>
+        <v>0.053923</v>
       </c>
       <c r="G62" s="7">
-        <v>0.293275</v>
+        <v>0.293224</v>
       </c>
       <c r="H62" s="7">
-        <v>0.371135</v>
+        <v>0.37107999999999997</v>
       </c>
       <c r="I62" s="7">
-        <v>0.508259</v>
+        <v>0.508199</v>
       </c>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
@@ -9007,19 +9007,19 @@
         <v>5</v>
       </c>
       <c r="E68" s="7">
-        <v>0.037944</v>
+        <v>0.036635</v>
       </c>
       <c r="F68" s="7">
-        <v>0.07569</v>
+        <v>0.074333</v>
       </c>
       <c r="G68" s="7">
-        <v>0.07209800000000001</v>
+        <v>0.070746</v>
       </c>
       <c r="H68" s="7">
-        <v>0.160403</v>
+        <v>0.15894</v>
       </c>
       <c r="I68" s="7">
-        <v>0.32398899999999997</v>
+        <v>0.322319</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
@@ -9369,19 +9369,19 @@
         <v>6</v>
       </c>
       <c r="E80" s="7">
-        <v>0.07276200000000001</v>
+        <v>0.07276099999999999</v>
       </c>
       <c r="F80" s="7">
-        <v>0.19385000000000002</v>
+        <v>0.193849</v>
       </c>
       <c r="G80" s="7">
-        <v>0.270885</v>
+        <v>0.270883</v>
       </c>
       <c r="H80" s="7">
-        <v>0.442166</v>
+        <v>0.442164</v>
       </c>
       <c r="I80" s="7">
-        <v>0.9317319999999999</v>
+        <v>0.9317310000000001</v>
       </c>
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
@@ -9735,19 +9735,19 @@
         <v>3</v>
       </c>
       <c r="E92" s="7">
-        <v>0.044745</v>
+        <v>0.044744</v>
       </c>
       <c r="F92" s="7">
         <v>0.106663</v>
       </c>
       <c r="G92" s="7">
-        <v>0.15152</v>
+        <v>0.151519</v>
       </c>
       <c r="H92" s="7">
-        <v>0.200875</v>
+        <v>0.200874</v>
       </c>
       <c r="I92" s="7">
-        <v>0.375637</v>
+        <v>0.375636</v>
       </c>
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
@@ -9886,19 +9886,19 @@
         <v>5</v>
       </c>
       <c r="E97" s="7">
-        <v>0.062907</v>
+        <v>0.062214</v>
       </c>
       <c r="F97" s="7">
-        <v>0.070648</v>
+        <v>0.069951</v>
       </c>
       <c r="G97" s="7">
-        <v>0.135846</v>
+        <v>0.135106</v>
       </c>
       <c r="H97" s="7">
-        <v>0.325942</v>
+        <v>0.32507800000000003</v>
       </c>
       <c r="I97" s="7">
-        <v>0.49742600000000003</v>
+        <v>0.49645000000000006</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
@@ -10009,13 +10009,13 @@
         <v>0.019962999999999998</v>
       </c>
       <c r="F101" s="7">
-        <v>0.064766</v>
+        <v>0.064765</v>
       </c>
       <c r="G101" s="7">
-        <v>0.123727</v>
+        <v>0.123726</v>
       </c>
       <c r="H101" s="7">
-        <v>0.15735200000000002</v>
+        <v>0.157351</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
@@ -10066,16 +10066,16 @@
         <v>7</v>
       </c>
       <c r="E103" s="7">
-        <v>0.053593</v>
+        <v>0.05359</v>
       </c>
       <c r="F103" s="7">
-        <v>0.154006</v>
+        <v>0.154003</v>
       </c>
       <c r="G103" s="7">
-        <v>0.39000599999999996</v>
+        <v>0.390002</v>
       </c>
       <c r="H103" s="7">
-        <v>0.553141</v>
+        <v>0.553136</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
@@ -10192,16 +10192,16 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.108455</v>
+        <v>0.10819699999999999</v>
       </c>
       <c r="F107" s="7">
-        <v>0.104404</v>
+        <v>0.104147</v>
       </c>
       <c r="G107" s="7">
-        <v>0.545693</v>
+        <v>0.545334</v>
       </c>
       <c r="H107" s="7">
-        <v>0.64265</v>
+        <v>0.642268</v>
       </c>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
@@ -10252,10 +10252,10 @@
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>0.07809300000000001</v>
+        <v>0.08161500000000001</v>
       </c>
       <c r="F109" s="7">
-        <v>0.241084</v>
+        <v>0.245139</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
@@ -10767,19 +10767,19 @@
         <v>5</v>
       </c>
       <c r="E126" s="7">
-        <v>0.056427</v>
+        <v>0.07733799999999999</v>
       </c>
       <c r="F126" s="7">
-        <v>0.064632</v>
+        <v>0.08570499999999999</v>
       </c>
       <c r="G126" s="7">
-        <v>0.420629</v>
+        <v>0.44874899999999995</v>
       </c>
       <c r="H126" s="7">
-        <v>0.585041</v>
+        <v>0.616416</v>
       </c>
       <c r="I126" s="7">
-        <v>0.866743</v>
+        <v>0.903694</v>
       </c>
       <c r="J126" s="7"/>
       <c r="K126" s="7"/>
@@ -11343,22 +11343,22 @@
         <v>6</v>
       </c>
       <c r="E144" s="7">
-        <v>0.0017519999999999999</v>
+        <v>0.001936</v>
       </c>
       <c r="F144" s="7">
-        <v>0.022534000000000002</v>
+        <v>0.022721</v>
       </c>
       <c r="G144" s="7">
-        <v>0.069366</v>
+        <v>0.069562</v>
       </c>
       <c r="H144" s="7">
-        <v>0.277798</v>
+        <v>0.278032</v>
       </c>
       <c r="I144" s="7">
-        <v>0.23823</v>
+        <v>0.238457</v>
       </c>
       <c r="J144" s="7">
-        <v>0.81694</v>
+        <v>0.817273</v>
       </c>
       <c r="K144" s="7"/>
     </row>
@@ -11539,22 +11539,22 @@
         <v>6</v>
       </c>
       <c r="E150" s="7">
-        <v>0.052452</v>
+        <v>0.052454</v>
       </c>
       <c r="F150" s="7">
-        <v>0.048417</v>
+        <v>0.048419</v>
       </c>
       <c r="G150" s="7">
-        <v>0.08831099999999999</v>
+        <v>0.088314</v>
       </c>
       <c r="H150" s="7">
-        <v>0.228549</v>
+        <v>0.228552</v>
       </c>
       <c r="I150" s="7">
-        <v>0.26011399999999996</v>
+        <v>0.260116</v>
       </c>
       <c r="J150" s="7">
-        <v>1.4722479999999998</v>
+        <v>1.4722540000000002</v>
       </c>
       <c r="K150" s="7"/>
     </row>
@@ -11944,22 +11944,22 @@
         <v>7</v>
       </c>
       <c r="E163" s="7">
-        <v>0.171069</v>
+        <v>0.170979</v>
       </c>
       <c r="F163" s="7">
-        <v>-0.058676000000000006</v>
+        <v>-0.058747999999999995</v>
       </c>
       <c r="G163" s="7">
-        <v>-0.16872800000000002</v>
+        <v>-0.168792</v>
       </c>
       <c r="H163" s="7">
-        <v>0.040346</v>
+        <v>0.040267</v>
       </c>
       <c r="I163" s="7">
-        <v>1.007018</v>
+        <v>1.006863</v>
       </c>
       <c r="J163" s="7">
-        <v>3.658888</v>
+        <v>3.6585300000000003</v>
       </c>
       <c r="K163" s="7"/>
     </row>
@@ -11977,16 +11977,16 @@
         <v>4</v>
       </c>
       <c r="E164" s="7">
-        <v>0.11760899999999999</v>
+        <v>0.118791</v>
       </c>
       <c r="F164" s="7">
-        <v>0.13324</v>
+        <v>0.134439</v>
       </c>
       <c r="G164" s="7">
-        <v>0.170048</v>
+        <v>0.171287</v>
       </c>
       <c r="H164" s="7">
-        <v>0.306707</v>
+        <v>0.30809000000000003</v>
       </c>
       <c r="I164" s="7"/>
       <c r="J164" s="7"/>
@@ -12064,19 +12064,19 @@
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="7">
-        <v>0.054152</v>
+        <v>0.057002</v>
       </c>
       <c r="F167" s="7">
-        <v>0.098336</v>
+        <v>0.10130499999999999</v>
       </c>
       <c r="G167" s="7">
-        <v>0.10677099999999999</v>
+        <v>0.109763</v>
       </c>
       <c r="H167" s="7">
-        <v>0.140976</v>
+        <v>0.144061</v>
       </c>
       <c r="I167" s="7">
-        <v>0.270536</v>
+        <v>0.27397099999999996</v>
       </c>
       <c r="J167" s="7"/>
       <c r="K167" s="7"/>
@@ -12450,25 +12450,25 @@
         <v>3</v>
       </c>
       <c r="E179" s="7">
-        <v>0.045833000000000006</v>
+        <v>0.045877999999999995</v>
       </c>
       <c r="F179" s="7">
-        <v>0.086103</v>
+        <v>0.086151</v>
       </c>
       <c r="G179" s="7">
-        <v>0.140086</v>
+        <v>0.140136</v>
       </c>
       <c r="H179" s="7">
-        <v>0.226329</v>
+        <v>0.226383</v>
       </c>
       <c r="I179" s="7">
-        <v>0.403022</v>
+        <v>0.403083</v>
       </c>
       <c r="J179" s="7">
-        <v>1.824384</v>
+        <v>1.824507</v>
       </c>
       <c r="K179" s="7">
-        <v>6.687494</v>
+        <v>6.68783</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -13506,16 +13506,16 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>0.139093</v>
+        <v>0.13881500000000002</v>
       </c>
       <c r="F213" s="7">
-        <v>-0.007696</v>
+        <v>-0.007937999999999999</v>
       </c>
       <c r="G213" s="7">
-        <v>-0.140337</v>
+        <v>-0.140547</v>
       </c>
       <c r="H213" s="7">
-        <v>0.087927</v>
+        <v>0.087661</v>
       </c>
       <c r="I213" s="7"/>
       <c r="J213" s="7"/>
@@ -13773,19 +13773,19 @@
         <v>3</v>
       </c>
       <c r="E222" s="7">
-        <v>0.067075</v>
+        <v>0.073279</v>
       </c>
       <c r="F222" s="7">
-        <v>0.063804</v>
+        <v>0.069988</v>
       </c>
       <c r="G222" s="7">
-        <v>0.134723</v>
+        <v>0.14132</v>
       </c>
       <c r="H222" s="7">
-        <v>0.276356</v>
+        <v>0.28377600000000003</v>
       </c>
       <c r="I222" s="7">
-        <v>0.527045</v>
+        <v>0.535922</v>
       </c>
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
@@ -14155,25 +14155,25 @@
         <v>4</v>
       </c>
       <c r="E234" s="7">
-        <v>0.06793199999999999</v>
+        <v>0.067943</v>
       </c>
       <c r="F234" s="7">
-        <v>0.074951</v>
+        <v>0.074963</v>
       </c>
       <c r="G234" s="7">
-        <v>0.079774</v>
+        <v>0.079786</v>
       </c>
       <c r="H234" s="7">
-        <v>0.178889</v>
+        <v>0.178902</v>
       </c>
       <c r="I234" s="7">
-        <v>0.40763</v>
+        <v>0.407646</v>
       </c>
       <c r="J234" s="7">
-        <v>1.9847620000000001</v>
+        <v>1.984795</v>
       </c>
       <c r="K234" s="7">
-        <v>5.837761</v>
+        <v>5.8378369999999995</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -14584,25 +14584,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.063962</v>
+        <v>0.065798</v>
       </c>
       <c r="F247" s="7">
-        <v>0.104967</v>
+        <v>0.106874</v>
       </c>
       <c r="G247" s="7">
-        <v>0.094483</v>
+        <v>0.096373</v>
       </c>
       <c r="H247" s="7">
-        <v>0.18747599999999998</v>
+        <v>0.189525</v>
       </c>
       <c r="I247" s="7">
-        <v>0.390821</v>
+        <v>0.393221</v>
       </c>
       <c r="J247" s="7">
-        <v>1.9881030000000002</v>
+        <v>1.993261</v>
       </c>
       <c r="K247" s="7">
-        <v>6.3948730000000005</v>
+        <v>6.407636999999999</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -15110,22 +15110,22 @@
         <v>6</v>
       </c>
       <c r="E263" s="7">
-        <v>0.054828</v>
+        <v>0.063294</v>
       </c>
       <c r="F263" s="7">
-        <v>0.038019</v>
+        <v>0.046349999999999995</v>
       </c>
       <c r="G263" s="7">
-        <v>0.34383800000000003</v>
+        <v>0.35462299999999997</v>
       </c>
       <c r="H263" s="7">
-        <v>0.34619999999999995</v>
+        <v>0.35700400000000004</v>
       </c>
       <c r="I263" s="7">
-        <v>0.530354</v>
+        <v>0.542636</v>
       </c>
       <c r="J263" s="7">
-        <v>2.6202820000000004</v>
+        <v>2.649336</v>
       </c>
       <c r="K263" s="7"/>
     </row>
@@ -15178,16 +15178,16 @@
         <v>6</v>
       </c>
       <c r="E265" s="7">
-        <v>-0.180729</v>
+        <v>-0.18136</v>
       </c>
       <c r="F265" s="7">
-        <v>-0.426382</v>
+        <v>-0.42682499999999995</v>
       </c>
       <c r="G265" s="7">
-        <v>-0.462617</v>
+        <v>-0.46303199999999994</v>
       </c>
       <c r="H265" s="7">
-        <v>-0.468157</v>
+        <v>-0.46856699999999996</v>
       </c>
       <c r="I265" s="7"/>
       <c r="J265" s="7"/>
@@ -15236,16 +15236,16 @@
         <v>6</v>
       </c>
       <c r="E267" s="7">
-        <v>0</v>
+        <v>0.145799</v>
       </c>
       <c r="F267" s="7">
-        <v>0</v>
+        <v>0.08155</v>
       </c>
       <c r="G267" s="7">
-        <v>0</v>
+        <v>0.15307700000000002</v>
       </c>
       <c r="H267" s="7">
-        <v>0</v>
+        <v>0.33083100000000004</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
@@ -15434,25 +15434,25 @@
         <v>1</v>
       </c>
       <c r="E273" s="7">
-        <v>0.033198</v>
+        <v>0.033137</v>
       </c>
       <c r="F273" s="7">
-        <v>0.09698499999999999</v>
+        <v>0.096921</v>
       </c>
       <c r="G273" s="7">
-        <v>0.206424</v>
+        <v>0.206353</v>
       </c>
       <c r="H273" s="7">
-        <v>0.28049199999999996</v>
+        <v>0.28041699999999997</v>
       </c>
       <c r="I273" s="7">
-        <v>0.46620100000000003</v>
+        <v>0.466115</v>
       </c>
       <c r="J273" s="7">
-        <v>2.354813</v>
+        <v>2.354616</v>
       </c>
       <c r="K273" s="7">
-        <v>3.990926</v>
+        <v>3.990634</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
@@ -15469,22 +15469,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.047744999999999996</v>
+        <v>0.048727</v>
       </c>
       <c r="F274" s="7">
-        <v>0.08116300000000001</v>
+        <v>0.082177</v>
       </c>
       <c r="G274" s="7">
-        <v>0.136479</v>
+        <v>0.137544</v>
       </c>
       <c r="H274" s="7">
-        <v>0.221032</v>
+        <v>0.222176</v>
       </c>
       <c r="I274" s="7">
-        <v>0.36216299999999996</v>
+        <v>0.36344</v>
       </c>
       <c r="J274" s="7">
-        <v>1.919558</v>
+        <v>1.922294</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -15677,25 +15677,25 @@
         <v>3</v>
       </c>
       <c r="E280" s="7">
-        <v>0</v>
+        <v>0.040777</v>
       </c>
       <c r="F280" s="7">
-        <v>0</v>
+        <v>0.092058</v>
       </c>
       <c r="G280" s="7">
-        <v>0</v>
+        <v>0.127193</v>
       </c>
       <c r="H280" s="7">
-        <v>0</v>
+        <v>0.238373</v>
       </c>
       <c r="I280" s="7">
-        <v>0</v>
+        <v>0.399513</v>
       </c>
       <c r="J280" s="7">
-        <v>0</v>
+        <v>2.287589</v>
       </c>
       <c r="K280" s="7">
-        <v>0</v>
+        <v>6.207673</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -15949,22 +15949,22 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0</v>
+        <v>0.03875</v>
       </c>
       <c r="F288" s="7">
-        <v>0</v>
+        <v>0.040416</v>
       </c>
       <c r="G288" s="7">
-        <v>0</v>
+        <v>0.304985</v>
       </c>
       <c r="H288" s="7">
-        <v>0</v>
+        <v>0.39828899999999995</v>
       </c>
       <c r="I288" s="7">
-        <v>0</v>
+        <v>0.606767</v>
       </c>
       <c r="J288" s="7">
-        <v>0</v>
+        <v>3.9584840000000003</v>
       </c>
       <c r="K288" s="7"/>
     </row>
@@ -15982,22 +15982,22 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.085791</v>
+        <v>0.08673299999999999</v>
       </c>
       <c r="F289" s="7">
-        <v>0.034919</v>
+        <v>0.035817999999999996</v>
       </c>
       <c r="G289" s="7">
-        <v>0.140672</v>
+        <v>0.14166299999999998</v>
       </c>
       <c r="H289" s="7">
-        <v>0.303836</v>
+        <v>0.304968</v>
       </c>
       <c r="I289" s="7">
-        <v>0.530401</v>
+        <v>0.53173</v>
       </c>
       <c r="J289" s="7">
-        <v>1.643954</v>
+        <v>1.646249</v>
       </c>
       <c r="K289" s="7"/>
     </row>
@@ -16182,25 +16182,25 @@
         <v>5</v>
       </c>
       <c r="E295" s="7">
-        <v>0.04561</v>
+        <v>0.048563</v>
       </c>
       <c r="F295" s="7">
-        <v>0.019767999999999997</v>
+        <v>0.022648</v>
       </c>
       <c r="G295" s="7">
-        <v>0.091013</v>
+        <v>0.094094</v>
       </c>
       <c r="H295" s="7">
-        <v>0.23473400000000003</v>
+        <v>0.238221</v>
       </c>
       <c r="I295" s="7">
-        <v>0.499867</v>
+        <v>0.504103</v>
       </c>
       <c r="J295" s="7">
-        <v>1.8232249999999999</v>
+        <v>1.8311979999999999</v>
       </c>
       <c r="K295" s="7">
-        <v>9.332224</v>
+        <v>9.361403000000001</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -16384,22 +16384,22 @@
         <v>5</v>
       </c>
       <c r="E301" s="7">
-        <v>0.072309</v>
+        <v>0.069684</v>
       </c>
       <c r="F301" s="7">
-        <v>0.062951</v>
+        <v>0.060348</v>
       </c>
       <c r="G301" s="7">
-        <v>0.064873</v>
+        <v>0.062264999999999994</v>
       </c>
       <c r="H301" s="7">
-        <v>0.10729799999999999</v>
+        <v>0.104587</v>
       </c>
       <c r="I301" s="7">
-        <v>0.229928</v>
+        <v>0.226916</v>
       </c>
       <c r="J301" s="7">
-        <v>1.596839</v>
+        <v>1.5904800000000001</v>
       </c>
       <c r="K301" s="7"/>
     </row>
@@ -16541,22 +16541,22 @@
         <v>7</v>
       </c>
       <c r="E306" s="7">
-        <v>0</v>
+        <v>0.194374</v>
       </c>
       <c r="F306" s="7">
-        <v>0</v>
+        <v>-0.077038</v>
       </c>
       <c r="G306" s="7">
-        <v>0</v>
+        <v>-0.212588</v>
       </c>
       <c r="H306" s="7">
-        <v>0</v>
+        <v>0.005918</v>
       </c>
       <c r="I306" s="7">
-        <v>0</v>
+        <v>0.983314</v>
       </c>
       <c r="J306" s="7">
-        <v>0</v>
+        <v>3.57091</v>
       </c>
       <c r="K306" s="7"/>
     </row>
@@ -16574,22 +16574,22 @@
         <v>5</v>
       </c>
       <c r="E307" s="7">
-        <v>0.03077</v>
+        <v>0.030742</v>
       </c>
       <c r="F307" s="7">
-        <v>0.058251</v>
+        <v>0.058221999999999996</v>
       </c>
       <c r="G307" s="7">
-        <v>0.16763000000000003</v>
+        <v>0.167598</v>
       </c>
       <c r="H307" s="7">
-        <v>0.214413</v>
+        <v>0.214381</v>
       </c>
       <c r="I307" s="7">
-        <v>0.36257599999999995</v>
+        <v>0.362539</v>
       </c>
       <c r="J307" s="7">
-        <v>0.438149</v>
+        <v>0.43811</v>
       </c>
       <c r="K307" s="7"/>
     </row>
@@ -16762,22 +16762,22 @@
         <v>3</v>
       </c>
       <c r="E313" s="7">
-        <v>0.060614</v>
+        <v>0.061313000000000006</v>
       </c>
       <c r="F313" s="7">
-        <v>0.115132</v>
+        <v>0.115867</v>
       </c>
       <c r="G313" s="7">
-        <v>0.185397</v>
+        <v>0.18617699999999998</v>
       </c>
       <c r="H313" s="7">
-        <v>0.32559800000000005</v>
+        <v>0.326471</v>
       </c>
       <c r="I313" s="7">
-        <v>0.544404</v>
+        <v>0.5454209999999999</v>
       </c>
       <c r="J313" s="7">
-        <v>2.819793</v>
+        <v>2.822309</v>
       </c>
       <c r="K313" s="7"/>
     </row>
@@ -16828,22 +16828,22 @@
         <v>5</v>
       </c>
       <c r="E315" s="7">
-        <v>0.064861</v>
+        <v>0.067052</v>
       </c>
       <c r="F315" s="7">
-        <v>0.057051</v>
+        <v>0.059226</v>
       </c>
       <c r="G315" s="7">
-        <v>0.06689300000000001</v>
+        <v>0.069088</v>
       </c>
       <c r="H315" s="7">
-        <v>0.251743</v>
+        <v>0.25431899999999996</v>
       </c>
       <c r="I315" s="7">
-        <v>0.41991999999999996</v>
+        <v>0.422841</v>
       </c>
       <c r="J315" s="7">
-        <v>2.021132</v>
+        <v>2.027348</v>
       </c>
       <c r="K315" s="7"/>
     </row>
@@ -16861,22 +16861,22 @@
         <v>5</v>
       </c>
       <c r="E316" s="7">
-        <v>0.067475</v>
+        <v>0.069686</v>
       </c>
       <c r="F316" s="7">
-        <v>0.065797</v>
+        <v>0.068004</v>
       </c>
       <c r="G316" s="7">
-        <v>0.056811999999999994</v>
+        <v>0.059000000000000004</v>
       </c>
       <c r="H316" s="7">
-        <v>0.235263</v>
+        <v>0.237821</v>
       </c>
       <c r="I316" s="7">
-        <v>0.417337</v>
+        <v>0.420272</v>
       </c>
       <c r="J316" s="7">
-        <v>2.0326150000000003</v>
+        <v>2.038895</v>
       </c>
       <c r="K316" s="7"/>
     </row>
@@ -17086,25 +17086,25 @@
         <v>2</v>
       </c>
       <c r="E323" s="7">
-        <v>0</v>
+        <v>0.039686</v>
       </c>
       <c r="F323" s="7">
-        <v>0</v>
+        <v>0.095748</v>
       </c>
       <c r="G323" s="7">
-        <v>0</v>
+        <v>0.149209</v>
       </c>
       <c r="H323" s="7">
-        <v>0</v>
+        <v>0.242194</v>
       </c>
       <c r="I323" s="7">
-        <v>0</v>
+        <v>0.398885</v>
       </c>
       <c r="J323" s="7">
-        <v>0</v>
+        <v>2.116886</v>
       </c>
       <c r="K323" s="7">
-        <v>0</v>
+        <v>3.8959910000000004</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
@@ -17119,25 +17119,25 @@
       </c>
       <c r="D324" s="6"/>
       <c r="E324" s="7">
-        <v>0</v>
+        <v>0.027312</v>
       </c>
       <c r="F324" s="7">
-        <v>0</v>
+        <v>0.075177</v>
       </c>
       <c r="G324" s="7">
-        <v>0</v>
+        <v>0.10578699999999999</v>
       </c>
       <c r="H324" s="7">
-        <v>0</v>
+        <v>0.13858399999999998</v>
       </c>
       <c r="I324" s="7">
-        <v>0</v>
+        <v>0.235429</v>
       </c>
       <c r="J324" s="7">
-        <v>0</v>
+        <v>1.3549250000000002</v>
       </c>
       <c r="K324" s="7">
-        <v>0</v>
+        <v>6.21541</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
@@ -17224,25 +17224,25 @@
         <v>3</v>
       </c>
       <c r="E327" s="7">
-        <v>0</v>
+        <v>0.041981000000000004</v>
       </c>
       <c r="F327" s="7">
-        <v>0</v>
+        <v>0.092033</v>
       </c>
       <c r="G327" s="7">
-        <v>0</v>
+        <v>0.134959</v>
       </c>
       <c r="H327" s="7">
-        <v>0</v>
+        <v>0.247456</v>
       </c>
       <c r="I327" s="7">
-        <v>0</v>
+        <v>0.40779699999999997</v>
       </c>
       <c r="J327" s="7">
-        <v>0</v>
+        <v>2.251436</v>
       </c>
       <c r="K327" s="7">
-        <v>0</v>
+        <v>6.370528</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -17350,25 +17350,25 @@
         <v>4</v>
       </c>
       <c r="E331" s="7">
-        <v>0</v>
+        <v>0.04944</v>
       </c>
       <c r="F331" s="7">
-        <v>0</v>
+        <v>0.093404</v>
       </c>
       <c r="G331" s="7">
-        <v>0</v>
+        <v>0.10475899999999999</v>
       </c>
       <c r="H331" s="7">
-        <v>0</v>
+        <v>0.26185400000000003</v>
       </c>
       <c r="I331" s="7">
-        <v>0</v>
+        <v>0.41021599999999997</v>
       </c>
       <c r="J331" s="7">
-        <v>0</v>
+        <v>2.268802</v>
       </c>
       <c r="K331" s="7">
-        <v>0</v>
+        <v>7.206309</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
@@ -17420,19 +17420,19 @@
         <v>5</v>
       </c>
       <c r="E333" s="7">
-        <v>0.073145</v>
+        <v>0.076975</v>
       </c>
       <c r="F333" s="7">
-        <v>0.078873</v>
+        <v>0.08272299999999999</v>
       </c>
       <c r="G333" s="7">
-        <v>0.086621</v>
+        <v>0.090498</v>
       </c>
       <c r="H333" s="7">
-        <v>0.22986499999999999</v>
+        <v>0.234254</v>
       </c>
       <c r="I333" s="7">
-        <v>0.383894</v>
+        <v>0.388833</v>
       </c>
       <c r="J333" s="7"/>
       <c r="K333" s="7"/>
@@ -17682,25 +17682,25 @@
         <v>6</v>
       </c>
       <c r="E341" s="7">
-        <v>0</v>
+        <v>0.06399300000000001</v>
       </c>
       <c r="F341" s="7">
-        <v>0</v>
+        <v>0.119805</v>
       </c>
       <c r="G341" s="7">
-        <v>0</v>
+        <v>0.09704499999999999</v>
       </c>
       <c r="H341" s="7">
-        <v>0</v>
+        <v>0.23971599999999998</v>
       </c>
       <c r="I341" s="7">
-        <v>0</v>
+        <v>0.386809</v>
       </c>
       <c r="J341" s="7">
-        <v>0</v>
+        <v>1.8057759999999998</v>
       </c>
       <c r="K341" s="7">
-        <v>0</v>
+        <v>4.923026</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
@@ -17717,25 +17717,25 @@
         <v>7</v>
       </c>
       <c r="E342" s="7">
-        <v>0</v>
+        <v>0.178647</v>
       </c>
       <c r="F342" s="7">
-        <v>0</v>
+        <v>-0.066648</v>
       </c>
       <c r="G342" s="7">
-        <v>0</v>
+        <v>-0.20308099999999998</v>
       </c>
       <c r="H342" s="7">
-        <v>0</v>
+        <v>0.012983</v>
       </c>
       <c r="I342" s="7">
-        <v>0</v>
+        <v>0.92875</v>
       </c>
       <c r="J342" s="7">
-        <v>0</v>
+        <v>3.620002</v>
       </c>
       <c r="K342" s="7">
-        <v>0</v>
+        <v>11.472536999999999</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
@@ -17808,25 +17808,25 @@
         <v>6</v>
       </c>
       <c r="E345" s="7">
-        <v>0</v>
+        <v>0.059210000000000006</v>
       </c>
       <c r="F345" s="7">
-        <v>0</v>
+        <v>0.064079</v>
       </c>
       <c r="G345" s="7">
-        <v>0</v>
+        <v>0.42060699999999995</v>
       </c>
       <c r="H345" s="7">
-        <v>0</v>
+        <v>0.440219</v>
       </c>
       <c r="I345" s="7">
-        <v>0</v>
+        <v>0.789942</v>
       </c>
       <c r="J345" s="7">
-        <v>0</v>
+        <v>2.731834</v>
       </c>
       <c r="K345" s="7">
-        <v>0</v>
+        <v>8.298126</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -17843,16 +17843,16 @@
         <v>7</v>
       </c>
       <c r="E346" s="7">
-        <v>0</v>
+        <v>0.178623</v>
       </c>
       <c r="F346" s="7">
-        <v>0</v>
+        <v>-0.074642</v>
       </c>
       <c r="G346" s="7">
-        <v>0</v>
+        <v>-0.206657</v>
       </c>
       <c r="H346" s="7">
-        <v>0</v>
+        <v>-0.012114</v>
       </c>
       <c r="I346" s="7"/>
       <c r="J346" s="7"/>
@@ -17872,25 +17872,25 @@
         <v>7</v>
       </c>
       <c r="E347" s="7">
-        <v>0</v>
+        <v>0.187292</v>
       </c>
       <c r="F347" s="7">
-        <v>0</v>
+        <v>-0.06496299999999999</v>
       </c>
       <c r="G347" s="7">
-        <v>0</v>
+        <v>-0.188595</v>
       </c>
       <c r="H347" s="7">
-        <v>0</v>
+        <v>0.029224</v>
       </c>
       <c r="I347" s="7">
-        <v>0</v>
+        <v>0.97543</v>
       </c>
       <c r="J347" s="7">
-        <v>0</v>
+        <v>3.5123469999999997</v>
       </c>
       <c r="K347" s="7">
-        <v>0</v>
+        <v>11.964488</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
@@ -17938,22 +17938,22 @@
         <v>6</v>
       </c>
       <c r="E349" s="7">
-        <v>0</v>
+        <v>0.027871999999999997</v>
       </c>
       <c r="F349" s="7">
-        <v>0</v>
+        <v>-0.066999</v>
       </c>
       <c r="G349" s="7">
-        <v>0</v>
+        <v>0.085155</v>
       </c>
       <c r="H349" s="7">
-        <v>0</v>
+        <v>0.18793600000000002</v>
       </c>
       <c r="I349" s="7">
-        <v>0</v>
+        <v>0.351697</v>
       </c>
       <c r="J349" s="7">
-        <v>0</v>
+        <v>1.300662</v>
       </c>
       <c r="K349" s="7"/>
     </row>
@@ -17971,22 +17971,22 @@
         <v>5</v>
       </c>
       <c r="E350" s="7">
-        <v>0</v>
+        <v>0.050549</v>
       </c>
       <c r="F350" s="7">
-        <v>0</v>
+        <v>0.07387400000000001</v>
       </c>
       <c r="G350" s="7">
-        <v>0</v>
+        <v>0.032277</v>
       </c>
       <c r="H350" s="7">
-        <v>0</v>
+        <v>0.192657</v>
       </c>
       <c r="I350" s="7">
-        <v>0</v>
+        <v>0.304588</v>
       </c>
       <c r="J350" s="7">
-        <v>0</v>
+        <v>1.745249</v>
       </c>
       <c r="K350" s="7"/>
     </row>
@@ -18039,25 +18039,25 @@
         <v>6</v>
       </c>
       <c r="E352" s="7">
-        <v>0</v>
+        <v>0.084324</v>
       </c>
       <c r="F352" s="7">
-        <v>0</v>
+        <v>0.056747</v>
       </c>
       <c r="G352" s="7">
-        <v>0</v>
+        <v>0.150142</v>
       </c>
       <c r="H352" s="7">
-        <v>0</v>
+        <v>0.268641</v>
       </c>
       <c r="I352" s="7">
-        <v>0</v>
+        <v>0.5886549999999999</v>
       </c>
       <c r="J352" s="7">
-        <v>0</v>
+        <v>1.597454</v>
       </c>
       <c r="K352" s="7">
-        <v>0</v>
+        <v>6.848229</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
@@ -18074,22 +18074,22 @@
         <v>6</v>
       </c>
       <c r="E353" s="7">
-        <v>0</v>
+        <v>0.074508</v>
       </c>
       <c r="F353" s="7">
-        <v>0</v>
+        <v>0.23654</v>
       </c>
       <c r="G353" s="7">
-        <v>0</v>
+        <v>0.338853</v>
       </c>
       <c r="H353" s="7">
-        <v>0</v>
+        <v>0.376933</v>
       </c>
       <c r="I353" s="7">
-        <v>0</v>
+        <v>0.582009</v>
       </c>
       <c r="J353" s="7">
-        <v>0</v>
+        <v>1.490095</v>
       </c>
       <c r="K353" s="7"/>
     </row>
@@ -18107,25 +18107,25 @@
         <v>5</v>
       </c>
       <c r="E354" s="7">
-        <v>0</v>
+        <v>0.023783</v>
       </c>
       <c r="F354" s="7">
-        <v>0</v>
+        <v>-0.060665</v>
       </c>
       <c r="G354" s="7">
-        <v>0</v>
+        <v>0.058461</v>
       </c>
       <c r="H354" s="7">
-        <v>0</v>
+        <v>0.251804</v>
       </c>
       <c r="I354" s="7">
-        <v>0</v>
+        <v>0.41892</v>
       </c>
       <c r="J354" s="7">
-        <v>0</v>
+        <v>0.927689</v>
       </c>
       <c r="K354" s="7">
-        <v>0</v>
+        <v>4.229526</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -18142,25 +18142,25 @@
         <v>4</v>
       </c>
       <c r="E355" s="7">
-        <v>0</v>
+        <v>0.046675</v>
       </c>
       <c r="F355" s="7">
-        <v>0</v>
+        <v>0.082888</v>
       </c>
       <c r="G355" s="7">
-        <v>0</v>
+        <v>0.075945</v>
       </c>
       <c r="H355" s="7">
-        <v>0</v>
+        <v>0.21384599999999998</v>
       </c>
       <c r="I355" s="7">
-        <v>0</v>
+        <v>0.349013</v>
       </c>
       <c r="J355" s="7">
-        <v>0</v>
+        <v>2.050127</v>
       </c>
       <c r="K355" s="7">
-        <v>0</v>
+        <v>6.990039</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
@@ -18280,25 +18280,25 @@
         <v>3</v>
       </c>
       <c r="E359" s="7">
-        <v>0</v>
+        <v>0.039882</v>
       </c>
       <c r="F359" s="7">
-        <v>0</v>
+        <v>0.085672</v>
       </c>
       <c r="G359" s="7">
-        <v>0</v>
+        <v>0.13425700000000002</v>
       </c>
       <c r="H359" s="7">
-        <v>0</v>
+        <v>0.237562</v>
       </c>
       <c r="I359" s="7">
-        <v>0</v>
+        <v>0.395726</v>
       </c>
       <c r="J359" s="7">
-        <v>0</v>
+        <v>2.240012</v>
       </c>
       <c r="K359" s="7">
-        <v>0</v>
+        <v>6.070179</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
@@ -18350,25 +18350,25 @@
         <v>5</v>
       </c>
       <c r="E361" s="7">
-        <v>0</v>
+        <v>0.051547</v>
       </c>
       <c r="F361" s="7">
-        <v>0</v>
+        <v>0.065468</v>
       </c>
       <c r="G361" s="7">
-        <v>0</v>
+        <v>0.14391299999999999</v>
       </c>
       <c r="H361" s="7">
-        <v>0</v>
+        <v>0.252077</v>
       </c>
       <c r="I361" s="7">
-        <v>0</v>
+        <v>0.365578</v>
       </c>
       <c r="J361" s="7">
-        <v>0</v>
+        <v>1.555041</v>
       </c>
       <c r="K361" s="7">
-        <v>0</v>
+        <v>6.331378999999999</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
@@ -18385,22 +18385,22 @@
         <v>6</v>
       </c>
       <c r="E362" s="7">
-        <v>0</v>
+        <v>0.014245</v>
       </c>
       <c r="F362" s="7">
-        <v>0</v>
+        <v>0.114009</v>
       </c>
       <c r="G362" s="7">
-        <v>0</v>
+        <v>0.077721</v>
       </c>
       <c r="H362" s="7">
-        <v>0</v>
+        <v>0.121647</v>
       </c>
       <c r="I362" s="7">
-        <v>0</v>
+        <v>0.146892</v>
       </c>
       <c r="J362" s="7">
-        <v>0</v>
+        <v>1.5007249999999999</v>
       </c>
       <c r="K362" s="7"/>
     </row>
@@ -18418,22 +18418,22 @@
         <v>5</v>
       </c>
       <c r="E363" s="7">
-        <v>0</v>
+        <v>0.060225999999999995</v>
       </c>
       <c r="F363" s="7">
-        <v>0</v>
+        <v>0.116064</v>
       </c>
       <c r="G363" s="7">
-        <v>0</v>
+        <v>0.06871100000000001</v>
       </c>
       <c r="H363" s="7">
-        <v>0</v>
+        <v>0.10621399999999999</v>
       </c>
       <c r="I363" s="7">
-        <v>0</v>
+        <v>0.20006900000000002</v>
       </c>
       <c r="J363" s="7">
-        <v>0</v>
+        <v>1.7826320000000002</v>
       </c>
       <c r="K363" s="7"/>
     </row>
@@ -18596,22 +18596,22 @@
       </c>
       <c r="D369" s="6"/>
       <c r="E369" s="7">
-        <v>0</v>
+        <v>0.037614</v>
       </c>
       <c r="F369" s="7">
-        <v>0</v>
+        <v>0.059802</v>
       </c>
       <c r="G369" s="7">
-        <v>0</v>
+        <v>0.108291</v>
       </c>
       <c r="H369" s="7">
-        <v>0</v>
+        <v>0.22496200000000002</v>
       </c>
       <c r="I369" s="7">
-        <v>0</v>
+        <v>0.300342</v>
       </c>
       <c r="J369" s="7">
-        <v>0</v>
+        <v>1.605411</v>
       </c>
       <c r="K369" s="7"/>
     </row>
@@ -19487,25 +19487,25 @@
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="7">
-        <v>0.038619</v>
+        <v>0.039513</v>
       </c>
       <c r="F398" s="7">
-        <v>0.05501</v>
+        <v>0.055918999999999996</v>
       </c>
       <c r="G398" s="7">
-        <v>0.150108</v>
+        <v>0.151098</v>
       </c>
       <c r="H398" s="7">
-        <v>0.23453</v>
+        <v>0.235593</v>
       </c>
       <c r="I398" s="7">
-        <v>0.352416</v>
+        <v>0.35357999999999995</v>
       </c>
       <c r="J398" s="7">
-        <v>1.612743</v>
+        <v>1.614992</v>
       </c>
       <c r="K398" s="7">
-        <v>6.5105759999999995</v>
+        <v>6.517042</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
@@ -19712,25 +19712,25 @@
       </c>
       <c r="D405" s="6"/>
       <c r="E405" s="7">
-        <v>0.041089</v>
+        <v>0.04106</v>
       </c>
       <c r="F405" s="7">
-        <v>0.050319</v>
+        <v>0.05029</v>
       </c>
       <c r="G405" s="7">
-        <v>0.099673</v>
+        <v>0.099642</v>
       </c>
       <c r="H405" s="7">
-        <v>0.231347</v>
+        <v>0.231312</v>
       </c>
       <c r="I405" s="7">
-        <v>0.232516</v>
+        <v>0.23248100000000002</v>
       </c>
       <c r="J405" s="7">
-        <v>1.274068</v>
+        <v>1.2740040000000001</v>
       </c>
       <c r="K405" s="7">
-        <v>9.464376999999999</v>
+        <v>9.464084</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
@@ -19871,7 +19871,7 @@
         <v>6</v>
       </c>
       <c r="E410" s="7">
-        <v>0.013028999999999999</v>
+        <v>0.013571999999999999</v>
       </c>
       <c r="F410" s="7"/>
       <c r="G410" s="7"/>
@@ -19892,19 +19892,19 @@
       </c>
       <c r="D411" s="6"/>
       <c r="E411" s="7">
-        <v>0.062676</v>
+        <v>0.06235</v>
       </c>
       <c r="F411" s="7">
-        <v>0.049837</v>
+        <v>0.049515</v>
       </c>
       <c r="G411" s="7">
-        <v>0.24800699999999998</v>
+        <v>0.24762499999999998</v>
       </c>
       <c r="H411" s="7">
-        <v>0.26406199999999996</v>
+        <v>0.263675</v>
       </c>
       <c r="I411" s="7">
-        <v>0.390857</v>
+        <v>0.39043100000000003</v>
       </c>
       <c r="J411" s="7"/>
       <c r="K411" s="7"/>
@@ -20278,25 +20278,25 @@
         <v>6</v>
       </c>
       <c r="E423" s="7">
-        <v>0</v>
+        <v>0.023138000000000002</v>
       </c>
       <c r="F423" s="7">
-        <v>0</v>
+        <v>-0.070127</v>
       </c>
       <c r="G423" s="7">
-        <v>0</v>
+        <v>0.071217</v>
       </c>
       <c r="H423" s="7">
-        <v>0</v>
+        <v>0.08661899999999999</v>
       </c>
       <c r="I423" s="7">
-        <v>0</v>
+        <v>0.056561</v>
       </c>
       <c r="J423" s="7">
-        <v>0</v>
+        <v>0.9727800000000001</v>
       </c>
       <c r="K423" s="7">
-        <v>0</v>
+        <v>13.538955000000001</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.25">
@@ -20954,25 +20954,25 @@
         <v>4</v>
       </c>
       <c r="E443" s="7">
-        <v>0.041256</v>
+        <v>0.041220999999999994</v>
       </c>
       <c r="F443" s="7">
-        <v>0.070315</v>
+        <v>0.070279</v>
       </c>
       <c r="G443" s="7">
-        <v>0.14660700000000002</v>
+        <v>0.146568</v>
       </c>
       <c r="H443" s="7">
-        <v>0.303764</v>
+        <v>0.30372</v>
       </c>
       <c r="I443" s="7">
-        <v>0.504251</v>
+        <v>0.5042</v>
       </c>
       <c r="J443" s="7">
-        <v>2.468753</v>
+        <v>2.4686369999999997</v>
       </c>
       <c r="K443" s="7">
-        <v>6.079489</v>
+        <v>6.079252</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.25">
@@ -21456,25 +21456,25 @@
         <v>6</v>
       </c>
       <c r="E459" s="7">
-        <v>0.051289</v>
+        <v>0.051281</v>
       </c>
       <c r="F459" s="7">
-        <v>0.07513</v>
+        <v>0.075123</v>
       </c>
       <c r="G459" s="7">
-        <v>0.046501</v>
+        <v>0.046494</v>
       </c>
       <c r="H459" s="7">
-        <v>0.232228</v>
+        <v>0.232219</v>
       </c>
       <c r="I459" s="7">
-        <v>0.234058</v>
+        <v>0.23405</v>
       </c>
       <c r="J459" s="7">
-        <v>1.532128</v>
+        <v>1.5321109999999998</v>
       </c>
       <c r="K459" s="7">
-        <v>18.451432</v>
+        <v>18.451297</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.25">
@@ -21625,25 +21625,25 @@
         <v>3</v>
       </c>
       <c r="E464" s="7">
-        <v>0</v>
+        <v>0.036027</v>
       </c>
       <c r="F464" s="7">
-        <v>0</v>
+        <v>0.072918</v>
       </c>
       <c r="G464" s="7">
-        <v>0</v>
+        <v>0.12757300000000002</v>
       </c>
       <c r="H464" s="7">
-        <v>0</v>
+        <v>0.215202</v>
       </c>
       <c r="I464" s="7">
-        <v>0</v>
+        <v>0.34157699999999996</v>
       </c>
       <c r="J464" s="7">
-        <v>0</v>
+        <v>2.055876</v>
       </c>
       <c r="K464" s="7">
-        <v>0</v>
+        <v>6.066749</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
@@ -21934,19 +21934,19 @@
         <v>6</v>
       </c>
       <c r="E473" s="7">
-        <v>0.0056240000000000005</v>
+        <v>0.005644</v>
       </c>
       <c r="F473" s="7">
-        <v>0.09845599999999999</v>
+        <v>0.098477</v>
       </c>
       <c r="G473" s="7">
-        <v>0.08560600000000002</v>
+        <v>0.085627</v>
       </c>
       <c r="H473" s="7">
-        <v>0.117501</v>
+        <v>0.117523</v>
       </c>
       <c r="I473" s="7">
-        <v>0.610158</v>
+        <v>0.61019</v>
       </c>
       <c r="J473" s="7"/>
       <c r="K473" s="7"/>
@@ -22332,22 +22332,22 @@
         <v>3</v>
       </c>
       <c r="E485" s="7">
-        <v>0.035737</v>
+        <v>0.038194</v>
       </c>
       <c r="F485" s="7">
-        <v>0.141984</v>
+        <v>0.14469300000000002</v>
       </c>
       <c r="G485" s="7">
-        <v>0.253717</v>
+        <v>0.256691</v>
       </c>
       <c r="H485" s="7">
-        <v>0.363949</v>
+        <v>0.367185</v>
       </c>
       <c r="I485" s="7">
-        <v>0.606436</v>
+        <v>0.610247</v>
       </c>
       <c r="J485" s="7">
-        <v>2.369746</v>
+        <v>2.37774</v>
       </c>
       <c r="K485" s="7"/>
     </row>
@@ -22623,22 +22623,22 @@
         <v>5</v>
       </c>
       <c r="E494" s="7">
-        <v>0.046079</v>
+        <v>0.055204</v>
       </c>
       <c r="F494" s="7">
-        <v>0.070643</v>
+        <v>0.079982</v>
       </c>
       <c r="G494" s="7">
-        <v>0.35031799999999996</v>
+        <v>0.362097</v>
       </c>
       <c r="H494" s="7">
-        <v>0.41985100000000003</v>
+        <v>0.43223599999999995</v>
       </c>
       <c r="I494" s="7">
-        <v>0.575952</v>
+        <v>0.589699</v>
       </c>
       <c r="J494" s="7">
-        <v>2.365434</v>
+        <v>2.3947909999999997</v>
       </c>
       <c r="K494" s="7"/>
     </row>
@@ -24276,19 +24276,19 @@
         <v>1</v>
       </c>
       <c r="E547" s="7">
-        <v>0.03421</v>
+        <v>0.033878</v>
       </c>
       <c r="F547" s="7">
-        <v>0.100947</v>
+        <v>0.100594</v>
       </c>
       <c r="G547" s="7">
-        <v>0.212769</v>
+        <v>0.21237999999999999</v>
       </c>
       <c r="H547" s="7">
-        <v>0.28858</v>
+        <v>0.288167</v>
       </c>
       <c r="I547" s="7">
-        <v>0.479097</v>
+        <v>0.47862299999999997</v>
       </c>
       <c r="J547" s="7"/>
       <c r="K547" s="7"/>
@@ -25901,22 +25901,22 @@
         <v>6</v>
       </c>
       <c r="E598" s="7">
-        <v>0.056714</v>
+        <v>0.060659</v>
       </c>
       <c r="F598" s="7">
-        <v>0.049989</v>
+        <v>0.053908</v>
       </c>
       <c r="G598" s="7">
-        <v>0.14479</v>
+        <v>0.149063</v>
       </c>
       <c r="H598" s="7">
-        <v>0.31678999999999996</v>
+        <v>0.32170499999999996</v>
       </c>
       <c r="I598" s="7">
-        <v>0.426872</v>
+        <v>0.43219700000000005</v>
       </c>
       <c r="J598" s="7">
-        <v>1.883337</v>
+        <v>1.894099</v>
       </c>
       <c r="K598" s="7"/>
     </row>
@@ -25934,25 +25934,25 @@
         <v>7</v>
       </c>
       <c r="E599" s="7">
-        <v>0.166149</v>
+        <v>0.163353</v>
       </c>
       <c r="F599" s="7">
-        <v>-0.05319</v>
+        <v>-0.05546</v>
       </c>
       <c r="G599" s="7">
-        <v>-0.180003</v>
+        <v>-0.181969</v>
       </c>
       <c r="H599" s="7">
-        <v>0.013143</v>
+        <v>0.010714</v>
       </c>
       <c r="I599" s="7">
-        <v>0.9307850000000001</v>
+        <v>0.926156</v>
       </c>
       <c r="J599" s="7">
-        <v>3.68986</v>
+        <v>3.678617</v>
       </c>
       <c r="K599" s="7">
-        <v>12.567578000000001</v>
+        <v>12.535052</v>
       </c>
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.25">
@@ -25969,25 +25969,25 @@
         <v>6</v>
       </c>
       <c r="E600" s="7">
-        <v>-0.064097</v>
+        <v>-0.056476</v>
       </c>
       <c r="F600" s="7">
-        <v>-0.053793</v>
+        <v>-0.046086999999999996</v>
       </c>
       <c r="G600" s="7">
-        <v>-0.080465</v>
+        <v>-0.072977</v>
       </c>
       <c r="H600" s="7">
-        <v>-0.11052300000000001</v>
+        <v>-0.103279</v>
       </c>
       <c r="I600" s="7">
-        <v>-0.117547</v>
+        <v>-0.11036099999999999</v>
       </c>
       <c r="J600" s="7">
-        <v>0.345955</v>
+        <v>0.356916</v>
       </c>
       <c r="K600" s="7">
-        <v>2.942524</v>
+        <v>2.9746300000000003</v>
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.25">
@@ -26700,22 +26700,22 @@
         <v>5</v>
       </c>
       <c r="E623" s="7">
-        <v>0.032718</v>
+        <v>0.031636000000000004</v>
       </c>
       <c r="F623" s="7">
-        <v>0.037117</v>
+        <v>0.036031</v>
       </c>
       <c r="G623" s="7">
-        <v>0.083263</v>
+        <v>0.082129</v>
       </c>
       <c r="H623" s="7">
-        <v>0.18644100000000002</v>
+        <v>0.185199</v>
       </c>
       <c r="I623" s="7">
-        <v>0.263397</v>
+        <v>0.262074</v>
       </c>
       <c r="J623" s="7">
-        <v>1.139322</v>
+        <v>1.1370820000000001</v>
       </c>
       <c r="K623" s="7"/>
     </row>
@@ -26923,16 +26923,16 @@
         <v>5</v>
       </c>
       <c r="E630" s="7">
-        <v>0</v>
+        <v>0.036094</v>
       </c>
       <c r="F630" s="7">
-        <v>0</v>
+        <v>0.10387600000000001</v>
       </c>
       <c r="G630" s="7">
-        <v>0</v>
+        <v>0.22347</v>
       </c>
       <c r="H630" s="7">
-        <v>0</v>
+        <v>0.316806</v>
       </c>
       <c r="I630" s="7"/>
       <c r="J630" s="7"/>
@@ -27018,19 +27018,19 @@
         <v>5</v>
       </c>
       <c r="E633" s="7">
-        <v>0</v>
+        <v>0.033831</v>
       </c>
       <c r="F633" s="7">
-        <v>0</v>
+        <v>0.089209</v>
       </c>
       <c r="G633" s="7">
-        <v>0</v>
+        <v>0.17771499999999998</v>
       </c>
       <c r="H633" s="7">
-        <v>0</v>
+        <v>0.037072</v>
       </c>
       <c r="I633" s="7">
-        <v>0</v>
+        <v>0.109055</v>
       </c>
       <c r="J633" s="7"/>
       <c r="K633" s="7"/>
@@ -27049,22 +27049,22 @@
         <v>3</v>
       </c>
       <c r="E634" s="7">
-        <v>0</v>
+        <v>0.015667</v>
       </c>
       <c r="F634" s="7">
-        <v>0</v>
+        <v>0.042405</v>
       </c>
       <c r="G634" s="7">
-        <v>0</v>
+        <v>0.125699</v>
       </c>
       <c r="H634" s="7">
-        <v>0</v>
+        <v>0.171983</v>
       </c>
       <c r="I634" s="7">
-        <v>0</v>
+        <v>0.3483</v>
       </c>
       <c r="J634" s="7">
-        <v>0</v>
+        <v>1.779762</v>
       </c>
       <c r="K634" s="7"/>
     </row>
@@ -28018,22 +28018,22 @@
         <v>6</v>
       </c>
       <c r="E665" s="7">
-        <v>0.133444</v>
+        <v>0.13339600000000001</v>
       </c>
       <c r="F665" s="7">
-        <v>-0.157529</v>
+        <v>-0.15756399999999998</v>
       </c>
       <c r="G665" s="7">
-        <v>-0.092516</v>
+        <v>-0.092554</v>
       </c>
       <c r="H665" s="7">
-        <v>-0.015700000000000002</v>
+        <v>-0.015741</v>
       </c>
       <c r="I665" s="7">
-        <v>0.161869</v>
+        <v>0.16182</v>
       </c>
       <c r="J665" s="7">
-        <v>1.431209</v>
+        <v>1.4311070000000001</v>
       </c>
       <c r="K665" s="7"/>
     </row>
@@ -28309,25 +28309,25 @@
       </c>
       <c r="D674" s="6"/>
       <c r="E674" s="7">
-        <v>0.039644</v>
+        <v>0.039628000000000003</v>
       </c>
       <c r="F674" s="7">
-        <v>0.08823700000000001</v>
+        <v>0.08821999999999999</v>
       </c>
       <c r="G674" s="7">
-        <v>0.149875</v>
+        <v>0.149857</v>
       </c>
       <c r="H674" s="7">
-        <v>0.22007200000000002</v>
+        <v>0.220052</v>
       </c>
       <c r="I674" s="7">
-        <v>0.371348</v>
+        <v>0.371326</v>
       </c>
       <c r="J674" s="7">
-        <v>1.41256</v>
+        <v>1.4125210000000001</v>
       </c>
       <c r="K674" s="7">
-        <v>4.909485</v>
+        <v>4.909391</v>
       </c>
     </row>
     <row r="675" spans="1:11" x14ac:dyDescent="0.25">
@@ -28435,25 +28435,25 @@
         <v>5</v>
       </c>
       <c r="E678" s="7">
-        <v>0</v>
+        <v>0.034372</v>
       </c>
       <c r="F678" s="7">
-        <v>0</v>
+        <v>0.020362</v>
       </c>
       <c r="G678" s="7">
-        <v>0</v>
+        <v>-0.003588</v>
       </c>
       <c r="H678" s="7">
-        <v>0</v>
+        <v>0.15104499999999998</v>
       </c>
       <c r="I678" s="7">
-        <v>0</v>
+        <v>0.253313</v>
       </c>
       <c r="J678" s="7">
-        <v>0</v>
+        <v>1.6324180000000001</v>
       </c>
       <c r="K678" s="7">
-        <v>0</v>
+        <v>6.571708</v>
       </c>
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.25">
@@ -28468,22 +28468,22 @@
       </c>
       <c r="D679" s="6"/>
       <c r="E679" s="7">
-        <v>0.052516999999999994</v>
+        <v>0.052409</v>
       </c>
       <c r="F679" s="7">
-        <v>0.064853</v>
+        <v>0.06474300000000001</v>
       </c>
       <c r="G679" s="7">
-        <v>0.10850199999999999</v>
+        <v>0.10838800000000001</v>
       </c>
       <c r="H679" s="7">
-        <v>0.21753699999999998</v>
+        <v>0.217412</v>
       </c>
       <c r="I679" s="7">
-        <v>0.351112</v>
+        <v>0.350973</v>
       </c>
       <c r="J679" s="7">
-        <v>1.480105</v>
+        <v>1.4798490000000002</v>
       </c>
       <c r="K679" s="7"/>
     </row>
@@ -28501,25 +28501,25 @@
         <v>4</v>
       </c>
       <c r="E680" s="7">
-        <v>0.055518</v>
+        <v>0.055482</v>
       </c>
       <c r="F680" s="7">
-        <v>0.071523</v>
+        <v>0.071486</v>
       </c>
       <c r="G680" s="7">
-        <v>0.08904999999999999</v>
+        <v>0.089012</v>
       </c>
       <c r="H680" s="7">
-        <v>0.203796</v>
+        <v>0.203755</v>
       </c>
       <c r="I680" s="7">
-        <v>0.36538400000000004</v>
+        <v>0.365337</v>
       </c>
       <c r="J680" s="7">
-        <v>1.77115</v>
+        <v>1.7710540000000001</v>
       </c>
       <c r="K680" s="7">
-        <v>6.517132</v>
+        <v>6.516873</v>
       </c>
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.25">
@@ -28639,22 +28639,22 @@
         <v>6</v>
       </c>
       <c r="E684" s="7">
-        <v>0.14699500000000001</v>
+        <v>0.141947</v>
       </c>
       <c r="F684" s="7">
-        <v>0.065485</v>
+        <v>0.060796</v>
       </c>
       <c r="G684" s="7">
-        <v>0.026277</v>
+        <v>0.021761</v>
       </c>
       <c r="H684" s="7">
-        <v>0.196944</v>
+        <v>0.191676</v>
       </c>
       <c r="I684" s="7">
-        <v>0.214709</v>
+        <v>0.209363</v>
       </c>
       <c r="J684" s="7">
-        <v>0.88558</v>
+        <v>0.877282</v>
       </c>
       <c r="K684" s="7"/>
     </row>
@@ -28672,22 +28672,22 @@
         <v>3</v>
       </c>
       <c r="E685" s="7">
-        <v>0.048082</v>
+        <v>0.048692</v>
       </c>
       <c r="F685" s="7">
-        <v>0.081421</v>
+        <v>0.08205</v>
       </c>
       <c r="G685" s="7">
-        <v>0.13814099999999999</v>
+        <v>0.138804</v>
       </c>
       <c r="H685" s="7">
-        <v>0.251046</v>
+        <v>0.251774</v>
       </c>
       <c r="I685" s="7">
-        <v>0.447888</v>
+        <v>0.448731</v>
       </c>
       <c r="J685" s="7">
-        <v>2.2704400000000002</v>
+        <v>2.272343</v>
       </c>
       <c r="K685" s="7"/>
     </row>
@@ -28771,25 +28771,25 @@
         <v>6</v>
       </c>
       <c r="E688" s="7">
-        <v>0.069315</v>
+        <v>0.069825</v>
       </c>
       <c r="F688" s="7">
-        <v>0.068365</v>
+        <v>0.068874</v>
       </c>
       <c r="G688" s="7">
-        <v>0.39420099999999997</v>
+        <v>0.39486600000000005</v>
       </c>
       <c r="H688" s="7">
-        <v>0.423684</v>
+        <v>0.424362</v>
       </c>
       <c r="I688" s="7">
-        <v>0.5909</v>
+        <v>0.591658</v>
       </c>
       <c r="J688" s="7">
-        <v>2.916877</v>
+        <v>2.918744</v>
       </c>
       <c r="K688" s="7">
-        <v>10.720284</v>
+        <v>10.725871</v>
       </c>
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.25">
@@ -28975,22 +28975,22 @@
         <v>2</v>
       </c>
       <c r="E694" s="7">
-        <v>0.033102</v>
+        <v>0.034281</v>
       </c>
       <c r="F694" s="7">
-        <v>0.099467</v>
+        <v>0.100722</v>
       </c>
       <c r="G694" s="7">
-        <v>0.216067</v>
+        <v>0.217455</v>
       </c>
       <c r="H694" s="7">
-        <v>0.293288</v>
+        <v>0.294765</v>
       </c>
       <c r="I694" s="7">
-        <v>0.48536</v>
+        <v>0.487056</v>
       </c>
       <c r="J694" s="7">
-        <v>2.516186</v>
+        <v>2.5202</v>
       </c>
       <c r="K694" s="7"/>
     </row>
@@ -29155,22 +29155,22 @@
       </c>
       <c r="D700" s="6"/>
       <c r="E700" s="7">
-        <v>0.020109</v>
+        <v>0.02013</v>
       </c>
       <c r="F700" s="7">
-        <v>0.062871</v>
+        <v>0.062892</v>
       </c>
       <c r="G700" s="7">
-        <v>0.116623</v>
+        <v>0.116645</v>
       </c>
       <c r="H700" s="7">
-        <v>0.147873</v>
+        <v>0.147895</v>
       </c>
       <c r="I700" s="7">
-        <v>0.216392</v>
+        <v>0.216417</v>
       </c>
       <c r="J700" s="7">
-        <v>1.031876</v>
+        <v>1.031917</v>
       </c>
       <c r="K700" s="7"/>
     </row>
@@ -29397,16 +29397,16 @@
         <v>0.053970000000000004</v>
       </c>
       <c r="F707" s="7">
-        <v>0.114522</v>
+        <v>0.11452299999999999</v>
       </c>
       <c r="G707" s="7">
-        <v>0.13037100000000001</v>
+        <v>0.13037200000000002</v>
       </c>
       <c r="H707" s="7">
-        <v>0.35063099999999997</v>
+        <v>0.350632</v>
       </c>
       <c r="I707" s="7">
-        <v>0.294548</v>
+        <v>0.294549</v>
       </c>
       <c r="J707" s="7"/>
       <c r="K707" s="7"/>
@@ -29495,22 +29495,22 @@
         <v>6</v>
       </c>
       <c r="E710" s="7">
-        <v>0.13439199999999998</v>
+        <v>0.134223</v>
       </c>
       <c r="F710" s="7">
-        <v>0.001394</v>
+        <v>0.0012439999999999999</v>
       </c>
       <c r="G710" s="7">
-        <v>-0.116041</v>
+        <v>-0.116174</v>
       </c>
       <c r="H710" s="7">
-        <v>0.07212500000000001</v>
+        <v>0.071965</v>
       </c>
       <c r="I710" s="7">
-        <v>0.719733</v>
+        <v>0.7194759999999999</v>
       </c>
       <c r="J710" s="7">
-        <v>2.861151</v>
+        <v>2.8605739999999997</v>
       </c>
       <c r="K710" s="7"/>
     </row>
@@ -29625,22 +29625,22 @@
         <v>6</v>
       </c>
       <c r="E714" s="7">
-        <v>0.075464</v>
+        <v>0.075637</v>
       </c>
       <c r="F714" s="7">
-        <v>0.054464</v>
+        <v>0.054634</v>
       </c>
       <c r="G714" s="7">
-        <v>0.196987</v>
+        <v>0.19718</v>
       </c>
       <c r="H714" s="7">
-        <v>0.33878100000000005</v>
+        <v>0.33899700000000005</v>
       </c>
       <c r="I714" s="7">
-        <v>0.610472</v>
+        <v>0.610732</v>
       </c>
       <c r="J714" s="7">
-        <v>1.6041309999999998</v>
+        <v>1.6045509999999998</v>
       </c>
       <c r="K714" s="7"/>
     </row>
@@ -29836,19 +29836,19 @@
         <v>4</v>
       </c>
       <c r="E721" s="7">
-        <v>0.070022</v>
+        <v>0.074306</v>
       </c>
       <c r="F721" s="7">
-        <v>0.137652</v>
+        <v>0.142206</v>
       </c>
       <c r="G721" s="7">
-        <v>0.266953</v>
+        <v>0.272026</v>
       </c>
       <c r="H721" s="7">
-        <v>0.46224600000000005</v>
+        <v>0.4681</v>
       </c>
       <c r="I721" s="7">
-        <v>0.620602</v>
+        <v>0.62709</v>
       </c>
       <c r="J721" s="7"/>
       <c r="K721" s="7"/>
@@ -30096,19 +30096,19 @@
         <v>4</v>
       </c>
       <c r="E729" s="7">
-        <v>0.038775</v>
+        <v>0.038046</v>
       </c>
       <c r="F729" s="7">
-        <v>0.059642</v>
+        <v>0.058898</v>
       </c>
       <c r="G729" s="7">
-        <v>0.036593</v>
+        <v>0.035865</v>
       </c>
       <c r="H729" s="7">
-        <v>0.20131900000000003</v>
+        <v>0.200476</v>
       </c>
       <c r="I729" s="7">
-        <v>0.325568</v>
+        <v>0.324638</v>
       </c>
       <c r="J729" s="7"/>
       <c r="K729" s="7"/>
@@ -30127,22 +30127,22 @@
         <v>4</v>
       </c>
       <c r="E730" s="7">
-        <v>0.045031</v>
+        <v>0.046597</v>
       </c>
       <c r="F730" s="7">
-        <v>0.056691000000000005</v>
+        <v>0.058274</v>
       </c>
       <c r="G730" s="7">
-        <v>0.152113</v>
+        <v>0.153839</v>
       </c>
       <c r="H730" s="7">
-        <v>0.271115</v>
+        <v>0.273019</v>
       </c>
       <c r="I730" s="7">
-        <v>0.479684</v>
+        <v>0.4819</v>
       </c>
       <c r="J730" s="7">
-        <v>2.038615</v>
+        <v>2.043166</v>
       </c>
       <c r="K730" s="7"/>
     </row>
@@ -30346,22 +30346,22 @@
         <v>6</v>
       </c>
       <c r="E737" s="7">
-        <v>0.07493</v>
+        <v>0.075895</v>
       </c>
       <c r="F737" s="7">
-        <v>-0.058282</v>
+        <v>-0.057436</v>
       </c>
       <c r="G737" s="7">
-        <v>0.073022</v>
+        <v>0.073986</v>
       </c>
       <c r="H737" s="7">
-        <v>0.28644200000000003</v>
+        <v>0.287597</v>
       </c>
       <c r="I737" s="7">
-        <v>0.7553740000000001</v>
+        <v>0.7569499999999999</v>
       </c>
       <c r="J737" s="7">
-        <v>2.177797</v>
+        <v>2.18065</v>
       </c>
       <c r="K737" s="7"/>
     </row>
@@ -31568,19 +31568,19 @@
         <v>2</v>
       </c>
       <c r="E777" s="7">
-        <v>0</v>
+        <v>0.041705</v>
       </c>
       <c r="F777" s="7">
-        <v>0</v>
+        <v>0.12105600000000001</v>
       </c>
       <c r="G777" s="7">
-        <v>0</v>
+        <v>0.258703</v>
       </c>
       <c r="H777" s="7">
-        <v>0</v>
+        <v>0.35713500000000004</v>
       </c>
       <c r="I777" s="7">
-        <v>0</v>
+        <v>0.598134</v>
       </c>
       <c r="J777" s="7"/>
       <c r="K777" s="7"/>
@@ -31781,19 +31781,19 @@
         <v>6</v>
       </c>
       <c r="E784" s="7">
-        <v>0.022993</v>
+        <v>0.022994</v>
       </c>
       <c r="F784" s="7">
-        <v>0.213325</v>
+        <v>0.213327</v>
       </c>
       <c r="G784" s="7">
-        <v>0.385398</v>
+        <v>0.38539999999999996</v>
       </c>
       <c r="H784" s="7">
-        <v>0.626094</v>
+        <v>0.626096</v>
       </c>
       <c r="I784" s="7">
-        <v>0.670226</v>
+        <v>0.670228</v>
       </c>
       <c r="J784" s="7"/>
       <c r="K784" s="7"/>
@@ -32576,7 +32576,7 @@
         <v>6</v>
       </c>
       <c r="E809" s="7">
-        <v>0.074616</v>
+        <v>0.074463</v>
       </c>
       <c r="F809" s="7"/>
       <c r="G809" s="7"/>
@@ -33293,22 +33293,22 @@
       </c>
       <c r="D832" s="6"/>
       <c r="E832" s="7">
-        <v>0.019015</v>
+        <v>0.019023</v>
       </c>
       <c r="F832" s="7">
-        <v>0.056250999999999995</v>
+        <v>0.056258</v>
       </c>
       <c r="G832" s="7">
-        <v>0.085425</v>
+        <v>0.08543300000000001</v>
       </c>
       <c r="H832" s="7">
-        <v>0.121677</v>
+        <v>0.121686</v>
       </c>
       <c r="I832" s="7">
-        <v>0.21134799999999998</v>
+        <v>0.211357</v>
       </c>
       <c r="J832" s="7">
-        <v>1.201785</v>
+        <v>1.201801</v>
       </c>
       <c r="K832" s="7"/>
     </row>
@@ -33644,19 +33644,19 @@
         <v>5</v>
       </c>
       <c r="E843" s="7">
-        <v>0.084593</v>
+        <v>0.084908</v>
       </c>
       <c r="F843" s="7">
-        <v>0.056513</v>
+        <v>0.05682</v>
       </c>
       <c r="G843" s="7">
-        <v>0.32654200000000005</v>
+        <v>0.326927</v>
       </c>
       <c r="H843" s="7">
-        <v>0.365002</v>
+        <v>0.365398</v>
       </c>
       <c r="I843" s="7">
-        <v>0.5203479999999999</v>
+        <v>0.52079</v>
       </c>
       <c r="J843" s="7"/>
       <c r="K843" s="7"/>
@@ -33739,19 +33739,19 @@
         <v>6</v>
       </c>
       <c r="E846" s="7">
-        <v>0</v>
+        <v>-0.03283</v>
       </c>
       <c r="F846" s="7">
-        <v>0</v>
+        <v>0.010311999999999998</v>
       </c>
       <c r="G846" s="7">
-        <v>0</v>
+        <v>0.023968</v>
       </c>
       <c r="H846" s="7">
-        <v>0</v>
+        <v>0.225883</v>
       </c>
       <c r="I846" s="7">
-        <v>0</v>
+        <v>0.415089</v>
       </c>
       <c r="J846" s="7"/>
       <c r="K846" s="7"/>
@@ -33770,7 +33770,7 @@
         <v>5</v>
       </c>
       <c r="E847" s="7">
-        <v>0</v>
+        <v>0.04217</v>
       </c>
       <c r="F847" s="7"/>
       <c r="G847" s="7"/>
@@ -33793,19 +33793,19 @@
         <v>5</v>
       </c>
       <c r="E848" s="7">
-        <v>0.045979</v>
+        <v>0.047232</v>
       </c>
       <c r="F848" s="7">
-        <v>0.065726</v>
+        <v>0.06700400000000001</v>
       </c>
       <c r="G848" s="7">
-        <v>0.139988</v>
+        <v>0.141354</v>
       </c>
       <c r="H848" s="7">
-        <v>0.288682</v>
+        <v>0.290227</v>
       </c>
       <c r="I848" s="7">
-        <v>0.416115</v>
+        <v>0.41781199999999996</v>
       </c>
       <c r="J848" s="7"/>
       <c r="K848" s="7"/>
@@ -33845,19 +33845,19 @@
         <v>5</v>
       </c>
       <c r="E850" s="7">
-        <v>0</v>
+        <v>0.104818</v>
       </c>
       <c r="F850" s="7">
-        <v>0</v>
+        <v>0.202574</v>
       </c>
       <c r="G850" s="7">
-        <v>0</v>
+        <v>0.529362</v>
       </c>
       <c r="H850" s="7">
-        <v>0</v>
+        <v>0.49424500000000005</v>
       </c>
       <c r="I850" s="7">
-        <v>0</v>
+        <v>0.560624</v>
       </c>
       <c r="J850" s="7"/>
       <c r="K850" s="7"/>
@@ -33932,16 +33932,16 @@
         <v>6</v>
       </c>
       <c r="E853" s="7">
-        <v>0</v>
+        <v>0.031478</v>
       </c>
       <c r="F853" s="7">
-        <v>0</v>
+        <v>0.113748</v>
       </c>
       <c r="G853" s="7">
-        <v>0</v>
+        <v>0.063029</v>
       </c>
       <c r="H853" s="7">
-        <v>0</v>
+        <v>0.474338</v>
       </c>
       <c r="I853" s="7"/>
       <c r="J853" s="7"/>
@@ -34081,19 +34081,19 @@
         <v>3</v>
       </c>
       <c r="E858" s="7">
-        <v>0.12635</v>
+        <v>0.126255</v>
       </c>
       <c r="F858" s="7">
-        <v>0.24585200000000001</v>
+        <v>0.245747</v>
       </c>
       <c r="G858" s="7">
-        <v>0.286773</v>
+        <v>0.286665</v>
       </c>
       <c r="H858" s="7">
-        <v>0.386627</v>
+        <v>0.38651</v>
       </c>
       <c r="I858" s="7">
-        <v>0.48322699999999996</v>
+        <v>0.483103</v>
       </c>
       <c r="J858" s="7"/>
       <c r="K858" s="7"/>
@@ -34242,19 +34242,19 @@
         <v>4</v>
       </c>
       <c r="E863" s="7">
-        <v>0.067561</v>
+        <v>0.071341</v>
       </c>
       <c r="F863" s="7">
-        <v>0.079747</v>
+        <v>0.08356999999999999</v>
       </c>
       <c r="G863" s="7">
-        <v>0.157059</v>
+        <v>0.16115500000000002</v>
       </c>
       <c r="H863" s="7">
-        <v>0.28629899999999997</v>
+        <v>0.290852</v>
       </c>
       <c r="I863" s="7">
-        <v>0.546239</v>
+        <v>0.551713</v>
       </c>
       <c r="J863" s="7"/>
       <c r="K863" s="7"/>
@@ -34399,19 +34399,19 @@
         <v>6</v>
       </c>
       <c r="E868" s="7">
-        <v>0.078429</v>
+        <v>0.08237</v>
       </c>
       <c r="F868" s="7">
-        <v>0.039418</v>
+        <v>0.043217</v>
       </c>
       <c r="G868" s="7">
-        <v>0.140027</v>
+        <v>0.144194</v>
       </c>
       <c r="H868" s="7">
-        <v>0.26820499999999997</v>
+        <v>0.272841</v>
       </c>
       <c r="I868" s="7">
-        <v>0.063558</v>
+        <v>0.067445</v>
       </c>
       <c r="J868" s="7"/>
       <c r="K868" s="7"/>
@@ -34906,22 +34906,22 @@
         <v>3</v>
       </c>
       <c r="E883" s="7">
-        <v>0</v>
+        <v>0.036535000000000005</v>
       </c>
       <c r="F883" s="7">
-        <v>0</v>
+        <v>0.092609</v>
       </c>
       <c r="G883" s="7">
-        <v>0</v>
+        <v>0.19220800000000002</v>
       </c>
       <c r="H883" s="7">
-        <v>0</v>
+        <v>0.276211</v>
       </c>
       <c r="I883" s="7">
-        <v>0</v>
+        <v>0.46041699999999997</v>
       </c>
       <c r="J883" s="7">
-        <v>0</v>
+        <v>2.382005</v>
       </c>
       <c r="K883" s="7"/>
     </row>
@@ -35042,19 +35042,19 @@
         <v>6</v>
       </c>
       <c r="E887" s="7">
-        <v>0.078914</v>
+        <v>0.08025600000000001</v>
       </c>
       <c r="F887" s="7">
-        <v>0.090184</v>
+        <v>0.09154</v>
       </c>
       <c r="G887" s="7">
-        <v>0.427368</v>
+        <v>0.429143</v>
       </c>
       <c r="H887" s="7">
-        <v>0.48686300000000005</v>
+        <v>0.48871299999999995</v>
       </c>
       <c r="I887" s="7">
-        <v>0.682189</v>
+        <v>0.6842820000000001</v>
       </c>
       <c r="J887" s="7"/>
       <c r="K887" s="7"/>
@@ -35609,25 +35609,25 @@
         <v>6</v>
       </c>
       <c r="E904" s="7">
-        <v>0</v>
+        <v>0.036272</v>
       </c>
       <c r="F904" s="7">
-        <v>0</v>
+        <v>0.023032</v>
       </c>
       <c r="G904" s="7">
-        <v>0</v>
+        <v>0.08539</v>
       </c>
       <c r="H904" s="7">
-        <v>0</v>
+        <v>0.242029</v>
       </c>
       <c r="I904" s="7">
-        <v>0</v>
+        <v>0.295379</v>
       </c>
       <c r="J904" s="7">
-        <v>0</v>
+        <v>1.256711</v>
       </c>
       <c r="K904" s="7">
-        <v>0</v>
+        <v>4.465783</v>
       </c>
     </row>
     <row r="905" spans="1:11" x14ac:dyDescent="0.25">
@@ -35644,22 +35644,22 @@
         <v>4</v>
       </c>
       <c r="E905" s="7">
-        <v>0</v>
+        <v>0.066418</v>
       </c>
       <c r="F905" s="7">
-        <v>0</v>
+        <v>0.066807</v>
       </c>
       <c r="G905" s="7">
-        <v>0</v>
+        <v>0.08675000000000001</v>
       </c>
       <c r="H905" s="7">
-        <v>0</v>
+        <v>0.24081399999999997</v>
       </c>
       <c r="I905" s="7">
-        <v>0</v>
+        <v>0.416424</v>
       </c>
       <c r="J905" s="7">
-        <v>0</v>
+        <v>1.801276</v>
       </c>
       <c r="K905" s="7"/>
     </row>
@@ -35675,22 +35675,22 @@
       </c>
       <c r="D906" s="6"/>
       <c r="E906" s="7">
-        <v>0.042436</v>
+        <v>0.042434</v>
       </c>
       <c r="F906" s="7">
-        <v>0.073054</v>
+        <v>0.073052</v>
       </c>
       <c r="G906" s="7">
-        <v>0.090641</v>
+        <v>0.09063800000000001</v>
       </c>
       <c r="H906" s="7">
-        <v>0.132367</v>
+        <v>0.13236499999999998</v>
       </c>
       <c r="I906" s="7">
-        <v>0.23102799999999998</v>
+        <v>0.23102599999999998</v>
       </c>
       <c r="J906" s="7">
-        <v>1.35083</v>
+        <v>1.3508250000000002</v>
       </c>
       <c r="K906" s="7"/>
     </row>
@@ -35888,10 +35888,10 @@
         <v>6.688767</v>
       </c>
       <c r="J912" s="7">
-        <v>639.601851</v>
+        <v>639.6018250000001</v>
       </c>
       <c r="K912" s="7">
-        <v>6558.524961</v>
+        <v>6558.5246959999995</v>
       </c>
     </row>
     <row r="913" spans="1:11" x14ac:dyDescent="0.25">
@@ -36044,19 +36044,19 @@
         <v>2</v>
       </c>
       <c r="E917" s="7">
-        <v>0.034775</v>
+        <v>0.036063</v>
       </c>
       <c r="F917" s="7">
-        <v>0.075854</v>
+        <v>0.077193</v>
       </c>
       <c r="G917" s="7">
-        <v>0.162945</v>
+        <v>0.16439299999999998</v>
       </c>
       <c r="H917" s="7">
-        <v>0.259548</v>
+        <v>0.261115</v>
       </c>
       <c r="I917" s="7">
-        <v>0.427145</v>
+        <v>0.428921</v>
       </c>
       <c r="J917" s="7"/>
       <c r="K917" s="7"/>
@@ -36203,25 +36203,25 @@
         <v>6</v>
       </c>
       <c r="E922" s="7">
-        <v>0</v>
+        <v>0.126486</v>
       </c>
       <c r="F922" s="7">
-        <v>0</v>
+        <v>0.002153</v>
       </c>
       <c r="G922" s="7">
-        <v>0</v>
+        <v>-0.107837</v>
       </c>
       <c r="H922" s="7">
-        <v>0</v>
+        <v>0.08657400000000001</v>
       </c>
       <c r="I922" s="7">
-        <v>0</v>
+        <v>0.488915</v>
       </c>
       <c r="J922" s="7">
-        <v>0</v>
+        <v>1.924904</v>
       </c>
       <c r="K922" s="7">
-        <v>0</v>
+        <v>6.4736009999999995</v>
       </c>
     </row>
     <row r="923" spans="1:11" x14ac:dyDescent="0.25">
@@ -36306,25 +36306,25 @@
         <v>6</v>
       </c>
       <c r="E925" s="7">
-        <v>0</v>
+        <v>0.026314</v>
       </c>
       <c r="F925" s="7">
-        <v>0</v>
+        <v>0.071299</v>
       </c>
       <c r="G925" s="7">
-        <v>0</v>
+        <v>0.10462099999999999</v>
       </c>
       <c r="H925" s="7">
-        <v>0</v>
+        <v>0.127232</v>
       </c>
       <c r="I925" s="7">
-        <v>0</v>
+        <v>0.214539</v>
       </c>
       <c r="J925" s="7">
-        <v>0</v>
+        <v>1.189091</v>
       </c>
       <c r="K925" s="7">
-        <v>0</v>
+        <v>5.910915</v>
       </c>
     </row>
     <row r="926" spans="1:11" x14ac:dyDescent="0.25">
@@ -36339,25 +36339,25 @@
       </c>
       <c r="D926" s="6"/>
       <c r="E926" s="7">
-        <v>0</v>
+        <v>0.054024</v>
       </c>
       <c r="F926" s="7">
-        <v>0</v>
+        <v>0.113719</v>
       </c>
       <c r="G926" s="7">
-        <v>0</v>
+        <v>0.218021</v>
       </c>
       <c r="H926" s="7">
-        <v>0</v>
+        <v>0.311266</v>
       </c>
       <c r="I926" s="7">
-        <v>0</v>
+        <v>0.6595099999999999</v>
       </c>
       <c r="J926" s="7">
-        <v>0</v>
+        <v>2.879703</v>
       </c>
       <c r="K926" s="7">
-        <v>0</v>
+        <v>20.085924</v>
       </c>
     </row>
     <row r="927" spans="1:11" x14ac:dyDescent="0.25">
@@ -36673,25 +36673,25 @@
         <v>6</v>
       </c>
       <c r="E936" s="7">
-        <v>0.143626</v>
+        <v>0.143668</v>
       </c>
       <c r="F936" s="7">
-        <v>0.055729</v>
+        <v>0.055768000000000005</v>
       </c>
       <c r="G936" s="7">
-        <v>-0.044169</v>
+        <v>-0.044134</v>
       </c>
       <c r="H936" s="7">
-        <v>0.141658</v>
+        <v>0.1417</v>
       </c>
       <c r="I936" s="7">
-        <v>0.538988</v>
+        <v>0.539045</v>
       </c>
       <c r="J936" s="7">
-        <v>3.122591</v>
+        <v>3.122744</v>
       </c>
       <c r="K936" s="7">
-        <v>12.634777</v>
+        <v>12.635283</v>
       </c>
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.25">
@@ -36737,22 +36737,22 @@
         <v>5</v>
       </c>
       <c r="E938" s="7">
-        <v>0.048514999999999996</v>
+        <v>0.050695</v>
       </c>
       <c r="F938" s="7">
-        <v>0.150867</v>
+        <v>0.15326</v>
       </c>
       <c r="G938" s="7">
-        <v>0.220775</v>
+        <v>0.22331399999999998</v>
       </c>
       <c r="H938" s="7">
-        <v>0.318092</v>
+        <v>0.32083300000000003</v>
       </c>
       <c r="I938" s="7">
-        <v>0.542903</v>
+        <v>0.546111</v>
       </c>
       <c r="J938" s="7">
-        <v>1.868553</v>
+        <v>1.874518</v>
       </c>
       <c r="K938" s="7"/>
     </row>
@@ -37560,25 +37560,25 @@
         <v>5</v>
       </c>
       <c r="E965" s="7">
-        <v>0</v>
+        <v>0.06571500000000001</v>
       </c>
       <c r="F965" s="7">
-        <v>0</v>
+        <v>0.075683</v>
       </c>
       <c r="G965" s="7">
-        <v>0</v>
+        <v>0.092654</v>
       </c>
       <c r="H965" s="7">
-        <v>0</v>
+        <v>0.197711</v>
       </c>
       <c r="I965" s="7">
-        <v>0</v>
+        <v>0.341019</v>
       </c>
       <c r="J965" s="7">
-        <v>0</v>
+        <v>1.493226</v>
       </c>
       <c r="K965" s="7">
-        <v>0</v>
+        <v>6.016339</v>
       </c>
     </row>
     <row r="966" spans="1:11" x14ac:dyDescent="0.25">
@@ -37655,25 +37655,25 @@
         <v>4</v>
       </c>
       <c r="E968" s="7">
-        <v>0</v>
+        <v>0.037025</v>
       </c>
       <c r="F968" s="7">
-        <v>0</v>
+        <v>0.09518</v>
       </c>
       <c r="G968" s="7">
-        <v>0</v>
+        <v>0.145159</v>
       </c>
       <c r="H968" s="7">
-        <v>0</v>
+        <v>0.228354</v>
       </c>
       <c r="I968" s="7">
-        <v>0</v>
+        <v>0.352558</v>
       </c>
       <c r="J968" s="7">
-        <v>0</v>
+        <v>1.287466</v>
       </c>
       <c r="K968" s="7">
-        <v>0</v>
+        <v>4.845014</v>
       </c>
     </row>
     <row r="969" spans="1:11" x14ac:dyDescent="0.25">
@@ -37956,22 +37956,22 @@
         <v>2</v>
       </c>
       <c r="E977" s="7">
-        <v>0.035352999999999996</v>
+        <v>0.036626</v>
       </c>
       <c r="F977" s="7">
-        <v>0.088795</v>
+        <v>0.09013299999999999</v>
       </c>
       <c r="G977" s="7">
-        <v>0.188733</v>
+        <v>0.190194</v>
       </c>
       <c r="H977" s="7">
-        <v>0.268415</v>
+        <v>0.26997499999999997</v>
       </c>
       <c r="I977" s="7">
-        <v>0.43756999999999996</v>
+        <v>0.43933700000000003</v>
       </c>
       <c r="J977" s="7">
-        <v>1.798872</v>
+        <v>1.802312</v>
       </c>
       <c r="K977" s="7"/>
     </row>
@@ -38422,19 +38422,19 @@
         <v>6</v>
       </c>
       <c r="E991" s="7">
-        <v>0</v>
+        <v>0.029688</v>
       </c>
       <c r="F991" s="7">
-        <v>0</v>
+        <v>0.018943</v>
       </c>
       <c r="G991" s="7">
-        <v>0</v>
+        <v>0.430841</v>
       </c>
       <c r="H991" s="7">
-        <v>0</v>
+        <v>0.675057</v>
       </c>
       <c r="I991" s="7">
-        <v>0</v>
+        <v>1.039803</v>
       </c>
       <c r="J991" s="7"/>
       <c r="K991" s="7"/>
@@ -38486,22 +38486,22 @@
         <v>5</v>
       </c>
       <c r="E993" s="7">
-        <v>0</v>
+        <v>0.054254</v>
       </c>
       <c r="F993" s="7">
-        <v>0</v>
+        <v>0.040336</v>
       </c>
       <c r="G993" s="7">
-        <v>0</v>
+        <v>0.34877400000000003</v>
       </c>
       <c r="H993" s="7">
-        <v>0</v>
+        <v>0.481304</v>
       </c>
       <c r="I993" s="7">
-        <v>0</v>
+        <v>0.699888</v>
       </c>
       <c r="J993" s="7">
-        <v>0</v>
+        <v>2.420909</v>
       </c>
       <c r="K993" s="7"/>
     </row>
@@ -39109,25 +39109,25 @@
         <v>5</v>
       </c>
       <c r="E1012" s="7">
-        <v>0</v>
+        <v>0.07786</v>
       </c>
       <c r="F1012" s="7">
-        <v>0</v>
+        <v>0.069878</v>
       </c>
       <c r="G1012" s="7">
-        <v>0</v>
+        <v>0.073919</v>
       </c>
       <c r="H1012" s="7">
-        <v>0</v>
+        <v>0.20239000000000001</v>
       </c>
       <c r="I1012" s="7">
-        <v>0</v>
+        <v>0.263497</v>
       </c>
       <c r="J1012" s="7">
-        <v>0</v>
+        <v>1.204142</v>
       </c>
       <c r="K1012" s="7">
-        <v>0</v>
+        <v>4.727466</v>
       </c>
     </row>
     <row r="1013" spans="1:11" x14ac:dyDescent="0.25">
@@ -39291,25 +39291,25 @@
         <v>6</v>
       </c>
       <c r="E1018" s="7">
-        <v>0</v>
+        <v>0.086489</v>
       </c>
       <c r="F1018" s="7">
-        <v>0</v>
+        <v>0.095074</v>
       </c>
       <c r="G1018" s="7">
-        <v>0</v>
+        <v>0.243565</v>
       </c>
       <c r="H1018" s="7">
-        <v>0</v>
+        <v>0.234122</v>
       </c>
       <c r="I1018" s="7">
-        <v>0</v>
+        <v>0.472008</v>
       </c>
       <c r="J1018" s="7">
-        <v>0</v>
+        <v>2.204787</v>
       </c>
       <c r="K1018" s="7">
-        <v>0</v>
+        <v>8.429776</v>
       </c>
     </row>
     <row r="1019" spans="1:11" x14ac:dyDescent="0.25">
@@ -39578,25 +39578,25 @@
         <v>7</v>
       </c>
       <c r="E1027" s="7">
-        <v>0</v>
+        <v>0.17858000000000002</v>
       </c>
       <c r="F1027" s="7">
-        <v>0</v>
+        <v>-0.06757200000000001</v>
       </c>
       <c r="G1027" s="7">
-        <v>0</v>
+        <v>-0.20366099999999998</v>
       </c>
       <c r="H1027" s="7">
-        <v>0</v>
+        <v>0.028525000000000002</v>
       </c>
       <c r="I1027" s="7">
-        <v>0</v>
+        <v>0.985267</v>
       </c>
       <c r="J1027" s="7">
-        <v>0</v>
+        <v>3.685407</v>
       </c>
       <c r="K1027" s="7">
-        <v>0</v>
+        <v>12.414499000000001</v>
       </c>
     </row>
     <row r="1028" spans="1:11" x14ac:dyDescent="0.25">
@@ -39902,22 +39902,22 @@
         <v>6</v>
       </c>
       <c r="E1037" s="7">
-        <v>0.08483299999999999</v>
+        <v>0.085006</v>
       </c>
       <c r="F1037" s="7">
-        <v>0.037565</v>
+        <v>0.037731</v>
       </c>
       <c r="G1037" s="7">
-        <v>0.109655</v>
+        <v>0.109833</v>
       </c>
       <c r="H1037" s="7">
-        <v>0.246505</v>
+        <v>0.246704</v>
       </c>
       <c r="I1037" s="7">
-        <v>0.513016</v>
+        <v>0.513258</v>
       </c>
       <c r="J1037" s="7">
-        <v>1.8059280000000002</v>
+        <v>1.806376</v>
       </c>
       <c r="K1037" s="7"/>
     </row>
@@ -40459,25 +40459,25 @@
         <v>5</v>
       </c>
       <c r="E1054" s="7">
-        <v>0.059340000000000004</v>
+        <v>0.059372999999999995</v>
       </c>
       <c r="F1054" s="7">
-        <v>0.079809</v>
+        <v>0.07984200000000001</v>
       </c>
       <c r="G1054" s="7">
-        <v>0.08569399999999999</v>
+        <v>0.085727</v>
       </c>
       <c r="H1054" s="7">
-        <v>0.174414</v>
+        <v>0.174451</v>
       </c>
       <c r="I1054" s="7">
-        <v>0.239305</v>
+        <v>0.239344</v>
       </c>
       <c r="J1054" s="7">
-        <v>1.3151169999999999</v>
+        <v>1.315188</v>
       </c>
       <c r="K1054" s="7">
-        <v>7.271848</v>
+        <v>7.2721029999999995</v>
       </c>
     </row>
     <row r="1055" spans="1:11" x14ac:dyDescent="0.25">
@@ -40651,22 +40651,22 @@
         <v>6</v>
       </c>
       <c r="E1060" s="7">
-        <v>0.038610000000000005</v>
+        <v>0.039768</v>
       </c>
       <c r="F1060" s="7">
-        <v>0.053849999999999995</v>
+        <v>0.055023999999999997</v>
       </c>
       <c r="G1060" s="7">
-        <v>-0.0054410000000000005</v>
+        <v>-0.004332</v>
       </c>
       <c r="H1060" s="7">
-        <v>0.074701</v>
+        <v>0.075899</v>
       </c>
       <c r="I1060" s="7">
-        <v>0.07485800000000001</v>
+        <v>0.076056</v>
       </c>
       <c r="J1060" s="7">
-        <v>1.034556</v>
+        <v>1.036824</v>
       </c>
       <c r="K1060" s="7"/>
     </row>
@@ -40684,22 +40684,22 @@
         <v>6</v>
       </c>
       <c r="E1061" s="7">
-        <v>0.048975</v>
+        <v>0.048932</v>
       </c>
       <c r="F1061" s="7">
-        <v>0.027902999999999997</v>
+        <v>0.027860999999999997</v>
       </c>
       <c r="G1061" s="7">
-        <v>0.119131</v>
+        <v>0.119085</v>
       </c>
       <c r="H1061" s="7">
-        <v>0.255208</v>
+        <v>0.25515699999999997</v>
       </c>
       <c r="I1061" s="7">
-        <v>0.37166200000000005</v>
+        <v>0.37160699999999997</v>
       </c>
       <c r="J1061" s="7">
-        <v>1.488614</v>
+        <v>1.4885130000000002</v>
       </c>
       <c r="K1061" s="7"/>
     </row>
@@ -40717,19 +40717,19 @@
         <v>5</v>
       </c>
       <c r="E1062" s="7">
-        <v>0.039134</v>
+        <v>0.035242</v>
       </c>
       <c r="F1062" s="7">
-        <v>0.127439</v>
+        <v>0.123216</v>
       </c>
       <c r="G1062" s="7">
-        <v>0.18851700000000002</v>
+        <v>0.184065</v>
       </c>
       <c r="H1062" s="7">
-        <v>0.27642900000000004</v>
+        <v>0.271648</v>
       </c>
       <c r="I1062" s="7">
-        <v>0.313419</v>
+        <v>0.3085</v>
       </c>
       <c r="J1062" s="7"/>
       <c r="K1062" s="7"/>

--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>01.09.2026 09:28:38</t>
+    <t>01.09.2026 10:48:28</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -7793,25 +7793,25 @@
         <v>4</v>
       </c>
       <c r="E30" s="7">
-        <v>0.046558</v>
+        <v>0.041626</v>
       </c>
       <c r="F30" s="7">
-        <v>0.08537</v>
+        <v>0.08025600000000001</v>
       </c>
       <c r="G30" s="7">
-        <v>0.178391</v>
+        <v>0.172839</v>
       </c>
       <c r="H30" s="7">
-        <v>0.305313</v>
+        <v>0.299163</v>
       </c>
       <c r="I30" s="7">
-        <v>0.45577599999999996</v>
+        <v>0.448917</v>
       </c>
       <c r="J30" s="7">
-        <v>1.907789</v>
+        <v>1.8940880000000002</v>
       </c>
       <c r="K30" s="7">
-        <v>8.29473</v>
+        <v>8.250933999999999</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -9021,19 +9021,19 @@
         <v>5</v>
       </c>
       <c r="E68" s="7">
-        <v>0.042992</v>
+        <v>0.035698</v>
       </c>
       <c r="F68" s="7">
-        <v>0.069351</v>
+        <v>0.061871999999999996</v>
       </c>
       <c r="G68" s="7">
-        <v>0.06578</v>
+        <v>0.058326</v>
       </c>
       <c r="H68" s="7">
-        <v>0.153565</v>
+        <v>0.145497</v>
       </c>
       <c r="I68" s="7">
-        <v>0.31174</v>
+        <v>0.302566</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
@@ -9257,19 +9257,19 @@
         <v>3</v>
       </c>
       <c r="E76" s="7">
-        <v>0.027093</v>
+        <v>0.027096</v>
       </c>
       <c r="F76" s="7">
-        <v>0.091088</v>
+        <v>0.09109199999999999</v>
       </c>
       <c r="G76" s="7">
-        <v>0.21433700000000003</v>
+        <v>0.214342</v>
       </c>
       <c r="H76" s="7">
-        <v>0.28741700000000003</v>
+        <v>0.287422</v>
       </c>
       <c r="I76" s="7">
-        <v>0.44195500000000004</v>
+        <v>0.44195999999999996</v>
       </c>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
@@ -9718,19 +9718,19 @@
         <v>7</v>
       </c>
       <c r="E91" s="7">
-        <v>0.080665</v>
+        <v>0.080674</v>
       </c>
       <c r="F91" s="7">
-        <v>0.054957000000000006</v>
+        <v>0.054966</v>
       </c>
       <c r="G91" s="7">
-        <v>-0.186975</v>
+        <v>-0.186968</v>
       </c>
       <c r="H91" s="7">
-        <v>-0.013491</v>
+        <v>-0.013482000000000001</v>
       </c>
       <c r="I91" s="7">
-        <v>-0.003832</v>
+        <v>-0.003822</v>
       </c>
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
@@ -9900,19 +9900,19 @@
         <v>5</v>
       </c>
       <c r="E97" s="7">
-        <v>0.070766</v>
+        <v>0.062863</v>
       </c>
       <c r="F97" s="7">
-        <v>0.07337500000000001</v>
+        <v>0.065453</v>
       </c>
       <c r="G97" s="7">
-        <v>0.138739</v>
+        <v>0.130335</v>
       </c>
       <c r="H97" s="7">
-        <v>0.32932</v>
+        <v>0.319509</v>
       </c>
       <c r="I97" s="7">
-        <v>0.499631</v>
+        <v>0.48856299999999997</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
@@ -10020,16 +10020,16 @@
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="7">
-        <v>0.021348</v>
+        <v>0.021347</v>
       </c>
       <c r="F101" s="7">
-        <v>0.067308</v>
+        <v>0.06730699999999999</v>
       </c>
       <c r="G101" s="7">
-        <v>0.126409</v>
+        <v>0.126408</v>
       </c>
       <c r="H101" s="7">
-        <v>0.160115</v>
+        <v>0.16011399999999998</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
@@ -10080,16 +10080,16 @@
         <v>7</v>
       </c>
       <c r="E103" s="7">
-        <v>0.055219</v>
+        <v>0.055229999999999994</v>
       </c>
       <c r="F103" s="7">
-        <v>0.159873</v>
+        <v>0.159885</v>
       </c>
       <c r="G103" s="7">
-        <v>0.397072</v>
+        <v>0.397086</v>
       </c>
       <c r="H103" s="7">
-        <v>0.561036</v>
+        <v>0.561053</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
@@ -11553,22 +11553,22 @@
         <v>6</v>
       </c>
       <c r="E150" s="7">
-        <v>0.045224</v>
+        <v>0.03551</v>
       </c>
       <c r="F150" s="7">
-        <v>0.048076999999999995</v>
+        <v>0.038336</v>
       </c>
       <c r="G150" s="7">
-        <v>0.087958</v>
+        <v>0.077848</v>
       </c>
       <c r="H150" s="7">
-        <v>0.22815100000000002</v>
+        <v>0.216737</v>
       </c>
       <c r="I150" s="7">
-        <v>0.266409</v>
+        <v>0.25464</v>
       </c>
       <c r="J150" s="7">
-        <v>1.322779</v>
+        <v>1.3011920000000001</v>
       </c>
       <c r="K150" s="7"/>
     </row>
@@ -11586,16 +11586,16 @@
         <v>6</v>
       </c>
       <c r="E151" s="7">
-        <v>0.034315000000000005</v>
+        <v>0.034117</v>
       </c>
       <c r="F151" s="7">
-        <v>0.090975</v>
+        <v>0.09076599999999999</v>
       </c>
       <c r="G151" s="7">
-        <v>0.07469</v>
+        <v>0.074483</v>
       </c>
       <c r="H151" s="7">
-        <v>0.16355899999999998</v>
+        <v>0.163336</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="7"/>
@@ -11958,22 +11958,22 @@
         <v>7</v>
       </c>
       <c r="E163" s="7">
-        <v>0.170733</v>
+        <v>0.16863399999999998</v>
       </c>
       <c r="F163" s="7">
-        <v>-0.075721</v>
+        <v>-0.077378</v>
       </c>
       <c r="G163" s="7">
-        <v>-0.183781</v>
+        <v>-0.185244</v>
       </c>
       <c r="H163" s="7">
-        <v>0.021508</v>
+        <v>0.019676</v>
       </c>
       <c r="I163" s="7">
-        <v>0.927597</v>
+        <v>0.9241419999999999</v>
       </c>
       <c r="J163" s="7">
-        <v>3.467378</v>
+        <v>3.4593700000000003</v>
       </c>
       <c r="K163" s="7"/>
     </row>
@@ -12078,19 +12078,19 @@
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="7">
-        <v>0.046327999999999994</v>
+        <v>0.046620999999999996</v>
       </c>
       <c r="F167" s="7">
-        <v>0.093497</v>
+        <v>0.093803</v>
       </c>
       <c r="G167" s="7">
-        <v>0.10189500000000001</v>
+        <v>0.102204</v>
       </c>
       <c r="H167" s="7">
-        <v>0.13595000000000002</v>
+        <v>0.136268</v>
       </c>
       <c r="I167" s="7">
-        <v>0.264111</v>
+        <v>0.264465</v>
       </c>
       <c r="J167" s="7"/>
       <c r="K167" s="7"/>
@@ -12464,25 +12464,25 @@
         <v>3</v>
       </c>
       <c r="E179" s="7">
-        <v>0.047869</v>
+        <v>0.040814</v>
       </c>
       <c r="F179" s="7">
-        <v>0.088516</v>
+        <v>0.081188</v>
       </c>
       <c r="G179" s="7">
-        <v>0.142619</v>
+        <v>0.134926</v>
       </c>
       <c r="H179" s="7">
-        <v>0.229054</v>
+        <v>0.220779</v>
       </c>
       <c r="I179" s="7">
-        <v>0.40252699999999997</v>
+        <v>0.393084</v>
       </c>
       <c r="J179" s="7">
-        <v>1.785087</v>
+        <v>1.766337</v>
       </c>
       <c r="K179" s="7">
-        <v>6.680804</v>
+        <v>6.629094</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -12561,19 +12561,19 @@
         <v>6</v>
       </c>
       <c r="E182" s="7">
-        <v>0.043061999999999996</v>
+        <v>0.042979</v>
       </c>
       <c r="F182" s="7">
-        <v>0.08098699999999999</v>
+        <v>0.0809</v>
       </c>
       <c r="G182" s="7">
-        <v>0.096588</v>
+        <v>0.0965</v>
       </c>
       <c r="H182" s="7">
-        <v>0.292659</v>
+        <v>0.29255600000000004</v>
       </c>
       <c r="I182" s="7">
-        <v>0.299038</v>
+        <v>0.298934</v>
       </c>
       <c r="J182" s="7"/>
       <c r="K182" s="7"/>
@@ -14169,25 +14169,25 @@
         <v>4</v>
       </c>
       <c r="E234" s="7">
-        <v>0.07114899999999999</v>
+        <v>0.059345</v>
       </c>
       <c r="F234" s="7">
-        <v>0.077134</v>
+        <v>0.065264</v>
       </c>
       <c r="G234" s="7">
-        <v>0.081966</v>
+        <v>0.070043</v>
       </c>
       <c r="H234" s="7">
-        <v>0.181283</v>
+        <v>0.168265</v>
       </c>
       <c r="I234" s="7">
-        <v>0.40752099999999997</v>
+        <v>0.39201</v>
       </c>
       <c r="J234" s="7">
-        <v>1.967882</v>
+        <v>1.9351759999999998</v>
       </c>
       <c r="K234" s="7">
-        <v>5.838036</v>
+        <v>5.762682</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -14598,25 +14598,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.056152</v>
+        <v>0.054245</v>
       </c>
       <c r="F247" s="7">
-        <v>0.09719</v>
+        <v>0.09520899999999999</v>
       </c>
       <c r="G247" s="7">
-        <v>0.08678100000000001</v>
+        <v>0.084818</v>
       </c>
       <c r="H247" s="7">
-        <v>0.179118</v>
+        <v>0.17698899999999998</v>
       </c>
       <c r="I247" s="7">
-        <v>0.37345399999999995</v>
+        <v>0.370974</v>
       </c>
       <c r="J247" s="7">
-        <v>1.9246539999999999</v>
+        <v>1.919374</v>
       </c>
       <c r="K247" s="7">
-        <v>6.34283</v>
+        <v>6.329572</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -14893,25 +14893,25 @@
       </c>
       <c r="D256" s="6"/>
       <c r="E256" s="7">
-        <v>0.019287000000000002</v>
+        <v>0.020293000000000002</v>
       </c>
       <c r="F256" s="7">
-        <v>0.063816</v>
+        <v>0.064865</v>
       </c>
       <c r="G256" s="7">
-        <v>0.117604</v>
+        <v>0.118707</v>
       </c>
       <c r="H256" s="7">
-        <v>0.14921099999999998</v>
+        <v>0.150344</v>
       </c>
       <c r="I256" s="7">
-        <v>0.217699</v>
+        <v>0.2189</v>
       </c>
       <c r="J256" s="7">
-        <v>1.0431789999999999</v>
+        <v>1.0451949999999999</v>
       </c>
       <c r="K256" s="7">
-        <v>5.8788480000000005</v>
+        <v>5.885635</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -15124,22 +15124,22 @@
         <v>6</v>
       </c>
       <c r="E263" s="7">
-        <v>0.059639</v>
+        <v>0.058589</v>
       </c>
       <c r="F263" s="7">
-        <v>0.046185000000000004</v>
+        <v>0.045148</v>
       </c>
       <c r="G263" s="7">
-        <v>0.35441</v>
+        <v>0.35306800000000005</v>
       </c>
       <c r="H263" s="7">
-        <v>0.35679</v>
+        <v>0.35544600000000004</v>
       </c>
       <c r="I263" s="7">
-        <v>0.550247</v>
+        <v>0.548711</v>
       </c>
       <c r="J263" s="7">
-        <v>2.406489</v>
+        <v>2.403114</v>
       </c>
       <c r="K263" s="7"/>
     </row>
@@ -15250,16 +15250,16 @@
         <v>6</v>
       </c>
       <c r="E267" s="7">
-        <v>0</v>
+        <v>0.174837</v>
       </c>
       <c r="F267" s="7">
-        <v>0</v>
+        <v>0.0733</v>
       </c>
       <c r="G267" s="7">
-        <v>0</v>
+        <v>0.144281</v>
       </c>
       <c r="H267" s="7">
-        <v>0</v>
+        <v>0.320679</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
@@ -15483,22 +15483,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.054833</v>
+        <v>0.045935</v>
       </c>
       <c r="F274" s="7">
-        <v>0.08689</v>
+        <v>0.077722</v>
       </c>
       <c r="G274" s="7">
-        <v>0.142498</v>
+        <v>0.132861</v>
       </c>
       <c r="H274" s="7">
-        <v>0.227499</v>
+        <v>0.217145</v>
       </c>
       <c r="I274" s="7">
-        <v>0.369563</v>
+        <v>0.35801099999999997</v>
       </c>
       <c r="J274" s="7">
-        <v>1.903328</v>
+        <v>1.878838</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -15691,25 +15691,25 @@
         <v>3</v>
       </c>
       <c r="E280" s="7">
-        <v>0</v>
+        <v>0.036499000000000004</v>
       </c>
       <c r="F280" s="7">
-        <v>0</v>
+        <v>0.08577299999999999</v>
       </c>
       <c r="G280" s="7">
-        <v>0</v>
+        <v>0.12070600000000001</v>
       </c>
       <c r="H280" s="7">
-        <v>0</v>
+        <v>0.231247</v>
       </c>
       <c r="I280" s="7">
-        <v>0</v>
+        <v>0.388775</v>
       </c>
       <c r="J280" s="7">
-        <v>0</v>
+        <v>2.2311959999999997</v>
       </c>
       <c r="K280" s="7">
-        <v>0</v>
+        <v>6.1618960000000005</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -15996,22 +15996,22 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.083816</v>
+        <v>0.08348499999999999</v>
       </c>
       <c r="F289" s="7">
-        <v>0.036267999999999995</v>
+        <v>0.035952000000000005</v>
       </c>
       <c r="G289" s="7">
-        <v>0.142159</v>
+        <v>0.14181100000000002</v>
       </c>
       <c r="H289" s="7">
-        <v>0.305535</v>
+        <v>0.305137</v>
       </c>
       <c r="I289" s="7">
-        <v>0.514144</v>
+        <v>0.513682</v>
       </c>
       <c r="J289" s="7">
-        <v>1.60024</v>
+        <v>1.5994460000000001</v>
       </c>
       <c r="K289" s="7"/>
     </row>
@@ -16029,25 +16029,25 @@
         <v>6</v>
       </c>
       <c r="E290" s="7">
-        <v>0.102005</v>
+        <v>0.101902</v>
       </c>
       <c r="F290" s="7">
-        <v>0.018182</v>
+        <v>0.018087</v>
       </c>
       <c r="G290" s="7">
-        <v>-0.081652</v>
+        <v>-0.081737</v>
       </c>
       <c r="H290" s="7">
-        <v>0.09030200000000001</v>
+        <v>0.0902</v>
       </c>
       <c r="I290" s="7">
-        <v>0.471018</v>
+        <v>0.470881</v>
       </c>
       <c r="J290" s="7">
-        <v>2.9146820000000004</v>
+        <v>2.914319</v>
       </c>
       <c r="K290" s="7">
-        <v>12.939712</v>
+        <v>12.938417999999999</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -16099,19 +16099,19 @@
         <v>5</v>
       </c>
       <c r="E292" s="7">
-        <v>0</v>
+        <v>0.07279</v>
       </c>
       <c r="F292" s="7">
-        <v>0</v>
+        <v>0.048225</v>
       </c>
       <c r="G292" s="7">
-        <v>0</v>
+        <v>0.072832</v>
       </c>
       <c r="H292" s="7">
-        <v>0</v>
+        <v>0.18277200000000002</v>
       </c>
       <c r="I292" s="7">
-        <v>0</v>
+        <v>0.243518</v>
       </c>
       <c r="J292" s="7"/>
       <c r="K292" s="7"/>
@@ -16588,22 +16588,22 @@
         <v>5</v>
       </c>
       <c r="E307" s="7">
-        <v>0.035773</v>
+        <v>0.035821</v>
       </c>
       <c r="F307" s="7">
-        <v>0.053665000000000004</v>
+        <v>0.053714000000000005</v>
       </c>
       <c r="G307" s="7">
-        <v>0.16257000000000002</v>
+        <v>0.162624</v>
       </c>
       <c r="H307" s="7">
-        <v>0.20915099999999998</v>
+        <v>0.209207</v>
       </c>
       <c r="I307" s="7">
-        <v>0.349371</v>
+        <v>0.34943399999999997</v>
       </c>
       <c r="J307" s="7">
-        <v>0.41457299999999997</v>
+        <v>0.41463900000000004</v>
       </c>
       <c r="K307" s="7"/>
     </row>
@@ -17086,25 +17086,25 @@
         <v>2</v>
       </c>
       <c r="E323" s="7">
-        <v>0</v>
+        <v>0.037018</v>
       </c>
       <c r="F323" s="7">
-        <v>0</v>
+        <v>0.09616</v>
       </c>
       <c r="G323" s="7">
-        <v>0</v>
+        <v>0.149641</v>
       </c>
       <c r="H323" s="7">
-        <v>0</v>
+        <v>0.24266100000000002</v>
       </c>
       <c r="I323" s="7">
-        <v>0</v>
+        <v>0.394578</v>
       </c>
       <c r="J323" s="7">
-        <v>0</v>
+        <v>2.106951</v>
       </c>
       <c r="K323" s="7">
-        <v>0</v>
+        <v>3.890695</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
@@ -17119,25 +17119,25 @@
       </c>
       <c r="D324" s="6"/>
       <c r="E324" s="7">
-        <v>0</v>
+        <v>0.029394999999999998</v>
       </c>
       <c r="F324" s="7">
-        <v>0</v>
+        <v>0.077812</v>
       </c>
       <c r="G324" s="7">
-        <v>0</v>
+        <v>0.108498</v>
       </c>
       <c r="H324" s="7">
-        <v>0</v>
+        <v>0.141374</v>
       </c>
       <c r="I324" s="7">
-        <v>0</v>
+        <v>0.237928</v>
       </c>
       <c r="J324" s="7">
-        <v>0</v>
+        <v>1.328037</v>
       </c>
       <c r="K324" s="7">
-        <v>0</v>
+        <v>6.252835999999999</v>
       </c>
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
@@ -17224,25 +17224,25 @@
         <v>3</v>
       </c>
       <c r="E327" s="7">
-        <v>0</v>
+        <v>0.037206</v>
       </c>
       <c r="F327" s="7">
-        <v>0</v>
+        <v>0.086017</v>
       </c>
       <c r="G327" s="7">
-        <v>0</v>
+        <v>0.128707</v>
       </c>
       <c r="H327" s="7">
-        <v>0</v>
+        <v>0.240584</v>
       </c>
       <c r="I327" s="7">
-        <v>0</v>
+        <v>0.39771999999999996</v>
       </c>
       <c r="J327" s="7">
-        <v>0</v>
+        <v>2.199225</v>
       </c>
       <c r="K327" s="7">
-        <v>0</v>
+        <v>6.323527</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -17350,25 +17350,25 @@
         <v>4</v>
       </c>
       <c r="E331" s="7">
-        <v>0</v>
+        <v>0.045459</v>
       </c>
       <c r="F331" s="7">
-        <v>0</v>
+        <v>0.082148</v>
       </c>
       <c r="G331" s="7">
-        <v>0</v>
+        <v>0.093386</v>
       </c>
       <c r="H331" s="7">
-        <v>0</v>
+        <v>0.24886399999999997</v>
       </c>
       <c r="I331" s="7">
-        <v>0</v>
+        <v>0.39563699999999996</v>
       </c>
       <c r="J331" s="7">
-        <v>0</v>
+        <v>2.193705</v>
       </c>
       <c r="K331" s="7">
-        <v>0</v>
+        <v>7.11559</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
@@ -17420,19 +17420,19 @@
         <v>5</v>
       </c>
       <c r="E333" s="7">
-        <v>0.064432</v>
+        <v>0.061102</v>
       </c>
       <c r="F333" s="7">
-        <v>0.070396</v>
+        <v>0.067047</v>
       </c>
       <c r="G333" s="7">
-        <v>0.078083</v>
+        <v>0.07471</v>
       </c>
       <c r="H333" s="7">
-        <v>0.22020199999999998</v>
+        <v>0.21638400000000002</v>
       </c>
       <c r="I333" s="7">
-        <v>0.370182</v>
+        <v>0.365896</v>
       </c>
       <c r="J333" s="7"/>
       <c r="K333" s="7"/>
@@ -17682,25 +17682,25 @@
         <v>6</v>
       </c>
       <c r="E341" s="7">
-        <v>0</v>
+        <v>0.065819</v>
       </c>
       <c r="F341" s="7">
-        <v>0</v>
+        <v>0.109442</v>
       </c>
       <c r="G341" s="7">
-        <v>0</v>
+        <v>0.086892</v>
       </c>
       <c r="H341" s="7">
-        <v>0</v>
+        <v>0.228243</v>
       </c>
       <c r="I341" s="7">
-        <v>0</v>
+        <v>0.378786</v>
       </c>
       <c r="J341" s="7">
-        <v>0</v>
+        <v>1.731721</v>
       </c>
       <c r="K341" s="7">
-        <v>0</v>
+        <v>4.887541</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
@@ -17808,25 +17808,25 @@
         <v>6</v>
       </c>
       <c r="E345" s="7">
-        <v>0</v>
+        <v>0.031174</v>
       </c>
       <c r="F345" s="7">
-        <v>0</v>
+        <v>0.055049</v>
       </c>
       <c r="G345" s="7">
-        <v>0</v>
+        <v>0.408552</v>
       </c>
       <c r="H345" s="7">
-        <v>0</v>
+        <v>0.427998</v>
       </c>
       <c r="I345" s="7">
-        <v>0</v>
+        <v>0.773356</v>
       </c>
       <c r="J345" s="7">
-        <v>0</v>
+        <v>2.503211</v>
       </c>
       <c r="K345" s="7">
-        <v>0</v>
+        <v>8.254827</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -17843,16 +17843,16 @@
         <v>7</v>
       </c>
       <c r="E346" s="7">
-        <v>0</v>
+        <v>0.166083</v>
       </c>
       <c r="F346" s="7">
-        <v>0</v>
+        <v>-0.102173</v>
       </c>
       <c r="G346" s="7">
-        <v>0</v>
+        <v>-0.23026</v>
       </c>
       <c r="H346" s="7">
-        <v>0</v>
+        <v>-0.041505</v>
       </c>
       <c r="I346" s="7"/>
       <c r="J346" s="7"/>
@@ -17938,22 +17938,22 @@
         <v>6</v>
       </c>
       <c r="E349" s="7">
-        <v>0</v>
+        <v>0.010572</v>
       </c>
       <c r="F349" s="7">
-        <v>0</v>
+        <v>-0.074786</v>
       </c>
       <c r="G349" s="7">
-        <v>0</v>
+        <v>0.076098</v>
       </c>
       <c r="H349" s="7">
-        <v>0</v>
+        <v>0.17802099999999998</v>
       </c>
       <c r="I349" s="7">
-        <v>0</v>
+        <v>0.35383000000000003</v>
       </c>
       <c r="J349" s="7">
-        <v>0</v>
+        <v>1.20123</v>
       </c>
       <c r="K349" s="7"/>
     </row>
@@ -17971,22 +17971,22 @@
         <v>5</v>
       </c>
       <c r="E350" s="7">
-        <v>0</v>
+        <v>0.047929000000000006</v>
       </c>
       <c r="F350" s="7">
-        <v>0</v>
+        <v>0.058696</v>
       </c>
       <c r="G350" s="7">
-        <v>0</v>
+        <v>0.017686</v>
       </c>
       <c r="H350" s="7">
-        <v>0</v>
+        <v>0.17579999999999998</v>
       </c>
       <c r="I350" s="7">
-        <v>0</v>
+        <v>0.28745899999999996</v>
       </c>
       <c r="J350" s="7">
-        <v>0</v>
+        <v>1.6634719999999998</v>
       </c>
       <c r="K350" s="7"/>
     </row>
@@ -18039,25 +18039,25 @@
         <v>6</v>
       </c>
       <c r="E352" s="7">
-        <v>0</v>
+        <v>0.09402799999999999</v>
       </c>
       <c r="F352" s="7">
-        <v>0</v>
+        <v>0.070319</v>
       </c>
       <c r="G352" s="7">
-        <v>0</v>
+        <v>0.16491299999999998</v>
       </c>
       <c r="H352" s="7">
-        <v>0</v>
+        <v>0.284934</v>
       </c>
       <c r="I352" s="7">
-        <v>0</v>
+        <v>0.59191</v>
       </c>
       <c r="J352" s="7">
-        <v>0</v>
+        <v>1.589381</v>
       </c>
       <c r="K352" s="7">
-        <v>0</v>
+        <v>6.9986239999999995</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
@@ -18107,25 +18107,25 @@
         <v>5</v>
       </c>
       <c r="E354" s="7">
-        <v>0</v>
+        <v>0.000794</v>
       </c>
       <c r="F354" s="7">
-        <v>0</v>
+        <v>-0.082244</v>
       </c>
       <c r="G354" s="7">
-        <v>0</v>
+        <v>0.034146</v>
       </c>
       <c r="H354" s="7">
-        <v>0</v>
+        <v>0.223047</v>
       </c>
       <c r="I354" s="7">
-        <v>0</v>
+        <v>0.40338799999999997</v>
       </c>
       <c r="J354" s="7">
-        <v>0</v>
+        <v>0.788031</v>
       </c>
       <c r="K354" s="7">
-        <v>0</v>
+        <v>4.115953</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -18142,25 +18142,25 @@
         <v>4</v>
       </c>
       <c r="E355" s="7">
-        <v>0</v>
+        <v>0.043128</v>
       </c>
       <c r="F355" s="7">
-        <v>0</v>
+        <v>0.072281</v>
       </c>
       <c r="G355" s="7">
-        <v>0</v>
+        <v>0.065406</v>
       </c>
       <c r="H355" s="7">
-        <v>0</v>
+        <v>0.201956</v>
       </c>
       <c r="I355" s="7">
-        <v>0</v>
+        <v>0.334088</v>
       </c>
       <c r="J355" s="7">
-        <v>0</v>
+        <v>1.988159</v>
       </c>
       <c r="K355" s="7">
-        <v>0</v>
+        <v>6.903112999999999</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
@@ -18177,22 +18177,22 @@
         <v>5</v>
       </c>
       <c r="E356" s="7">
-        <v>0</v>
+        <v>0.026272000000000004</v>
       </c>
       <c r="F356" s="7">
-        <v>0</v>
+        <v>0.087874</v>
       </c>
       <c r="G356" s="7">
-        <v>0</v>
+        <v>0.153715</v>
       </c>
       <c r="H356" s="7">
-        <v>0</v>
+        <v>0.37532600000000005</v>
       </c>
       <c r="I356" s="7">
-        <v>0</v>
+        <v>0.44860500000000003</v>
       </c>
       <c r="J356" s="7">
-        <v>0</v>
+        <v>0.8679600000000001</v>
       </c>
       <c r="K356" s="7"/>
     </row>
@@ -18280,25 +18280,25 @@
         <v>3</v>
       </c>
       <c r="E359" s="7">
-        <v>0</v>
+        <v>0.036901</v>
       </c>
       <c r="F359" s="7">
-        <v>0</v>
+        <v>0.08052799999999999</v>
       </c>
       <c r="G359" s="7">
-        <v>0</v>
+        <v>0.128883</v>
       </c>
       <c r="H359" s="7">
-        <v>0</v>
+        <v>0.231698</v>
       </c>
       <c r="I359" s="7">
-        <v>0</v>
+        <v>0.38618899999999995</v>
       </c>
       <c r="J359" s="7">
-        <v>0</v>
+        <v>2.190382</v>
       </c>
       <c r="K359" s="7">
-        <v>0</v>
+        <v>6.031516</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
@@ -18350,25 +18350,25 @@
         <v>5</v>
       </c>
       <c r="E361" s="7">
-        <v>0</v>
+        <v>0.046397</v>
       </c>
       <c r="F361" s="7">
-        <v>0</v>
+        <v>0.06310500000000001</v>
       </c>
       <c r="G361" s="7">
-        <v>0</v>
+        <v>0.141376</v>
       </c>
       <c r="H361" s="7">
-        <v>0</v>
+        <v>0.2493</v>
       </c>
       <c r="I361" s="7">
-        <v>0</v>
+        <v>0.36749299999999996</v>
       </c>
       <c r="J361" s="7">
-        <v>0</v>
+        <v>1.454597</v>
       </c>
       <c r="K361" s="7">
-        <v>0</v>
+        <v>6.324832</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
@@ -18385,22 +18385,22 @@
         <v>6</v>
       </c>
       <c r="E362" s="7">
-        <v>0</v>
+        <v>-0.020870000000000003</v>
       </c>
       <c r="F362" s="7">
-        <v>0</v>
+        <v>0.086027</v>
       </c>
       <c r="G362" s="7">
-        <v>0</v>
+        <v>0.050649</v>
       </c>
       <c r="H362" s="7">
-        <v>0</v>
+        <v>0.09347200000000001</v>
       </c>
       <c r="I362" s="7">
-        <v>0</v>
+        <v>0.124212</v>
       </c>
       <c r="J362" s="7">
-        <v>0</v>
+        <v>1.3583889999999998</v>
       </c>
       <c r="K362" s="7"/>
     </row>
@@ -18418,22 +18418,22 @@
         <v>5</v>
       </c>
       <c r="E363" s="7">
-        <v>0</v>
+        <v>0.038314</v>
       </c>
       <c r="F363" s="7">
-        <v>0</v>
+        <v>0.09230600000000001</v>
       </c>
       <c r="G363" s="7">
-        <v>0</v>
+        <v>0.045961</v>
       </c>
       <c r="H363" s="7">
-        <v>0</v>
+        <v>0.082666</v>
       </c>
       <c r="I363" s="7">
-        <v>0</v>
+        <v>0.17506799999999997</v>
       </c>
       <c r="J363" s="7">
-        <v>0</v>
+        <v>1.652058</v>
       </c>
       <c r="K363" s="7"/>
     </row>
@@ -18563,25 +18563,25 @@
       </c>
       <c r="D368" s="6"/>
       <c r="E368" s="7">
-        <v>0.103382</v>
+        <v>0.103411</v>
       </c>
       <c r="F368" s="7">
-        <v>0.023835000000000002</v>
+        <v>0.023862</v>
       </c>
       <c r="G368" s="7">
-        <v>-0.080225</v>
+        <v>-0.080201</v>
       </c>
       <c r="H368" s="7">
-        <v>0.110859</v>
+        <v>0.11088800000000001</v>
       </c>
       <c r="I368" s="7">
-        <v>0.511045</v>
+        <v>0.511085</v>
       </c>
       <c r="J368" s="7">
-        <v>3.0125</v>
+        <v>3.0126049999999998</v>
       </c>
       <c r="K368" s="7">
-        <v>11.952046000000001</v>
+        <v>11.952384</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
@@ -18596,22 +18596,22 @@
       </c>
       <c r="D369" s="6"/>
       <c r="E369" s="7">
-        <v>0</v>
+        <v>0.030206</v>
       </c>
       <c r="F369" s="7">
-        <v>0</v>
+        <v>0.052725</v>
       </c>
       <c r="G369" s="7">
-        <v>0</v>
+        <v>0.10089000000000001</v>
       </c>
       <c r="H369" s="7">
-        <v>0</v>
+        <v>0.216782</v>
       </c>
       <c r="I369" s="7">
-        <v>0</v>
+        <v>0.296026</v>
       </c>
       <c r="J369" s="7">
-        <v>0</v>
+        <v>1.533511</v>
       </c>
       <c r="K369" s="7"/>
     </row>
@@ -18774,22 +18774,22 @@
         <v>3</v>
       </c>
       <c r="E375" s="7">
-        <v>0</v>
+        <v>0.023044</v>
       </c>
       <c r="F375" s="7">
-        <v>0</v>
+        <v>0.093368</v>
       </c>
       <c r="G375" s="7">
-        <v>0</v>
+        <v>0.19505</v>
       </c>
       <c r="H375" s="7">
-        <v>0</v>
+        <v>0.24979099999999999</v>
       </c>
       <c r="I375" s="7">
-        <v>0</v>
+        <v>0.403645</v>
       </c>
       <c r="J375" s="7">
-        <v>0</v>
+        <v>2.703951</v>
       </c>
       <c r="K375" s="7"/>
     </row>
@@ -18952,22 +18952,22 @@
         <v>7</v>
       </c>
       <c r="E381" s="7">
-        <v>0</v>
+        <v>0.005542</v>
       </c>
       <c r="F381" s="7">
-        <v>0</v>
+        <v>-0.035849</v>
       </c>
       <c r="G381" s="7">
-        <v>0</v>
+        <v>-0.047161999999999996</v>
       </c>
       <c r="H381" s="7">
-        <v>0</v>
+        <v>0.072416</v>
       </c>
       <c r="I381" s="7">
-        <v>0</v>
+        <v>-0.07956400000000001</v>
       </c>
       <c r="J381" s="7">
-        <v>0</v>
+        <v>1.4831379999999998</v>
       </c>
       <c r="K381" s="7"/>
     </row>
@@ -19487,25 +19487,25 @@
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="7">
-        <v>0.035234</v>
+        <v>0.035265</v>
       </c>
       <c r="F398" s="7">
-        <v>0.055778</v>
+        <v>0.055810000000000005</v>
       </c>
       <c r="G398" s="7">
-        <v>0.150945</v>
+        <v>0.15098</v>
       </c>
       <c r="H398" s="7">
-        <v>0.235429</v>
+        <v>0.235466</v>
       </c>
       <c r="I398" s="7">
-        <v>0.351429</v>
+        <v>0.35147</v>
       </c>
       <c r="J398" s="7">
-        <v>1.5362149999999999</v>
+        <v>1.5362909999999999</v>
       </c>
       <c r="K398" s="7">
-        <v>6.5573559999999995</v>
+        <v>6.557581</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
@@ -19712,25 +19712,25 @@
       </c>
       <c r="D405" s="6"/>
       <c r="E405" s="7">
-        <v>0.031875</v>
+        <v>0.031842</v>
       </c>
       <c r="F405" s="7">
-        <v>0.03916</v>
+        <v>0.039127</v>
       </c>
       <c r="G405" s="7">
-        <v>0.08799</v>
+        <v>0.087955</v>
       </c>
       <c r="H405" s="7">
-        <v>0.21826399999999999</v>
+        <v>0.218225</v>
       </c>
       <c r="I405" s="7">
-        <v>0.224082</v>
+        <v>0.224043</v>
       </c>
       <c r="J405" s="7">
-        <v>1.220448</v>
+        <v>1.220377</v>
       </c>
       <c r="K405" s="7">
-        <v>9.291633000000001</v>
+        <v>9.291302</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
@@ -19871,7 +19871,7 @@
         <v>6</v>
       </c>
       <c r="E410" s="7">
-        <v>0.021827</v>
+        <v>0.019181</v>
       </c>
       <c r="F410" s="7"/>
       <c r="G410" s="7"/>
@@ -20216,19 +20216,19 @@
         <v>5</v>
       </c>
       <c r="E421" s="7">
-        <v>0.063566</v>
+        <v>0.063565</v>
       </c>
       <c r="F421" s="7">
-        <v>0.080546</v>
+        <v>0.080545</v>
       </c>
       <c r="G421" s="7">
-        <v>0.182613</v>
+        <v>0.182612</v>
       </c>
       <c r="H421" s="7">
-        <v>0.533865</v>
+        <v>0.533864</v>
       </c>
       <c r="I421" s="7">
-        <v>0.455167</v>
+        <v>0.45516599999999996</v>
       </c>
       <c r="J421" s="7"/>
       <c r="K421" s="7"/>
@@ -20890,25 +20890,25 @@
         <v>1</v>
       </c>
       <c r="E441" s="7">
-        <v>0.032515999999999996</v>
+        <v>0.032515</v>
       </c>
       <c r="F441" s="7">
-        <v>0.105202</v>
+        <v>0.10520099999999999</v>
       </c>
       <c r="G441" s="7">
-        <v>0.213851</v>
+        <v>0.21384899999999998</v>
       </c>
       <c r="H441" s="7">
-        <v>0.28857099999999997</v>
+        <v>0.28857</v>
       </c>
       <c r="I441" s="7">
-        <v>0.46529400000000004</v>
+        <v>0.465293</v>
       </c>
       <c r="J441" s="7">
-        <v>2.558758</v>
+        <v>2.5587549999999997</v>
       </c>
       <c r="K441" s="7">
-        <v>4.392632</v>
+        <v>4.392626</v>
       </c>
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.25">
@@ -21014,16 +21014,16 @@
         <v>6</v>
       </c>
       <c r="E445" s="7">
-        <v>0.03851</v>
+        <v>0.038512</v>
       </c>
       <c r="F445" s="7">
-        <v>-0.000883</v>
+        <v>-0.000881</v>
       </c>
       <c r="G445" s="7">
-        <v>0.037219</v>
+        <v>0.037221000000000004</v>
       </c>
       <c r="H445" s="7">
-        <v>0.239129</v>
+        <v>0.239131</v>
       </c>
       <c r="I445" s="7"/>
       <c r="J445" s="7"/>
@@ -21297,19 +21297,19 @@
         <v>6</v>
       </c>
       <c r="E454" s="7">
-        <v>0.057989</v>
+        <v>0.057988</v>
       </c>
       <c r="F454" s="7">
-        <v>-0.016412</v>
+        <v>-0.016413</v>
       </c>
       <c r="G454" s="7">
-        <v>0.051485</v>
+        <v>0.051483999999999995</v>
       </c>
       <c r="H454" s="7">
-        <v>0.26366</v>
+        <v>0.263659</v>
       </c>
       <c r="I454" s="7">
-        <v>0.210202</v>
+        <v>0.210201</v>
       </c>
       <c r="J454" s="7"/>
       <c r="K454" s="7"/>
@@ -23009,19 +23009,19 @@
         <v>6</v>
       </c>
       <c r="E506" s="7">
-        <v>0</v>
+        <v>0.041393000000000006</v>
       </c>
       <c r="F506" s="7">
-        <v>0</v>
+        <v>0.050508</v>
       </c>
       <c r="G506" s="7">
-        <v>0</v>
+        <v>0.11372</v>
       </c>
       <c r="H506" s="7">
-        <v>0</v>
+        <v>0.271675</v>
       </c>
       <c r="I506" s="7">
-        <v>0</v>
+        <v>0.412117</v>
       </c>
       <c r="J506" s="7"/>
       <c r="K506" s="7"/>
@@ -23214,19 +23214,19 @@
         <v>6</v>
       </c>
       <c r="E513" s="7">
-        <v>0.17270700000000003</v>
+        <v>0.172705</v>
       </c>
       <c r="F513" s="7">
-        <v>-0.073074</v>
+        <v>-0.073075</v>
       </c>
       <c r="G513" s="7">
-        <v>-0.174188</v>
+        <v>-0.174189</v>
       </c>
       <c r="H513" s="7">
-        <v>0.014883</v>
+        <v>0.014882</v>
       </c>
       <c r="I513" s="7">
-        <v>0.90059</v>
+        <v>0.900588</v>
       </c>
       <c r="J513" s="7"/>
       <c r="K513" s="7"/>
@@ -23307,19 +23307,19 @@
         <v>7</v>
       </c>
       <c r="E516" s="7">
-        <v>0</v>
+        <v>0.005017000000000001</v>
       </c>
       <c r="F516" s="7">
-        <v>0</v>
+        <v>0.089548</v>
       </c>
       <c r="G516" s="7">
-        <v>0</v>
+        <v>0.163907</v>
       </c>
       <c r="H516" s="7">
-        <v>0</v>
+        <v>0.323628</v>
       </c>
       <c r="I516" s="7">
-        <v>0</v>
+        <v>0.28334</v>
       </c>
       <c r="J516" s="7"/>
       <c r="K516" s="7"/>
@@ -23532,19 +23532,19 @@
         <v>2</v>
       </c>
       <c r="E523" s="7">
-        <v>0</v>
+        <v>0.027385000000000003</v>
       </c>
       <c r="F523" s="7">
-        <v>0</v>
+        <v>0.09071699999999999</v>
       </c>
       <c r="G523" s="7">
-        <v>0</v>
+        <v>0.1905</v>
       </c>
       <c r="H523" s="7">
-        <v>0</v>
+        <v>0.237881</v>
       </c>
       <c r="I523" s="7">
-        <v>0</v>
+        <v>0.343124</v>
       </c>
       <c r="J523" s="7"/>
       <c r="K523" s="7"/>
@@ -23629,19 +23629,19 @@
         <v>4</v>
       </c>
       <c r="E526" s="7">
-        <v>0</v>
+        <v>0.027006000000000002</v>
       </c>
       <c r="F526" s="7">
-        <v>0</v>
+        <v>0.056634000000000004</v>
       </c>
       <c r="G526" s="7">
-        <v>0</v>
+        <v>0.091446</v>
       </c>
       <c r="H526" s="7">
-        <v>0</v>
+        <v>0.126238</v>
       </c>
       <c r="I526" s="7">
-        <v>0</v>
+        <v>0.197898</v>
       </c>
       <c r="J526" s="7"/>
       <c r="K526" s="7"/>
@@ -24057,19 +24057,19 @@
         <v>6</v>
       </c>
       <c r="E540" s="7">
-        <v>0</v>
+        <v>0.023672</v>
       </c>
       <c r="F540" s="7">
-        <v>0</v>
+        <v>0.046498</v>
       </c>
       <c r="G540" s="7">
-        <v>0</v>
+        <v>0.069269</v>
       </c>
       <c r="H540" s="7">
-        <v>0</v>
+        <v>0.08593400000000001</v>
       </c>
       <c r="I540" s="7">
-        <v>0</v>
+        <v>0.130833</v>
       </c>
       <c r="J540" s="7"/>
       <c r="K540" s="7"/>
@@ -24375,25 +24375,25 @@
         <v>5</v>
       </c>
       <c r="E550" s="7">
-        <v>0</v>
+        <v>0.057425</v>
       </c>
       <c r="F550" s="7">
-        <v>0</v>
+        <v>0.09247299999999999</v>
       </c>
       <c r="G550" s="7">
-        <v>0</v>
+        <v>0.123049</v>
       </c>
       <c r="H550" s="7">
-        <v>0</v>
+        <v>0.260839</v>
       </c>
       <c r="I550" s="7">
-        <v>0</v>
+        <v>0.39846899999999996</v>
       </c>
       <c r="J550" s="7">
-        <v>0</v>
+        <v>2.19141</v>
       </c>
       <c r="K550" s="7">
-        <v>0</v>
+        <v>10.543463999999998</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.25">
@@ -24435,25 +24435,25 @@
         <v>5</v>
       </c>
       <c r="E552" s="7">
-        <v>0</v>
+        <v>0.047483000000000004</v>
       </c>
       <c r="F552" s="7">
-        <v>0</v>
+        <v>0.053513000000000005</v>
       </c>
       <c r="G552" s="7">
-        <v>0</v>
+        <v>0.082057</v>
       </c>
       <c r="H552" s="7">
-        <v>0</v>
+        <v>0.153384</v>
       </c>
       <c r="I552" s="7">
-        <v>0</v>
+        <v>0.258913</v>
       </c>
       <c r="J552" s="7">
-        <v>0</v>
+        <v>1.293823</v>
       </c>
       <c r="K552" s="7">
-        <v>0</v>
+        <v>5.709902</v>
       </c>
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.25">
@@ -24470,25 +24470,25 @@
         <v>3</v>
       </c>
       <c r="E553" s="7">
-        <v>0</v>
+        <v>0.022987</v>
       </c>
       <c r="F553" s="7">
-        <v>0</v>
+        <v>0.07009699999999999</v>
       </c>
       <c r="G553" s="7">
-        <v>0</v>
+        <v>0.116051</v>
       </c>
       <c r="H553" s="7">
-        <v>0</v>
+        <v>0.15445399999999998</v>
       </c>
       <c r="I553" s="7">
-        <v>0</v>
+        <v>0.229816</v>
       </c>
       <c r="J553" s="7">
-        <v>0</v>
+        <v>1.182</v>
       </c>
       <c r="K553" s="7">
-        <v>0</v>
+        <v>6.500406000000001</v>
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.25">
@@ -24994,25 +24994,25 @@
         <v>6</v>
       </c>
       <c r="E569" s="7">
-        <v>0</v>
+        <v>0.039426</v>
       </c>
       <c r="F569" s="7">
-        <v>0</v>
+        <v>0.056158</v>
       </c>
       <c r="G569" s="7">
-        <v>0</v>
+        <v>0.09821400000000001</v>
       </c>
       <c r="H569" s="7">
-        <v>0</v>
+        <v>0.127606</v>
       </c>
       <c r="I569" s="7">
-        <v>0</v>
+        <v>0.215287</v>
       </c>
       <c r="J569" s="7">
-        <v>0</v>
+        <v>1.514532</v>
       </c>
       <c r="K569" s="7">
-        <v>0</v>
+        <v>6.825782</v>
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.25">
@@ -25215,25 +25215,25 @@
         <v>6</v>
       </c>
       <c r="E576" s="7">
-        <v>0</v>
+        <v>0.014567000000000002</v>
       </c>
       <c r="F576" s="7">
-        <v>0</v>
+        <v>0.0064529999999999995</v>
       </c>
       <c r="G576" s="7">
-        <v>0</v>
+        <v>-0.081004</v>
       </c>
       <c r="H576" s="7">
-        <v>0</v>
+        <v>0.097607</v>
       </c>
       <c r="I576" s="7">
-        <v>0</v>
+        <v>0.12543300000000002</v>
       </c>
       <c r="J576" s="7">
-        <v>0</v>
+        <v>1.100578</v>
       </c>
       <c r="K576" s="7">
-        <v>0</v>
+        <v>12.044481000000001</v>
       </c>
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.25">
@@ -25250,19 +25250,19 @@
         <v>3</v>
       </c>
       <c r="E577" s="7">
-        <v>0</v>
+        <v>0.013833999999999999</v>
       </c>
       <c r="F577" s="7">
-        <v>0</v>
+        <v>0.083356</v>
       </c>
       <c r="G577" s="7">
-        <v>0</v>
+        <v>0.135112</v>
       </c>
       <c r="H577" s="7">
-        <v>0</v>
+        <v>0.17457799999999998</v>
       </c>
       <c r="I577" s="7">
-        <v>0</v>
+        <v>0.282979</v>
       </c>
       <c r="J577" s="7"/>
       <c r="K577" s="7"/>
@@ -25624,19 +25624,19 @@
         <v>3</v>
       </c>
       <c r="E589" s="7">
-        <v>0.050315000000000006</v>
+        <v>0.050324999999999995</v>
       </c>
       <c r="F589" s="7">
-        <v>0.155026</v>
+        <v>0.155037</v>
       </c>
       <c r="G589" s="7">
-        <v>0.22162199999999999</v>
+        <v>0.221634</v>
       </c>
       <c r="H589" s="7">
-        <v>0.39557400000000004</v>
+        <v>0.395588</v>
       </c>
       <c r="I589" s="7">
-        <v>0.563456</v>
+        <v>0.56347</v>
       </c>
       <c r="J589" s="7"/>
       <c r="K589" s="7"/>
@@ -25777,22 +25777,22 @@
         <v>6</v>
       </c>
       <c r="E594" s="7">
-        <v>0</v>
+        <v>0.029512999999999998</v>
       </c>
       <c r="F594" s="7">
-        <v>0</v>
+        <v>0.041866</v>
       </c>
       <c r="G594" s="7">
-        <v>0</v>
+        <v>0.255757</v>
       </c>
       <c r="H594" s="7">
-        <v>0</v>
+        <v>0.271771</v>
       </c>
       <c r="I594" s="7">
-        <v>0</v>
+        <v>0.418823</v>
       </c>
       <c r="J594" s="7">
-        <v>0</v>
+        <v>2.384576</v>
       </c>
       <c r="K594" s="7"/>
     </row>
@@ -26169,16 +26169,16 @@
         <v>5</v>
       </c>
       <c r="E606" s="7">
-        <v>0.052223</v>
+        <v>0.052169999999999994</v>
       </c>
       <c r="F606" s="7">
-        <v>0.050786</v>
+        <v>0.050734</v>
       </c>
       <c r="G606" s="7">
-        <v>0.161006</v>
+        <v>0.16094799999999998</v>
       </c>
       <c r="H606" s="7">
-        <v>0.219879</v>
+        <v>0.219819</v>
       </c>
       <c r="I606" s="7"/>
       <c r="J606" s="7"/>
@@ -26925,16 +26925,16 @@
         <v>5</v>
       </c>
       <c r="E630" s="7">
-        <v>0</v>
+        <v>0.034152999999999996</v>
       </c>
       <c r="F630" s="7">
-        <v>0</v>
+        <v>0.10815</v>
       </c>
       <c r="G630" s="7">
-        <v>0</v>
+        <v>0.228207</v>
       </c>
       <c r="H630" s="7">
-        <v>0</v>
+        <v>0.321905</v>
       </c>
       <c r="I630" s="7"/>
       <c r="J630" s="7"/>
@@ -27365,19 +27365,19 @@
         <v>6</v>
       </c>
       <c r="E644" s="7">
-        <v>0.061799999999999994</v>
+        <v>0.062380000000000005</v>
       </c>
       <c r="F644" s="7">
-        <v>0.090192</v>
+        <v>0.09078699999999999</v>
       </c>
       <c r="G644" s="7">
-        <v>0.178765</v>
+        <v>0.17940799999999998</v>
       </c>
       <c r="H644" s="7">
-        <v>0.322855</v>
+        <v>0.323578</v>
       </c>
       <c r="I644" s="7">
-        <v>0.268221</v>
+        <v>0.268913</v>
       </c>
       <c r="J644" s="7"/>
       <c r="K644" s="7"/>
@@ -27456,16 +27456,16 @@
         <v>2</v>
       </c>
       <c r="E647" s="7">
-        <v>0</v>
+        <v>0.023647</v>
       </c>
       <c r="F647" s="7">
-        <v>0</v>
+        <v>0.112478</v>
       </c>
       <c r="G647" s="7">
-        <v>0</v>
+        <v>0.19761700000000001</v>
       </c>
       <c r="H647" s="7">
-        <v>0</v>
+        <v>0.256688</v>
       </c>
       <c r="I647" s="7"/>
       <c r="J647" s="7"/>
@@ -27710,19 +27710,19 @@
         <v>2</v>
       </c>
       <c r="E655" s="7">
-        <v>0</v>
+        <v>0.029618000000000002</v>
       </c>
       <c r="F655" s="7">
-        <v>0</v>
+        <v>0.104484</v>
       </c>
       <c r="G655" s="7">
-        <v>0</v>
+        <v>0.20775500000000002</v>
       </c>
       <c r="H655" s="7">
-        <v>0</v>
+        <v>0.281645</v>
       </c>
       <c r="I655" s="7">
-        <v>0</v>
+        <v>0.44723199999999996</v>
       </c>
       <c r="J655" s="7"/>
       <c r="K655" s="7"/>
@@ -28470,22 +28470,22 @@
       </c>
       <c r="D679" s="6"/>
       <c r="E679" s="7">
-        <v>0.052799</v>
+        <v>0.052793</v>
       </c>
       <c r="F679" s="7">
-        <v>0.062637</v>
+        <v>0.06263099999999999</v>
       </c>
       <c r="G679" s="7">
-        <v>0.106195</v>
+        <v>0.106189</v>
       </c>
       <c r="H679" s="7">
-        <v>0.215003</v>
+        <v>0.21499600000000002</v>
       </c>
       <c r="I679" s="7">
-        <v>0.343058</v>
+        <v>0.34305</v>
       </c>
       <c r="J679" s="7">
-        <v>1.43514</v>
+        <v>1.435126</v>
       </c>
       <c r="K679" s="7"/>
     </row>
@@ -28503,25 +28503,25 @@
         <v>4</v>
       </c>
       <c r="E680" s="7">
-        <v>0.057617</v>
+        <v>0.057622</v>
       </c>
       <c r="F680" s="7">
-        <v>0.068493</v>
+        <v>0.068498</v>
       </c>
       <c r="G680" s="7">
-        <v>0.08596999999999999</v>
+        <v>0.085975</v>
       </c>
       <c r="H680" s="7">
-        <v>0.20039200000000001</v>
+        <v>0.200398</v>
       </c>
       <c r="I680" s="7">
-        <v>0.355811</v>
+        <v>0.355817</v>
       </c>
       <c r="J680" s="7">
-        <v>1.7240739999999999</v>
+        <v>1.7240870000000001</v>
       </c>
       <c r="K680" s="7">
-        <v>6.485126</v>
+        <v>6.485161000000001</v>
       </c>
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.25">
@@ -28773,25 +28773,25 @@
         <v>6</v>
       </c>
       <c r="E688" s="7">
-        <v>0.06756999999999999</v>
+        <v>0.066649</v>
       </c>
       <c r="F688" s="7">
-        <v>0.0604</v>
+        <v>0.059485</v>
       </c>
       <c r="G688" s="7">
-        <v>0.38380699999999995</v>
+        <v>0.382613</v>
       </c>
       <c r="H688" s="7">
-        <v>0.41307000000000005</v>
+        <v>0.41185000000000005</v>
       </c>
       <c r="I688" s="7">
-        <v>0.576894</v>
+        <v>0.5755319999999999</v>
       </c>
       <c r="J688" s="7">
-        <v>2.668348</v>
+        <v>2.6651819999999997</v>
       </c>
       <c r="K688" s="7">
-        <v>10.650728999999998</v>
+        <v>10.640673</v>
       </c>
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.25">
@@ -29124,25 +29124,25 @@
         <v>2</v>
       </c>
       <c r="E699" s="7">
-        <v>0.040046</v>
+        <v>0.040045000000000004</v>
       </c>
       <c r="F699" s="7">
-        <v>0.111651</v>
+        <v>0.11164999999999999</v>
       </c>
       <c r="G699" s="7">
-        <v>0.20762699999999998</v>
+        <v>0.20762599999999998</v>
       </c>
       <c r="H699" s="7">
-        <v>0.280974</v>
+        <v>0.280972</v>
       </c>
       <c r="I699" s="7">
-        <v>0.466875</v>
+        <v>0.46687399999999996</v>
       </c>
       <c r="J699" s="7">
-        <v>2.509088</v>
+        <v>2.509084</v>
       </c>
       <c r="K699" s="7">
-        <v>4.276561</v>
+        <v>4.276557</v>
       </c>
     </row>
     <row r="700" spans="1:11" x14ac:dyDescent="0.25">
@@ -29396,19 +29396,19 @@
         <v>7</v>
       </c>
       <c r="E707" s="7">
-        <v>0.064387</v>
+        <v>0.064091</v>
       </c>
       <c r="F707" s="7">
-        <v>0.085114</v>
+        <v>0.08481299999999999</v>
       </c>
       <c r="G707" s="7">
-        <v>0.10054500000000001</v>
+        <v>0.100239</v>
       </c>
       <c r="H707" s="7">
-        <v>0.314993</v>
+        <v>0.314627</v>
       </c>
       <c r="I707" s="7">
-        <v>0.275036</v>
+        <v>0.274682</v>
       </c>
       <c r="J707" s="7"/>
       <c r="K707" s="7"/>
@@ -29497,22 +29497,22 @@
         <v>6</v>
       </c>
       <c r="E710" s="7">
-        <v>0.12198600000000001</v>
+        <v>0.1192</v>
       </c>
       <c r="F710" s="7">
-        <v>-0.017297</v>
+        <v>-0.019737</v>
       </c>
       <c r="G710" s="7">
-        <v>-0.13254</v>
+        <v>-0.134695</v>
       </c>
       <c r="H710" s="7">
-        <v>0.052114</v>
+        <v>0.049500999999999996</v>
       </c>
       <c r="I710" s="7">
-        <v>0.6611969999999999</v>
+        <v>0.657072</v>
       </c>
       <c r="J710" s="7">
-        <v>2.718287</v>
+        <v>2.709052</v>
       </c>
       <c r="K710" s="7"/>
     </row>
@@ -29691,7 +29691,7 @@
         <v>6</v>
       </c>
       <c r="E716" s="7">
-        <v>0</v>
+        <v>0.086725</v>
       </c>
       <c r="F716" s="7"/>
       <c r="G716" s="7"/>
@@ -29772,25 +29772,25 @@
       </c>
       <c r="D719" s="6"/>
       <c r="E719" s="7">
-        <v>0.020931</v>
+        <v>0.020932</v>
       </c>
       <c r="F719" s="7">
-        <v>0.066211</v>
+        <v>0.066212</v>
       </c>
       <c r="G719" s="7">
         <v>0.119322</v>
       </c>
       <c r="H719" s="7">
-        <v>0.151022</v>
+        <v>0.151023</v>
       </c>
       <c r="I719" s="7">
         <v>0.220735</v>
       </c>
       <c r="J719" s="7">
-        <v>1.035505</v>
+        <v>1.035506</v>
       </c>
       <c r="K719" s="7">
-        <v>5.835723000000001</v>
+        <v>5.835725999999999</v>
       </c>
     </row>
     <row r="720" spans="1:11" x14ac:dyDescent="0.25">
@@ -30098,19 +30098,19 @@
         <v>4</v>
       </c>
       <c r="E729" s="7">
-        <v>0.048255</v>
+        <v>0.043979</v>
       </c>
       <c r="F729" s="7">
-        <v>0.063995</v>
+        <v>0.05965499999999999</v>
       </c>
       <c r="G729" s="7">
-        <v>0.040852000000000006</v>
+        <v>0.036606</v>
       </c>
       <c r="H729" s="7">
-        <v>0.206255</v>
+        <v>0.20133500000000001</v>
       </c>
       <c r="I729" s="7">
-        <v>0.330604</v>
+        <v>0.325177</v>
       </c>
       <c r="J729" s="7"/>
       <c r="K729" s="7"/>
@@ -30348,22 +30348,22 @@
         <v>6</v>
       </c>
       <c r="E737" s="7">
-        <v>0.054543</v>
+        <v>0.050141</v>
       </c>
       <c r="F737" s="7">
-        <v>-0.070239</v>
+        <v>-0.07412</v>
       </c>
       <c r="G737" s="7">
-        <v>0.059397000000000005</v>
+        <v>0.054974999999999996</v>
       </c>
       <c r="H737" s="7">
-        <v>0.270107</v>
+        <v>0.264805</v>
       </c>
       <c r="I737" s="7">
-        <v>0.720633</v>
+        <v>0.7134520000000001</v>
       </c>
       <c r="J737" s="7">
-        <v>1.9586789999999998</v>
+        <v>1.9463300000000001</v>
       </c>
       <c r="K737" s="7"/>
     </row>
@@ -30826,10 +30826,10 @@
         <v>2</v>
       </c>
       <c r="E753" s="7">
-        <v>0</v>
+        <v>0.040151000000000006</v>
       </c>
       <c r="F753" s="7">
-        <v>0</v>
+        <v>0.128912</v>
       </c>
       <c r="G753" s="7"/>
       <c r="H753" s="7"/>
@@ -32258,19 +32258,19 @@
         <v>6</v>
       </c>
       <c r="E799" s="7">
-        <v>0.074836</v>
+        <v>0.074928</v>
       </c>
       <c r="F799" s="7">
-        <v>0.043468</v>
+        <v>0.043557</v>
       </c>
       <c r="G799" s="7">
-        <v>0.289505</v>
+        <v>0.289616</v>
       </c>
       <c r="H799" s="7">
-        <v>0.31704699999999997</v>
+        <v>0.31716</v>
       </c>
       <c r="I799" s="7">
-        <v>0.42392</v>
+        <v>0.42404200000000003</v>
       </c>
       <c r="J799" s="7"/>
       <c r="K799" s="7"/>
@@ -32578,7 +32578,7 @@
         <v>6</v>
       </c>
       <c r="E809" s="7">
-        <v>0.060486000000000005</v>
+        <v>0.060183999999999994</v>
       </c>
       <c r="F809" s="7"/>
       <c r="G809" s="7"/>
@@ -33264,22 +33264,22 @@
         <v>2</v>
       </c>
       <c r="E831" s="7">
-        <v>0</v>
+        <v>0.031303</v>
       </c>
       <c r="F831" s="7">
-        <v>0</v>
+        <v>0.104139</v>
       </c>
       <c r="G831" s="7">
-        <v>0</v>
+        <v>0.215719</v>
       </c>
       <c r="H831" s="7">
-        <v>0</v>
+        <v>0.290946</v>
       </c>
       <c r="I831" s="7">
-        <v>0</v>
+        <v>0.47271700000000005</v>
       </c>
       <c r="J831" s="7">
-        <v>0</v>
+        <v>2.6403969999999997</v>
       </c>
       <c r="K831" s="7"/>
     </row>
@@ -33741,19 +33741,19 @@
         <v>6</v>
       </c>
       <c r="E846" s="7">
-        <v>0</v>
+        <v>-0.04851</v>
       </c>
       <c r="F846" s="7">
-        <v>0</v>
+        <v>-0.050317999999999995</v>
       </c>
       <c r="G846" s="7">
-        <v>0</v>
+        <v>-0.037482</v>
       </c>
       <c r="H846" s="7">
-        <v>0</v>
+        <v>0.152316</v>
       </c>
       <c r="I846" s="7">
-        <v>0</v>
+        <v>0.33590699999999996</v>
       </c>
       <c r="J846" s="7"/>
       <c r="K846" s="7"/>
@@ -33772,7 +33772,7 @@
         <v>5</v>
       </c>
       <c r="E847" s="7">
-        <v>0</v>
+        <v>0.04076</v>
       </c>
       <c r="F847" s="7"/>
       <c r="G847" s="7"/>
@@ -33795,19 +33795,19 @@
         <v>5</v>
       </c>
       <c r="E848" s="7">
-        <v>0.05508</v>
+        <v>0.045246</v>
       </c>
       <c r="F848" s="7">
-        <v>0.07085899999999999</v>
+        <v>0.060877999999999995</v>
       </c>
       <c r="G848" s="7">
-        <v>0.145478</v>
+        <v>0.134802</v>
       </c>
       <c r="H848" s="7">
-        <v>0.29488800000000004</v>
+        <v>0.28282</v>
       </c>
       <c r="I848" s="7">
-        <v>0.42338099999999995</v>
+        <v>0.410115</v>
       </c>
       <c r="J848" s="7"/>
       <c r="K848" s="7"/>
@@ -33847,19 +33847,19 @@
         <v>5</v>
       </c>
       <c r="E850" s="7">
-        <v>0</v>
+        <v>0.09418599999999999</v>
       </c>
       <c r="F850" s="7">
-        <v>0</v>
+        <v>0.19050599999999998</v>
       </c>
       <c r="G850" s="7">
-        <v>0</v>
+        <v>0.514014</v>
       </c>
       <c r="H850" s="7">
-        <v>0</v>
+        <v>0.47924999999999995</v>
       </c>
       <c r="I850" s="7">
-        <v>0</v>
+        <v>0.5374410000000001</v>
       </c>
       <c r="J850" s="7"/>
       <c r="K850" s="7"/>
@@ -33934,16 +33934,16 @@
         <v>6</v>
       </c>
       <c r="E853" s="7">
-        <v>0</v>
+        <v>0.090602</v>
       </c>
       <c r="F853" s="7">
-        <v>0</v>
+        <v>0.113699</v>
       </c>
       <c r="G853" s="7">
-        <v>0</v>
+        <v>0.062983</v>
       </c>
       <c r="H853" s="7">
-        <v>0</v>
+        <v>0.474274</v>
       </c>
       <c r="I853" s="7"/>
       <c r="J853" s="7"/>
@@ -34083,19 +34083,19 @@
         <v>3</v>
       </c>
       <c r="E858" s="7">
-        <v>0.114131</v>
+        <v>0.11412699999999999</v>
       </c>
       <c r="F858" s="7">
-        <v>0.229276</v>
+        <v>0.229272</v>
       </c>
       <c r="G858" s="7">
-        <v>0.269653</v>
+        <v>0.269649</v>
       </c>
       <c r="H858" s="7">
-        <v>0.368178</v>
+        <v>0.36817300000000003</v>
       </c>
       <c r="I858" s="7">
-        <v>0.465446</v>
+        <v>0.465441</v>
       </c>
       <c r="J858" s="7"/>
       <c r="K858" s="7"/>
@@ -34306,19 +34306,19 @@
         <v>5</v>
       </c>
       <c r="E865" s="7">
-        <v>0.052674000000000006</v>
+        <v>0.052601</v>
       </c>
       <c r="F865" s="7">
-        <v>0.152995</v>
+        <v>0.152916</v>
       </c>
       <c r="G865" s="7">
-        <v>0.17752099999999998</v>
+        <v>0.17744</v>
       </c>
       <c r="H865" s="7">
-        <v>0.244071</v>
+        <v>0.24398499999999998</v>
       </c>
       <c r="I865" s="7">
-        <v>0.45622999999999997</v>
+        <v>0.456129</v>
       </c>
       <c r="J865" s="7"/>
       <c r="K865" s="7"/>
@@ -34401,19 +34401,19 @@
         <v>6</v>
       </c>
       <c r="E868" s="7">
-        <v>0.084536</v>
+        <v>0.08341100000000001</v>
       </c>
       <c r="F868" s="7">
-        <v>0.040566000000000005</v>
+        <v>0.039487999999999995</v>
       </c>
       <c r="G868" s="7">
-        <v>0.141287</v>
+        <v>0.140104</v>
       </c>
       <c r="H868" s="7">
-        <v>0.269607</v>
+        <v>0.268291</v>
       </c>
       <c r="I868" s="7">
-        <v>0.071852</v>
+        <v>0.070741</v>
       </c>
       <c r="J868" s="7"/>
       <c r="K868" s="7"/>
@@ -34599,19 +34599,19 @@
         <v>6</v>
       </c>
       <c r="E874" s="7">
-        <v>0.052411000000000006</v>
+        <v>0.109906</v>
       </c>
       <c r="F874" s="7">
-        <v>-0.051035000000000004</v>
+        <v>0.000809</v>
       </c>
       <c r="G874" s="7">
-        <v>-0.138903</v>
+        <v>-0.091859</v>
       </c>
       <c r="H874" s="7">
-        <v>0.028990000000000002</v>
+        <v>0.085206</v>
       </c>
       <c r="I874" s="7">
-        <v>0.353858</v>
+        <v>0.427823</v>
       </c>
       <c r="J874" s="7"/>
       <c r="K874" s="7"/>
@@ -35009,25 +35009,25 @@
         <v>3</v>
       </c>
       <c r="E886" s="7">
-        <v>0</v>
+        <v>0.037333</v>
       </c>
       <c r="F886" s="7">
-        <v>0</v>
+        <v>0.099473</v>
       </c>
       <c r="G886" s="7">
-        <v>0</v>
+        <v>0.203459</v>
       </c>
       <c r="H886" s="7">
-        <v>0</v>
+        <v>0.29059999999999997</v>
       </c>
       <c r="I886" s="7">
-        <v>0</v>
+        <v>0.4843</v>
       </c>
       <c r="J886" s="7">
-        <v>0</v>
+        <v>1.9614250000000002</v>
       </c>
       <c r="K886" s="7">
-        <v>0</v>
+        <v>5.040625</v>
       </c>
     </row>
     <row r="887" spans="1:11" x14ac:dyDescent="0.25">
@@ -35044,19 +35044,19 @@
         <v>6</v>
       </c>
       <c r="E887" s="7">
-        <v>0.070896</v>
+        <v>0.069055</v>
       </c>
       <c r="F887" s="7">
-        <v>0.08230399999999999</v>
+        <v>0.080444</v>
       </c>
       <c r="G887" s="7">
-        <v>0.417051</v>
+        <v>0.414615</v>
       </c>
       <c r="H887" s="7">
-        <v>0.476117</v>
+        <v>0.473579</v>
       </c>
       <c r="I887" s="7">
-        <v>0.665454</v>
+        <v>0.66259</v>
       </c>
       <c r="J887" s="7"/>
       <c r="K887" s="7"/>
@@ -35875,25 +35875,25 @@
         <v>7</v>
       </c>
       <c r="E912" s="7">
-        <v>0</v>
+        <v>0.16721699999999998</v>
       </c>
       <c r="F912" s="7">
-        <v>0</v>
+        <v>0.622369</v>
       </c>
       <c r="G912" s="7">
-        <v>0</v>
+        <v>1.3385390000000001</v>
       </c>
       <c r="H912" s="7">
-        <v>0</v>
+        <v>2.102276</v>
       </c>
       <c r="I912" s="7">
-        <v>0</v>
+        <v>6.732717</v>
       </c>
       <c r="J912" s="7">
-        <v>0</v>
+        <v>613.035972</v>
       </c>
       <c r="K912" s="7">
-        <v>0</v>
+        <v>6292.1862009999995</v>
       </c>
     </row>
     <row r="913" spans="1:11" x14ac:dyDescent="0.25">
@@ -36046,19 +36046,19 @@
         <v>2</v>
       </c>
       <c r="E917" s="7">
-        <v>0.036814</v>
+        <v>0.034328</v>
       </c>
       <c r="F917" s="7">
-        <v>0.08079599999999999</v>
+        <v>0.078204</v>
       </c>
       <c r="G917" s="7">
-        <v>0.16828700000000002</v>
+        <v>0.165486</v>
       </c>
       <c r="H917" s="7">
-        <v>0.265333</v>
+        <v>0.262299</v>
       </c>
       <c r="I917" s="7">
-        <v>0.430116</v>
+        <v>0.42668599999999995</v>
       </c>
       <c r="J917" s="7"/>
       <c r="K917" s="7"/>
@@ -36308,25 +36308,25 @@
         <v>6</v>
       </c>
       <c r="E925" s="7">
-        <v>0</v>
+        <v>0.028895</v>
       </c>
       <c r="F925" s="7">
-        <v>0</v>
+        <v>0.07342800000000001</v>
       </c>
       <c r="G925" s="7">
-        <v>0</v>
+        <v>0.106816</v>
       </c>
       <c r="H925" s="7">
-        <v>0</v>
+        <v>0.129473</v>
       </c>
       <c r="I925" s="7">
-        <v>0</v>
+        <v>0.21654</v>
       </c>
       <c r="J925" s="7">
-        <v>0</v>
+        <v>1.16598</v>
       </c>
       <c r="K925" s="7">
-        <v>0</v>
+        <v>5.969944000000001</v>
       </c>
     </row>
     <row r="926" spans="1:11" x14ac:dyDescent="0.25">
@@ -36341,25 +36341,25 @@
       </c>
       <c r="D926" s="6"/>
       <c r="E926" s="7">
-        <v>0</v>
+        <v>0.036282</v>
       </c>
       <c r="F926" s="7">
-        <v>0</v>
+        <v>0.101557</v>
       </c>
       <c r="G926" s="7">
-        <v>0</v>
+        <v>0.20472</v>
       </c>
       <c r="H926" s="7">
-        <v>0</v>
+        <v>0.296947</v>
       </c>
       <c r="I926" s="7">
-        <v>0</v>
+        <v>0.635177</v>
       </c>
       <c r="J926" s="7">
-        <v>0</v>
+        <v>2.8373369999999998</v>
       </c>
       <c r="K926" s="7">
-        <v>0</v>
+        <v>19.855667</v>
       </c>
     </row>
     <row r="927" spans="1:11" x14ac:dyDescent="0.25">
@@ -36675,25 +36675,25 @@
         <v>6</v>
       </c>
       <c r="E936" s="7">
-        <v>0.113041</v>
+        <v>0.11305899999999999</v>
       </c>
       <c r="F936" s="7">
-        <v>0.023433000000000002</v>
+        <v>0.023450000000000002</v>
       </c>
       <c r="G936" s="7">
-        <v>-0.073409</v>
+        <v>-0.073394</v>
       </c>
       <c r="H936" s="7">
-        <v>0.106733</v>
+        <v>0.106751</v>
       </c>
       <c r="I936" s="7">
-        <v>0.47999699999999995</v>
+        <v>0.480021</v>
       </c>
       <c r="J936" s="7">
-        <v>2.998105</v>
+        <v>2.99817</v>
       </c>
       <c r="K936" s="7">
-        <v>12.186783</v>
+        <v>12.186995</v>
       </c>
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.25">
@@ -36739,22 +36739,22 @@
         <v>5</v>
       </c>
       <c r="E938" s="7">
-        <v>0.068997</v>
+        <v>0.062688</v>
       </c>
       <c r="F938" s="7">
-        <v>0.166572</v>
+        <v>0.159687</v>
       </c>
       <c r="G938" s="7">
-        <v>0.237435</v>
+        <v>0.230131</v>
       </c>
       <c r="H938" s="7">
-        <v>0.33608</v>
+        <v>0.32819400000000004</v>
       </c>
       <c r="I938" s="7">
-        <v>0.552475</v>
+        <v>0.543312</v>
       </c>
       <c r="J938" s="7">
-        <v>1.8525880000000001</v>
+        <v>1.835751</v>
       </c>
       <c r="K938" s="7"/>
     </row>
@@ -37112,19 +37112,19 @@
         <v>6</v>
       </c>
       <c r="E949" s="7">
-        <v>0</v>
+        <v>0.133015</v>
       </c>
       <c r="F949" s="7">
-        <v>0</v>
+        <v>0.011013</v>
       </c>
       <c r="G949" s="7">
-        <v>0</v>
+        <v>0.060400999999999996</v>
       </c>
       <c r="H949" s="7">
-        <v>0</v>
+        <v>0.277387</v>
       </c>
       <c r="I949" s="7">
-        <v>0</v>
+        <v>0.412119</v>
       </c>
       <c r="J949" s="7"/>
       <c r="K949" s="7"/>
@@ -37604,25 +37604,25 @@
         <v>5</v>
       </c>
       <c r="E967" s="7">
-        <v>0</v>
+        <v>0.056813</v>
       </c>
       <c r="F967" s="7">
-        <v>0</v>
+        <v>0.068019</v>
       </c>
       <c r="G967" s="7">
-        <v>0</v>
+        <v>0.084868</v>
       </c>
       <c r="H967" s="7">
-        <v>0</v>
+        <v>0.189177</v>
       </c>
       <c r="I967" s="7">
-        <v>0</v>
+        <v>0.33210500000000004</v>
       </c>
       <c r="J967" s="7">
-        <v>0</v>
+        <v>1.423517</v>
       </c>
       <c r="K967" s="7">
-        <v>0</v>
+        <v>5.971513</v>
       </c>
     </row>
     <row r="968" spans="1:11" x14ac:dyDescent="0.25">
@@ -37699,25 +37699,25 @@
         <v>4</v>
       </c>
       <c r="E970" s="7">
-        <v>0</v>
+        <v>0.034222999999999996</v>
       </c>
       <c r="F970" s="7">
-        <v>0</v>
+        <v>0.097774</v>
       </c>
       <c r="G970" s="7">
-        <v>0</v>
+        <v>0.147872</v>
       </c>
       <c r="H970" s="7">
-        <v>0</v>
+        <v>0.231264</v>
       </c>
       <c r="I970" s="7">
-        <v>0</v>
+        <v>0.353902</v>
       </c>
       <c r="J970" s="7">
-        <v>0</v>
+        <v>1.237786</v>
       </c>
       <c r="K970" s="7">
-        <v>0</v>
+        <v>4.864993999999999</v>
       </c>
     </row>
     <row r="971" spans="1:11" x14ac:dyDescent="0.25">
@@ -38466,19 +38466,19 @@
         <v>6</v>
       </c>
       <c r="E993" s="7">
-        <v>0</v>
+        <v>0.010677</v>
       </c>
       <c r="F993" s="7">
-        <v>0</v>
+        <v>-0.010515000000000002</v>
       </c>
       <c r="G993" s="7">
-        <v>0</v>
+        <v>0.38947499999999996</v>
       </c>
       <c r="H993" s="7">
-        <v>0</v>
+        <v>0.62663</v>
       </c>
       <c r="I993" s="7">
-        <v>0</v>
+        <v>1.000727</v>
       </c>
       <c r="J993" s="7"/>
       <c r="K993" s="7"/>
@@ -38530,22 +38530,22 @@
         <v>5</v>
       </c>
       <c r="E995" s="7">
-        <v>0</v>
+        <v>0.044596</v>
       </c>
       <c r="F995" s="7">
-        <v>0</v>
+        <v>0.031079</v>
       </c>
       <c r="G995" s="7">
-        <v>0</v>
+        <v>0.33677100000000004</v>
       </c>
       <c r="H995" s="7">
-        <v>0</v>
+        <v>0.468122</v>
       </c>
       <c r="I995" s="7">
-        <v>0</v>
+        <v>0.6873260000000001</v>
       </c>
       <c r="J995" s="7">
-        <v>0</v>
+        <v>2.307952</v>
       </c>
       <c r="K995" s="7"/>
     </row>
@@ -39153,25 +39153,25 @@
         <v>5</v>
       </c>
       <c r="E1014" s="7">
-        <v>0</v>
+        <v>0.068358</v>
       </c>
       <c r="F1014" s="7">
-        <v>0</v>
+        <v>0.058917000000000004</v>
       </c>
       <c r="G1014" s="7">
-        <v>0</v>
+        <v>0.062917</v>
       </c>
       <c r="H1014" s="7">
-        <v>0</v>
+        <v>0.19007100000000002</v>
       </c>
       <c r="I1014" s="7">
-        <v>0</v>
+        <v>0.248689</v>
       </c>
       <c r="J1014" s="7">
-        <v>0</v>
+        <v>1.135743</v>
       </c>
       <c r="K1014" s="7">
-        <v>0</v>
+        <v>4.674113</v>
       </c>
     </row>
     <row r="1015" spans="1:11" x14ac:dyDescent="0.25">
@@ -39335,25 +39335,25 @@
         <v>6</v>
       </c>
       <c r="E1020" s="7">
-        <v>0</v>
+        <v>0.068673</v>
       </c>
       <c r="F1020" s="7">
-        <v>0</v>
+        <v>0.083218</v>
       </c>
       <c r="G1020" s="7">
-        <v>0</v>
+        <v>0.230101</v>
       </c>
       <c r="H1020" s="7">
-        <v>0</v>
+        <v>0.220762</v>
       </c>
       <c r="I1020" s="7">
-        <v>0</v>
+        <v>0.452102</v>
       </c>
       <c r="J1020" s="7">
-        <v>0</v>
+        <v>2.08394</v>
       </c>
       <c r="K1020" s="7">
-        <v>0</v>
+        <v>8.410175</v>
       </c>
     </row>
     <row r="1021" spans="1:11" x14ac:dyDescent="0.25">
@@ -39622,25 +39622,25 @@
         <v>7</v>
       </c>
       <c r="E1029" s="7">
-        <v>0</v>
+        <v>0.174067</v>
       </c>
       <c r="F1029" s="7">
-        <v>0</v>
+        <v>-0.087451</v>
       </c>
       <c r="G1029" s="7">
-        <v>0</v>
+        <v>-0.220639</v>
       </c>
       <c r="H1029" s="7">
-        <v>0</v>
+        <v>0.0065969999999999996</v>
       </c>
       <c r="I1029" s="7">
-        <v>0</v>
+        <v>0.900271</v>
       </c>
       <c r="J1029" s="7">
-        <v>0</v>
+        <v>3.487622</v>
       </c>
       <c r="K1029" s="7">
-        <v>0</v>
+        <v>12.266448</v>
       </c>
     </row>
     <row r="1030" spans="1:11" x14ac:dyDescent="0.25">
@@ -39946,22 +39946,22 @@
         <v>6</v>
       </c>
       <c r="E1039" s="7">
-        <v>0.088319</v>
+        <v>0.08436500000000001</v>
       </c>
       <c r="F1039" s="7">
-        <v>0.037413</v>
+        <v>0.033644</v>
       </c>
       <c r="G1039" s="7">
-        <v>0.109493</v>
+        <v>0.105462</v>
       </c>
       <c r="H1039" s="7">
-        <v>0.246322</v>
+        <v>0.241794</v>
       </c>
       <c r="I1039" s="7">
-        <v>0.49914499999999995</v>
+        <v>0.49369799999999997</v>
       </c>
       <c r="J1039" s="7">
-        <v>1.752734</v>
+        <v>1.742733</v>
       </c>
       <c r="K1039" s="7"/>
     </row>
@@ -40503,25 +40503,25 @@
         <v>5</v>
       </c>
       <c r="E1056" s="7">
-        <v>0.059960000000000006</v>
+        <v>0.05985</v>
       </c>
       <c r="F1056" s="7">
-        <v>0.066333</v>
+        <v>0.066222</v>
       </c>
       <c r="G1056" s="7">
-        <v>0.072144</v>
+        <v>0.072033</v>
       </c>
       <c r="H1056" s="7">
-        <v>0.15975799999999998</v>
+        <v>0.159637</v>
       </c>
       <c r="I1056" s="7">
-        <v>0.224987</v>
+        <v>0.22486</v>
       </c>
       <c r="J1056" s="7">
-        <v>1.258179</v>
+        <v>1.257945</v>
       </c>
       <c r="K1056" s="7">
-        <v>7.1545119999999995</v>
+        <v>7.153665999999999</v>
       </c>
     </row>
     <row r="1057" spans="1:11" x14ac:dyDescent="0.25">
@@ -40728,22 +40728,22 @@
         <v>6</v>
       </c>
       <c r="E1063" s="7">
-        <v>0.047023999999999996</v>
+        <v>0.042747</v>
       </c>
       <c r="F1063" s="7">
-        <v>0.025092</v>
+        <v>0.020904</v>
       </c>
       <c r="G1063" s="7">
-        <v>0.11607100000000001</v>
+        <v>0.111511</v>
       </c>
       <c r="H1063" s="7">
-        <v>0.251776</v>
+        <v>0.246662</v>
       </c>
       <c r="I1063" s="7">
-        <v>0.37160899999999997</v>
+        <v>0.366006</v>
       </c>
       <c r="J1063" s="7">
-        <v>1.424498</v>
+        <v>1.4145930000000002</v>
       </c>
       <c r="K1063" s="7"/>
     </row>
@@ -40761,19 +40761,19 @@
         <v>5</v>
       </c>
       <c r="E1064" s="7">
-        <v>0.060887000000000004</v>
+        <v>0.061197999999999995</v>
       </c>
       <c r="F1064" s="7">
-        <v>0.13767200000000002</v>
+        <v>0.138006</v>
       </c>
       <c r="G1064" s="7">
-        <v>0.19930499999999998</v>
+        <v>0.19965599999999997</v>
       </c>
       <c r="H1064" s="7">
-        <v>0.288015</v>
+        <v>0.288393</v>
       </c>
       <c r="I1064" s="7">
-        <v>0.32359099999999996</v>
+        <v>0.323979</v>
       </c>
       <c r="J1064" s="7"/>
       <c r="K1064" s="7"/>

--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>02.09.2026 09:29:33</t>
+    <t>02.09.2026 10:13:39</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -6967,25 +6967,25 @@
         <v>1</v>
       </c>
       <c r="E6" s="7">
-        <v>0</v>
+        <v>0.01918</v>
       </c>
       <c r="F6" s="7">
-        <v>0</v>
+        <v>0.072057</v>
       </c>
       <c r="G6" s="7">
-        <v>0</v>
+        <v>0.17857199999999998</v>
       </c>
       <c r="H6" s="7">
-        <v>0</v>
+        <v>0.251619</v>
       </c>
       <c r="I6" s="7">
-        <v>0</v>
+        <v>0.430253</v>
       </c>
       <c r="J6" s="7">
-        <v>0</v>
+        <v>2.456244</v>
       </c>
       <c r="K6" s="7">
-        <v>0</v>
+        <v>3.980175</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -8624,25 +8624,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.025560999999999997</v>
+        <v>0.025878</v>
       </c>
       <c r="F55" s="7">
-        <v>0.022928999999999998</v>
+        <v>0.023243999999999997</v>
       </c>
       <c r="G55" s="7">
-        <v>-0.027721</v>
+        <v>-0.027421</v>
       </c>
       <c r="H55" s="7">
-        <v>0.15949</v>
+        <v>0.159847</v>
       </c>
       <c r="I55" s="7">
-        <v>0.193095</v>
+        <v>0.193463</v>
       </c>
       <c r="J55" s="7">
-        <v>0.7384869999999999</v>
+        <v>0.739023</v>
       </c>
       <c r="K55" s="7">
-        <v>6.344099</v>
+        <v>6.3463639999999995</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -8926,22 +8926,22 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.085304</v>
+        <v>0.085413</v>
       </c>
       <c r="F65" s="7">
-        <v>0.030379999999999997</v>
+        <v>0.030484</v>
       </c>
       <c r="G65" s="7">
-        <v>0.041976000000000006</v>
+        <v>0.042081999999999994</v>
       </c>
       <c r="H65" s="7">
-        <v>-0.050085</v>
+        <v>-0.049989</v>
       </c>
       <c r="I65" s="7">
-        <v>0.040423</v>
+        <v>0.040529</v>
       </c>
       <c r="J65" s="7">
-        <v>2.234786</v>
+        <v>2.235113</v>
       </c>
       <c r="K65" s="7"/>
     </row>
@@ -9021,19 +9021,19 @@
         <v>5</v>
       </c>
       <c r="E68" s="7">
-        <v>0.033926</v>
+        <v>0.034173</v>
       </c>
       <c r="F68" s="7">
-        <v>0.054833999999999994</v>
+        <v>0.055086</v>
       </c>
       <c r="G68" s="7">
-        <v>0.056515</v>
+        <v>0.056768</v>
       </c>
       <c r="H68" s="7">
-        <v>0.143537</v>
+        <v>0.14381</v>
       </c>
       <c r="I68" s="7">
-        <v>0.298363</v>
+        <v>0.298674</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
@@ -10080,16 +10080,16 @@
         <v>7</v>
       </c>
       <c r="E103" s="7">
-        <v>0.055556999999999995</v>
+        <v>0.055552000000000004</v>
       </c>
       <c r="F103" s="7">
-        <v>0.152531</v>
+        <v>0.152526</v>
       </c>
       <c r="G103" s="7">
-        <v>0.39752000000000004</v>
+        <v>0.397513</v>
       </c>
       <c r="H103" s="7">
-        <v>0.5615359999999999</v>
+        <v>0.56153</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
@@ -11927,19 +11927,19 @@
         <v>7</v>
       </c>
       <c r="E162" s="7">
-        <v>0.024173</v>
+        <v>0.023991</v>
       </c>
       <c r="F162" s="7">
-        <v>-0.39115900000000003</v>
+        <v>-0.391267</v>
       </c>
       <c r="G162" s="7">
-        <v>-0.741589</v>
+        <v>-0.741635</v>
       </c>
       <c r="H162" s="7">
-        <v>-0.846183</v>
+        <v>-0.8462109999999999</v>
       </c>
       <c r="I162" s="7">
-        <v>-0.875943</v>
+        <v>-0.8759650000000001</v>
       </c>
       <c r="J162" s="7"/>
       <c r="K162" s="7"/>
@@ -12078,19 +12078,19 @@
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="7">
-        <v>0.045345</v>
+        <v>0.040052000000000004</v>
       </c>
       <c r="F167" s="7">
-        <v>0.09082599999999999</v>
+        <v>0.085303</v>
       </c>
       <c r="G167" s="7">
-        <v>0.10086</v>
+        <v>0.09528600000000001</v>
       </c>
       <c r="H167" s="7">
-        <v>0.134883</v>
+        <v>0.129137</v>
       </c>
       <c r="I167" s="7">
-        <v>0.259395</v>
+        <v>0.253018</v>
       </c>
       <c r="J167" s="7"/>
       <c r="K167" s="7"/>
@@ -12371,19 +12371,19 @@
         <v>7</v>
       </c>
       <c r="E176" s="7">
-        <v>-0.042</v>
+        <v>-0.041527</v>
       </c>
       <c r="F176" s="7">
-        <v>0.05566499999999999</v>
+        <v>0.056186999999999994</v>
       </c>
       <c r="G176" s="7">
-        <v>-0.077858</v>
+        <v>-0.077402</v>
       </c>
       <c r="H176" s="7">
-        <v>0.018941</v>
+        <v>0.019444</v>
       </c>
       <c r="I176" s="7">
-        <v>0.15148799999999998</v>
+        <v>0.152057</v>
       </c>
       <c r="J176" s="7"/>
       <c r="K176" s="7"/>
@@ -12429,25 +12429,25 @@
         <v>6</v>
       </c>
       <c r="E178" s="7">
-        <v>0.033122</v>
+        <v>0.032799</v>
       </c>
       <c r="F178" s="7">
-        <v>0.065931</v>
+        <v>0.065598</v>
       </c>
       <c r="G178" s="7">
-        <v>0.09114599999999999</v>
+        <v>0.090806</v>
       </c>
       <c r="H178" s="7">
-        <v>0.138523</v>
+        <v>0.138168</v>
       </c>
       <c r="I178" s="7">
-        <v>0.228877</v>
+        <v>0.228493</v>
       </c>
       <c r="J178" s="7">
-        <v>1.299877</v>
+        <v>1.299159</v>
       </c>
       <c r="K178" s="7">
-        <v>5.698249</v>
+        <v>5.6961580000000005</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -12881,25 +12881,25 @@
         <v>3</v>
       </c>
       <c r="E192" s="7">
-        <v>0.031425999999999996</v>
+        <v>0.031423</v>
       </c>
       <c r="F192" s="7">
-        <v>0.075875</v>
+        <v>0.075873</v>
       </c>
       <c r="G192" s="7">
-        <v>0.094763</v>
+        <v>0.09476000000000001</v>
       </c>
       <c r="H192" s="7">
-        <v>0.144314</v>
+        <v>0.144311</v>
       </c>
       <c r="I192" s="7">
-        <v>0.22572199999999998</v>
+        <v>0.225719</v>
       </c>
       <c r="J192" s="7">
-        <v>1.678097</v>
+        <v>1.67809</v>
       </c>
       <c r="K192" s="7">
-        <v>8.088612000000001</v>
+        <v>8.088587</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -14598,25 +14598,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.050051</v>
+        <v>0.047195999999999995</v>
       </c>
       <c r="F247" s="7">
-        <v>0.086365</v>
+        <v>0.08341100000000001</v>
       </c>
       <c r="G247" s="7">
-        <v>0.080503</v>
+        <v>0.077565</v>
       </c>
       <c r="H247" s="7">
-        <v>0.172307</v>
+        <v>0.169119</v>
       </c>
       <c r="I247" s="7">
-        <v>0.36344299999999996</v>
+        <v>0.359736</v>
       </c>
       <c r="J247" s="7">
-        <v>1.888571</v>
+        <v>1.880717</v>
       </c>
       <c r="K247" s="7">
-        <v>6.306337999999999</v>
+        <v>6.2864700000000004</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -15691,25 +15691,25 @@
         <v>3</v>
       </c>
       <c r="E280" s="7">
-        <v>0</v>
+        <v>0.033702</v>
       </c>
       <c r="F280" s="7">
-        <v>0</v>
+        <v>0.081275</v>
       </c>
       <c r="G280" s="7">
-        <v>0</v>
+        <v>0.11768200000000001</v>
       </c>
       <c r="H280" s="7">
-        <v>0</v>
+        <v>0.22792500000000002</v>
       </c>
       <c r="I280" s="7">
-        <v>0</v>
+        <v>0.38181899999999996</v>
       </c>
       <c r="J280" s="7">
-        <v>0</v>
+        <v>2.213215</v>
       </c>
       <c r="K280" s="7">
-        <v>0</v>
+        <v>6.142885</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -16099,19 +16099,19 @@
         <v>5</v>
       </c>
       <c r="E292" s="7">
-        <v>0</v>
+        <v>0.050594</v>
       </c>
       <c r="F292" s="7">
-        <v>0</v>
+        <v>0.025833</v>
       </c>
       <c r="G292" s="7">
-        <v>0</v>
+        <v>0.050635000000000006</v>
       </c>
       <c r="H292" s="7">
-        <v>0</v>
+        <v>0.158301</v>
       </c>
       <c r="I292" s="7">
-        <v>0</v>
+        <v>0.208343</v>
       </c>
       <c r="J292" s="7"/>
       <c r="K292" s="7"/>
@@ -16588,22 +16588,22 @@
         <v>5</v>
       </c>
       <c r="E307" s="7">
-        <v>0.032544</v>
+        <v>0.032548</v>
       </c>
       <c r="F307" s="7">
-        <v>0.046246</v>
+        <v>0.04625</v>
       </c>
       <c r="G307" s="7">
-        <v>0.158946</v>
+        <v>0.15895</v>
       </c>
       <c r="H307" s="7">
-        <v>0.205382</v>
+        <v>0.20538599999999999</v>
       </c>
       <c r="I307" s="7">
-        <v>0.34747300000000003</v>
+        <v>0.34747799999999995</v>
       </c>
       <c r="J307" s="7">
-        <v>0.40720399999999995</v>
+        <v>0.40720999999999996</v>
       </c>
       <c r="K307" s="7"/>
     </row>
@@ -17088,25 +17088,25 @@
         <v>2</v>
       </c>
       <c r="E323" s="7">
-        <v>0</v>
+        <v>0.03696</v>
       </c>
       <c r="F323" s="7">
-        <v>0</v>
+        <v>0.09533799999999999</v>
       </c>
       <c r="G323" s="7">
-        <v>0</v>
+        <v>0.14957700000000002</v>
       </c>
       <c r="H323" s="7">
-        <v>0</v>
+        <v>0.242592</v>
       </c>
       <c r="I323" s="7">
-        <v>0</v>
+        <v>0.391918</v>
       </c>
       <c r="J323" s="7">
-        <v>0</v>
+        <v>2.098303</v>
       </c>
       <c r="K323" s="7">
-        <v>0</v>
+        <v>3.8906240000000003</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
@@ -17226,25 +17226,25 @@
         <v>3</v>
       </c>
       <c r="E327" s="7">
-        <v>0</v>
+        <v>0.034525</v>
       </c>
       <c r="F327" s="7">
-        <v>0</v>
+        <v>0.082208</v>
       </c>
       <c r="G327" s="7">
-        <v>0</v>
+        <v>0.125789</v>
       </c>
       <c r="H327" s="7">
-        <v>0</v>
+        <v>0.237378</v>
       </c>
       <c r="I327" s="7">
-        <v>0</v>
+        <v>0.39063000000000003</v>
       </c>
       <c r="J327" s="7">
-        <v>0</v>
+        <v>2.1817949999999997</v>
       </c>
       <c r="K327" s="7">
-        <v>0</v>
+        <v>6.307193999999999</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -17422,19 +17422,19 @@
         <v>5</v>
       </c>
       <c r="E333" s="7">
-        <v>0.05586</v>
+        <v>0.048194</v>
       </c>
       <c r="F333" s="7">
-        <v>0.062469000000000004</v>
+        <v>0.054755000000000005</v>
       </c>
       <c r="G333" s="7">
-        <v>0.069401</v>
+        <v>0.061637000000000004</v>
       </c>
       <c r="H333" s="7">
-        <v>0.210375</v>
+        <v>0.201588</v>
       </c>
       <c r="I333" s="7">
-        <v>0.356025</v>
+        <v>0.34618000000000004</v>
       </c>
       <c r="J333" s="7"/>
       <c r="K333" s="7"/>
@@ -17810,25 +17810,25 @@
         <v>6</v>
       </c>
       <c r="E345" s="7">
-        <v>0</v>
+        <v>0.014074999999999999</v>
       </c>
       <c r="F345" s="7">
-        <v>0</v>
+        <v>-0.054174</v>
       </c>
       <c r="G345" s="7">
-        <v>0</v>
+        <v>0.385196</v>
       </c>
       <c r="H345" s="7">
-        <v>0</v>
+        <v>0.40432</v>
       </c>
       <c r="I345" s="7">
-        <v>0</v>
+        <v>0.746288</v>
       </c>
       <c r="J345" s="7">
-        <v>0</v>
+        <v>2.418833</v>
       </c>
       <c r="K345" s="7">
-        <v>0</v>
+        <v>8.079734</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -17845,16 +17845,16 @@
         <v>7</v>
       </c>
       <c r="E346" s="7">
-        <v>0</v>
+        <v>0.146393</v>
       </c>
       <c r="F346" s="7">
-        <v>0</v>
+        <v>-0.103852</v>
       </c>
       <c r="G346" s="7">
-        <v>0</v>
+        <v>-0.243258</v>
       </c>
       <c r="H346" s="7">
-        <v>0</v>
+        <v>-0.05769</v>
       </c>
       <c r="I346" s="7"/>
       <c r="J346" s="7"/>
@@ -17940,22 +17940,22 @@
         <v>6</v>
       </c>
       <c r="E349" s="7">
-        <v>0</v>
+        <v>-0.003461</v>
       </c>
       <c r="F349" s="7">
-        <v>0</v>
+        <v>-0.104835</v>
       </c>
       <c r="G349" s="7">
-        <v>0</v>
+        <v>0.061155</v>
       </c>
       <c r="H349" s="7">
-        <v>0</v>
+        <v>0.161662</v>
       </c>
       <c r="I349" s="7">
-        <v>0</v>
+        <v>0.33520099999999997</v>
       </c>
       <c r="J349" s="7">
-        <v>0</v>
+        <v>1.158243</v>
       </c>
       <c r="K349" s="7"/>
     </row>
@@ -17973,22 +17973,22 @@
         <v>5</v>
       </c>
       <c r="E350" s="7">
-        <v>0</v>
+        <v>0.041866</v>
       </c>
       <c r="F350" s="7">
-        <v>0</v>
+        <v>0.052194000000000004</v>
       </c>
       <c r="G350" s="7">
-        <v>0</v>
+        <v>0.011798</v>
       </c>
       <c r="H350" s="7">
-        <v>0</v>
+        <v>0.16899699999999998</v>
       </c>
       <c r="I350" s="7">
-        <v>0</v>
+        <v>0.277527</v>
       </c>
       <c r="J350" s="7">
-        <v>0</v>
+        <v>1.6329859999999998</v>
       </c>
       <c r="K350" s="7"/>
     </row>
@@ -18041,25 +18041,25 @@
         <v>6</v>
       </c>
       <c r="E352" s="7">
-        <v>0</v>
+        <v>0.092073</v>
       </c>
       <c r="F352" s="7">
-        <v>0</v>
+        <v>0.063127</v>
       </c>
       <c r="G352" s="7">
-        <v>0</v>
+        <v>0.162832</v>
       </c>
       <c r="H352" s="7">
-        <v>0</v>
+        <v>0.282638</v>
       </c>
       <c r="I352" s="7">
-        <v>0</v>
+        <v>0.573213</v>
       </c>
       <c r="J352" s="7">
-        <v>0</v>
+        <v>1.560164</v>
       </c>
       <c r="K352" s="7">
-        <v>0</v>
+        <v>7.010205999999999</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
@@ -18109,25 +18109,25 @@
         <v>5</v>
       </c>
       <c r="E354" s="7">
-        <v>0</v>
+        <v>-0.007566000000000001</v>
       </c>
       <c r="F354" s="7">
-        <v>0</v>
+        <v>-0.097328</v>
       </c>
       <c r="G354" s="7">
-        <v>0</v>
+        <v>0.025507</v>
       </c>
       <c r="H354" s="7">
-        <v>0</v>
+        <v>0.21283000000000002</v>
       </c>
       <c r="I354" s="7">
-        <v>0</v>
+        <v>0.39387</v>
       </c>
       <c r="J354" s="7">
-        <v>0</v>
+        <v>0.754683</v>
       </c>
       <c r="K354" s="7">
-        <v>0</v>
+        <v>4.070085000000001</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -18144,25 +18144,25 @@
         <v>4</v>
       </c>
       <c r="E355" s="7">
-        <v>0</v>
+        <v>0.03844</v>
       </c>
       <c r="F355" s="7">
-        <v>0</v>
+        <v>0.066507</v>
       </c>
       <c r="G355" s="7">
-        <v>0</v>
+        <v>0.060618</v>
       </c>
       <c r="H355" s="7">
-        <v>0</v>
+        <v>0.196554</v>
       </c>
       <c r="I355" s="7">
-        <v>0</v>
+        <v>0.324765</v>
       </c>
       <c r="J355" s="7">
-        <v>0</v>
+        <v>1.961813</v>
       </c>
       <c r="K355" s="7">
-        <v>0</v>
+        <v>6.8713999999999995</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
@@ -18179,22 +18179,22 @@
         <v>5</v>
       </c>
       <c r="E356" s="7">
-        <v>0</v>
+        <v>0.031684000000000004</v>
       </c>
       <c r="F356" s="7">
-        <v>0</v>
+        <v>0.092066</v>
       </c>
       <c r="G356" s="7">
-        <v>0</v>
+        <v>0.159798</v>
       </c>
       <c r="H356" s="7">
-        <v>0</v>
+        <v>0.38257800000000003</v>
       </c>
       <c r="I356" s="7">
-        <v>0</v>
+        <v>0.45049500000000003</v>
       </c>
       <c r="J356" s="7">
-        <v>0</v>
+        <v>0.8595579999999999</v>
       </c>
       <c r="K356" s="7"/>
     </row>
@@ -18282,25 +18282,25 @@
         <v>3</v>
       </c>
       <c r="E359" s="7">
-        <v>0</v>
+        <v>0.034779</v>
       </c>
       <c r="F359" s="7">
-        <v>0</v>
+        <v>0.077276</v>
       </c>
       <c r="G359" s="7">
-        <v>0</v>
+        <v>0.126571</v>
       </c>
       <c r="H359" s="7">
-        <v>0</v>
+        <v>0.229177</v>
       </c>
       <c r="I359" s="7">
-        <v>0</v>
+        <v>0.380017</v>
       </c>
       <c r="J359" s="7">
-        <v>0</v>
+        <v>2.17523</v>
       </c>
       <c r="K359" s="7">
-        <v>0</v>
+        <v>6.019676</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
@@ -18352,25 +18352,25 @@
         <v>5</v>
       </c>
       <c r="E361" s="7">
-        <v>0</v>
+        <v>0.040047</v>
       </c>
       <c r="F361" s="7">
-        <v>0</v>
+        <v>0.046673</v>
       </c>
       <c r="G361" s="7">
-        <v>0</v>
+        <v>0.13445000000000001</v>
       </c>
       <c r="H361" s="7">
-        <v>0</v>
+        <v>0.24171900000000002</v>
       </c>
       <c r="I361" s="7">
-        <v>0</v>
+        <v>0.35745399999999994</v>
       </c>
       <c r="J361" s="7">
-        <v>0</v>
+        <v>1.431667</v>
       </c>
       <c r="K361" s="7">
-        <v>0</v>
+        <v>6.289868</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
@@ -18387,22 +18387,22 @@
         <v>6</v>
       </c>
       <c r="E362" s="7">
-        <v>0</v>
+        <v>-0.030438</v>
       </c>
       <c r="F362" s="7">
-        <v>0</v>
+        <v>0.04245</v>
       </c>
       <c r="G362" s="7">
-        <v>0</v>
+        <v>0.040381</v>
       </c>
       <c r="H362" s="7">
-        <v>0</v>
+        <v>0.08278600000000001</v>
       </c>
       <c r="I362" s="7">
-        <v>0</v>
+        <v>0.11274200000000001</v>
       </c>
       <c r="J362" s="7">
-        <v>0</v>
+        <v>1.322243</v>
       </c>
       <c r="K362" s="7"/>
     </row>
@@ -18420,22 +18420,22 @@
         <v>5</v>
       </c>
       <c r="E363" s="7">
-        <v>0</v>
+        <v>0.034317</v>
       </c>
       <c r="F363" s="7">
-        <v>0</v>
+        <v>0.088007</v>
       </c>
       <c r="G363" s="7">
-        <v>0</v>
+        <v>0.041934</v>
       </c>
       <c r="H363" s="7">
-        <v>0</v>
+        <v>0.078498</v>
       </c>
       <c r="I363" s="7">
-        <v>0</v>
+        <v>0.163472</v>
       </c>
       <c r="J363" s="7">
-        <v>0</v>
+        <v>1.6313849999999999</v>
       </c>
       <c r="K363" s="7"/>
     </row>
@@ -18598,22 +18598,22 @@
       </c>
       <c r="D369" s="6"/>
       <c r="E369" s="7">
-        <v>0</v>
+        <v>0.027924</v>
       </c>
       <c r="F369" s="7">
-        <v>0</v>
+        <v>0.042950999999999996</v>
       </c>
       <c r="G369" s="7">
-        <v>0</v>
+        <v>0.09845100000000001</v>
       </c>
       <c r="H369" s="7">
-        <v>0</v>
+        <v>0.214086</v>
       </c>
       <c r="I369" s="7">
-        <v>0</v>
+        <v>0.292702</v>
       </c>
       <c r="J369" s="7">
-        <v>0</v>
+        <v>1.512438</v>
       </c>
       <c r="K369" s="7"/>
     </row>
@@ -19489,25 +19489,25 @@
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="7">
-        <v>0.029062</v>
+        <v>0.028174</v>
       </c>
       <c r="F398" s="7">
-        <v>0.043521000000000004</v>
+        <v>0.042621</v>
       </c>
       <c r="G398" s="7">
-        <v>0.14408300000000002</v>
+        <v>0.143096</v>
       </c>
       <c r="H398" s="7">
-        <v>0.22806200000000001</v>
+        <v>0.22700299999999998</v>
       </c>
       <c r="I398" s="7">
-        <v>0.339652</v>
+        <v>0.338496</v>
       </c>
       <c r="J398" s="7">
-        <v>1.519966</v>
+        <v>1.517792</v>
       </c>
       <c r="K398" s="7">
-        <v>6.515687000000001</v>
+        <v>6.509203</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
@@ -21427,22 +21427,22 @@
         <v>7</v>
       </c>
       <c r="E458" s="7">
-        <v>0</v>
+        <v>-0.48865499999999995</v>
       </c>
       <c r="F458" s="7">
-        <v>0</v>
+        <v>-0.482854</v>
       </c>
       <c r="G458" s="7">
-        <v>0</v>
+        <v>-0.45115</v>
       </c>
       <c r="H458" s="7">
-        <v>0</v>
+        <v>-0.452951</v>
       </c>
       <c r="I458" s="7">
-        <v>0</v>
+        <v>-0.573418</v>
       </c>
       <c r="J458" s="7">
-        <v>0</v>
+        <v>0.6413899999999999</v>
       </c>
       <c r="K458" s="7"/>
     </row>
@@ -23013,19 +23013,19 @@
         <v>6</v>
       </c>
       <c r="E506" s="7">
-        <v>0</v>
+        <v>0.035344</v>
       </c>
       <c r="F506" s="7">
-        <v>0</v>
+        <v>0.031966999999999995</v>
       </c>
       <c r="G506" s="7">
-        <v>0</v>
+        <v>0.10725</v>
       </c>
       <c r="H506" s="7">
-        <v>0</v>
+        <v>0.26428799999999997</v>
       </c>
       <c r="I506" s="7">
-        <v>0</v>
+        <v>0.40369900000000003</v>
       </c>
       <c r="J506" s="7"/>
       <c r="K506" s="7"/>
@@ -23311,19 +23311,19 @@
         <v>7</v>
       </c>
       <c r="E516" s="7">
-        <v>0</v>
+        <v>-0.005979</v>
       </c>
       <c r="F516" s="7">
-        <v>0</v>
+        <v>0.054432999999999995</v>
       </c>
       <c r="G516" s="7">
-        <v>0</v>
+        <v>0.151172</v>
       </c>
       <c r="H516" s="7">
-        <v>0</v>
+        <v>0.309146</v>
       </c>
       <c r="I516" s="7">
-        <v>0</v>
+        <v>0.261776</v>
       </c>
       <c r="J516" s="7"/>
       <c r="K516" s="7"/>
@@ -23536,19 +23536,19 @@
         <v>2</v>
       </c>
       <c r="E523" s="7">
-        <v>0</v>
+        <v>0.02828</v>
       </c>
       <c r="F523" s="7">
-        <v>0</v>
+        <v>0.09011100000000001</v>
       </c>
       <c r="G523" s="7">
-        <v>0</v>
+        <v>0.191537</v>
       </c>
       <c r="H523" s="7">
-        <v>0</v>
+        <v>0.238959</v>
       </c>
       <c r="I523" s="7">
-        <v>0</v>
+        <v>0.33972499999999994</v>
       </c>
       <c r="J523" s="7"/>
       <c r="K523" s="7"/>
@@ -23633,19 +23633,19 @@
         <v>4</v>
       </c>
       <c r="E526" s="7">
-        <v>0</v>
+        <v>0.027286</v>
       </c>
       <c r="F526" s="7">
-        <v>0</v>
+        <v>0.051272000000000005</v>
       </c>
       <c r="G526" s="7">
-        <v>0</v>
+        <v>0.091744</v>
       </c>
       <c r="H526" s="7">
-        <v>0</v>
+        <v>0.126546</v>
       </c>
       <c r="I526" s="7">
-        <v>0</v>
+        <v>0.189999</v>
       </c>
       <c r="J526" s="7"/>
       <c r="K526" s="7"/>
@@ -24061,19 +24061,19 @@
         <v>6</v>
       </c>
       <c r="E540" s="7">
-        <v>0</v>
+        <v>0.023889999999999998</v>
       </c>
       <c r="F540" s="7">
-        <v>0</v>
+        <v>0.040976</v>
       </c>
       <c r="G540" s="7">
-        <v>0</v>
+        <v>0.069497</v>
       </c>
       <c r="H540" s="7">
-        <v>0</v>
+        <v>0.086166</v>
       </c>
       <c r="I540" s="7">
-        <v>0</v>
+        <v>0.126979</v>
       </c>
       <c r="J540" s="7"/>
       <c r="K540" s="7"/>
@@ -24379,25 +24379,25 @@
         <v>5</v>
       </c>
       <c r="E550" s="7">
-        <v>0</v>
+        <v>0.05556</v>
       </c>
       <c r="F550" s="7">
-        <v>0</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="G550" s="7">
-        <v>0</v>
+        <v>0.121067</v>
       </c>
       <c r="H550" s="7">
-        <v>0</v>
+        <v>0.258614</v>
       </c>
       <c r="I550" s="7">
-        <v>0</v>
+        <v>0.39448300000000003</v>
       </c>
       <c r="J550" s="7">
-        <v>0</v>
+        <v>2.152057</v>
       </c>
       <c r="K550" s="7">
-        <v>0</v>
+        <v>10.531714</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.25">
@@ -24439,25 +24439,25 @@
         <v>5</v>
       </c>
       <c r="E552" s="7">
-        <v>0</v>
+        <v>0.045678</v>
       </c>
       <c r="F552" s="7">
-        <v>0</v>
+        <v>0.041178</v>
       </c>
       <c r="G552" s="7">
-        <v>0</v>
+        <v>0.080193</v>
       </c>
       <c r="H552" s="7">
-        <v>0</v>
+        <v>0.151397</v>
       </c>
       <c r="I552" s="7">
-        <v>0</v>
+        <v>0.254469</v>
       </c>
       <c r="J552" s="7">
-        <v>0</v>
+        <v>1.2869110000000001</v>
       </c>
       <c r="K552" s="7">
-        <v>0</v>
+        <v>5.6832259999999994</v>
       </c>
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.25">
@@ -24474,25 +24474,25 @@
         <v>3</v>
       </c>
       <c r="E553" s="7">
-        <v>0</v>
+        <v>0.023273000000000002</v>
       </c>
       <c r="F553" s="7">
-        <v>0</v>
+        <v>0.065384</v>
       </c>
       <c r="G553" s="7">
-        <v>0</v>
+        <v>0.11636300000000001</v>
       </c>
       <c r="H553" s="7">
-        <v>0</v>
+        <v>0.154777</v>
       </c>
       <c r="I553" s="7">
-        <v>0</v>
+        <v>0.22706600000000002</v>
       </c>
       <c r="J553" s="7">
-        <v>0</v>
+        <v>1.181711</v>
       </c>
       <c r="K553" s="7">
-        <v>0</v>
+        <v>6.514569</v>
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.25">
@@ -24998,25 +24998,25 @@
         <v>6</v>
       </c>
       <c r="E569" s="7">
-        <v>0</v>
+        <v>0.036711</v>
       </c>
       <c r="F569" s="7">
-        <v>0</v>
+        <v>0.048263999999999994</v>
       </c>
       <c r="G569" s="7">
-        <v>0</v>
+        <v>0.095345</v>
       </c>
       <c r="H569" s="7">
-        <v>0</v>
+        <v>0.12465999999999999</v>
       </c>
       <c r="I569" s="7">
-        <v>0</v>
+        <v>0.20878799999999997</v>
       </c>
       <c r="J569" s="7">
-        <v>0</v>
+        <v>1.502217</v>
       </c>
       <c r="K569" s="7">
-        <v>0</v>
+        <v>6.80429</v>
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.25">
@@ -25219,25 +25219,25 @@
         <v>6</v>
       </c>
       <c r="E576" s="7">
-        <v>0</v>
+        <v>0.012044</v>
       </c>
       <c r="F576" s="7">
-        <v>0</v>
+        <v>0.002202</v>
       </c>
       <c r="G576" s="7">
-        <v>0</v>
+        <v>-0.083289</v>
       </c>
       <c r="H576" s="7">
-        <v>0</v>
+        <v>0.094878</v>
       </c>
       <c r="I576" s="7">
-        <v>0</v>
+        <v>0.123864</v>
       </c>
       <c r="J576" s="7">
-        <v>0</v>
+        <v>1.054149</v>
       </c>
       <c r="K576" s="7">
-        <v>0</v>
+        <v>12.032339</v>
       </c>
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.25">
@@ -25254,19 +25254,19 @@
         <v>3</v>
       </c>
       <c r="E577" s="7">
-        <v>0</v>
+        <v>0.014185000000000001</v>
       </c>
       <c r="F577" s="7">
-        <v>0</v>
+        <v>0.065214</v>
       </c>
       <c r="G577" s="7">
-        <v>0</v>
+        <v>0.13550399999999999</v>
       </c>
       <c r="H577" s="7">
-        <v>0</v>
+        <v>0.174984</v>
       </c>
       <c r="I577" s="7">
-        <v>0</v>
+        <v>0.280113</v>
       </c>
       <c r="J577" s="7"/>
       <c r="K577" s="7"/>
@@ -27524,19 +27524,19 @@
         <v>1</v>
       </c>
       <c r="E649" s="7">
-        <v>0.032014999999999995</v>
+        <v>0.032031000000000004</v>
       </c>
       <c r="F649" s="7">
-        <v>0.098009</v>
+        <v>0.098027</v>
       </c>
       <c r="G649" s="7">
-        <v>0.211111</v>
+        <v>0.21112999999999998</v>
       </c>
       <c r="H649" s="7">
-        <v>0.276795</v>
+        <v>0.276815</v>
       </c>
       <c r="I649" s="7">
-        <v>0.431771</v>
+        <v>0.431793</v>
       </c>
       <c r="J649" s="7"/>
       <c r="K649" s="7"/>
@@ -28474,22 +28474,22 @@
       </c>
       <c r="D679" s="6"/>
       <c r="E679" s="7">
-        <v>0.051045</v>
+        <v>0.051143999999999995</v>
       </c>
       <c r="F679" s="7">
-        <v>0.057054999999999995</v>
+        <v>0.057153999999999996</v>
       </c>
       <c r="G679" s="7">
-        <v>0.104352</v>
+        <v>0.10445600000000001</v>
       </c>
       <c r="H679" s="7">
-        <v>0.21297899999999997</v>
+        <v>0.213093</v>
       </c>
       <c r="I679" s="7">
-        <v>0.33584200000000003</v>
+        <v>0.33596800000000004</v>
       </c>
       <c r="J679" s="7">
-        <v>1.42952</v>
+        <v>1.4297479999999998</v>
       </c>
       <c r="K679" s="7"/>
     </row>
@@ -28507,25 +28507,25 @@
         <v>4</v>
       </c>
       <c r="E680" s="7">
-        <v>0.056368999999999995</v>
+        <v>0.05637400000000001</v>
       </c>
       <c r="F680" s="7">
-        <v>0.069993</v>
+        <v>0.06999799999999999</v>
       </c>
       <c r="G680" s="7">
-        <v>0.084689</v>
+        <v>0.084694</v>
       </c>
       <c r="H680" s="7">
-        <v>0.19897600000000001</v>
+        <v>0.198982</v>
       </c>
       <c r="I680" s="7">
-        <v>0.349461</v>
+        <v>0.34946699999999997</v>
       </c>
       <c r="J680" s="7">
-        <v>1.7155619999999998</v>
+        <v>1.715575</v>
       </c>
       <c r="K680" s="7">
-        <v>6.469337</v>
+        <v>6.469373000000001</v>
       </c>
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.25">
@@ -28779,25 +28779,25 @@
         <v>6</v>
       </c>
       <c r="E688" s="7">
-        <v>0.054211</v>
+        <v>0.053077</v>
       </c>
       <c r="F688" s="7">
-        <v>-0.008805</v>
+        <v>-0.009871999999999999</v>
       </c>
       <c r="G688" s="7">
-        <v>0.36649099999999996</v>
+        <v>0.36502</v>
       </c>
       <c r="H688" s="7">
-        <v>0.395388</v>
+        <v>0.39388599999999996</v>
       </c>
       <c r="I688" s="7">
-        <v>0.5588960000000001</v>
+        <v>0.557218</v>
       </c>
       <c r="J688" s="7">
-        <v>2.6045049999999996</v>
+        <v>2.6006240000000003</v>
       </c>
       <c r="K688" s="7">
-        <v>10.467175</v>
+        <v>10.454830999999999</v>
       </c>
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.25">
@@ -29503,22 +29503,22 @@
         <v>6</v>
       </c>
       <c r="E710" s="7">
-        <v>0.102356</v>
+        <v>0.102188</v>
       </c>
       <c r="F710" s="7">
-        <v>-0.028184</v>
+        <v>-0.028332000000000003</v>
       </c>
       <c r="G710" s="7">
-        <v>-0.14771800000000002</v>
+        <v>-0.147847</v>
       </c>
       <c r="H710" s="7">
-        <v>0.033706</v>
+        <v>0.033549</v>
       </c>
       <c r="I710" s="7">
-        <v>0.614895</v>
+        <v>0.61465</v>
       </c>
       <c r="J710" s="7">
-        <v>2.677942</v>
+        <v>2.677384</v>
       </c>
       <c r="K710" s="7"/>
     </row>
@@ -30104,19 +30104,19 @@
         <v>4</v>
       </c>
       <c r="E729" s="7">
-        <v>0.044886</v>
+        <v>0.047262000000000005</v>
       </c>
       <c r="F729" s="7">
-        <v>0.063429</v>
+        <v>0.065847</v>
       </c>
       <c r="G729" s="7">
-        <v>0.037507</v>
+        <v>0.039867</v>
       </c>
       <c r="H729" s="7">
-        <v>0.202378</v>
+        <v>0.205113</v>
       </c>
       <c r="I729" s="7">
-        <v>0.318965</v>
+        <v>0.321964</v>
       </c>
       <c r="J729" s="7"/>
       <c r="K729" s="7"/>
@@ -32979,19 +32979,19 @@
         <v>2</v>
       </c>
       <c r="E822" s="7">
-        <v>0</v>
+        <v>0.038563</v>
       </c>
       <c r="F822" s="7">
-        <v>0</v>
+        <v>0.094903</v>
       </c>
       <c r="G822" s="7">
-        <v>0</v>
+        <v>0.206799</v>
       </c>
       <c r="H822" s="7">
-        <v>0</v>
+        <v>0.344651</v>
       </c>
       <c r="I822" s="7">
-        <v>0</v>
+        <v>0.47588299999999994</v>
       </c>
       <c r="J822" s="7"/>
       <c r="K822" s="7"/>
@@ -33553,22 +33553,22 @@
         <v>6</v>
       </c>
       <c r="E840" s="7">
-        <v>0.041769999999999995</v>
+        <v>0.041794000000000005</v>
       </c>
       <c r="F840" s="7">
-        <v>-0.056366</v>
+        <v>-0.056344000000000005</v>
       </c>
       <c r="G840" s="7">
-        <v>0.34741</v>
+        <v>0.34744100000000006</v>
       </c>
       <c r="H840" s="7">
-        <v>0.381262</v>
+        <v>0.38129399999999997</v>
       </c>
       <c r="I840" s="7">
-        <v>0.5626380000000001</v>
+        <v>0.562674</v>
       </c>
       <c r="J840" s="7">
-        <v>2.041809</v>
+        <v>2.041879</v>
       </c>
       <c r="K840" s="7"/>
     </row>
@@ -33747,19 +33747,19 @@
         <v>6</v>
       </c>
       <c r="E846" s="7">
-        <v>0</v>
+        <v>-0.032813</v>
       </c>
       <c r="F846" s="7">
-        <v>0</v>
+        <v>-0.050892</v>
       </c>
       <c r="G846" s="7">
-        <v>0</v>
+        <v>-0.021602999999999997</v>
       </c>
       <c r="H846" s="7">
-        <v>0</v>
+        <v>0.171326</v>
       </c>
       <c r="I846" s="7">
-        <v>0</v>
+        <v>0.342289</v>
       </c>
       <c r="J846" s="7"/>
       <c r="K846" s="7"/>
@@ -33778,7 +33778,7 @@
         <v>5</v>
       </c>
       <c r="E847" s="7">
-        <v>0</v>
+        <v>0.034602</v>
       </c>
       <c r="F847" s="7"/>
       <c r="G847" s="7"/>
@@ -33853,19 +33853,19 @@
         <v>5</v>
       </c>
       <c r="E850" s="7">
-        <v>0</v>
+        <v>0.08263899999999999</v>
       </c>
       <c r="F850" s="7">
-        <v>0</v>
+        <v>0.08373900000000001</v>
       </c>
       <c r="G850" s="7">
-        <v>0</v>
+        <v>0.49803600000000003</v>
       </c>
       <c r="H850" s="7">
-        <v>0</v>
+        <v>0.463639</v>
       </c>
       <c r="I850" s="7">
-        <v>0</v>
+        <v>0.530033</v>
       </c>
       <c r="J850" s="7"/>
       <c r="K850" s="7"/>
@@ -33940,16 +33940,16 @@
         <v>6</v>
       </c>
       <c r="E853" s="7">
-        <v>0</v>
+        <v>0.09314700000000001</v>
       </c>
       <c r="F853" s="7">
-        <v>0</v>
+        <v>0.10007400000000001</v>
       </c>
       <c r="G853" s="7">
-        <v>0</v>
+        <v>0.065463</v>
       </c>
       <c r="H853" s="7">
-        <v>0</v>
+        <v>0.47771399999999997</v>
       </c>
       <c r="I853" s="7"/>
       <c r="J853" s="7"/>
@@ -34089,19 +34089,19 @@
         <v>3</v>
       </c>
       <c r="E858" s="7">
-        <v>0.11551399999999999</v>
+        <v>0.115808</v>
       </c>
       <c r="F858" s="7">
-        <v>0.24253599999999997</v>
+        <v>0.242864</v>
       </c>
       <c r="G858" s="7">
-        <v>0.27123</v>
+        <v>0.271565</v>
       </c>
       <c r="H858" s="7">
-        <v>0.36987699999999996</v>
+        <v>0.370238</v>
       </c>
       <c r="I858" s="7">
-        <v>0.456318</v>
+        <v>0.456702</v>
       </c>
       <c r="J858" s="7"/>
       <c r="K858" s="7"/>
@@ -34118,25 +34118,25 @@
       </c>
       <c r="D859" s="6"/>
       <c r="E859" s="7">
-        <v>0.030150999999999997</v>
+        <v>0.030149</v>
       </c>
       <c r="F859" s="7">
-        <v>0.076925</v>
+        <v>0.076923</v>
       </c>
       <c r="G859" s="7">
-        <v>0.14027900000000001</v>
+        <v>0.14027699999999999</v>
       </c>
       <c r="H859" s="7">
-        <v>0.18572</v>
+        <v>0.185718</v>
       </c>
       <c r="I859" s="7">
-        <v>0.28941500000000003</v>
+        <v>0.289413</v>
       </c>
       <c r="J859" s="7">
-        <v>1.61587</v>
+        <v>1.615865</v>
       </c>
       <c r="K859" s="7">
-        <v>8.371756</v>
+        <v>8.371739999999999</v>
       </c>
     </row>
     <row r="860" spans="1:11" x14ac:dyDescent="0.25">
@@ -34407,19 +34407,19 @@
         <v>6</v>
       </c>
       <c r="E868" s="7">
-        <v>0.081199</v>
+        <v>0.07714800000000001</v>
       </c>
       <c r="F868" s="7">
-        <v>0.036084</v>
+        <v>0.032203</v>
       </c>
       <c r="G868" s="7">
-        <v>0.137775</v>
+        <v>0.133513</v>
       </c>
       <c r="H868" s="7">
-        <v>0.2657</v>
+        <v>0.260959</v>
       </c>
       <c r="I868" s="7">
-        <v>0.06958</v>
+        <v>0.06557400000000001</v>
       </c>
       <c r="J868" s="7"/>
       <c r="K868" s="7"/>
@@ -35893,13 +35893,13 @@
         <v>2.133827</v>
       </c>
       <c r="I912" s="7">
-        <v>6.6699649999999995</v>
+        <v>6.669966</v>
       </c>
       <c r="J912" s="7">
-        <v>641.644018</v>
+        <v>641.644021</v>
       </c>
       <c r="K912" s="7">
-        <v>6467.4681519999995</v>
+        <v>6467.468181</v>
       </c>
     </row>
     <row r="913" spans="1:11" x14ac:dyDescent="0.25">
@@ -36314,25 +36314,25 @@
         <v>6</v>
       </c>
       <c r="E925" s="7">
-        <v>0</v>
+        <v>0.027225000000000003</v>
       </c>
       <c r="F925" s="7">
-        <v>0</v>
+        <v>0.060471000000000004</v>
       </c>
       <c r="G925" s="7">
-        <v>0</v>
+        <v>0.105021</v>
       </c>
       <c r="H925" s="7">
-        <v>0</v>
+        <v>0.12764</v>
       </c>
       <c r="I925" s="7">
-        <v>0</v>
+        <v>0.211195</v>
       </c>
       <c r="J925" s="7">
-        <v>0</v>
+        <v>1.166016</v>
       </c>
       <c r="K925" s="7">
-        <v>0</v>
+        <v>5.974711</v>
       </c>
     </row>
     <row r="926" spans="1:11" x14ac:dyDescent="0.25">
@@ -36347,25 +36347,25 @@
       </c>
       <c r="D926" s="6"/>
       <c r="E926" s="7">
-        <v>0</v>
+        <v>0.030203999999999998</v>
       </c>
       <c r="F926" s="7">
-        <v>0</v>
+        <v>0.074522</v>
       </c>
       <c r="G926" s="7">
-        <v>0</v>
+        <v>0.197655</v>
       </c>
       <c r="H926" s="7">
-        <v>0</v>
+        <v>0.28934</v>
       </c>
       <c r="I926" s="7">
-        <v>0</v>
+        <v>0.609577</v>
       </c>
       <c r="J926" s="7">
-        <v>0</v>
+        <v>2.6184480000000003</v>
       </c>
       <c r="K926" s="7">
-        <v>0</v>
+        <v>19.733353</v>
       </c>
     </row>
     <row r="927" spans="1:11" x14ac:dyDescent="0.25">
@@ -36681,25 +36681,25 @@
         <v>6</v>
       </c>
       <c r="E936" s="7">
-        <v>0.095988</v>
+        <v>0.095404</v>
       </c>
       <c r="F936" s="7">
-        <v>0.015256</v>
+        <v>0.014716</v>
       </c>
       <c r="G936" s="7">
-        <v>-0.087606</v>
+        <v>-0.088092</v>
       </c>
       <c r="H936" s="7">
-        <v>0.08977600000000001</v>
+        <v>0.08919600000000001</v>
       </c>
       <c r="I936" s="7">
-        <v>0.452827</v>
+        <v>0.45205300000000004</v>
       </c>
       <c r="J936" s="7">
-        <v>2.923686</v>
+        <v>2.9215969999999998</v>
       </c>
       <c r="K936" s="7">
-        <v>11.997971</v>
+        <v>11.991051</v>
       </c>
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.25">
@@ -37118,19 +37118,19 @@
         <v>6</v>
       </c>
       <c r="E949" s="7">
-        <v>0</v>
+        <v>0.10785700000000001</v>
       </c>
       <c r="F949" s="7">
-        <v>0</v>
+        <v>-0.055281000000000004</v>
       </c>
       <c r="G949" s="7">
-        <v>0</v>
+        <v>0.036855</v>
       </c>
       <c r="H949" s="7">
-        <v>0</v>
+        <v>0.249023</v>
       </c>
       <c r="I949" s="7">
-        <v>0</v>
+        <v>0.372606</v>
       </c>
       <c r="J949" s="7"/>
       <c r="K949" s="7"/>
@@ -37149,25 +37149,25 @@
         <v>6</v>
       </c>
       <c r="E950" s="7">
-        <v>0.04698</v>
+        <v>0.046932</v>
       </c>
       <c r="F950" s="7">
-        <v>0.096304</v>
+        <v>0.09625500000000001</v>
       </c>
       <c r="G950" s="7">
-        <v>0.169603</v>
+        <v>0.16954999999999998</v>
       </c>
       <c r="H950" s="7">
-        <v>0.218088</v>
+        <v>0.218032</v>
       </c>
       <c r="I950" s="7">
-        <v>0.515154</v>
+        <v>0.515085</v>
       </c>
       <c r="J950" s="7">
-        <v>1.6558009999999999</v>
+        <v>1.655681</v>
       </c>
       <c r="K950" s="7">
-        <v>9.92227</v>
+        <v>9.921774000000001</v>
       </c>
     </row>
     <row r="951" spans="1:11" x14ac:dyDescent="0.25">
@@ -37283,7 +37283,7 @@
         <v>6</v>
       </c>
       <c r="E954" s="7">
-        <v>0</v>
+        <v>0.083494</v>
       </c>
       <c r="F954" s="7"/>
       <c r="G954" s="7"/>
@@ -37450,19 +37450,19 @@
         <v>3</v>
       </c>
       <c r="E961" s="7">
-        <v>0.044835</v>
+        <v>0.044726999999999996</v>
       </c>
       <c r="F961" s="7">
-        <v>0.036975</v>
+        <v>0.036867000000000004</v>
       </c>
       <c r="G961" s="7">
-        <v>0.07216</v>
+        <v>0.072048</v>
       </c>
       <c r="H961" s="7">
-        <v>0.17962499999999998</v>
+        <v>0.179502</v>
       </c>
       <c r="I961" s="7">
-        <v>0.395694</v>
+        <v>0.39554900000000004</v>
       </c>
       <c r="J961" s="7"/>
       <c r="K961" s="7"/>
@@ -37610,25 +37610,25 @@
         <v>5</v>
       </c>
       <c r="E967" s="7">
-        <v>0</v>
+        <v>0.05080199999999999</v>
       </c>
       <c r="F967" s="7">
-        <v>0</v>
+        <v>0.052621</v>
       </c>
       <c r="G967" s="7">
-        <v>0</v>
+        <v>0.07869799999999999</v>
       </c>
       <c r="H967" s="7">
-        <v>0</v>
+        <v>0.182413</v>
       </c>
       <c r="I967" s="7">
-        <v>0</v>
+        <v>0.32333599999999996</v>
       </c>
       <c r="J967" s="7">
-        <v>0</v>
+        <v>1.391577</v>
       </c>
       <c r="K967" s="7">
-        <v>0</v>
+        <v>5.935605000000001</v>
       </c>
     </row>
     <row r="968" spans="1:11" x14ac:dyDescent="0.25">
@@ -37705,25 +37705,25 @@
         <v>4</v>
       </c>
       <c r="E970" s="7">
-        <v>0</v>
+        <v>0.034769999999999995</v>
       </c>
       <c r="F970" s="7">
-        <v>0</v>
+        <v>0.09512999999999999</v>
       </c>
       <c r="G970" s="7">
-        <v>0</v>
+        <v>0.148478</v>
       </c>
       <c r="H970" s="7">
-        <v>0</v>
+        <v>0.231914</v>
       </c>
       <c r="I970" s="7">
-        <v>0</v>
+        <v>0.353414</v>
       </c>
       <c r="J970" s="7">
-        <v>0</v>
+        <v>1.230719</v>
       </c>
       <c r="K970" s="7">
-        <v>0</v>
+        <v>4.870588000000001</v>
       </c>
     </row>
     <row r="971" spans="1:11" x14ac:dyDescent="0.25">
@@ -38536,22 +38536,22 @@
         <v>5</v>
       </c>
       <c r="E995" s="7">
-        <v>0</v>
+        <v>0.024752</v>
       </c>
       <c r="F995" s="7">
-        <v>0</v>
+        <v>-0.021467999999999998</v>
       </c>
       <c r="G995" s="7">
-        <v>0</v>
+        <v>0.311376</v>
       </c>
       <c r="H995" s="7">
-        <v>0</v>
+        <v>0.440232</v>
       </c>
       <c r="I995" s="7">
-        <v>0</v>
+        <v>0.651404</v>
       </c>
       <c r="J995" s="7">
-        <v>0</v>
+        <v>2.2467070000000002</v>
       </c>
       <c r="K995" s="7"/>
     </row>
@@ -38672,22 +38672,22 @@
         <v>5</v>
       </c>
       <c r="E999" s="7">
-        <v>0.043972</v>
+        <v>0.044295999999999995</v>
       </c>
       <c r="F999" s="7">
-        <v>0.08176299999999999</v>
+        <v>0.08209899999999999</v>
       </c>
       <c r="G999" s="7">
-        <v>0.125665</v>
+        <v>0.126015</v>
       </c>
       <c r="H999" s="7">
-        <v>0.320994</v>
+        <v>0.321404</v>
       </c>
       <c r="I999" s="7">
-        <v>0.358665</v>
+        <v>0.35908700000000005</v>
       </c>
       <c r="J999" s="7">
-        <v>0.854132</v>
+        <v>0.854708</v>
       </c>
       <c r="K999" s="7"/>
     </row>
@@ -39159,25 +39159,25 @@
         <v>5</v>
       </c>
       <c r="E1014" s="7">
-        <v>0</v>
+        <v>0.060569</v>
       </c>
       <c r="F1014" s="7">
-        <v>0</v>
+        <v>0.039849</v>
       </c>
       <c r="G1014" s="7">
-        <v>0</v>
+        <v>0.055167</v>
       </c>
       <c r="H1014" s="7">
-        <v>0</v>
+        <v>0.18139500000000003</v>
       </c>
       <c r="I1014" s="7">
-        <v>0</v>
+        <v>0.238153</v>
       </c>
       <c r="J1014" s="7">
-        <v>0</v>
+        <v>1.0947230000000001</v>
       </c>
       <c r="K1014" s="7">
-        <v>0</v>
+        <v>4.636425</v>
       </c>
     </row>
     <row r="1015" spans="1:11" x14ac:dyDescent="0.25">
@@ -39341,25 +39341,25 @@
         <v>6</v>
       </c>
       <c r="E1020" s="7">
-        <v>0</v>
+        <v>0.053114999999999996</v>
       </c>
       <c r="F1020" s="7">
-        <v>0</v>
+        <v>0.000853</v>
       </c>
       <c r="G1020" s="7">
-        <v>0</v>
+        <v>0.212193</v>
       </c>
       <c r="H1020" s="7">
-        <v>0</v>
+        <v>0.202989</v>
       </c>
       <c r="I1020" s="7">
-        <v>0</v>
+        <v>0.42782800000000004</v>
       </c>
       <c r="J1020" s="7">
-        <v>0</v>
+        <v>2.034826</v>
       </c>
       <c r="K1020" s="7">
-        <v>0</v>
+        <v>8.284411</v>
       </c>
     </row>
     <row r="1021" spans="1:11" x14ac:dyDescent="0.25">
@@ -39628,25 +39628,25 @@
         <v>7</v>
       </c>
       <c r="E1029" s="7">
-        <v>0</v>
+        <v>0.150107</v>
       </c>
       <c r="F1029" s="7">
-        <v>0</v>
+        <v>-0.093689</v>
       </c>
       <c r="G1029" s="7">
-        <v>0</v>
+        <v>-0.23654399999999998</v>
       </c>
       <c r="H1029" s="7">
-        <v>0</v>
+        <v>-0.013946</v>
       </c>
       <c r="I1029" s="7">
-        <v>0</v>
+        <v>0.8203520000000001</v>
       </c>
       <c r="J1029" s="7">
-        <v>0</v>
+        <v>3.430383</v>
       </c>
       <c r="K1029" s="7">
-        <v>0</v>
+        <v>11.878748</v>
       </c>
     </row>
     <row r="1030" spans="1:11" x14ac:dyDescent="0.25">
@@ -39952,22 +39952,22 @@
         <v>6</v>
       </c>
       <c r="E1039" s="7">
-        <v>0.08645</v>
+        <v>0.084229</v>
       </c>
       <c r="F1039" s="7">
-        <v>0.031639</v>
+        <v>0.029529999999999997</v>
       </c>
       <c r="G1039" s="7">
-        <v>0.107588</v>
+        <v>0.10532400000000001</v>
       </c>
       <c r="H1039" s="7">
-        <v>0.24418299999999998</v>
+        <v>0.24163900000000002</v>
       </c>
       <c r="I1039" s="7">
-        <v>0.48503599999999997</v>
+        <v>0.48200000000000004</v>
       </c>
       <c r="J1039" s="7">
-        <v>1.741314</v>
+        <v>1.73571</v>
       </c>
       <c r="K1039" s="7"/>
     </row>
@@ -40509,25 +40509,25 @@
         <v>5</v>
       </c>
       <c r="E1056" s="7">
-        <v>0.053505000000000004</v>
+        <v>0.053499</v>
       </c>
       <c r="F1056" s="7">
-        <v>0.060153</v>
+        <v>0.060148</v>
       </c>
       <c r="G1056" s="7">
-        <v>0.065614</v>
+        <v>0.065609</v>
       </c>
       <c r="H1056" s="7">
-        <v>0.152694</v>
+        <v>0.152689</v>
       </c>
       <c r="I1056" s="7">
-        <v>0.21257500000000001</v>
+        <v>0.212569</v>
       </c>
       <c r="J1056" s="7">
-        <v>1.229763</v>
+        <v>1.229753</v>
       </c>
       <c r="K1056" s="7">
-        <v>7.094639</v>
+        <v>7.094600000000001</v>
       </c>
     </row>
     <row r="1057" spans="1:11" x14ac:dyDescent="0.25">
@@ -40734,22 +40734,22 @@
         <v>6</v>
       </c>
       <c r="E1063" s="7">
-        <v>0.038907</v>
+        <v>0.038347</v>
       </c>
       <c r="F1063" s="7">
-        <v>-0.005868</v>
+        <v>-0.006404</v>
       </c>
       <c r="G1063" s="7">
-        <v>0.10741899999999999</v>
+        <v>0.106821</v>
       </c>
       <c r="H1063" s="7">
-        <v>0.242072</v>
+        <v>0.241402</v>
       </c>
       <c r="I1063" s="7">
-        <v>0.35922699999999996</v>
+        <v>0.35849400000000003</v>
       </c>
       <c r="J1063" s="7">
-        <v>1.371157</v>
+        <v>1.369878</v>
       </c>
       <c r="K1063" s="7"/>
     </row>
@@ -40767,19 +40767,19 @@
         <v>5</v>
       </c>
       <c r="E1064" s="7">
-        <v>0.066577</v>
+        <v>0.068314</v>
       </c>
       <c r="F1064" s="7">
-        <v>0.149199</v>
+        <v>0.151071</v>
       </c>
       <c r="G1064" s="7">
-        <v>0.20573699999999998</v>
+        <v>0.207702</v>
       </c>
       <c r="H1064" s="7">
-        <v>0.294923</v>
+        <v>0.297033</v>
       </c>
       <c r="I1064" s="7">
-        <v>0.32807699999999995</v>
+        <v>0.33024099999999995</v>
       </c>
       <c r="J1064" s="7"/>
       <c r="K1064" s="7"/>

--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>04.09.2026 09:32:31</t>
+    <t>04.09.2026 12:35:23</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -7002,25 +7002,25 @@
         <v>5</v>
       </c>
       <c r="E7" s="7">
-        <v>0.058466</v>
+        <v>0.058476</v>
       </c>
       <c r="F7" s="7">
-        <v>0.059085</v>
+        <v>0.059095</v>
       </c>
       <c r="G7" s="7">
-        <v>0.22683499999999998</v>
+        <v>0.226847</v>
       </c>
       <c r="H7" s="7">
-        <v>0.242684</v>
+        <v>0.242696</v>
       </c>
       <c r="I7" s="7">
-        <v>0.398237</v>
+        <v>0.39825099999999997</v>
       </c>
       <c r="J7" s="7">
-        <v>1.330574</v>
+        <v>1.330597</v>
       </c>
       <c r="K7" s="7">
-        <v>2.7107940000000004</v>
+        <v>2.710831</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -7412,25 +7412,25 @@
         <v>7</v>
       </c>
       <c r="E19" s="7">
-        <v>0</v>
+        <v>0.154646</v>
       </c>
       <c r="F19" s="7">
-        <v>0</v>
+        <v>0.069105</v>
       </c>
       <c r="G19" s="7">
-        <v>0</v>
+        <v>0.509203</v>
       </c>
       <c r="H19" s="7">
-        <v>0</v>
+        <v>0.9885240000000001</v>
       </c>
       <c r="I19" s="7">
-        <v>0</v>
+        <v>0.916275</v>
       </c>
       <c r="J19" s="7">
-        <v>0</v>
+        <v>1.6150479999999998</v>
       </c>
       <c r="K19" s="7">
-        <v>0</v>
+        <v>10.702924000000001</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -7793,25 +7793,25 @@
         <v>4</v>
       </c>
       <c r="E30" s="7">
-        <v>0.039415</v>
+        <v>0.039484</v>
       </c>
       <c r="F30" s="7">
-        <v>0.069105</v>
+        <v>0.069175</v>
       </c>
       <c r="G30" s="7">
-        <v>0.177529</v>
+        <v>0.177607</v>
       </c>
       <c r="H30" s="7">
-        <v>0.29759</v>
+        <v>0.29767499999999997</v>
       </c>
       <c r="I30" s="7">
-        <v>0.468161</v>
+        <v>0.468258</v>
       </c>
       <c r="J30" s="7">
-        <v>1.8821729999999999</v>
+        <v>1.8823619999999999</v>
       </c>
       <c r="K30" s="7">
-        <v>8.193687</v>
+        <v>8.19429</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -8296,25 +8296,25 @@
         <v>6</v>
       </c>
       <c r="E45" s="7">
-        <v>0</v>
+        <v>0.042335000000000005</v>
       </c>
       <c r="F45" s="7">
-        <v>0</v>
+        <v>0.0073950000000000005</v>
       </c>
       <c r="G45" s="7">
-        <v>0</v>
+        <v>0.036313</v>
       </c>
       <c r="H45" s="7">
-        <v>0</v>
+        <v>0.158002</v>
       </c>
       <c r="I45" s="7">
-        <v>0</v>
+        <v>0.246035</v>
       </c>
       <c r="J45" s="7">
-        <v>0</v>
+        <v>0.934903</v>
       </c>
       <c r="K45" s="7">
-        <v>0</v>
+        <v>2.869492</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -8399,25 +8399,25 @@
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="7">
-        <v>0</v>
+        <v>0.019782</v>
       </c>
       <c r="F48" s="7">
-        <v>0</v>
+        <v>0.052309</v>
       </c>
       <c r="G48" s="7">
-        <v>0</v>
+        <v>0.110247</v>
       </c>
       <c r="H48" s="7">
-        <v>0</v>
+        <v>0.20975000000000002</v>
       </c>
       <c r="I48" s="7">
-        <v>0</v>
+        <v>0.3528</v>
       </c>
       <c r="J48" s="7">
-        <v>0</v>
+        <v>1.998662</v>
       </c>
       <c r="K48" s="7">
-        <v>0</v>
+        <v>5.386472</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -8432,25 +8432,25 @@
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7">
-        <v>0</v>
+        <v>0.012843</v>
       </c>
       <c r="F49" s="7">
-        <v>0</v>
+        <v>0.029868000000000002</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>0.06348</v>
       </c>
       <c r="H49" s="7">
-        <v>0</v>
+        <v>0.174974</v>
       </c>
       <c r="I49" s="7">
-        <v>0</v>
+        <v>0.31818799999999997</v>
       </c>
       <c r="J49" s="7">
-        <v>0</v>
+        <v>1.7798640000000001</v>
       </c>
       <c r="K49" s="7">
-        <v>0</v>
+        <v>5.890016</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -9021,19 +9021,19 @@
         <v>5</v>
       </c>
       <c r="E68" s="7">
-        <v>0.028435000000000002</v>
+        <v>0.027611</v>
       </c>
       <c r="F68" s="7">
-        <v>0.044871</v>
+        <v>0.044032999999999996</v>
       </c>
       <c r="G68" s="7">
-        <v>0.09285</v>
+        <v>0.091973</v>
       </c>
       <c r="H68" s="7">
-        <v>0.144901</v>
+        <v>0.143983</v>
       </c>
       <c r="I68" s="7">
-        <v>0.30182</v>
+        <v>0.300776</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
@@ -9900,19 +9900,19 @@
         <v>5</v>
       </c>
       <c r="E97" s="7">
-        <v>0.056410999999999996</v>
+        <v>0.055725</v>
       </c>
       <c r="F97" s="7">
-        <v>0.00784</v>
+        <v>0.0071860000000000005</v>
       </c>
       <c r="G97" s="7">
-        <v>0.19310300000000002</v>
+        <v>0.192329</v>
       </c>
       <c r="H97" s="7">
-        <v>0.311548</v>
+        <v>0.310697</v>
       </c>
       <c r="I97" s="7">
-        <v>0.479949</v>
+        <v>0.478988</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
@@ -10080,16 +10080,16 @@
         <v>7</v>
       </c>
       <c r="E103" s="7">
-        <v>0.051365999999999995</v>
+        <v>0.051362</v>
       </c>
       <c r="F103" s="7">
-        <v>0.14846600000000001</v>
+        <v>0.148461</v>
       </c>
       <c r="G103" s="7">
-        <v>0.404063</v>
+        <v>0.404058</v>
       </c>
       <c r="H103" s="7">
-        <v>0.563728</v>
+        <v>0.563722</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
@@ -10266,10 +10266,10 @@
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>0.069769</v>
+        <v>0.070757</v>
       </c>
       <c r="F109" s="7">
-        <v>0.20442799999999997</v>
+        <v>0.20553999999999997</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
@@ -10959,22 +10959,22 @@
         <v>5</v>
       </c>
       <c r="E132" s="7">
-        <v>0.020304000000000003</v>
+        <v>0.019974000000000002</v>
       </c>
       <c r="F132" s="7">
-        <v>0.062379</v>
+        <v>0.062036</v>
       </c>
       <c r="G132" s="7">
-        <v>0.11955</v>
+        <v>0.11918799999999999</v>
       </c>
       <c r="H132" s="7">
-        <v>0.154333</v>
+        <v>0.15396</v>
       </c>
       <c r="I132" s="7">
-        <v>0.21909800000000001</v>
+        <v>0.218705</v>
       </c>
       <c r="J132" s="7">
-        <v>1.0417100000000001</v>
+        <v>1.04105</v>
       </c>
       <c r="K132" s="7"/>
     </row>
@@ -11027,25 +11027,25 @@
         <v>3</v>
       </c>
       <c r="E134" s="7">
-        <v>0.046118</v>
+        <v>0.046127</v>
       </c>
       <c r="F134" s="7">
-        <v>0.10808899999999999</v>
+        <v>0.108099</v>
       </c>
       <c r="G134" s="7">
-        <v>0.150748</v>
+        <v>0.150758</v>
       </c>
       <c r="H134" s="7">
-        <v>0.19989200000000001</v>
+        <v>0.19990200000000002</v>
       </c>
       <c r="I134" s="7">
-        <v>0.379278</v>
+        <v>0.37929</v>
       </c>
       <c r="J134" s="7">
-        <v>1.654468</v>
+        <v>1.654491</v>
       </c>
       <c r="K134" s="7">
-        <v>3.118917</v>
+        <v>3.1189530000000003</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -11532,10 +11532,10 @@
         <v>0.218635</v>
       </c>
       <c r="I149" s="7">
-        <v>0.221174</v>
+        <v>0.221173</v>
       </c>
       <c r="J149" s="7">
-        <v>0.835178</v>
+        <v>0.8351770000000001</v>
       </c>
       <c r="K149" s="7"/>
     </row>
@@ -11553,22 +11553,22 @@
         <v>6</v>
       </c>
       <c r="E150" s="7">
-        <v>0.027978</v>
+        <v>0.028260999999999998</v>
       </c>
       <c r="F150" s="7">
-        <v>0.017304</v>
+        <v>0.017585</v>
       </c>
       <c r="G150" s="7">
-        <v>0.121866</v>
+        <v>0.12217599999999999</v>
       </c>
       <c r="H150" s="7">
-        <v>0.216087</v>
+        <v>0.216422</v>
       </c>
       <c r="I150" s="7">
-        <v>0.29773</v>
+        <v>0.298087</v>
       </c>
       <c r="J150" s="7">
-        <v>1.286873</v>
+        <v>1.287503</v>
       </c>
       <c r="K150" s="7"/>
     </row>
@@ -11958,22 +11958,22 @@
         <v>7</v>
       </c>
       <c r="E163" s="7">
-        <v>0.16138100000000002</v>
+        <v>0.16167</v>
       </c>
       <c r="F163" s="7">
-        <v>-0.058994</v>
+        <v>-0.058759</v>
       </c>
       <c r="G163" s="7">
-        <v>-0.119511</v>
+        <v>-0.119292</v>
       </c>
       <c r="H163" s="7">
-        <v>0.015432999999999999</v>
+        <v>0.015686</v>
       </c>
       <c r="I163" s="7">
-        <v>0.8314360000000001</v>
+        <v>0.831892</v>
       </c>
       <c r="J163" s="7">
-        <v>3.4555399999999996</v>
+        <v>3.4566500000000002</v>
       </c>
       <c r="K163" s="7"/>
     </row>
@@ -11991,16 +11991,16 @@
         <v>4</v>
       </c>
       <c r="E164" s="7">
-        <v>0.09102600000000001</v>
+        <v>0.092042</v>
       </c>
       <c r="F164" s="7">
-        <v>0.115736</v>
+        <v>0.116775</v>
       </c>
       <c r="G164" s="7">
-        <v>0.209844</v>
+        <v>0.21097000000000002</v>
       </c>
       <c r="H164" s="7">
-        <v>0.316632</v>
+        <v>0.317858</v>
       </c>
       <c r="I164" s="7"/>
       <c r="J164" s="7"/>
@@ -12078,19 +12078,19 @@
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="7">
-        <v>0.032848999999999996</v>
+        <v>0.039945</v>
       </c>
       <c r="F167" s="7">
-        <v>0.080389</v>
+        <v>0.087811</v>
       </c>
       <c r="G167" s="7">
-        <v>0.113079</v>
+        <v>0.120726</v>
       </c>
       <c r="H167" s="7">
-        <v>0.128484</v>
+        <v>0.136237</v>
       </c>
       <c r="I167" s="7">
-        <v>0.25029</v>
+        <v>0.25888</v>
       </c>
       <c r="J167" s="7"/>
       <c r="K167" s="7"/>
@@ -12371,19 +12371,19 @@
         <v>7</v>
       </c>
       <c r="E176" s="7">
-        <v>-0.036448999999999995</v>
+        <v>-0.033617</v>
       </c>
       <c r="F176" s="7">
-        <v>0.074505</v>
+        <v>0.077663</v>
       </c>
       <c r="G176" s="7">
-        <v>0.022362000000000003</v>
+        <v>0.025367</v>
       </c>
       <c r="H176" s="7">
-        <v>0.038355</v>
+        <v>0.041407</v>
       </c>
       <c r="I176" s="7">
-        <v>0.22683599999999998</v>
+        <v>0.230442</v>
       </c>
       <c r="J176" s="7"/>
       <c r="K176" s="7"/>
@@ -12432,22 +12432,22 @@
         <v>0.027146</v>
       </c>
       <c r="F178" s="7">
-        <v>0.068088</v>
+        <v>0.068087</v>
       </c>
       <c r="G178" s="7">
-        <v>0.114755</v>
+        <v>0.11475400000000001</v>
       </c>
       <c r="H178" s="7">
-        <v>0.139924</v>
+        <v>0.139923</v>
       </c>
       <c r="I178" s="7">
-        <v>0.241141</v>
+        <v>0.24114000000000002</v>
       </c>
       <c r="J178" s="7">
-        <v>1.302706</v>
+        <v>1.3027039999999999</v>
       </c>
       <c r="K178" s="7">
-        <v>5.706489</v>
+        <v>5.706484000000001</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -12464,25 +12464,25 @@
         <v>3</v>
       </c>
       <c r="E179" s="7">
-        <v>0.034466000000000004</v>
+        <v>0.037823</v>
       </c>
       <c r="F179" s="7">
-        <v>0.069179</v>
+        <v>0.072648</v>
       </c>
       <c r="G179" s="7">
-        <v>0.13672399999999998</v>
+        <v>0.140412</v>
       </c>
       <c r="H179" s="7">
-        <v>0.216329</v>
+        <v>0.220275</v>
       </c>
       <c r="I179" s="7">
-        <v>0.392806</v>
+        <v>0.39732599999999996</v>
       </c>
       <c r="J179" s="7">
-        <v>1.739971</v>
+        <v>1.748861</v>
       </c>
       <c r="K179" s="7">
-        <v>6.603282</v>
+        <v>6.627953</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -13520,16 +13520,16 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>0.126478</v>
+        <v>0.127964</v>
       </c>
       <c r="F213" s="7">
-        <v>-0.006875</v>
+        <v>-0.005565</v>
       </c>
       <c r="G213" s="7">
-        <v>-0.10913600000000001</v>
+        <v>-0.10796099999999999</v>
       </c>
       <c r="H213" s="7">
-        <v>0.066276</v>
+        <v>0.067682</v>
       </c>
       <c r="I213" s="7"/>
       <c r="J213" s="7"/>
@@ -13760,13 +13760,13 @@
         <v>6</v>
       </c>
       <c r="E221" s="7">
-        <v>0.089397</v>
+        <v>0.088116</v>
       </c>
       <c r="F221" s="7">
-        <v>0.04002</v>
+        <v>0.038797</v>
       </c>
       <c r="G221" s="7">
-        <v>0.13079000000000002</v>
+        <v>0.129461</v>
       </c>
       <c r="H221" s="7"/>
       <c r="I221" s="7"/>
@@ -13787,19 +13787,19 @@
         <v>3</v>
       </c>
       <c r="E222" s="7">
-        <v>0.052092</v>
+        <v>0.056566</v>
       </c>
       <c r="F222" s="7">
-        <v>0.034825</v>
+        <v>0.039224999999999996</v>
       </c>
       <c r="G222" s="7">
-        <v>0.13139099999999998</v>
+        <v>0.13620100000000002</v>
       </c>
       <c r="H222" s="7">
-        <v>0.257099</v>
+        <v>0.262443</v>
       </c>
       <c r="I222" s="7">
-        <v>0.495516</v>
+        <v>0.5018739999999999</v>
       </c>
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
@@ -14136,25 +14136,25 @@
         <v>4</v>
       </c>
       <c r="E233" s="7">
-        <v>0.051486000000000004</v>
+        <v>0.051482</v>
       </c>
       <c r="F233" s="7">
-        <v>0.0721</v>
+        <v>0.072096</v>
       </c>
       <c r="G233" s="7">
-        <v>0.17586200000000002</v>
+        <v>0.17585699999999999</v>
       </c>
       <c r="H233" s="7">
-        <v>0.289376</v>
+        <v>0.289371</v>
       </c>
       <c r="I233" s="7">
-        <v>0.49487699999999996</v>
+        <v>0.49487200000000003</v>
       </c>
       <c r="J233" s="7">
-        <v>1.972954</v>
+        <v>1.972942</v>
       </c>
       <c r="K233" s="7">
-        <v>7.0177369999999994</v>
+        <v>7.017704999999999</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -14171,25 +14171,25 @@
         <v>4</v>
       </c>
       <c r="E234" s="7">
-        <v>0.050286</v>
+        <v>0.054683</v>
       </c>
       <c r="F234" s="7">
-        <v>0.050246000000000006</v>
+        <v>0.054643</v>
       </c>
       <c r="G234" s="7">
-        <v>0.066786</v>
+        <v>0.071253</v>
       </c>
       <c r="H234" s="7">
-        <v>0.160115</v>
+        <v>0.16497299999999998</v>
       </c>
       <c r="I234" s="7">
-        <v>0.387537</v>
+        <v>0.393347</v>
       </c>
       <c r="J234" s="7">
-        <v>1.9140039999999998</v>
+        <v>1.926205</v>
       </c>
       <c r="K234" s="7">
-        <v>5.686971</v>
+        <v>5.714971</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -14600,25 +14600,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.040912</v>
+        <v>0.044261</v>
       </c>
       <c r="F247" s="7">
-        <v>0.075627</v>
+        <v>0.07908699999999999</v>
       </c>
       <c r="G247" s="7">
-        <v>0.091228</v>
+        <v>0.094739</v>
       </c>
       <c r="H247" s="7">
-        <v>0.16672399999999998</v>
+        <v>0.170478</v>
       </c>
       <c r="I247" s="7">
-        <v>0.36133400000000004</v>
+        <v>0.365714</v>
       </c>
       <c r="J247" s="7">
-        <v>1.8748150000000001</v>
+        <v>1.8840649999999999</v>
       </c>
       <c r="K247" s="7">
-        <v>6.267696999999999</v>
+        <v>6.291079999999999</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -15126,22 +15126,22 @@
         <v>6</v>
       </c>
       <c r="E263" s="7">
-        <v>0.03338</v>
+        <v>0.038593999999999996</v>
       </c>
       <c r="F263" s="7">
-        <v>-0.028534999999999998</v>
+        <v>-0.023633</v>
       </c>
       <c r="G263" s="7">
-        <v>0.356232</v>
+        <v>0.363075</v>
       </c>
       <c r="H263" s="7">
-        <v>0.333169</v>
+        <v>0.339895</v>
       </c>
       <c r="I263" s="7">
-        <v>0.5173409999999999</v>
+        <v>0.5249969999999999</v>
       </c>
       <c r="J263" s="7">
-        <v>2.3215850000000002</v>
+        <v>2.3383439999999998</v>
       </c>
       <c r="K263" s="7"/>
     </row>
@@ -15252,16 +15252,16 @@
         <v>6</v>
       </c>
       <c r="E267" s="7">
-        <v>0</v>
+        <v>0.193255</v>
       </c>
       <c r="F267" s="7">
-        <v>0</v>
+        <v>0.08463699999999999</v>
       </c>
       <c r="G267" s="7">
-        <v>0</v>
+        <v>0.19255299999999997</v>
       </c>
       <c r="H267" s="7">
-        <v>0</v>
+        <v>0.346168</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
@@ -15345,25 +15345,25 @@
         <v>5</v>
       </c>
       <c r="E270" s="7">
-        <v>0.026791</v>
+        <v>0.026791999999999996</v>
       </c>
       <c r="F270" s="7">
-        <v>0.06361</v>
+        <v>0.063611</v>
       </c>
       <c r="G270" s="7">
-        <v>0.115024</v>
+        <v>0.11502599999999999</v>
       </c>
       <c r="H270" s="7">
-        <v>0.131127</v>
+        <v>0.131129</v>
       </c>
       <c r="I270" s="7">
-        <v>0.244253</v>
+        <v>0.244255</v>
       </c>
       <c r="J270" s="7">
-        <v>1.363304</v>
+        <v>1.363307</v>
       </c>
       <c r="K270" s="7">
-        <v>6.46591</v>
+        <v>6.46592</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -15485,22 +15485,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.036608</v>
+        <v>0.039772</v>
       </c>
       <c r="F274" s="7">
-        <v>0.062511</v>
+        <v>0.065754</v>
       </c>
       <c r="G274" s="7">
-        <v>0.141382</v>
+        <v>0.144866</v>
       </c>
       <c r="H274" s="7">
-        <v>0.210872</v>
+        <v>0.214567</v>
       </c>
       <c r="I274" s="7">
-        <v>0.368464</v>
+        <v>0.37264</v>
       </c>
       <c r="J274" s="7">
-        <v>1.853452</v>
+        <v>1.8621610000000002</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -15693,25 +15693,25 @@
         <v>3</v>
       </c>
       <c r="E280" s="7">
-        <v>0</v>
+        <v>0.030898</v>
       </c>
       <c r="F280" s="7">
-        <v>0</v>
+        <v>0.08059699999999999</v>
       </c>
       <c r="G280" s="7">
-        <v>0</v>
+        <v>0.134022</v>
       </c>
       <c r="H280" s="7">
-        <v>0</v>
+        <v>0.229862</v>
       </c>
       <c r="I280" s="7">
-        <v>0</v>
+        <v>0.39710999999999996</v>
       </c>
       <c r="J280" s="7">
-        <v>0</v>
+        <v>2.218285</v>
       </c>
       <c r="K280" s="7">
-        <v>0</v>
+        <v>6.140562</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -15965,22 +15965,22 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0</v>
+        <v>0.011436</v>
       </c>
       <c r="F288" s="7">
-        <v>0</v>
+        <v>-0.054332000000000005</v>
       </c>
       <c r="G288" s="7">
-        <v>0</v>
+        <v>0.337858</v>
       </c>
       <c r="H288" s="7">
-        <v>0</v>
+        <v>0.36318</v>
       </c>
       <c r="I288" s="7">
-        <v>0</v>
+        <v>0.594178</v>
       </c>
       <c r="J288" s="7">
-        <v>0</v>
+        <v>3.614214</v>
       </c>
       <c r="K288" s="7"/>
     </row>
@@ -15998,22 +15998,22 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.089245</v>
+        <v>0.089715</v>
       </c>
       <c r="F289" s="7">
-        <v>0.016835</v>
+        <v>0.017274</v>
       </c>
       <c r="G289" s="7">
-        <v>0.143836</v>
+        <v>0.14432999999999999</v>
       </c>
       <c r="H289" s="7">
-        <v>0.30973</v>
+        <v>0.31029599999999996</v>
       </c>
       <c r="I289" s="7">
-        <v>0.49473999999999996</v>
+        <v>0.49538499999999996</v>
       </c>
       <c r="J289" s="7">
-        <v>1.576368</v>
+        <v>1.57748</v>
       </c>
       <c r="K289" s="7"/>
     </row>
@@ -16101,19 +16101,19 @@
         <v>5</v>
       </c>
       <c r="E292" s="7">
-        <v>0</v>
+        <v>0.013773</v>
       </c>
       <c r="F292" s="7">
-        <v>0</v>
+        <v>-0.011356999999999999</v>
       </c>
       <c r="G292" s="7">
-        <v>0</v>
+        <v>0.055311000000000006</v>
       </c>
       <c r="H292" s="7">
-        <v>0</v>
+        <v>0.120918</v>
       </c>
       <c r="I292" s="7">
-        <v>0</v>
+        <v>0.214527</v>
       </c>
       <c r="J292" s="7"/>
       <c r="K292" s="7"/>
@@ -16165,22 +16165,22 @@
         <v>6</v>
       </c>
       <c r="E294" s="7">
-        <v>-0.015462</v>
+        <v>-0.015467999999999999</v>
       </c>
       <c r="F294" s="7">
-        <v>-0.118026</v>
+        <v>-0.11803100000000001</v>
       </c>
       <c r="G294" s="7">
-        <v>0.06715499999999999</v>
+        <v>0.067149</v>
       </c>
       <c r="H294" s="7">
-        <v>0.22965699999999997</v>
+        <v>0.22965</v>
       </c>
       <c r="I294" s="7">
-        <v>0.215688</v>
+        <v>0.21568</v>
       </c>
       <c r="J294" s="7">
-        <v>0.22023700000000002</v>
+        <v>0.22023</v>
       </c>
       <c r="K294" s="7"/>
     </row>
@@ -16198,25 +16198,25 @@
         <v>5</v>
       </c>
       <c r="E295" s="7">
-        <v>0.033657</v>
+        <v>0.033292999999999996</v>
       </c>
       <c r="F295" s="7">
-        <v>-0.026819000000000003</v>
+        <v>-0.027161</v>
       </c>
       <c r="G295" s="7">
-        <v>0.091169</v>
+        <v>0.090785</v>
       </c>
       <c r="H295" s="7">
-        <v>0.204462</v>
+        <v>0.204038</v>
       </c>
       <c r="I295" s="7">
-        <v>0.481559</v>
+        <v>0.48103700000000005</v>
       </c>
       <c r="J295" s="7">
-        <v>1.677063</v>
+        <v>1.676121</v>
       </c>
       <c r="K295" s="7">
-        <v>9.014647</v>
+        <v>9.011122</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -16400,22 +16400,22 @@
         <v>5</v>
       </c>
       <c r="E301" s="7">
-        <v>0.04514</v>
+        <v>0.053144</v>
       </c>
       <c r="F301" s="7">
-        <v>0.028339</v>
+        <v>0.036213999999999996</v>
       </c>
       <c r="G301" s="7">
-        <v>0.05533299999999999</v>
+        <v>0.063415</v>
       </c>
       <c r="H301" s="7">
-        <v>0.076462</v>
+        <v>0.08470599999999999</v>
       </c>
       <c r="I301" s="7">
-        <v>0.190868</v>
+        <v>0.199987</v>
       </c>
       <c r="J301" s="7">
-        <v>1.437412</v>
+        <v>1.456078</v>
       </c>
       <c r="K301" s="7"/>
     </row>
@@ -16557,22 +16557,22 @@
         <v>7</v>
       </c>
       <c r="E306" s="7">
-        <v>0</v>
+        <v>0.18340599999999999</v>
       </c>
       <c r="F306" s="7">
-        <v>0</v>
+        <v>-0.071965</v>
       </c>
       <c r="G306" s="7">
-        <v>0</v>
+        <v>-0.142198</v>
       </c>
       <c r="H306" s="7">
-        <v>0</v>
+        <v>-0.021044</v>
       </c>
       <c r="I306" s="7">
-        <v>0</v>
+        <v>0.8010670000000001</v>
       </c>
       <c r="J306" s="7">
-        <v>0</v>
+        <v>3.3609519999999997</v>
       </c>
       <c r="K306" s="7"/>
     </row>
@@ -16590,22 +16590,22 @@
         <v>5</v>
       </c>
       <c r="E307" s="7">
-        <v>0.029514</v>
+        <v>0.029521000000000002</v>
       </c>
       <c r="F307" s="7">
-        <v>0.038102</v>
+        <v>0.038109000000000004</v>
       </c>
       <c r="G307" s="7">
-        <v>0.173824</v>
+        <v>0.173832</v>
       </c>
       <c r="H307" s="7">
-        <v>0.203885</v>
+        <v>0.203893</v>
       </c>
       <c r="I307" s="7">
-        <v>0.341403</v>
+        <v>0.341412</v>
       </c>
       <c r="J307" s="7">
-        <v>0.40545699999999996</v>
+        <v>0.405467</v>
       </c>
       <c r="K307" s="7"/>
     </row>
@@ -16778,22 +16778,22 @@
         <v>3</v>
       </c>
       <c r="E313" s="7">
-        <v>0.048725</v>
+        <v>0.049155</v>
       </c>
       <c r="F313" s="7">
-        <v>0.092532</v>
+        <v>0.09298000000000001</v>
       </c>
       <c r="G313" s="7">
-        <v>0.177297</v>
+        <v>0.17778</v>
       </c>
       <c r="H313" s="7">
-        <v>0.31082</v>
+        <v>0.311358</v>
       </c>
       <c r="I313" s="7">
-        <v>0.519266</v>
+        <v>0.519889</v>
       </c>
       <c r="J313" s="7">
-        <v>2.757392</v>
+        <v>2.758934</v>
       </c>
       <c r="K313" s="7"/>
     </row>
@@ -16811,22 +16811,22 @@
         <v>5</v>
       </c>
       <c r="E314" s="7">
-        <v>0.038632</v>
+        <v>0.039753</v>
       </c>
       <c r="F314" s="7">
-        <v>0.012313000000000001</v>
+        <v>0.013405</v>
       </c>
       <c r="G314" s="7">
-        <v>0.074893</v>
+        <v>0.076053</v>
       </c>
       <c r="H314" s="7">
-        <v>0.219546</v>
+        <v>0.220862</v>
       </c>
       <c r="I314" s="7">
-        <v>0.399704</v>
+        <v>0.401215</v>
       </c>
       <c r="J314" s="7">
-        <v>1.87245</v>
+        <v>1.87555</v>
       </c>
       <c r="K314" s="7"/>
     </row>
@@ -16844,22 +16844,22 @@
         <v>5</v>
       </c>
       <c r="E315" s="7">
-        <v>0.044535</v>
+        <v>0.046213</v>
       </c>
       <c r="F315" s="7">
-        <v>0.019923</v>
+        <v>0.021561</v>
       </c>
       <c r="G315" s="7">
-        <v>0.074345</v>
+        <v>0.076071</v>
       </c>
       <c r="H315" s="7">
-        <v>0.205173</v>
+        <v>0.20711</v>
       </c>
       <c r="I315" s="7">
-        <v>0.399089</v>
+        <v>0.401337</v>
       </c>
       <c r="J315" s="7">
-        <v>1.8731639999999998</v>
+        <v>1.87778</v>
       </c>
       <c r="K315" s="7"/>
     </row>
@@ -17090,25 +17090,25 @@
         <v>2</v>
       </c>
       <c r="E323" s="7">
-        <v>0</v>
+        <v>0.035778</v>
       </c>
       <c r="F323" s="7">
-        <v>0</v>
+        <v>0.097965</v>
       </c>
       <c r="G323" s="7">
-        <v>0</v>
+        <v>0.152714</v>
       </c>
       <c r="H323" s="7">
-        <v>0</v>
+        <v>0.24393</v>
       </c>
       <c r="I323" s="7">
-        <v>0</v>
+        <v>0.3983</v>
       </c>
       <c r="J323" s="7">
-        <v>0</v>
+        <v>2.101639</v>
       </c>
       <c r="K323" s="7">
-        <v>0</v>
+        <v>3.8894740000000003</v>
       </c>
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
@@ -17228,25 +17228,25 @@
         <v>3</v>
       </c>
       <c r="E327" s="7">
-        <v>0</v>
+        <v>0.031960999999999996</v>
       </c>
       <c r="F327" s="7">
-        <v>0</v>
+        <v>0.081475</v>
       </c>
       <c r="G327" s="7">
-        <v>0</v>
+        <v>0.14138299999999998</v>
       </c>
       <c r="H327" s="7">
-        <v>0</v>
+        <v>0.23949</v>
       </c>
       <c r="I327" s="7">
-        <v>0</v>
+        <v>0.407065</v>
       </c>
       <c r="J327" s="7">
-        <v>0</v>
+        <v>2.187227</v>
       </c>
       <c r="K327" s="7">
-        <v>0</v>
+        <v>6.309253</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -17354,25 +17354,25 @@
         <v>4</v>
       </c>
       <c r="E331" s="7">
-        <v>0</v>
+        <v>0.033875</v>
       </c>
       <c r="F331" s="7">
-        <v>0</v>
+        <v>0.072373</v>
       </c>
       <c r="G331" s="7">
-        <v>0</v>
+        <v>0.12125999999999999</v>
       </c>
       <c r="H331" s="7">
-        <v>0</v>
+        <v>0.244468</v>
       </c>
       <c r="I331" s="7">
-        <v>0</v>
+        <v>0.40964300000000003</v>
       </c>
       <c r="J331" s="7">
-        <v>0</v>
+        <v>2.167722</v>
       </c>
       <c r="K331" s="7">
-        <v>0</v>
+        <v>7.081976</v>
       </c>
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
@@ -17424,19 +17424,19 @@
         <v>5</v>
       </c>
       <c r="E333" s="7">
-        <v>0.030769</v>
+        <v>0.039119</v>
       </c>
       <c r="F333" s="7">
-        <v>0.036603</v>
+        <v>0.045</v>
       </c>
       <c r="G333" s="7">
-        <v>0.069829</v>
+        <v>0.078496</v>
       </c>
       <c r="H333" s="7">
-        <v>0.192056</v>
+        <v>0.20171299999999998</v>
       </c>
       <c r="I333" s="7">
-        <v>0.338271</v>
+        <v>0.34911200000000003</v>
       </c>
       <c r="J333" s="7"/>
       <c r="K333" s="7"/>
@@ -17686,25 +17686,25 @@
         <v>6</v>
       </c>
       <c r="E341" s="7">
-        <v>0</v>
+        <v>0.033618</v>
       </c>
       <c r="F341" s="7">
-        <v>0</v>
+        <v>0.08984500000000001</v>
       </c>
       <c r="G341" s="7">
-        <v>0</v>
+        <v>0.102777</v>
       </c>
       <c r="H341" s="7">
-        <v>0</v>
+        <v>0.212819</v>
       </c>
       <c r="I341" s="7">
-        <v>0</v>
+        <v>0.388287</v>
       </c>
       <c r="J341" s="7">
-        <v>0</v>
+        <v>1.6872530000000001</v>
       </c>
       <c r="K341" s="7">
-        <v>0</v>
+        <v>4.776392</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
@@ -17812,25 +17812,25 @@
         <v>6</v>
       </c>
       <c r="E345" s="7">
-        <v>0</v>
+        <v>0.01754</v>
       </c>
       <c r="F345" s="7">
-        <v>0</v>
+        <v>-0.064794</v>
       </c>
       <c r="G345" s="7">
-        <v>0</v>
+        <v>0.42103900000000005</v>
       </c>
       <c r="H345" s="7">
-        <v>0</v>
+        <v>0.400681</v>
       </c>
       <c r="I345" s="7">
-        <v>0</v>
+        <v>0.73687</v>
       </c>
       <c r="J345" s="7">
-        <v>0</v>
+        <v>2.409975</v>
       </c>
       <c r="K345" s="7">
-        <v>0</v>
+        <v>7.992451</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -17876,25 +17876,25 @@
         <v>7</v>
       </c>
       <c r="E347" s="7">
-        <v>0</v>
+        <v>0.17646499999999998</v>
       </c>
       <c r="F347" s="7">
-        <v>0</v>
+        <v>-0.059167</v>
       </c>
       <c r="G347" s="7">
-        <v>0</v>
+        <v>-0.13594</v>
       </c>
       <c r="H347" s="7">
-        <v>0</v>
+        <v>0.003754</v>
       </c>
       <c r="I347" s="7">
-        <v>0</v>
+        <v>0.800557</v>
       </c>
       <c r="J347" s="7">
-        <v>0</v>
+        <v>3.3092219999999997</v>
       </c>
       <c r="K347" s="7">
-        <v>0</v>
+        <v>11.417167</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
@@ -17942,22 +17942,22 @@
         <v>6</v>
       </c>
       <c r="E349" s="7">
-        <v>0</v>
+        <v>-0.009091</v>
       </c>
       <c r="F349" s="7">
-        <v>0</v>
+        <v>-0.121006</v>
       </c>
       <c r="G349" s="7">
-        <v>0</v>
+        <v>0.108304</v>
       </c>
       <c r="H349" s="7">
-        <v>0</v>
+        <v>0.15482100000000001</v>
       </c>
       <c r="I349" s="7">
-        <v>0</v>
+        <v>0.34417000000000003</v>
       </c>
       <c r="J349" s="7">
-        <v>0</v>
+        <v>1.145532</v>
       </c>
       <c r="K349" s="7"/>
     </row>
@@ -17975,22 +17975,22 @@
         <v>5</v>
       </c>
       <c r="E350" s="7">
-        <v>0</v>
+        <v>0.03169</v>
       </c>
       <c r="F350" s="7">
-        <v>0</v>
+        <v>0.043271</v>
       </c>
       <c r="G350" s="7">
-        <v>0</v>
+        <v>0.050132</v>
       </c>
       <c r="H350" s="7">
-        <v>0</v>
+        <v>0.167271</v>
       </c>
       <c r="I350" s="7">
-        <v>0</v>
+        <v>0.31518599999999997</v>
       </c>
       <c r="J350" s="7">
-        <v>0</v>
+        <v>1.6290989999999999</v>
       </c>
       <c r="K350" s="7"/>
     </row>
@@ -18043,25 +18043,25 @@
         <v>6</v>
       </c>
       <c r="E352" s="7">
-        <v>0</v>
+        <v>0.104231</v>
       </c>
       <c r="F352" s="7">
-        <v>0</v>
+        <v>0.06438100000000001</v>
       </c>
       <c r="G352" s="7">
-        <v>0</v>
+        <v>0.132913</v>
       </c>
       <c r="H352" s="7">
-        <v>0</v>
+        <v>0.286212</v>
       </c>
       <c r="I352" s="7">
-        <v>0</v>
+        <v>0.559772</v>
       </c>
       <c r="J352" s="7">
-        <v>0</v>
+        <v>1.567298</v>
       </c>
       <c r="K352" s="7">
-        <v>0</v>
+        <v>6.943555</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
@@ -18078,22 +18078,22 @@
         <v>6</v>
       </c>
       <c r="E353" s="7">
-        <v>0</v>
+        <v>0.08359</v>
       </c>
       <c r="F353" s="7">
-        <v>0</v>
+        <v>0.24285199999999998</v>
       </c>
       <c r="G353" s="7">
-        <v>0</v>
+        <v>0.342688</v>
       </c>
       <c r="H353" s="7">
-        <v>0</v>
+        <v>0.36633000000000004</v>
       </c>
       <c r="I353" s="7">
-        <v>0</v>
+        <v>0.563501</v>
       </c>
       <c r="J353" s="7">
-        <v>0</v>
+        <v>1.4024619999999999</v>
       </c>
       <c r="K353" s="7"/>
     </row>
@@ -18111,25 +18111,25 @@
         <v>5</v>
       </c>
       <c r="E354" s="7">
-        <v>0</v>
+        <v>-0.009094999999999999</v>
       </c>
       <c r="F354" s="7">
-        <v>0</v>
+        <v>-0.10863400000000001</v>
       </c>
       <c r="G354" s="7">
-        <v>0</v>
+        <v>0.071227</v>
       </c>
       <c r="H354" s="7">
-        <v>0</v>
+        <v>0.21412199999999998</v>
       </c>
       <c r="I354" s="7">
-        <v>0</v>
+        <v>0.421706</v>
       </c>
       <c r="J354" s="7">
-        <v>0</v>
+        <v>0.7565529999999999</v>
       </c>
       <c r="K354" s="7">
-        <v>0</v>
+        <v>4.054460000000001</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -18146,25 +18146,25 @@
         <v>4</v>
       </c>
       <c r="E355" s="7">
-        <v>0</v>
+        <v>0.030647</v>
       </c>
       <c r="F355" s="7">
-        <v>0</v>
+        <v>0.059487</v>
       </c>
       <c r="G355" s="7">
-        <v>0</v>
+        <v>0.08855</v>
       </c>
       <c r="H355" s="7">
-        <v>0</v>
+        <v>0.19533</v>
       </c>
       <c r="I355" s="7">
-        <v>0</v>
+        <v>0.353332</v>
       </c>
       <c r="J355" s="7">
-        <v>0</v>
+        <v>1.958783</v>
       </c>
       <c r="K355" s="7">
-        <v>0</v>
+        <v>6.84604</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
@@ -18181,22 +18181,22 @@
         <v>5</v>
       </c>
       <c r="E356" s="7">
-        <v>0</v>
+        <v>0.053357</v>
       </c>
       <c r="F356" s="7">
-        <v>0</v>
+        <v>0.10517099999999999</v>
       </c>
       <c r="G356" s="7">
-        <v>0</v>
+        <v>0.214399</v>
       </c>
       <c r="H356" s="7">
-        <v>0</v>
+        <v>0.409714</v>
       </c>
       <c r="I356" s="7">
-        <v>0</v>
+        <v>0.507631</v>
       </c>
       <c r="J356" s="7">
-        <v>0</v>
+        <v>0.896055</v>
       </c>
       <c r="K356" s="7"/>
     </row>
@@ -18284,25 +18284,25 @@
         <v>3</v>
       </c>
       <c r="E359" s="7">
-        <v>0</v>
+        <v>0.030816</v>
       </c>
       <c r="F359" s="7">
-        <v>0</v>
+        <v>0.075585</v>
       </c>
       <c r="G359" s="7">
-        <v>0</v>
+        <v>0.139811</v>
       </c>
       <c r="H359" s="7">
-        <v>0</v>
+        <v>0.229749</v>
       </c>
       <c r="I359" s="7">
-        <v>0</v>
+        <v>0.396288</v>
       </c>
       <c r="J359" s="7">
-        <v>0</v>
+        <v>2.176708</v>
       </c>
       <c r="K359" s="7">
-        <v>0</v>
+        <v>6.0095920000000005</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
@@ -18354,25 +18354,25 @@
         <v>5</v>
       </c>
       <c r="E361" s="7">
-        <v>0</v>
+        <v>0.034161000000000004</v>
       </c>
       <c r="F361" s="7">
-        <v>0</v>
+        <v>0.035928</v>
       </c>
       <c r="G361" s="7">
-        <v>0</v>
+        <v>0.181596</v>
       </c>
       <c r="H361" s="7">
-        <v>0</v>
+        <v>0.23950600000000002</v>
       </c>
       <c r="I361" s="7">
-        <v>0</v>
+        <v>0.372836</v>
       </c>
       <c r="J361" s="7">
-        <v>0</v>
+        <v>1.4273330000000002</v>
       </c>
       <c r="K361" s="7">
-        <v>0</v>
+        <v>6.227751</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
@@ -18422,22 +18422,22 @@
         <v>5</v>
       </c>
       <c r="E363" s="7">
-        <v>0</v>
+        <v>0.037564</v>
       </c>
       <c r="F363" s="7">
-        <v>0</v>
+        <v>0.10960800000000001</v>
       </c>
       <c r="G363" s="7">
-        <v>0</v>
+        <v>0.136905</v>
       </c>
       <c r="H363" s="7">
-        <v>0</v>
+        <v>0.098306</v>
       </c>
       <c r="I363" s="7">
-        <v>0</v>
+        <v>0.224073</v>
       </c>
       <c r="J363" s="7">
-        <v>0</v>
+        <v>1.679714</v>
       </c>
       <c r="K363" s="7"/>
     </row>
@@ -18509,16 +18509,16 @@
         <v>7</v>
       </c>
       <c r="E366" s="7">
-        <v>0.051871</v>
+        <v>0.04983</v>
       </c>
       <c r="F366" s="7">
-        <v>-0.0054800000000000005</v>
+        <v>-0.00741</v>
       </c>
       <c r="G366" s="7">
-        <v>0.11646000000000001</v>
+        <v>0.11429299999999999</v>
       </c>
       <c r="H366" s="7">
-        <v>0.176562</v>
+        <v>0.17427800000000002</v>
       </c>
       <c r="I366" s="7"/>
       <c r="J366" s="7"/>
@@ -18600,22 +18600,22 @@
       </c>
       <c r="D369" s="6"/>
       <c r="E369" s="7">
-        <v>0</v>
+        <v>0.024537</v>
       </c>
       <c r="F369" s="7">
-        <v>0</v>
+        <v>0.037265</v>
       </c>
       <c r="G369" s="7">
-        <v>0</v>
+        <v>0.119642</v>
       </c>
       <c r="H369" s="7">
-        <v>0</v>
+        <v>0.213004</v>
       </c>
       <c r="I369" s="7">
-        <v>0</v>
+        <v>0.330845</v>
       </c>
       <c r="J369" s="7">
-        <v>0</v>
+        <v>1.510199</v>
       </c>
       <c r="K369" s="7"/>
     </row>
@@ -19491,25 +19491,25 @@
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="7">
-        <v>0.025556000000000002</v>
+        <v>0.026303</v>
       </c>
       <c r="F398" s="7">
-        <v>0.034251000000000004</v>
+        <v>0.035004</v>
       </c>
       <c r="G398" s="7">
-        <v>0.18144300000000002</v>
+        <v>0.182304</v>
       </c>
       <c r="H398" s="7">
-        <v>0.228981</v>
+        <v>0.229876</v>
       </c>
       <c r="I398" s="7">
-        <v>0.34491900000000003</v>
+        <v>0.345899</v>
       </c>
       <c r="J398" s="7">
-        <v>1.521851</v>
+        <v>1.523688</v>
       </c>
       <c r="K398" s="7">
-        <v>6.49639</v>
+        <v>6.501851</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
@@ -19846,19 +19846,19 @@
         <v>4</v>
       </c>
       <c r="E409" s="7">
-        <v>0.070837</v>
+        <v>0.071253</v>
       </c>
       <c r="F409" s="7">
-        <v>0.016864</v>
+        <v>0.017259</v>
       </c>
       <c r="G409" s="7">
-        <v>0.35405299999999995</v>
+        <v>0.35457900000000003</v>
       </c>
       <c r="H409" s="7">
-        <v>0.299695</v>
+        <v>0.3002</v>
       </c>
       <c r="I409" s="7">
-        <v>0.44148600000000005</v>
+        <v>0.442046</v>
       </c>
       <c r="J409" s="7"/>
       <c r="K409" s="7"/>
@@ -19877,10 +19877,10 @@
         <v>6</v>
       </c>
       <c r="E410" s="7">
-        <v>-0.020276000000000002</v>
+        <v>-0.021194</v>
       </c>
       <c r="F410" s="7">
-        <v>0.019698</v>
+        <v>0.018743</v>
       </c>
       <c r="G410" s="7"/>
       <c r="H410" s="7"/>
@@ -21633,25 +21633,25 @@
         <v>3</v>
       </c>
       <c r="E464" s="7">
-        <v>0</v>
+        <v>0.031874</v>
       </c>
       <c r="F464" s="7">
-        <v>0</v>
+        <v>0.06607</v>
       </c>
       <c r="G464" s="7">
-        <v>0</v>
+        <v>0.136128</v>
       </c>
       <c r="H464" s="7">
-        <v>0</v>
+        <v>0.213812</v>
       </c>
       <c r="I464" s="7">
-        <v>0</v>
+        <v>0.340625</v>
       </c>
       <c r="J464" s="7">
-        <v>0</v>
+        <v>1.998736</v>
       </c>
       <c r="K464" s="7">
-        <v>0</v>
+        <v>6.049277</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
@@ -22311,16 +22311,16 @@
         <v>2</v>
       </c>
       <c r="E484" s="7">
-        <v>0</v>
+        <v>0.031313</v>
       </c>
       <c r="F484" s="7">
-        <v>0</v>
+        <v>0.099498</v>
       </c>
       <c r="G484" s="7">
-        <v>0</v>
+        <v>0.235517</v>
       </c>
       <c r="H484" s="7">
-        <v>0</v>
+        <v>0.31852199999999997</v>
       </c>
       <c r="I484" s="7"/>
       <c r="J484" s="7"/>
@@ -22340,22 +22340,22 @@
         <v>3</v>
       </c>
       <c r="E485" s="7">
-        <v>0</v>
+        <v>0.031556</v>
       </c>
       <c r="F485" s="7">
-        <v>0</v>
+        <v>0.130125</v>
       </c>
       <c r="G485" s="7">
-        <v>0</v>
+        <v>0.262559</v>
       </c>
       <c r="H485" s="7">
-        <v>0</v>
+        <v>0.361444</v>
       </c>
       <c r="I485" s="7">
-        <v>0</v>
+        <v>0.6089950000000001</v>
       </c>
       <c r="J485" s="7">
-        <v>0</v>
+        <v>2.240641</v>
       </c>
       <c r="K485" s="7"/>
     </row>
@@ -22631,22 +22631,22 @@
         <v>5</v>
       </c>
       <c r="E494" s="7">
-        <v>0.030371000000000002</v>
+        <v>0.031766</v>
       </c>
       <c r="F494" s="7">
-        <v>0.0020930000000000002</v>
+        <v>0.003449</v>
       </c>
       <c r="G494" s="7">
-        <v>0.358075</v>
+        <v>0.359914</v>
       </c>
       <c r="H494" s="7">
-        <v>0.404319</v>
+        <v>0.40622</v>
       </c>
       <c r="I494" s="7">
-        <v>0.56979</v>
+        <v>0.571916</v>
       </c>
       <c r="J494" s="7">
-        <v>2.163646</v>
+        <v>2.167929</v>
       </c>
       <c r="K494" s="7"/>
     </row>
@@ -22827,16 +22827,16 @@
         <v>6</v>
       </c>
       <c r="E500" s="7">
-        <v>0.015545</v>
+        <v>0.015507</v>
       </c>
       <c r="F500" s="7">
-        <v>0.009156</v>
+        <v>0.009119</v>
       </c>
       <c r="G500" s="7">
-        <v>0.019729</v>
+        <v>0.019691</v>
       </c>
       <c r="H500" s="7">
-        <v>0.07831</v>
+        <v>0.078271</v>
       </c>
       <c r="I500" s="7"/>
       <c r="J500" s="7"/>
@@ -22955,19 +22955,19 @@
         <v>6</v>
       </c>
       <c r="E504" s="7">
-        <v>0.019562</v>
+        <v>0.019563999999999998</v>
       </c>
       <c r="F504" s="7">
-        <v>0.058890000000000005</v>
+        <v>0.058892</v>
       </c>
       <c r="G504" s="7">
-        <v>0.101473</v>
+        <v>0.10147500000000001</v>
       </c>
       <c r="H504" s="7">
-        <v>0.117963</v>
+        <v>0.117965</v>
       </c>
       <c r="I504" s="7">
-        <v>0.108865</v>
+        <v>0.10886699999999999</v>
       </c>
       <c r="J504" s="7"/>
       <c r="K504" s="7"/>
@@ -23017,19 +23017,19 @@
         <v>6</v>
       </c>
       <c r="E506" s="7">
-        <v>0</v>
+        <v>0.037575</v>
       </c>
       <c r="F506" s="7">
-        <v>0</v>
+        <v>0.027801</v>
       </c>
       <c r="G506" s="7">
-        <v>0</v>
+        <v>0.123237</v>
       </c>
       <c r="H506" s="7">
-        <v>0</v>
+        <v>0.25623999999999997</v>
       </c>
       <c r="I506" s="7">
-        <v>0</v>
+        <v>0.408617</v>
       </c>
       <c r="J506" s="7"/>
       <c r="K506" s="7"/>
@@ -23315,19 +23315,19 @@
         <v>7</v>
       </c>
       <c r="E516" s="7">
-        <v>0</v>
+        <v>-0.035734</v>
       </c>
       <c r="F516" s="7">
-        <v>0</v>
+        <v>0.013528</v>
       </c>
       <c r="G516" s="7">
-        <v>0</v>
+        <v>0.142514</v>
       </c>
       <c r="H516" s="7">
-        <v>0</v>
+        <v>0.275455</v>
       </c>
       <c r="I516" s="7">
-        <v>0</v>
+        <v>0.252133</v>
       </c>
       <c r="J516" s="7"/>
       <c r="K516" s="7"/>
@@ -23540,19 +23540,19 @@
         <v>2</v>
       </c>
       <c r="E523" s="7">
-        <v>0</v>
+        <v>0.028754</v>
       </c>
       <c r="F523" s="7">
-        <v>0</v>
+        <v>0.08992499999999999</v>
       </c>
       <c r="G523" s="7">
-        <v>0</v>
+        <v>0.19078900000000001</v>
       </c>
       <c r="H523" s="7">
-        <v>0</v>
+        <v>0.24111999999999997</v>
       </c>
       <c r="I523" s="7">
-        <v>0</v>
+        <v>0.337978</v>
       </c>
       <c r="J523" s="7"/>
       <c r="K523" s="7"/>
@@ -23637,19 +23637,19 @@
         <v>4</v>
       </c>
       <c r="E526" s="7">
-        <v>0</v>
+        <v>0.025076</v>
       </c>
       <c r="F526" s="7">
-        <v>0</v>
+        <v>0.055382999999999995</v>
       </c>
       <c r="G526" s="7">
-        <v>0</v>
+        <v>0.108223</v>
       </c>
       <c r="H526" s="7">
-        <v>0</v>
+        <v>0.128391</v>
       </c>
       <c r="I526" s="7">
-        <v>0</v>
+        <v>0.1974</v>
       </c>
       <c r="J526" s="7"/>
       <c r="K526" s="7"/>
@@ -24065,19 +24065,19 @@
         <v>6</v>
       </c>
       <c r="E540" s="7">
-        <v>0</v>
+        <v>0.021716000000000003</v>
       </c>
       <c r="F540" s="7">
-        <v>0</v>
+        <v>0.044995</v>
       </c>
       <c r="G540" s="7">
-        <v>0</v>
+        <v>0.07638099999999999</v>
       </c>
       <c r="H540" s="7">
-        <v>0</v>
+        <v>0.087981</v>
       </c>
       <c r="I540" s="7">
-        <v>0</v>
+        <v>0.131939</v>
       </c>
       <c r="J540" s="7"/>
       <c r="K540" s="7"/>
@@ -24284,19 +24284,19 @@
         <v>1</v>
       </c>
       <c r="E547" s="7">
-        <v>0</v>
+        <v>0.033048</v>
       </c>
       <c r="F547" s="7">
-        <v>0</v>
+        <v>0.10327299999999999</v>
       </c>
       <c r="G547" s="7">
-        <v>0</v>
+        <v>0.218089</v>
       </c>
       <c r="H547" s="7">
-        <v>0</v>
+        <v>0.296815</v>
       </c>
       <c r="I547" s="7">
-        <v>0</v>
+        <v>0.476579</v>
       </c>
       <c r="J547" s="7"/>
       <c r="K547" s="7"/>
@@ -24348,25 +24348,25 @@
         <v>2</v>
       </c>
       <c r="E549" s="7">
-        <v>0</v>
+        <v>0.040251999999999996</v>
       </c>
       <c r="F549" s="7">
-        <v>0</v>
+        <v>0.099787</v>
       </c>
       <c r="G549" s="7">
-        <v>0</v>
+        <v>0.134216</v>
       </c>
       <c r="H549" s="7">
-        <v>0</v>
+        <v>0.18532099999999999</v>
       </c>
       <c r="I549" s="7">
-        <v>0</v>
+        <v>0.359114</v>
       </c>
       <c r="J549" s="7">
-        <v>0</v>
+        <v>2.0857490000000003</v>
       </c>
       <c r="K549" s="7">
-        <v>0</v>
+        <v>3.7150670000000003</v>
       </c>
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.25">
@@ -24383,25 +24383,25 @@
         <v>5</v>
       </c>
       <c r="E550" s="7">
-        <v>0</v>
+        <v>0.053532</v>
       </c>
       <c r="F550" s="7">
-        <v>0</v>
+        <v>0.083664</v>
       </c>
       <c r="G550" s="7">
-        <v>0</v>
+        <v>0.15515800000000002</v>
       </c>
       <c r="H550" s="7">
-        <v>0</v>
+        <v>0.257285</v>
       </c>
       <c r="I550" s="7">
-        <v>0</v>
+        <v>0.41848100000000005</v>
       </c>
       <c r="J550" s="7">
-        <v>0</v>
+        <v>2.14873</v>
       </c>
       <c r="K550" s="7">
-        <v>0</v>
+        <v>10.511115</v>
       </c>
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.25">
@@ -24443,25 +24443,25 @@
         <v>5</v>
       </c>
       <c r="E552" s="7">
-        <v>0</v>
+        <v>0.044367000000000004</v>
       </c>
       <c r="F552" s="7">
-        <v>0</v>
+        <v>0.04294</v>
       </c>
       <c r="G552" s="7">
-        <v>0</v>
+        <v>0.11221199999999999</v>
       </c>
       <c r="H552" s="7">
-        <v>0</v>
+        <v>0.155358</v>
       </c>
       <c r="I552" s="7">
-        <v>0</v>
+        <v>0.260209</v>
       </c>
       <c r="J552" s="7">
-        <v>0</v>
+        <v>1.29478</v>
       </c>
       <c r="K552" s="7">
-        <v>0</v>
+        <v>5.711582</v>
       </c>
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.25">
@@ -24478,25 +24478,25 @@
         <v>3</v>
       </c>
       <c r="E553" s="7">
-        <v>0</v>
+        <v>0.021167</v>
       </c>
       <c r="F553" s="7">
-        <v>0</v>
+        <v>0.064038</v>
       </c>
       <c r="G553" s="7">
-        <v>0</v>
+        <v>0.11785399999999999</v>
       </c>
       <c r="H553" s="7">
-        <v>0</v>
+        <v>0.155428</v>
       </c>
       <c r="I553" s="7">
-        <v>0</v>
+        <v>0.225658</v>
       </c>
       <c r="J553" s="7">
-        <v>0</v>
+        <v>1.1829399999999999</v>
       </c>
       <c r="K553" s="7">
-        <v>0</v>
+        <v>6.480438</v>
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.25">
@@ -25002,25 +25002,25 @@
         <v>6</v>
       </c>
       <c r="E569" s="7">
-        <v>0</v>
+        <v>0.038866</v>
       </c>
       <c r="F569" s="7">
-        <v>0</v>
+        <v>0.056121</v>
       </c>
       <c r="G569" s="7">
-        <v>0</v>
+        <v>0.125835</v>
       </c>
       <c r="H569" s="7">
-        <v>0</v>
+        <v>0.13117</v>
       </c>
       <c r="I569" s="7">
-        <v>0</v>
+        <v>0.21395</v>
       </c>
       <c r="J569" s="7">
-        <v>0</v>
+        <v>1.516699</v>
       </c>
       <c r="K569" s="7">
-        <v>0</v>
+        <v>6.827116</v>
       </c>
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.25">
@@ -25223,25 +25223,25 @@
         <v>6</v>
       </c>
       <c r="E576" s="7">
-        <v>0</v>
+        <v>0.012908999999999999</v>
       </c>
       <c r="F576" s="7">
-        <v>0</v>
+        <v>-0.026415</v>
       </c>
       <c r="G576" s="7">
-        <v>0</v>
+        <v>-0.020383</v>
       </c>
       <c r="H576" s="7">
-        <v>0</v>
+        <v>0.083689</v>
       </c>
       <c r="I576" s="7">
-        <v>0</v>
+        <v>0.174385</v>
       </c>
       <c r="J576" s="7">
-        <v>0</v>
+        <v>1.033156</v>
       </c>
       <c r="K576" s="7">
-        <v>0</v>
+        <v>11.985706</v>
       </c>
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.25">
@@ -25258,19 +25258,19 @@
         <v>3</v>
       </c>
       <c r="E577" s="7">
-        <v>0</v>
+        <v>0.008357999999999999</v>
       </c>
       <c r="F577" s="7">
-        <v>0</v>
+        <v>0.057518</v>
       </c>
       <c r="G577" s="7">
-        <v>0</v>
+        <v>0.149544</v>
       </c>
       <c r="H577" s="7">
-        <v>0</v>
+        <v>0.17089</v>
       </c>
       <c r="I577" s="7">
-        <v>0</v>
+        <v>0.280237</v>
       </c>
       <c r="J577" s="7"/>
       <c r="K577" s="7"/>
@@ -25785,22 +25785,22 @@
         <v>6</v>
       </c>
       <c r="E594" s="7">
-        <v>0</v>
+        <v>0.011755</v>
       </c>
       <c r="F594" s="7">
-        <v>0</v>
+        <v>0.004866</v>
       </c>
       <c r="G594" s="7">
-        <v>0</v>
+        <v>0.284242</v>
       </c>
       <c r="H594" s="7">
-        <v>0</v>
+        <v>0.271069</v>
       </c>
       <c r="I594" s="7">
-        <v>0</v>
+        <v>0.422445</v>
       </c>
       <c r="J594" s="7">
-        <v>0</v>
+        <v>2.36314</v>
       </c>
       <c r="K594" s="7"/>
     </row>
@@ -25911,22 +25911,22 @@
         <v>6</v>
       </c>
       <c r="E598" s="7">
-        <v>0.037617</v>
+        <v>0.045909000000000005</v>
       </c>
       <c r="F598" s="7">
-        <v>-0.028991</v>
+        <v>-0.021232</v>
       </c>
       <c r="G598" s="7">
-        <v>0.155888</v>
+        <v>0.165125</v>
       </c>
       <c r="H598" s="7">
-        <v>0.293493</v>
+        <v>0.303829</v>
       </c>
       <c r="I598" s="7">
-        <v>0.414496</v>
+        <v>0.42579900000000004</v>
       </c>
       <c r="J598" s="7">
-        <v>1.7178129999999998</v>
+        <v>1.73953</v>
       </c>
       <c r="K598" s="7"/>
     </row>
@@ -25944,25 +25944,25 @@
         <v>7</v>
       </c>
       <c r="E599" s="7">
-        <v>0.133887</v>
+        <v>0.159104</v>
       </c>
       <c r="F599" s="7">
-        <v>-0.073755</v>
+        <v>-0.053156</v>
       </c>
       <c r="G599" s="7">
-        <v>-0.126108</v>
+        <v>-0.10667299999999999</v>
       </c>
       <c r="H599" s="7">
-        <v>-0.033276</v>
+        <v>-0.011776</v>
       </c>
       <c r="I599" s="7">
-        <v>0.7130670000000001</v>
+        <v>0.751165</v>
       </c>
       <c r="J599" s="7">
-        <v>3.430313</v>
+        <v>3.528841</v>
       </c>
       <c r="K599" s="7">
-        <v>11.666828</v>
+        <v>11.948534</v>
       </c>
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.25">
@@ -25979,25 +25979,25 @@
         <v>6</v>
       </c>
       <c r="E600" s="7">
-        <v>-0.061454</v>
+        <v>-0.059328000000000006</v>
       </c>
       <c r="F600" s="7">
-        <v>-0.02043</v>
+        <v>-0.01821</v>
       </c>
       <c r="G600" s="7">
-        <v>-0.036747999999999996</v>
+        <v>-0.034565</v>
       </c>
       <c r="H600" s="7">
-        <v>-0.083581</v>
+        <v>-0.081504</v>
       </c>
       <c r="I600" s="7">
-        <v>-0.081151</v>
+        <v>-0.079069</v>
       </c>
       <c r="J600" s="7">
-        <v>0.358791</v>
+        <v>0.36186999999999997</v>
       </c>
       <c r="K600" s="7">
-        <v>3.033783</v>
+        <v>3.0429239999999997</v>
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.25">
@@ -26078,25 +26078,25 @@
         <v>6</v>
       </c>
       <c r="E603" s="7">
-        <v>0.081983</v>
+        <v>0.108124</v>
       </c>
       <c r="F603" s="7">
-        <v>0.016413999999999998</v>
+        <v>0.040971</v>
       </c>
       <c r="G603" s="7">
-        <v>-0.095677</v>
+        <v>-0.07382799999999999</v>
       </c>
       <c r="H603" s="7">
-        <v>0.092354</v>
+        <v>0.11874599999999999</v>
       </c>
       <c r="I603" s="7">
-        <v>0.42029299999999997</v>
+        <v>0.454608</v>
       </c>
       <c r="J603" s="7">
-        <v>3.057962</v>
+        <v>3.156004</v>
       </c>
       <c r="K603" s="7">
-        <v>13.219447</v>
+        <v>13.562994000000002</v>
       </c>
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.25">
@@ -26710,22 +26710,22 @@
         <v>5</v>
       </c>
       <c r="E623" s="7">
-        <v>0.042899</v>
+        <v>0.048921</v>
       </c>
       <c r="F623" s="7">
-        <v>0.014891000000000001</v>
+        <v>0.020751</v>
       </c>
       <c r="G623" s="7">
-        <v>0.118891</v>
+        <v>0.125352</v>
       </c>
       <c r="H623" s="7">
-        <v>0.192256</v>
+        <v>0.19914</v>
       </c>
       <c r="I623" s="7">
-        <v>0.283393</v>
+        <v>0.290804</v>
       </c>
       <c r="J623" s="7">
-        <v>1.067388</v>
+        <v>1.079326</v>
       </c>
       <c r="K623" s="7"/>
     </row>
@@ -26933,16 +26933,16 @@
         <v>5</v>
       </c>
       <c r="E630" s="7">
-        <v>0</v>
+        <v>0.036035</v>
       </c>
       <c r="F630" s="7">
-        <v>0</v>
+        <v>0.10732100000000001</v>
       </c>
       <c r="G630" s="7">
-        <v>0</v>
+        <v>0.22886099999999998</v>
       </c>
       <c r="H630" s="7">
-        <v>0</v>
+        <v>0.32562199999999997</v>
       </c>
       <c r="I630" s="7"/>
       <c r="J630" s="7"/>
@@ -27028,19 +27028,19 @@
         <v>5</v>
       </c>
       <c r="E633" s="7">
-        <v>0</v>
+        <v>0.031623</v>
       </c>
       <c r="F633" s="7">
-        <v>0</v>
+        <v>0.09059900000000001</v>
       </c>
       <c r="G633" s="7">
-        <v>0</v>
+        <v>0.18095300000000003</v>
       </c>
       <c r="H633" s="7">
-        <v>0</v>
+        <v>0.041989</v>
       </c>
       <c r="I633" s="7">
-        <v>0</v>
+        <v>0.154695</v>
       </c>
       <c r="J633" s="7"/>
       <c r="K633" s="7"/>
@@ -27059,22 +27059,22 @@
         <v>3</v>
       </c>
       <c r="E634" s="7">
-        <v>0</v>
+        <v>0.033995000000000004</v>
       </c>
       <c r="F634" s="7">
-        <v>0</v>
+        <v>0.03553</v>
       </c>
       <c r="G634" s="7">
-        <v>0</v>
+        <v>0.124723</v>
       </c>
       <c r="H634" s="7">
-        <v>0</v>
+        <v>0.16853100000000001</v>
       </c>
       <c r="I634" s="7">
-        <v>0</v>
+        <v>0.33725499999999997</v>
       </c>
       <c r="J634" s="7">
-        <v>0</v>
+        <v>1.727545</v>
       </c>
       <c r="K634" s="7"/>
     </row>
@@ -28030,22 +28030,22 @@
         <v>6</v>
       </c>
       <c r="E665" s="7">
-        <v>0</v>
+        <v>0.107694</v>
       </c>
       <c r="F665" s="7">
-        <v>0</v>
+        <v>-0.143358</v>
       </c>
       <c r="G665" s="7">
-        <v>0</v>
+        <v>-0.11226000000000001</v>
       </c>
       <c r="H665" s="7">
-        <v>0</v>
+        <v>-0.052297</v>
       </c>
       <c r="I665" s="7">
-        <v>0</v>
+        <v>0.11542999999999999</v>
       </c>
       <c r="J665" s="7">
-        <v>0</v>
+        <v>1.30308</v>
       </c>
       <c r="K665" s="7"/>
     </row>
@@ -28156,25 +28156,25 @@
         <v>6</v>
       </c>
       <c r="E669" s="7">
-        <v>0.039299</v>
+        <v>0.03798</v>
       </c>
       <c r="F669" s="7">
-        <v>0.048585</v>
+        <v>0.047254</v>
       </c>
       <c r="G669" s="7">
-        <v>0.16187200000000002</v>
+        <v>0.160397</v>
       </c>
       <c r="H669" s="7">
-        <v>0.25919000000000003</v>
+        <v>0.257593</v>
       </c>
       <c r="I669" s="7">
-        <v>0.36206200000000005</v>
+        <v>0.36033299999999996</v>
       </c>
       <c r="J669" s="7">
-        <v>1.016961</v>
+        <v>1.014402</v>
       </c>
       <c r="K669" s="7">
-        <v>2.169245</v>
+        <v>2.1652240000000003</v>
       </c>
     </row>
     <row r="670" spans="1:11" x14ac:dyDescent="0.25">
@@ -28447,25 +28447,25 @@
         <v>5</v>
       </c>
       <c r="E678" s="7">
-        <v>0</v>
+        <v>0.007089</v>
       </c>
       <c r="F678" s="7">
-        <v>0</v>
+        <v>0.001015</v>
       </c>
       <c r="G678" s="7">
-        <v>0</v>
+        <v>0.013224</v>
       </c>
       <c r="H678" s="7">
-        <v>0</v>
+        <v>0.130852</v>
       </c>
       <c r="I678" s="7">
-        <v>0</v>
+        <v>0.263691</v>
       </c>
       <c r="J678" s="7">
-        <v>0</v>
+        <v>1.5260980000000002</v>
       </c>
       <c r="K678" s="7">
-        <v>0</v>
+        <v>6.421105</v>
       </c>
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.25">
@@ -28480,22 +28480,22 @@
       </c>
       <c r="D679" s="6"/>
       <c r="E679" s="7">
-        <v>0.050202</v>
+        <v>0.050206999999999995</v>
       </c>
       <c r="F679" s="7">
-        <v>0.058441</v>
+        <v>0.058446</v>
       </c>
       <c r="G679" s="7">
-        <v>0.137415</v>
+        <v>0.13742000000000001</v>
       </c>
       <c r="H679" s="7">
-        <v>0.21909700000000001</v>
+        <v>0.219103</v>
       </c>
       <c r="I679" s="7">
-        <v>0.34403300000000003</v>
+        <v>0.34404</v>
       </c>
       <c r="J679" s="7">
-        <v>1.4417740000000001</v>
+        <v>1.441785</v>
       </c>
       <c r="K679" s="7"/>
     </row>
@@ -28513,25 +28513,25 @@
         <v>4</v>
       </c>
       <c r="E680" s="7">
-        <v>0.054881</v>
+        <v>0.05489</v>
       </c>
       <c r="F680" s="7">
-        <v>0.070171</v>
+        <v>0.07017999999999999</v>
       </c>
       <c r="G680" s="7">
-        <v>0.118379</v>
+        <v>0.11838900000000001</v>
       </c>
       <c r="H680" s="7">
-        <v>0.204061</v>
+        <v>0.204071</v>
       </c>
       <c r="I680" s="7">
-        <v>0.363076</v>
+        <v>0.36308799999999997</v>
       </c>
       <c r="J680" s="7">
-        <v>1.727078</v>
+        <v>1.727102</v>
       </c>
       <c r="K680" s="7">
-        <v>6.4909349999999995</v>
+        <v>6.4910000000000005</v>
       </c>
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.25">
@@ -28651,22 +28651,22 @@
         <v>6</v>
       </c>
       <c r="E684" s="7">
-        <v>0.08662</v>
+        <v>0.11185700000000001</v>
       </c>
       <c r="F684" s="7">
-        <v>0.018175</v>
+        <v>0.041823</v>
       </c>
       <c r="G684" s="7">
-        <v>-0.014578</v>
+        <v>0.008308</v>
       </c>
       <c r="H684" s="7">
-        <v>0.127744</v>
+        <v>0.153936</v>
       </c>
       <c r="I684" s="7">
-        <v>0.21329499999999998</v>
+        <v>0.24147400000000002</v>
       </c>
       <c r="J684" s="7">
-        <v>0.6965720000000001</v>
+        <v>0.7359749999999999</v>
       </c>
       <c r="K684" s="7"/>
     </row>
@@ -28684,22 +28684,22 @@
         <v>3</v>
       </c>
       <c r="E685" s="7">
-        <v>0.032422</v>
+        <v>0.036629999999999996</v>
       </c>
       <c r="F685" s="7">
-        <v>0.058244</v>
+        <v>0.062557</v>
       </c>
       <c r="G685" s="7">
-        <v>0.131034</v>
+        <v>0.135644</v>
       </c>
       <c r="H685" s="7">
-        <v>0.234189</v>
+        <v>0.23921900000000001</v>
       </c>
       <c r="I685" s="7">
-        <v>0.42631399999999997</v>
+        <v>0.432127</v>
       </c>
       <c r="J685" s="7">
-        <v>2.1781479999999998</v>
+        <v>2.1911009999999997</v>
       </c>
       <c r="K685" s="7"/>
     </row>
@@ -28785,25 +28785,25 @@
         <v>6</v>
       </c>
       <c r="E688" s="7">
-        <v>0.053303</v>
+        <v>0.052432999999999994</v>
       </c>
       <c r="F688" s="7">
-        <v>-0.024779</v>
+        <v>-0.025584</v>
       </c>
       <c r="G688" s="7">
-        <v>0.385408</v>
+        <v>0.384264</v>
       </c>
       <c r="H688" s="7">
-        <v>0.394301</v>
+        <v>0.393149</v>
       </c>
       <c r="I688" s="7">
-        <v>0.567112</v>
+        <v>0.565817</v>
       </c>
       <c r="J688" s="7">
-        <v>2.6016969999999997</v>
+        <v>2.5987220000000004</v>
       </c>
       <c r="K688" s="7">
-        <v>10.451047</v>
+        <v>10.441588</v>
       </c>
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.25">
@@ -28989,22 +28989,22 @@
         <v>2</v>
       </c>
       <c r="E694" s="7">
-        <v>0.032851</v>
+        <v>0.03375</v>
       </c>
       <c r="F694" s="7">
-        <v>0.10309499999999999</v>
+        <v>0.104056</v>
       </c>
       <c r="G694" s="7">
-        <v>0.222584</v>
+        <v>0.223649</v>
       </c>
       <c r="H694" s="7">
-        <v>0.30267900000000003</v>
+        <v>0.303814</v>
       </c>
       <c r="I694" s="7">
-        <v>0.48369599999999996</v>
+        <v>0.484989</v>
       </c>
       <c r="J694" s="7">
-        <v>2.519291</v>
+        <v>2.522357</v>
       </c>
       <c r="K694" s="7"/>
     </row>
@@ -29509,22 +29509,22 @@
         <v>6</v>
       </c>
       <c r="E710" s="7">
-        <v>0.132139</v>
+        <v>0.13278700000000002</v>
       </c>
       <c r="F710" s="7">
-        <v>0.002741</v>
+        <v>0.003316</v>
       </c>
       <c r="G710" s="7">
-        <v>-0.069702</v>
+        <v>-0.069169</v>
       </c>
       <c r="H710" s="7">
-        <v>0.059352999999999996</v>
+        <v>0.059960000000000006</v>
       </c>
       <c r="I710" s="7">
-        <v>0.603934</v>
+        <v>0.604853</v>
       </c>
       <c r="J710" s="7">
-        <v>2.769194</v>
+        <v>2.771354</v>
       </c>
       <c r="K710" s="7"/>
     </row>
@@ -29639,22 +29639,22 @@
         <v>6</v>
       </c>
       <c r="E714" s="7">
-        <v>0.10872299999999999</v>
+        <v>0.108758</v>
       </c>
       <c r="F714" s="7">
-        <v>0.08375500000000001</v>
+        <v>0.083789</v>
       </c>
       <c r="G714" s="7">
-        <v>0.195423</v>
+        <v>0.195461</v>
       </c>
       <c r="H714" s="7">
-        <v>0.367206</v>
+        <v>0.367249</v>
       </c>
       <c r="I714" s="7">
-        <v>0.596212</v>
+        <v>0.596263</v>
       </c>
       <c r="J714" s="7">
-        <v>1.5981589999999999</v>
+        <v>1.5982409999999998</v>
       </c>
       <c r="K714" s="7"/>
     </row>
@@ -29850,19 +29850,19 @@
         <v>4</v>
       </c>
       <c r="E721" s="7">
-        <v>0.048799</v>
+        <v>0.045306</v>
       </c>
       <c r="F721" s="7">
-        <v>0.098906</v>
+        <v>0.095246</v>
       </c>
       <c r="G721" s="7">
-        <v>0.27254100000000003</v>
+        <v>0.26830200000000004</v>
       </c>
       <c r="H721" s="7">
-        <v>0.43945</v>
+        <v>0.43465600000000004</v>
       </c>
       <c r="I721" s="7">
-        <v>0.62945</v>
+        <v>0.624023</v>
       </c>
       <c r="J721" s="7"/>
       <c r="K721" s="7"/>
@@ -30110,19 +30110,19 @@
         <v>4</v>
       </c>
       <c r="E729" s="7">
-        <v>0.047462</v>
+        <v>0.050655</v>
       </c>
       <c r="F729" s="7">
-        <v>0.062478</v>
+        <v>0.065718</v>
       </c>
       <c r="G729" s="7">
-        <v>0.065623</v>
+        <v>0.068872</v>
       </c>
       <c r="H729" s="7">
-        <v>0.201218</v>
+        <v>0.20488099999999998</v>
       </c>
       <c r="I729" s="7">
-        <v>0.39272100000000004</v>
+        <v>0.39696800000000004</v>
       </c>
       <c r="J729" s="7"/>
       <c r="K729" s="7"/>
@@ -30141,22 +30141,22 @@
         <v>4</v>
       </c>
       <c r="E730" s="7">
-        <v>0.011707</v>
+        <v>0.013111</v>
       </c>
       <c r="F730" s="7">
-        <v>0.012726999999999999</v>
+        <v>0.014133</v>
       </c>
       <c r="G730" s="7">
-        <v>0.11771599999999999</v>
+        <v>0.119268</v>
       </c>
       <c r="H730" s="7">
-        <v>0.225135</v>
+        <v>0.22683499999999998</v>
       </c>
       <c r="I730" s="7">
-        <v>0.396802</v>
+        <v>0.398741</v>
       </c>
       <c r="J730" s="7">
-        <v>1.874898</v>
+        <v>1.878889</v>
       </c>
       <c r="K730" s="7"/>
     </row>
@@ -30360,22 +30360,22 @@
         <v>6</v>
       </c>
       <c r="E737" s="7">
-        <v>0.032286</v>
+        <v>0.033397</v>
       </c>
       <c r="F737" s="7">
-        <v>-0.10482200000000001</v>
+        <v>-0.10385799999999999</v>
       </c>
       <c r="G737" s="7">
-        <v>0.115959</v>
+        <v>0.11715999999999999</v>
       </c>
       <c r="H737" s="7">
-        <v>0.255158</v>
+        <v>0.256509</v>
       </c>
       <c r="I737" s="7">
-        <v>0.707762</v>
+        <v>0.7095999999999999</v>
       </c>
       <c r="J737" s="7">
-        <v>1.900426</v>
+        <v>1.903548</v>
       </c>
       <c r="K737" s="7"/>
     </row>
@@ -31584,19 +31584,19 @@
         <v>2</v>
       </c>
       <c r="E777" s="7">
-        <v>0</v>
+        <v>0.041955</v>
       </c>
       <c r="F777" s="7">
-        <v>0</v>
+        <v>0.127046</v>
       </c>
       <c r="G777" s="7">
-        <v>0</v>
+        <v>0.26760300000000004</v>
       </c>
       <c r="H777" s="7">
-        <v>0</v>
+        <v>0.369742</v>
       </c>
       <c r="I777" s="7">
-        <v>0</v>
+        <v>0.5991599999999999</v>
       </c>
       <c r="J777" s="7"/>
       <c r="K777" s="7"/>
@@ -31735,19 +31735,19 @@
         <v>2</v>
       </c>
       <c r="E782" s="7">
-        <v>0.036213999999999996</v>
+        <v>0.036126</v>
       </c>
       <c r="F782" s="7">
-        <v>0.07803399999999999</v>
+        <v>0.077943</v>
       </c>
       <c r="G782" s="7">
-        <v>0.154459</v>
+        <v>0.154361</v>
       </c>
       <c r="H782" s="7">
-        <v>0.241022</v>
+        <v>0.240917</v>
       </c>
       <c r="I782" s="7">
-        <v>0.424573</v>
+        <v>0.424452</v>
       </c>
       <c r="J782" s="7"/>
       <c r="K782" s="7"/>
@@ -32594,7 +32594,7 @@
         <v>6</v>
       </c>
       <c r="E809" s="7">
-        <v>0.113292</v>
+        <v>0.11360200000000001</v>
       </c>
       <c r="F809" s="7"/>
       <c r="G809" s="7"/>
@@ -33563,22 +33563,22 @@
         <v>6</v>
       </c>
       <c r="E840" s="7">
-        <v>0.028843999999999998</v>
+        <v>0.028877</v>
       </c>
       <c r="F840" s="7">
-        <v>-0.08955</v>
+        <v>-0.089521</v>
       </c>
       <c r="G840" s="7">
-        <v>0.37337699999999996</v>
+        <v>0.373421</v>
       </c>
       <c r="H840" s="7">
-        <v>0.37355400000000005</v>
+        <v>0.373598</v>
       </c>
       <c r="I840" s="7">
-        <v>0.557821</v>
+        <v>0.557871</v>
       </c>
       <c r="J840" s="7">
-        <v>2.024834</v>
+        <v>2.02493</v>
       </c>
       <c r="K840" s="7"/>
     </row>
@@ -33757,19 +33757,19 @@
         <v>6</v>
       </c>
       <c r="E846" s="7">
-        <v>0</v>
+        <v>-0.072191</v>
       </c>
       <c r="F846" s="7">
-        <v>0</v>
+        <v>-0.09202</v>
       </c>
       <c r="G846" s="7">
-        <v>0</v>
+        <v>-0.016611</v>
       </c>
       <c r="H846" s="7">
-        <v>0</v>
+        <v>0.130949</v>
       </c>
       <c r="I846" s="7">
-        <v>0</v>
+        <v>0.334798</v>
       </c>
       <c r="J846" s="7"/>
       <c r="K846" s="7"/>
@@ -33788,7 +33788,7 @@
         <v>5</v>
       </c>
       <c r="E847" s="7">
-        <v>0</v>
+        <v>0.034471</v>
       </c>
       <c r="F847" s="7"/>
       <c r="G847" s="7"/>
@@ -33811,19 +33811,19 @@
         <v>5</v>
       </c>
       <c r="E848" s="7">
-        <v>0.038171</v>
+        <v>0.039219</v>
       </c>
       <c r="F848" s="7">
-        <v>0.042477999999999995</v>
+        <v>0.04353100000000001</v>
       </c>
       <c r="G848" s="7">
-        <v>0.141842</v>
+        <v>0.142995</v>
       </c>
       <c r="H848" s="7">
-        <v>0.275334</v>
+        <v>0.276622</v>
       </c>
       <c r="I848" s="7">
-        <v>0.435525</v>
+        <v>0.436975</v>
       </c>
       <c r="J848" s="7"/>
       <c r="K848" s="7"/>
@@ -33863,19 +33863,19 @@
         <v>5</v>
       </c>
       <c r="E850" s="7">
-        <v>0</v>
+        <v>0.032507</v>
       </c>
       <c r="F850" s="7">
-        <v>0</v>
+        <v>0.040802</v>
       </c>
       <c r="G850" s="7">
-        <v>0</v>
+        <v>0.448272</v>
       </c>
       <c r="H850" s="7">
-        <v>0</v>
+        <v>0.419531</v>
       </c>
       <c r="I850" s="7">
-        <v>0</v>
+        <v>0.504838</v>
       </c>
       <c r="J850" s="7"/>
       <c r="K850" s="7"/>
@@ -33950,16 +33950,16 @@
         <v>6</v>
       </c>
       <c r="E853" s="7">
-        <v>0</v>
+        <v>0.08163999999999999</v>
       </c>
       <c r="F853" s="7">
-        <v>0</v>
+        <v>0.087719</v>
       </c>
       <c r="G853" s="7">
-        <v>0</v>
+        <v>0.106434</v>
       </c>
       <c r="H853" s="7">
-        <v>0</v>
+        <v>0.469575</v>
       </c>
       <c r="I853" s="7"/>
       <c r="J853" s="7"/>
@@ -34260,19 +34260,19 @@
         <v>4</v>
       </c>
       <c r="E863" s="7">
-        <v>0.056346999999999994</v>
+        <v>0.058252</v>
       </c>
       <c r="F863" s="7">
-        <v>0.052191999999999995</v>
+        <v>0.054089</v>
       </c>
       <c r="G863" s="7">
-        <v>0.15341100000000002</v>
+        <v>0.15549</v>
       </c>
       <c r="H863" s="7">
-        <v>0.268585</v>
+        <v>0.270872</v>
       </c>
       <c r="I863" s="7">
-        <v>0.505811</v>
+        <v>0.508526</v>
       </c>
       <c r="J863" s="7"/>
       <c r="K863" s="7"/>
@@ -34322,19 +34322,19 @@
         <v>5</v>
       </c>
       <c r="E865" s="7">
-        <v>0.060652</v>
+        <v>0.060407999999999996</v>
       </c>
       <c r="F865" s="7">
-        <v>0.180818</v>
+        <v>0.180546</v>
       </c>
       <c r="G865" s="7">
-        <v>0.205154</v>
+        <v>0.204877</v>
       </c>
       <c r="H865" s="7">
-        <v>0.258593</v>
+        <v>0.25830400000000003</v>
       </c>
       <c r="I865" s="7">
-        <v>0.45813400000000004</v>
+        <v>0.4578</v>
       </c>
       <c r="J865" s="7"/>
       <c r="K865" s="7"/>
@@ -34417,19 +34417,19 @@
         <v>6</v>
       </c>
       <c r="E868" s="7">
-        <v>0.073068</v>
+        <v>0.074772</v>
       </c>
       <c r="F868" s="7">
-        <v>0.033136</v>
+        <v>0.034777</v>
       </c>
       <c r="G868" s="7">
-        <v>0.131552</v>
+        <v>0.133349</v>
       </c>
       <c r="H868" s="7">
-        <v>0.266503</v>
+        <v>0.26851400000000003</v>
       </c>
       <c r="I868" s="7">
-        <v>0.092097</v>
+        <v>0.09383100000000001</v>
       </c>
       <c r="J868" s="7"/>
       <c r="K868" s="7"/>
@@ -34924,22 +34924,22 @@
         <v>3</v>
       </c>
       <c r="E883" s="7">
-        <v>0</v>
+        <v>0.034821</v>
       </c>
       <c r="F883" s="7">
-        <v>0</v>
+        <v>0.095111</v>
       </c>
       <c r="G883" s="7">
-        <v>0</v>
+        <v>0.196326</v>
       </c>
       <c r="H883" s="7">
-        <v>0</v>
+        <v>0.282692</v>
       </c>
       <c r="I883" s="7">
-        <v>0</v>
+        <v>0.45693300000000003</v>
       </c>
       <c r="J883" s="7">
-        <v>0</v>
+        <v>2.353339</v>
       </c>
       <c r="K883" s="7"/>
     </row>
@@ -35060,19 +35060,19 @@
         <v>6</v>
       </c>
       <c r="E887" s="7">
-        <v>0.059918</v>
+        <v>0.059358</v>
       </c>
       <c r="F887" s="7">
-        <v>-0.006932000000000001</v>
+        <v>-0.007456000000000001</v>
       </c>
       <c r="G887" s="7">
-        <v>0.423245</v>
+        <v>0.42249400000000004</v>
       </c>
       <c r="H887" s="7">
-        <v>0.459442</v>
+        <v>0.458671</v>
       </c>
       <c r="I887" s="7">
-        <v>0.6539870000000001</v>
+        <v>0.653113</v>
       </c>
       <c r="J887" s="7"/>
       <c r="K887" s="7"/>
@@ -35629,25 +35629,25 @@
         <v>6</v>
       </c>
       <c r="E904" s="7">
-        <v>0</v>
+        <v>0.020426000000000003</v>
       </c>
       <c r="F904" s="7">
-        <v>0</v>
+        <v>-0.008423</v>
       </c>
       <c r="G904" s="7">
-        <v>0</v>
+        <v>0.114259</v>
       </c>
       <c r="H904" s="7">
-        <v>0</v>
+        <v>0.218979</v>
       </c>
       <c r="I904" s="7">
-        <v>0</v>
+        <v>0.323952</v>
       </c>
       <c r="J904" s="7">
-        <v>0</v>
+        <v>1.138311</v>
       </c>
       <c r="K904" s="7">
-        <v>0</v>
+        <v>4.396403</v>
       </c>
     </row>
     <row r="905" spans="1:11" x14ac:dyDescent="0.25">
@@ -35664,22 +35664,22 @@
         <v>4</v>
       </c>
       <c r="E905" s="7">
-        <v>0</v>
+        <v>0.054436</v>
       </c>
       <c r="F905" s="7">
-        <v>0</v>
+        <v>0.041333</v>
       </c>
       <c r="G905" s="7">
-        <v>0</v>
+        <v>0.10607</v>
       </c>
       <c r="H905" s="7">
-        <v>0</v>
+        <v>0.22033000000000003</v>
       </c>
       <c r="I905" s="7">
-        <v>0</v>
+        <v>0.410003</v>
       </c>
       <c r="J905" s="7">
-        <v>0</v>
+        <v>1.698582</v>
       </c>
       <c r="K905" s="7"/>
     </row>
@@ -35893,25 +35893,25 @@
         <v>7</v>
       </c>
       <c r="E912" s="7">
-        <v>0.188974</v>
+        <v>0.188975</v>
       </c>
       <c r="F912" s="7">
-        <v>0.632872</v>
+        <v>0.632873</v>
       </c>
       <c r="G912" s="7">
-        <v>1.404582</v>
+        <v>1.4045830000000001</v>
       </c>
       <c r="H912" s="7">
-        <v>2.1833590000000003</v>
+        <v>2.1833609999999997</v>
       </c>
       <c r="I912" s="7">
-        <v>6.895444</v>
+        <v>6.895449</v>
       </c>
       <c r="J912" s="7">
-        <v>651.80125</v>
+        <v>651.801659</v>
       </c>
       <c r="K912" s="7">
-        <v>6688.938622</v>
+        <v>6688.942813000001</v>
       </c>
     </row>
     <row r="913" spans="1:11" x14ac:dyDescent="0.25">
@@ -36064,19 +36064,19 @@
         <v>2</v>
       </c>
       <c r="E917" s="7">
-        <v>0.033813</v>
+        <v>0.034356</v>
       </c>
       <c r="F917" s="7">
-        <v>0.072617</v>
+        <v>0.073181</v>
       </c>
       <c r="G917" s="7">
-        <v>0.16770600000000002</v>
+        <v>0.16832</v>
       </c>
       <c r="H917" s="7">
-        <v>0.262799</v>
+        <v>0.263462</v>
       </c>
       <c r="I917" s="7">
-        <v>0.437714</v>
+        <v>0.43847</v>
       </c>
       <c r="J917" s="7"/>
       <c r="K917" s="7"/>
@@ -36223,25 +36223,25 @@
         <v>6</v>
       </c>
       <c r="E922" s="7">
-        <v>0</v>
+        <v>0.126442</v>
       </c>
       <c r="F922" s="7">
-        <v>0</v>
+        <v>0.009345</v>
       </c>
       <c r="G922" s="7">
-        <v>0</v>
+        <v>-0.054207</v>
       </c>
       <c r="H922" s="7">
-        <v>0</v>
+        <v>0.077977</v>
       </c>
       <c r="I922" s="7">
-        <v>0</v>
+        <v>0.417289</v>
       </c>
       <c r="J922" s="7">
-        <v>0</v>
+        <v>1.8495169999999999</v>
       </c>
       <c r="K922" s="7">
-        <v>0</v>
+        <v>6.378171999999999</v>
       </c>
     </row>
     <row r="923" spans="1:11" x14ac:dyDescent="0.25">
@@ -36757,22 +36757,22 @@
         <v>5</v>
       </c>
       <c r="E938" s="7">
-        <v>0.062949</v>
+        <v>0.06608399999999999</v>
       </c>
       <c r="F938" s="7">
-        <v>0.132592</v>
+        <v>0.135933</v>
       </c>
       <c r="G938" s="7">
-        <v>0.254463</v>
+        <v>0.258163</v>
       </c>
       <c r="H938" s="7">
-        <v>0.32962</v>
+        <v>0.33354100000000003</v>
       </c>
       <c r="I938" s="7">
-        <v>0.552252</v>
+        <v>0.55683</v>
       </c>
       <c r="J938" s="7">
-        <v>1.812933</v>
+        <v>1.82123</v>
       </c>
       <c r="K938" s="7"/>
     </row>
@@ -37626,25 +37626,25 @@
         <v>5</v>
       </c>
       <c r="E967" s="7">
-        <v>0</v>
+        <v>0.052366</v>
       </c>
       <c r="F967" s="7">
-        <v>0</v>
+        <v>0.047451</v>
       </c>
       <c r="G967" s="7">
-        <v>0</v>
+        <v>0.09007199999999999</v>
       </c>
       <c r="H967" s="7">
-        <v>0</v>
+        <v>0.181834</v>
       </c>
       <c r="I967" s="7">
-        <v>0</v>
+        <v>0.342699</v>
       </c>
       <c r="J967" s="7">
-        <v>0</v>
+        <v>1.390406</v>
       </c>
       <c r="K967" s="7">
-        <v>0</v>
+        <v>5.923831</v>
       </c>
     </row>
     <row r="968" spans="1:11" x14ac:dyDescent="0.25">
@@ -37723,25 +37723,25 @@
         <v>4</v>
       </c>
       <c r="E970" s="7">
-        <v>0</v>
+        <v>0.034841000000000004</v>
       </c>
       <c r="F970" s="7">
-        <v>0</v>
+        <v>0.092089</v>
       </c>
       <c r="G970" s="7">
-        <v>0</v>
+        <v>0.15881</v>
       </c>
       <c r="H970" s="7">
-        <v>0</v>
+        <v>0.233143</v>
       </c>
       <c r="I970" s="7">
-        <v>0</v>
+        <v>0.36837200000000003</v>
       </c>
       <c r="J970" s="7">
-        <v>0</v>
+        <v>1.232944</v>
       </c>
       <c r="K970" s="7">
-        <v>0</v>
+        <v>4.869013</v>
       </c>
     </row>
     <row r="971" spans="1:11" x14ac:dyDescent="0.25">
@@ -38024,22 +38024,22 @@
         <v>2</v>
       </c>
       <c r="E979" s="7">
-        <v>0</v>
+        <v>0.031428</v>
       </c>
       <c r="F979" s="7">
-        <v>0</v>
+        <v>0.08519399999999999</v>
       </c>
       <c r="G979" s="7">
-        <v>0</v>
+        <v>0.18823299999999998</v>
       </c>
       <c r="H979" s="7">
-        <v>0</v>
+        <v>0.269022</v>
       </c>
       <c r="I979" s="7">
-        <v>0</v>
+        <v>0.42865400000000003</v>
       </c>
       <c r="J979" s="7">
-        <v>0</v>
+        <v>1.79377</v>
       </c>
       <c r="K979" s="7"/>
     </row>
@@ -38490,19 +38490,19 @@
         <v>6</v>
       </c>
       <c r="E993" s="7">
-        <v>0</v>
+        <v>0.005576</v>
       </c>
       <c r="F993" s="7">
-        <v>0</v>
+        <v>-0.129163</v>
       </c>
       <c r="G993" s="7">
-        <v>0</v>
+        <v>0.379234</v>
       </c>
       <c r="H993" s="7">
-        <v>0</v>
+        <v>0.571426</v>
       </c>
       <c r="I993" s="7">
-        <v>0</v>
+        <v>0.9666800000000001</v>
       </c>
       <c r="J993" s="7"/>
       <c r="K993" s="7"/>
@@ -38554,22 +38554,22 @@
         <v>5</v>
       </c>
       <c r="E995" s="7">
-        <v>0</v>
+        <v>0.024661</v>
       </c>
       <c r="F995" s="7">
-        <v>0</v>
+        <v>-0.057674</v>
       </c>
       <c r="G995" s="7">
-        <v>0</v>
+        <v>0.34280900000000003</v>
       </c>
       <c r="H995" s="7">
-        <v>0</v>
+        <v>0.433322</v>
       </c>
       <c r="I995" s="7">
-        <v>0</v>
+        <v>0.663211</v>
       </c>
       <c r="J995" s="7">
-        <v>0</v>
+        <v>2.231129</v>
       </c>
       <c r="K995" s="7"/>
     </row>
@@ -39177,25 +39177,25 @@
         <v>5</v>
       </c>
       <c r="E1014" s="7">
-        <v>0</v>
+        <v>0.061902</v>
       </c>
       <c r="F1014" s="7">
-        <v>0</v>
+        <v>0.030501999999999998</v>
       </c>
       <c r="G1014" s="7">
-        <v>0</v>
+        <v>0.076698</v>
       </c>
       <c r="H1014" s="7">
-        <v>0</v>
+        <v>0.17810700000000002</v>
       </c>
       <c r="I1014" s="7">
-        <v>0</v>
+        <v>0.24848299999999998</v>
       </c>
       <c r="J1014" s="7">
-        <v>0</v>
+        <v>1.088894</v>
       </c>
       <c r="K1014" s="7">
-        <v>0</v>
+        <v>4.615441000000001</v>
       </c>
     </row>
     <row r="1015" spans="1:11" x14ac:dyDescent="0.25">
@@ -39359,25 +39359,25 @@
         <v>6</v>
       </c>
       <c r="E1020" s="7">
-        <v>0</v>
+        <v>0.050888</v>
       </c>
       <c r="F1020" s="7">
-        <v>0</v>
+        <v>-0.014912000000000002</v>
       </c>
       <c r="G1020" s="7">
-        <v>0</v>
+        <v>0.237198</v>
       </c>
       <c r="H1020" s="7">
-        <v>0</v>
+        <v>0.202744</v>
       </c>
       <c r="I1020" s="7">
-        <v>0</v>
+        <v>0.421704</v>
       </c>
       <c r="J1020" s="7">
-        <v>0</v>
+        <v>2.034208</v>
       </c>
       <c r="K1020" s="7">
-        <v>0</v>
+        <v>8.261631999999999</v>
       </c>
     </row>
     <row r="1021" spans="1:11" x14ac:dyDescent="0.25">
@@ -39646,25 +39646,25 @@
         <v>7</v>
       </c>
       <c r="E1029" s="7">
-        <v>0</v>
+        <v>0.169535</v>
       </c>
       <c r="F1029" s="7">
-        <v>0</v>
+        <v>-0.066416</v>
       </c>
       <c r="G1029" s="7">
-        <v>0</v>
+        <v>-0.13611</v>
       </c>
       <c r="H1029" s="7">
-        <v>0</v>
+        <v>0.0028060000000000003</v>
       </c>
       <c r="I1029" s="7">
-        <v>0</v>
+        <v>0.805259</v>
       </c>
       <c r="J1029" s="7">
-        <v>0</v>
+        <v>3.505648</v>
       </c>
       <c r="K1029" s="7">
-        <v>0</v>
+        <v>11.762025000000001</v>
       </c>
     </row>
     <row r="1030" spans="1:11" x14ac:dyDescent="0.25">
@@ -39970,22 +39970,22 @@
         <v>6</v>
       </c>
       <c r="E1039" s="7">
-        <v>0.097653</v>
+        <v>0.099639</v>
       </c>
       <c r="F1039" s="7">
-        <v>0.036926</v>
+        <v>0.038801999999999996</v>
       </c>
       <c r="G1039" s="7">
-        <v>0.10411899999999999</v>
+        <v>0.106117</v>
       </c>
       <c r="H1039" s="7">
-        <v>0.25156</v>
+        <v>0.253824</v>
       </c>
       <c r="I1039" s="7">
-        <v>0.48079500000000003</v>
+        <v>0.483474</v>
       </c>
       <c r="J1039" s="7">
-        <v>1.757568</v>
+        <v>1.762557</v>
       </c>
       <c r="K1039" s="7"/>
     </row>
@@ -40529,25 +40529,25 @@
         <v>5</v>
       </c>
       <c r="E1056" s="7">
-        <v>0.054223</v>
+        <v>0.054218999999999996</v>
       </c>
       <c r="F1056" s="7">
-        <v>0.053856</v>
+        <v>0.053852000000000004</v>
       </c>
       <c r="G1056" s="7">
-        <v>0.090716</v>
+        <v>0.09071199999999999</v>
       </c>
       <c r="H1056" s="7">
-        <v>0.154035</v>
+        <v>0.154031</v>
       </c>
       <c r="I1056" s="7">
-        <v>0.23783100000000001</v>
+        <v>0.23782699999999998</v>
       </c>
       <c r="J1056" s="7">
-        <v>1.232356</v>
+        <v>1.232348</v>
       </c>
       <c r="K1056" s="7">
-        <v>7.084188</v>
+        <v>7.084159</v>
       </c>
     </row>
     <row r="1057" spans="1:11" x14ac:dyDescent="0.25">
@@ -40754,22 +40754,22 @@
         <v>6</v>
       </c>
       <c r="E1063" s="7">
-        <v>0.029238</v>
+        <v>0.029018000000000002</v>
       </c>
       <c r="F1063" s="7">
-        <v>-0.016833</v>
+        <v>-0.017043</v>
       </c>
       <c r="G1063" s="7">
-        <v>0.13185</v>
+        <v>0.131608</v>
       </c>
       <c r="H1063" s="7">
-        <v>0.242774</v>
+        <v>0.24250800000000003</v>
       </c>
       <c r="I1063" s="7">
-        <v>0.383406</v>
+        <v>0.38311</v>
       </c>
       <c r="J1063" s="7">
-        <v>1.3724969999999999</v>
+        <v>1.371991</v>
       </c>
       <c r="K1063" s="7"/>
     </row>
@@ -40787,19 +40787,19 @@
         <v>5</v>
       </c>
       <c r="E1064" s="7">
-        <v>0.067406</v>
+        <v>0.068381</v>
       </c>
       <c r="F1064" s="7">
-        <v>0.149671</v>
+        <v>0.150721</v>
       </c>
       <c r="G1064" s="7">
-        <v>0.21651199999999998</v>
+        <v>0.217623</v>
       </c>
       <c r="H1064" s="7">
-        <v>0.295105</v>
+        <v>0.296288</v>
       </c>
       <c r="I1064" s="7">
-        <v>0.33948300000000003</v>
+        <v>0.34070700000000004</v>
       </c>
       <c r="J1064" s="7"/>
       <c r="K1064" s="7"/>

--- a/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>10.09.2026 09:19:49</t>
+    <t>10.09.2026 12:49:28</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -7020,25 +7020,25 @@
         <v>5</v>
       </c>
       <c r="E7" s="7">
-        <v>0.023413</v>
+        <v>0.023414</v>
       </c>
       <c r="F7" s="7">
-        <v>0.091186</v>
+        <v>0.091187</v>
       </c>
       <c r="G7" s="7">
-        <v>0.238783</v>
+        <v>0.238785</v>
       </c>
       <c r="H7" s="7">
-        <v>0.23838499999999999</v>
+        <v>0.238386</v>
       </c>
       <c r="I7" s="7">
-        <v>0.377832</v>
+        <v>0.377834</v>
       </c>
       <c r="J7" s="7">
-        <v>1.312947</v>
+        <v>1.3129499999999998</v>
       </c>
       <c r="K7" s="7">
-        <v>2.680789</v>
+        <v>2.680794</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -7430,25 +7430,25 @@
         <v>7</v>
       </c>
       <c r="E19" s="7">
-        <v>0</v>
+        <v>0.21266400000000002</v>
       </c>
       <c r="F19" s="7">
-        <v>0</v>
+        <v>0.15424200000000002</v>
       </c>
       <c r="G19" s="7">
-        <v>0</v>
+        <v>0.32974800000000004</v>
       </c>
       <c r="H19" s="7">
-        <v>0</v>
+        <v>1.074324</v>
       </c>
       <c r="I19" s="7">
-        <v>0</v>
+        <v>1.0189190000000001</v>
       </c>
       <c r="J19" s="7">
-        <v>0</v>
+        <v>1.642381</v>
       </c>
       <c r="K19" s="7">
-        <v>0</v>
+        <v>11.196686999999999</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -7811,25 +7811,25 @@
         <v>4</v>
       </c>
       <c r="E30" s="7">
-        <v>0.037755000000000004</v>
+        <v>0.040184</v>
       </c>
       <c r="F30" s="7">
-        <v>0.088285</v>
+        <v>0.090833</v>
       </c>
       <c r="G30" s="7">
-        <v>0.18868300000000002</v>
+        <v>0.191466</v>
       </c>
       <c r="H30" s="7">
-        <v>0.31416</v>
+        <v>0.317237</v>
       </c>
       <c r="I30" s="7">
-        <v>0.485005</v>
+        <v>0.488481</v>
       </c>
       <c r="J30" s="7">
-        <v>1.826898</v>
+        <v>1.833516</v>
       </c>
       <c r="K30" s="7">
-        <v>8.311093</v>
+        <v>8.332891</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -8314,25 +8314,25 @@
         <v>6</v>
       </c>
       <c r="E45" s="7">
-        <v>0</v>
+        <v>0.058439</v>
       </c>
       <c r="F45" s="7">
-        <v>0</v>
+        <v>0.058791</v>
       </c>
       <c r="G45" s="7">
-        <v>0</v>
+        <v>0.09763899999999999</v>
       </c>
       <c r="H45" s="7">
-        <v>0</v>
+        <v>0.201769</v>
       </c>
       <c r="I45" s="7">
-        <v>0</v>
+        <v>0.309056</v>
       </c>
       <c r="J45" s="7">
-        <v>0</v>
+        <v>0.9368770000000001</v>
       </c>
       <c r="K45" s="7">
-        <v>0</v>
+        <v>3.011516</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -8417,25 +8417,25 @@
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="7">
-        <v>0</v>
+        <v>0.020143</v>
       </c>
       <c r="F48" s="7">
-        <v>0</v>
+        <v>0.059751000000000005</v>
       </c>
       <c r="G48" s="7">
-        <v>0</v>
+        <v>0.126242</v>
       </c>
       <c r="H48" s="7">
-        <v>0</v>
+        <v>0.220657</v>
       </c>
       <c r="I48" s="7">
-        <v>0</v>
+        <v>0.358413</v>
       </c>
       <c r="J48" s="7">
-        <v>0</v>
+        <v>2.0138030000000002</v>
       </c>
       <c r="K48" s="7">
-        <v>0</v>
+        <v>5.442519999999999</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -8450,25 +8450,25 @@
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7">
-        <v>0</v>
+        <v>0.017626</v>
       </c>
       <c r="F49" s="7">
-        <v>0</v>
+        <v>0.047112999999999995</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>0.090293</v>
       </c>
       <c r="H49" s="7">
-        <v>0</v>
+        <v>0.19256299999999998</v>
       </c>
       <c r="I49" s="7">
-        <v>0</v>
+        <v>0.33362200000000003</v>
       </c>
       <c r="J49" s="7">
-        <v>0</v>
+        <v>1.806399</v>
       </c>
       <c r="K49" s="7">
-        <v>0</v>
+        <v>5.99745</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -9039,19 +9039,19 @@
         <v>5</v>
       </c>
       <c r="E68" s="7">
-        <v>0.0311</v>
+        <v>0.031902</v>
       </c>
       <c r="F68" s="7">
-        <v>0.076278</v>
+        <v>0.077115</v>
       </c>
       <c r="G68" s="7">
-        <v>0.140624</v>
+        <v>0.141511</v>
       </c>
       <c r="H68" s="7">
-        <v>0.16647099999999998</v>
+        <v>0.167378</v>
       </c>
       <c r="I68" s="7">
-        <v>0.317702</v>
+        <v>0.318727</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
@@ -9889,19 +9889,19 @@
         <v>6</v>
       </c>
       <c r="E96" s="7">
-        <v>0.018971000000000002</v>
+        <v>0.025241</v>
       </c>
       <c r="F96" s="7">
-        <v>0.074041</v>
+        <v>0.08065</v>
       </c>
       <c r="G96" s="7">
-        <v>0.17082799999999998</v>
+        <v>0.178032</v>
       </c>
       <c r="H96" s="7">
-        <v>0.23116199999999998</v>
+        <v>0.238737</v>
       </c>
       <c r="I96" s="7">
-        <v>0.337024</v>
+        <v>0.34525100000000003</v>
       </c>
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
@@ -9920,19 +9920,19 @@
         <v>5</v>
       </c>
       <c r="E97" s="7">
-        <v>0.061903</v>
+        <v>0.062637</v>
       </c>
       <c r="F97" s="7">
-        <v>0.067831</v>
+        <v>0.06857</v>
       </c>
       <c r="G97" s="7">
-        <v>0.263766</v>
+        <v>0.26464</v>
       </c>
       <c r="H97" s="7">
-        <v>0.35222099999999995</v>
+        <v>0.353157</v>
       </c>
       <c r="I97" s="7">
-        <v>0.500537</v>
+        <v>0.501576</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
@@ -10100,16 +10100,16 @@
         <v>7</v>
       </c>
       <c r="E103" s="7">
-        <v>0.05412</v>
+        <v>0.054117</v>
       </c>
       <c r="F103" s="7">
-        <v>0.151992</v>
+        <v>0.151988</v>
       </c>
       <c r="G103" s="7">
-        <v>0.414578</v>
+        <v>0.414574</v>
       </c>
       <c r="H103" s="7">
-        <v>0.58421</v>
+        <v>0.584205</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
@@ -10286,10 +10286,10 @@
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>0.071821</v>
+        <v>0.074624</v>
       </c>
       <c r="F109" s="7">
-        <v>0.255783</v>
+        <v>0.259066</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
@@ -10679,19 +10679,19 @@
         <v>5</v>
       </c>
       <c r="E122" s="7">
-        <v>-0.013474</v>
+        <v>0.05320299999999999</v>
       </c>
       <c r="F122" s="7">
-        <v>0.023342</v>
+        <v>0.092507</v>
       </c>
       <c r="G122" s="7">
-        <v>0.259015</v>
+        <v>0.344108</v>
       </c>
       <c r="H122" s="7">
-        <v>0.330293</v>
+        <v>0.420203</v>
       </c>
       <c r="I122" s="7">
-        <v>0.526976</v>
+        <v>0.63018</v>
       </c>
       <c r="J122" s="7"/>
       <c r="K122" s="7"/>
@@ -10772,19 +10772,19 @@
         <v>6</v>
       </c>
       <c r="E125" s="7">
-        <v>0.026949</v>
+        <v>0.026944</v>
       </c>
       <c r="F125" s="7">
-        <v>0.010641000000000001</v>
+        <v>0.010636000000000001</v>
       </c>
       <c r="G125" s="7">
-        <v>0.479613</v>
+        <v>0.47960500000000006</v>
       </c>
       <c r="H125" s="7">
-        <v>0.700828</v>
+        <v>0.7008190000000001</v>
       </c>
       <c r="I125" s="7">
-        <v>1.2045409999999999</v>
+        <v>1.204529</v>
       </c>
       <c r="J125" s="7"/>
       <c r="K125" s="7"/>
@@ -11577,22 +11577,22 @@
         <v>6</v>
       </c>
       <c r="E150" s="7">
-        <v>0.030331999999999998</v>
+        <v>0.030291000000000002</v>
       </c>
       <c r="F150" s="7">
-        <v>0.058545</v>
+        <v>0.058503</v>
       </c>
       <c r="G150" s="7">
-        <v>0.166914</v>
+        <v>0.16686800000000002</v>
       </c>
       <c r="H150" s="7">
-        <v>0.24262799999999998</v>
+        <v>0.242579</v>
       </c>
       <c r="I150" s="7">
-        <v>0.333476</v>
+        <v>0.333423</v>
       </c>
       <c r="J150" s="7">
-        <v>1.3588689999999999</v>
+        <v>1.3587770000000001</v>
       </c>
       <c r="K150" s="7"/>
     </row>
@@ -11610,16 +11610,16 @@
         <v>6</v>
       </c>
       <c r="E151" s="7">
-        <v>-0.031618</v>
+        <v>-0.031714</v>
       </c>
       <c r="F151" s="7">
-        <v>0.054424</v>
+        <v>0.054319</v>
       </c>
       <c r="G151" s="7">
-        <v>0.085746</v>
+        <v>0.085638</v>
       </c>
       <c r="H151" s="7">
-        <v>0.14903</v>
+        <v>0.148916</v>
       </c>
       <c r="I151" s="7"/>
       <c r="J151" s="7"/>
@@ -11668,19 +11668,19 @@
         <v>5</v>
       </c>
       <c r="E153" s="7">
-        <v>0.022421000000000003</v>
+        <v>0.021953</v>
       </c>
       <c r="F153" s="7">
-        <v>0.084285</v>
+        <v>0.083788</v>
       </c>
       <c r="G153" s="7">
-        <v>0.160925</v>
+        <v>0.160393</v>
       </c>
       <c r="H153" s="7">
-        <v>0.221491</v>
+        <v>0.220932</v>
       </c>
       <c r="I153" s="7">
-        <v>0.342831</v>
+        <v>0.342216</v>
       </c>
       <c r="J153" s="7"/>
       <c r="K153" s="7"/>
@@ -11982,22 +11982,22 @@
         <v>7</v>
       </c>
       <c r="E163" s="7">
-        <v>0.06707</v>
+        <v>0.06804299999999999</v>
       </c>
       <c r="F163" s="7">
-        <v>0.035844999999999995</v>
+        <v>0.036789</v>
       </c>
       <c r="G163" s="7">
-        <v>-0.113827</v>
+        <v>-0.113019</v>
       </c>
       <c r="H163" s="7">
-        <v>0.029660000000000002</v>
+        <v>0.030598</v>
       </c>
       <c r="I163" s="7">
-        <v>0.842023</v>
+        <v>0.843703</v>
       </c>
       <c r="J163" s="7">
-        <v>3.731653</v>
+        <v>3.735967</v>
       </c>
       <c r="K163" s="7"/>
     </row>
@@ -12015,16 +12015,16 @@
         <v>4</v>
       </c>
       <c r="E164" s="7">
-        <v>0.080505</v>
+        <v>0.081673</v>
       </c>
       <c r="F164" s="7">
-        <v>0.139304</v>
+        <v>0.140536</v>
       </c>
       <c r="G164" s="7">
-        <v>0.239084</v>
+        <v>0.240425</v>
       </c>
       <c r="H164" s="7">
-        <v>0.32440399999999997</v>
+        <v>0.32583599999999996</v>
       </c>
       <c r="I164" s="7"/>
       <c r="J164" s="7"/>
@@ -12490,25 +12490,25 @@
         <v>3</v>
       </c>
       <c r="E179" s="7">
-        <v>0.028675000000000003</v>
+        <v>0.028924</v>
       </c>
       <c r="F179" s="7">
-        <v>0.084383</v>
+        <v>0.084645</v>
       </c>
       <c r="G179" s="7">
-        <v>0.158788</v>
+        <v>0.15906800000000001</v>
       </c>
       <c r="H179" s="7">
-        <v>0.22915600000000003</v>
+        <v>0.229453</v>
       </c>
       <c r="I179" s="7">
-        <v>0.394507</v>
+        <v>0.39484400000000003</v>
       </c>
       <c r="J179" s="7">
-        <v>1.732212</v>
+        <v>1.7328720000000002</v>
       </c>
       <c r="K179" s="7">
-        <v>6.668904</v>
+        <v>6.670757</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -12775,22 +12775,22 @@
         <v>6</v>
       </c>
       <c r="E188" s="7">
-        <v>0.042138999999999996</v>
+        <v>0.0421</v>
       </c>
       <c r="F188" s="7">
-        <v>0.041037</v>
+        <v>0.040999</v>
       </c>
       <c r="G188" s="7">
-        <v>0.452061</v>
+        <v>0.452006</v>
       </c>
       <c r="H188" s="7">
-        <v>0.5012530000000001</v>
+        <v>0.501197</v>
       </c>
       <c r="I188" s="7">
-        <v>0.643476</v>
+        <v>0.6434139999999999</v>
       </c>
       <c r="J188" s="7">
-        <v>2.963742</v>
+        <v>2.963594</v>
       </c>
       <c r="K188" s="7"/>
     </row>
@@ -13209,7 +13209,7 @@
         <v>6</v>
       </c>
       <c r="E202" s="7">
-        <v>0.051749</v>
+        <v>0.051047</v>
       </c>
       <c r="F202" s="7"/>
       <c r="G202" s="7"/>
@@ -13517,16 +13517,16 @@
         <v>5</v>
       </c>
       <c r="E212" s="7">
-        <v>0.025200999999999998</v>
+        <v>0.023921</v>
       </c>
       <c r="F212" s="7">
-        <v>-0.01183</v>
+        <v>-0.013064</v>
       </c>
       <c r="G212" s="7">
-        <v>0.09272</v>
+        <v>0.091355</v>
       </c>
       <c r="H212" s="7">
-        <v>0.130667</v>
+        <v>0.129255</v>
       </c>
       <c r="I212" s="7"/>
       <c r="J212" s="7"/>
@@ -13546,16 +13546,16 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>0.032039</v>
+        <v>0.040423999999999995</v>
       </c>
       <c r="F213" s="7">
-        <v>0.046147999999999995</v>
+        <v>0.054646999999999994</v>
       </c>
       <c r="G213" s="7">
-        <v>-0.106602</v>
+        <v>-0.099344</v>
       </c>
       <c r="H213" s="7">
-        <v>0.061804</v>
+        <v>0.07043</v>
       </c>
       <c r="I213" s="7"/>
       <c r="J213" s="7"/>
@@ -13786,13 +13786,13 @@
         <v>6</v>
       </c>
       <c r="E221" s="7">
-        <v>0.066969</v>
+        <v>0.066653</v>
       </c>
       <c r="F221" s="7">
-        <v>0.115423</v>
+        <v>0.115092</v>
       </c>
       <c r="G221" s="7">
-        <v>0.20275200000000002</v>
+        <v>0.202396</v>
       </c>
       <c r="H221" s="7"/>
       <c r="I221" s="7"/>
@@ -13813,19 +13813,19 @@
         <v>3</v>
       </c>
       <c r="E222" s="7">
-        <v>0.029307</v>
+        <v>0.03198</v>
       </c>
       <c r="F222" s="7">
-        <v>0.069633</v>
+        <v>0.072411</v>
       </c>
       <c r="G222" s="7">
-        <v>0.151039</v>
+        <v>0.154028</v>
       </c>
       <c r="H222" s="7">
-        <v>0.275645</v>
+        <v>0.27895800000000004</v>
       </c>
       <c r="I222" s="7">
-        <v>0.510091</v>
+        <v>0.5140129999999999</v>
       </c>
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
@@ -14009,19 +14009,19 @@
         <v>0.050132</v>
       </c>
       <c r="G228" s="7">
-        <v>0.33285899999999996</v>
+        <v>0.33286</v>
       </c>
       <c r="H228" s="7">
         <v>0.292711</v>
       </c>
       <c r="I228" s="7">
-        <v>0.46808</v>
+        <v>0.468081</v>
       </c>
       <c r="J228" s="7">
-        <v>1.8339699999999999</v>
+        <v>1.833971</v>
       </c>
       <c r="K228" s="7">
-        <v>3.224103</v>
+        <v>3.224105</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -14199,25 +14199,25 @@
         <v>4</v>
       </c>
       <c r="E234" s="7">
-        <v>0.043872999999999995</v>
+        <v>0.046088</v>
       </c>
       <c r="F234" s="7">
-        <v>0.077988</v>
+        <v>0.080275</v>
       </c>
       <c r="G234" s="7">
-        <v>0.09008200000000001</v>
+        <v>0.092394</v>
       </c>
       <c r="H234" s="7">
-        <v>0.17655300000000002</v>
+        <v>0.179049</v>
       </c>
       <c r="I234" s="7">
-        <v>0.39289799999999997</v>
+        <v>0.39585299999999995</v>
       </c>
       <c r="J234" s="7">
-        <v>1.962275</v>
+        <v>1.968559</v>
       </c>
       <c r="K234" s="7">
-        <v>5.765622</v>
+        <v>5.779974999999999</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -14409,25 +14409,25 @@
         <v>6</v>
       </c>
       <c r="E240" s="7">
-        <v>0.025091000000000002</v>
+        <v>0.025027</v>
       </c>
       <c r="F240" s="7">
-        <v>0.028729</v>
+        <v>0.028665</v>
       </c>
       <c r="G240" s="7">
-        <v>0.35966299999999995</v>
+        <v>0.359578</v>
       </c>
       <c r="H240" s="7">
-        <v>0.27586099999999997</v>
+        <v>0.27578199999999997</v>
       </c>
       <c r="I240" s="7">
-        <v>0.39137</v>
+        <v>0.39128300000000005</v>
       </c>
       <c r="J240" s="7">
-        <v>2.70867</v>
+        <v>2.7084379999999997</v>
       </c>
       <c r="K240" s="7">
-        <v>6.415710000000001</v>
+        <v>6.415247000000001</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -14931,7 +14931,7 @@
         <v>0.060328999999999994</v>
       </c>
       <c r="G256" s="7">
-        <v>0.118758</v>
+        <v>0.118757</v>
       </c>
       <c r="H256" s="7">
         <v>0.156513</v>
@@ -15026,19 +15026,19 @@
         <v>6</v>
       </c>
       <c r="E259" s="7">
-        <v>0.17948799999999998</v>
+        <v>0.179302</v>
       </c>
       <c r="F259" s="7">
-        <v>-0.01623</v>
+        <v>-0.016385</v>
       </c>
       <c r="G259" s="7">
-        <v>-0.015298</v>
+        <v>-0.015454</v>
       </c>
       <c r="H259" s="7">
-        <v>0.023856000000000002</v>
+        <v>0.023695</v>
       </c>
       <c r="I259" s="7">
-        <v>0.12622</v>
+        <v>0.12604300000000002</v>
       </c>
       <c r="J259" s="7"/>
       <c r="K259" s="7"/>
@@ -15156,22 +15156,22 @@
         <v>6</v>
       </c>
       <c r="E263" s="7">
-        <v>0.013239</v>
+        <v>0.013261</v>
       </c>
       <c r="F263" s="7">
-        <v>0.03167</v>
+        <v>0.031691</v>
       </c>
       <c r="G263" s="7">
-        <v>0.394955</v>
+        <v>0.394985</v>
       </c>
       <c r="H263" s="7">
-        <v>0.35979700000000003</v>
+        <v>0.359825</v>
       </c>
       <c r="I263" s="7">
-        <v>0.521239</v>
+        <v>0.521271</v>
       </c>
       <c r="J263" s="7">
-        <v>2.4220580000000003</v>
+        <v>2.42213</v>
       </c>
       <c r="K263" s="7"/>
     </row>
@@ -15282,16 +15282,16 @@
         <v>6</v>
       </c>
       <c r="E267" s="7">
-        <v>0</v>
+        <v>0.192994</v>
       </c>
       <c r="F267" s="7">
-        <v>0</v>
+        <v>0.154153</v>
       </c>
       <c r="G267" s="7">
-        <v>0</v>
+        <v>0.24357900000000002</v>
       </c>
       <c r="H267" s="7">
-        <v>0</v>
+        <v>0.39899500000000004</v>
       </c>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
@@ -15515,22 +15515,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.035714</v>
+        <v>0.03804</v>
       </c>
       <c r="F274" s="7">
-        <v>0.08130000000000001</v>
+        <v>0.083728</v>
       </c>
       <c r="G274" s="7">
-        <v>0.165384</v>
+        <v>0.168001</v>
       </c>
       <c r="H274" s="7">
-        <v>0.225769</v>
+        <v>0.228521</v>
       </c>
       <c r="I274" s="7">
-        <v>0.37762500000000004</v>
+        <v>0.380719</v>
       </c>
       <c r="J274" s="7">
-        <v>1.851423</v>
+        <v>1.857826</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -15723,25 +15723,25 @@
         <v>3</v>
       </c>
       <c r="E280" s="7">
-        <v>0</v>
+        <v>0.027199</v>
       </c>
       <c r="F280" s="7">
-        <v>0</v>
+        <v>0.088648</v>
       </c>
       <c r="G280" s="7">
-        <v>0</v>
+        <v>0.15248</v>
       </c>
       <c r="H280" s="7">
-        <v>0</v>
+        <v>0.243558</v>
       </c>
       <c r="I280" s="7">
-        <v>0</v>
+        <v>0.401638</v>
       </c>
       <c r="J280" s="7">
-        <v>0</v>
+        <v>2.22108</v>
       </c>
       <c r="K280" s="7">
-        <v>0</v>
+        <v>6.225993</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -15995,22 +15995,22 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0</v>
+        <v>0.048471</v>
       </c>
       <c r="F288" s="7">
-        <v>0</v>
+        <v>0.018778</v>
       </c>
       <c r="G288" s="7">
-        <v>0</v>
+        <v>0.442088</v>
       </c>
       <c r="H288" s="7">
-        <v>0</v>
+        <v>0.426888</v>
       </c>
       <c r="I288" s="7">
-        <v>0</v>
+        <v>0.6555259999999999</v>
       </c>
       <c r="J288" s="7">
-        <v>0</v>
+        <v>3.769108</v>
       </c>
       <c r="K288" s="7"/>
     </row>
@@ -16028,22 +16028,22 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.073339</v>
+        <v>0.073217</v>
       </c>
       <c r="F289" s="7">
-        <v>0.0876</v>
+        <v>0.087477</v>
       </c>
       <c r="G289" s="7">
-        <v>0.137313</v>
+        <v>0.137183</v>
       </c>
       <c r="H289" s="7">
-        <v>0.337918</v>
+        <v>0.337766</v>
       </c>
       <c r="I289" s="7">
-        <v>0.520376</v>
+        <v>0.520203</v>
       </c>
       <c r="J289" s="7">
-        <v>1.6141999999999999</v>
+        <v>1.6139029999999999</v>
       </c>
       <c r="K289" s="7"/>
     </row>
@@ -16228,25 +16228,25 @@
         <v>5</v>
       </c>
       <c r="E295" s="7">
-        <v>0.020074</v>
+        <v>0.019721</v>
       </c>
       <c r="F295" s="7">
-        <v>0.009944</v>
+        <v>0.009595</v>
       </c>
       <c r="G295" s="7">
-        <v>0.138048</v>
+        <v>0.137654</v>
       </c>
       <c r="H295" s="7">
-        <v>0.23197900000000002</v>
+        <v>0.231553</v>
       </c>
       <c r="I295" s="7">
-        <v>0.51613</v>
+        <v>0.515605</v>
       </c>
       <c r="J295" s="7">
-        <v>1.693585</v>
+        <v>1.692653</v>
       </c>
       <c r="K295" s="7">
-        <v>9.308287</v>
+        <v>9.304719</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -16430,22 +16430,22 @@
         <v>5</v>
       </c>
       <c r="E301" s="7">
-        <v>0.040964</v>
+        <v>0.04237199999999999</v>
       </c>
       <c r="F301" s="7">
-        <v>0.065889</v>
+        <v>0.06733</v>
       </c>
       <c r="G301" s="7">
-        <v>0.09346</v>
+        <v>0.09493800000000001</v>
       </c>
       <c r="H301" s="7">
-        <v>0.10074</v>
+        <v>0.102228</v>
       </c>
       <c r="I301" s="7">
-        <v>0.21009599999999998</v>
+        <v>0.211732</v>
       </c>
       <c r="J301" s="7">
-        <v>1.46775</v>
+        <v>1.471087</v>
       </c>
       <c r="K301" s="7"/>
     </row>
@@ -16587,22 +16587,22 @@
         <v>7</v>
       </c>
       <c r="E306" s="7">
-        <v>0</v>
+        <v>0.075102</v>
       </c>
       <c r="F306" s="7">
-        <v>0</v>
+        <v>0.043536</v>
       </c>
       <c r="G306" s="7">
-        <v>0</v>
+        <v>-0.147659</v>
       </c>
       <c r="H306" s="7">
-        <v>0</v>
+        <v>-0.0048259999999999996</v>
       </c>
       <c r="I306" s="7">
-        <v>0</v>
+        <v>0.818479</v>
       </c>
       <c r="J306" s="7">
-        <v>0</v>
+        <v>3.664652</v>
       </c>
       <c r="K306" s="7"/>
     </row>
@@ -16620,22 +16620,22 @@
         <v>5</v>
       </c>
       <c r="E307" s="7">
-        <v>0.034359</v>
+        <v>0.034392</v>
       </c>
       <c r="F307" s="7">
-        <v>0.059454</v>
+        <v>0.059488000000000006</v>
       </c>
       <c r="G307" s="7">
-        <v>0.196146</v>
+        <v>0.19618300000000002</v>
       </c>
       <c r="H307" s="7">
-        <v>0.222586</v>
+        <v>0.222624</v>
       </c>
       <c r="I307" s="7">
-        <v>0.352649</v>
+        <v>0.352692</v>
       </c>
       <c r="J307" s="7">
-        <v>0.418665</v>
+        <v>0.41871</v>
       </c>
       <c r="K307" s="7"/>
     </row>
@@ -16808,22 +16808,22 @@
         <v>3</v>
       </c>
       <c r="E313" s="7">
-        <v>0.035831</v>
+        <v>0.036317</v>
       </c>
       <c r="F313" s="7">
-        <v>0.104551</v>
+        <v>0.10507</v>
       </c>
       <c r="G313" s="7">
-        <v>0.194374</v>
+        <v>0.19493400000000002</v>
       </c>
       <c r="H313" s="7">
-        <v>0.326262</v>
+        <v>0.326884</v>
       </c>
       <c r="I313" s="7">
-        <v>0.526057</v>
+        <v>0.526773</v>
       </c>
       <c r="J313" s="7">
-        <v>2.7797250000000004</v>
+        <v>2.781499</v>
       </c>
       <c r="K313" s="7"/>
     </row>
@@ -16841,22 +16841,22 @@
         <v>5</v>
       </c>
       <c r="E314" s="7">
-        <v>0.030516</v>
+        <v>0.029577</v>
       </c>
       <c r="F314" s="7">
-        <v>0.054855</v>
+        <v>0.053893</v>
       </c>
       <c r="G314" s="7">
-        <v>0.118295</v>
+        <v>0.117276</v>
       </c>
       <c r="H314" s="7">
-        <v>0.24826399999999998</v>
+        <v>0.24712599999999998</v>
       </c>
       <c r="I314" s="7">
-        <v>0.427813</v>
+        <v>0.426512</v>
       </c>
       <c r="J314" s="7">
-        <v>1.94345</v>
+        <v>1.940767</v>
       </c>
       <c r="K314" s="7"/>
     </row>
@@ -16874,22 +16874,22 @@
         <v>5</v>
       </c>
       <c r="E315" s="7">
-        <v>0.030326</v>
+        <v>0.028957</v>
       </c>
       <c r="F315" s="7">
-        <v>0.060191</v>
+        <v>0.058781999999999994</v>
       </c>
       <c r="G315" s="7">
-        <v>0.120913</v>
+        <v>0.119423</v>
       </c>
       <c r="H315" s="7">
-        <v>0.231001</v>
+        <v>0.22936499999999999</v>
       </c>
       <c r="I315" s="7">
-        <v>0.422125</v>
+        <v>0.420234</v>
       </c>
       <c r="J315" s="7">
-        <v>1.936426</v>
+        <v>1.9325219999999999</v>
       </c>
       <c r="K315" s="7"/>
     </row>
@@ -17258,25 +17258,25 @@
         <v>3</v>
       </c>
       <c r="E327" s="7">
-        <v>0</v>
+        <v>0.027972999999999998</v>
       </c>
       <c r="F327" s="7">
-        <v>0</v>
+        <v>0.088854</v>
       </c>
       <c r="G327" s="7">
-        <v>0</v>
+        <v>0.159444</v>
       </c>
       <c r="H327" s="7">
-        <v>0</v>
+        <v>0.252817</v>
       </c>
       <c r="I327" s="7">
-        <v>0</v>
+        <v>0.410602</v>
       </c>
       <c r="J327" s="7">
-        <v>0</v>
+        <v>2.18777</v>
       </c>
       <c r="K327" s="7">
-        <v>0</v>
+        <v>6.392192</v>
       </c>
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
@@ -17842,25 +17842,25 @@
         <v>6</v>
       </c>
       <c r="E345" s="7">
-        <v>0</v>
+        <v>0.035515</v>
       </c>
       <c r="F345" s="7">
-        <v>0</v>
+        <v>0.041542</v>
       </c>
       <c r="G345" s="7">
-        <v>0</v>
+        <v>0.5161169999999999</v>
       </c>
       <c r="H345" s="7">
-        <v>0</v>
+        <v>0.483725</v>
       </c>
       <c r="I345" s="7">
-        <v>0</v>
+        <v>0.774601</v>
       </c>
       <c r="J345" s="7">
-        <v>0</v>
+        <v>2.682875</v>
       </c>
       <c r="K345" s="7">
-        <v>0</v>
+        <v>8.439549</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -17877,16 +17877,16 @@
         <v>7</v>
       </c>
       <c r="E346" s="7">
-        <v>0</v>
+        <v>0.068426</v>
       </c>
       <c r="F346" s="7">
-        <v>0</v>
+        <v>0.035175</v>
       </c>
       <c r="G346" s="7">
-        <v>0</v>
+        <v>-0.14346899999999999</v>
       </c>
       <c r="H346" s="7">
-        <v>0</v>
+        <v>-0.025539999999999997</v>
       </c>
       <c r="I346" s="7"/>
       <c r="J346" s="7"/>
@@ -17906,25 +17906,25 @@
         <v>7</v>
       </c>
       <c r="E347" s="7">
-        <v>0</v>
+        <v>0.084756</v>
       </c>
       <c r="F347" s="7">
-        <v>0</v>
+        <v>0.049733</v>
       </c>
       <c r="G347" s="7">
-        <v>0</v>
+        <v>-0.12373799999999999</v>
       </c>
       <c r="H347" s="7">
-        <v>0</v>
+        <v>0.025705</v>
       </c>
       <c r="I347" s="7">
-        <v>0</v>
+        <v>0.827733</v>
       </c>
       <c r="J347" s="7">
-        <v>0</v>
+        <v>3.6405790000000002</v>
       </c>
       <c r="K347" s="7">
-        <v>0</v>
+        <v>11.762544</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
@@ -17972,22 +17972,22 @@
         <v>6</v>
       </c>
       <c r="E349" s="7">
-        <v>0</v>
+        <v>0.006175000000000001</v>
       </c>
       <c r="F349" s="7">
-        <v>0</v>
+        <v>-0.049906</v>
       </c>
       <c r="G349" s="7">
-        <v>0</v>
+        <v>0.173506</v>
       </c>
       <c r="H349" s="7">
-        <v>0</v>
+        <v>0.196435</v>
       </c>
       <c r="I349" s="7">
-        <v>0</v>
+        <v>0.38323799999999997</v>
       </c>
       <c r="J349" s="7">
-        <v>0</v>
+        <v>1.25468</v>
       </c>
       <c r="K349" s="7"/>
     </row>
@@ -18005,22 +18005,22 @@
         <v>5</v>
       </c>
       <c r="E350" s="7">
-        <v>0</v>
+        <v>0.030267</v>
       </c>
       <c r="F350" s="7">
-        <v>0</v>
+        <v>0.065682</v>
       </c>
       <c r="G350" s="7">
-        <v>0</v>
+        <v>0.08690899999999999</v>
       </c>
       <c r="H350" s="7">
-        <v>0</v>
+        <v>0.190326</v>
       </c>
       <c r="I350" s="7">
-        <v>0</v>
+        <v>0.334349</v>
       </c>
       <c r="J350" s="7">
-        <v>0</v>
+        <v>1.631356</v>
       </c>
       <c r="K350" s="7"/>
     </row>
@@ -18073,25 +18073,25 @@
         <v>6</v>
       </c>
       <c r="E352" s="7">
-        <v>0</v>
+        <v>0.110294</v>
       </c>
       <c r="F352" s="7">
-        <v>0</v>
+        <v>0.13803200000000002</v>
       </c>
       <c r="G352" s="7">
-        <v>0</v>
+        <v>0.121859</v>
       </c>
       <c r="H352" s="7">
-        <v>0</v>
+        <v>0.316473</v>
       </c>
       <c r="I352" s="7">
-        <v>0</v>
+        <v>0.586382</v>
       </c>
       <c r="J352" s="7">
-        <v>0</v>
+        <v>1.640017</v>
       </c>
       <c r="K352" s="7">
-        <v>0</v>
+        <v>6.967753</v>
       </c>
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
@@ -18108,22 +18108,22 @@
         <v>6</v>
       </c>
       <c r="E353" s="7">
-        <v>0</v>
+        <v>0.026223</v>
       </c>
       <c r="F353" s="7">
-        <v>0</v>
+        <v>0.19754000000000002</v>
       </c>
       <c r="G353" s="7">
-        <v>0</v>
+        <v>0.329416</v>
       </c>
       <c r="H353" s="7">
-        <v>0</v>
+        <v>0.340837</v>
       </c>
       <c r="I353" s="7">
-        <v>0</v>
+        <v>0.549993</v>
       </c>
       <c r="J353" s="7">
-        <v>0</v>
+        <v>1.351148</v>
       </c>
       <c r="K353" s="7"/>
     </row>
@@ -18141,25 +18141,25 @@
         <v>5</v>
       </c>
       <c r="E354" s="7">
-        <v>0</v>
+        <v>-0.004673</v>
       </c>
       <c r="F354" s="7">
-        <v>0</v>
+        <v>-0.031899000000000004</v>
       </c>
       <c r="G354" s="7">
-        <v>0</v>
+        <v>0.148458</v>
       </c>
       <c r="H354" s="7">
-        <v>0</v>
+        <v>0.26026900000000003</v>
       </c>
       <c r="I354" s="7">
-        <v>0</v>
+        <v>0.458022</v>
       </c>
       <c r="J354" s="7">
-        <v>0</v>
+        <v>0.902126</v>
       </c>
       <c r="K354" s="7">
-        <v>0</v>
+        <v>4.2348</v>
       </c>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
@@ -18176,25 +18176,25 @@
         <v>4</v>
       </c>
       <c r="E355" s="7">
-        <v>0</v>
+        <v>0.029179</v>
       </c>
       <c r="F355" s="7">
-        <v>0</v>
+        <v>0.074159</v>
       </c>
       <c r="G355" s="7">
-        <v>0</v>
+        <v>0.11473900000000001</v>
       </c>
       <c r="H355" s="7">
-        <v>0</v>
+        <v>0.213297</v>
       </c>
       <c r="I355" s="7">
-        <v>0</v>
+        <v>0.363689</v>
       </c>
       <c r="J355" s="7">
-        <v>0</v>
+        <v>1.9597200000000001</v>
       </c>
       <c r="K355" s="7">
-        <v>0</v>
+        <v>6.988937</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
@@ -18384,25 +18384,25 @@
         <v>5</v>
       </c>
       <c r="E361" s="7">
-        <v>0</v>
+        <v>0.015813999999999998</v>
       </c>
       <c r="F361" s="7">
-        <v>0</v>
+        <v>0.064633</v>
       </c>
       <c r="G361" s="7">
-        <v>0</v>
+        <v>0.21695699999999998</v>
       </c>
       <c r="H361" s="7">
-        <v>0</v>
+        <v>0.251897</v>
       </c>
       <c r="I361" s="7">
-        <v>0</v>
+        <v>0.369799</v>
       </c>
       <c r="J361" s="7">
-        <v>0</v>
+        <v>1.481487</v>
       </c>
       <c r="K361" s="7">
-        <v>0</v>
+        <v>6.234833</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
@@ -18419,22 +18419,22 @@
         <v>6</v>
       </c>
       <c r="E362" s="7">
-        <v>0</v>
+        <v>-0.062354</v>
       </c>
       <c r="F362" s="7">
-        <v>0</v>
+        <v>0.019659</v>
       </c>
       <c r="G362" s="7">
-        <v>0</v>
+        <v>0.12518700000000002</v>
       </c>
       <c r="H362" s="7">
-        <v>0</v>
+        <v>0.067382</v>
       </c>
       <c r="I362" s="7">
-        <v>0</v>
+        <v>0.13224</v>
       </c>
       <c r="J362" s="7">
-        <v>0</v>
+        <v>1.3198079999999999</v>
       </c>
       <c r="K362" s="7"/>
     </row>
@@ -18452,22 +18452,22 @@
         <v>5</v>
       </c>
       <c r="E363" s="7">
-        <v>0</v>
+        <v>0.030944</v>
       </c>
       <c r="F363" s="7">
-        <v>0</v>
+        <v>0.08401</v>
       </c>
       <c r="G363" s="7">
-        <v>0</v>
+        <v>0.16206700000000002</v>
       </c>
       <c r="H363" s="7">
-        <v>0</v>
+        <v>0.092293</v>
       </c>
       <c r="I363" s="7">
-        <v>0</v>
+        <v>0.19964600000000002</v>
       </c>
       <c r="J363" s="7">
-        <v>0</v>
+        <v>1.6503780000000001</v>
       </c>
       <c r="K363" s="7"/>
     </row>
@@ -18632,22 +18632,22 @@
       </c>
       <c r="D369" s="6"/>
       <c r="E369" s="7">
-        <v>0.021551999999999998</v>
+        <v>0.022834</v>
       </c>
       <c r="F369" s="7">
-        <v>0.056061</v>
+        <v>0.057386999999999994</v>
       </c>
       <c r="G369" s="7">
-        <v>0.141824</v>
+        <v>0.143257</v>
       </c>
       <c r="H369" s="7">
-        <v>0.225156</v>
+        <v>0.226693</v>
       </c>
       <c r="I369" s="7">
-        <v>0.340562</v>
+        <v>0.34224400000000005</v>
       </c>
       <c r="J369" s="7">
-        <v>1.5105179999999998</v>
+        <v>1.513669</v>
       </c>
       <c r="K369" s="7"/>
     </row>
@@ -18810,22 +18810,22 @@
         <v>3</v>
       </c>
       <c r="E375" s="7">
-        <v>0</v>
+        <v>0.023374000000000002</v>
       </c>
       <c r="F375" s="7">
-        <v>0</v>
+        <v>0.086942</v>
       </c>
       <c r="G375" s="7">
-        <v>0</v>
+        <v>0.188796</v>
       </c>
       <c r="H375" s="7">
-        <v>0</v>
+        <v>0.256752</v>
       </c>
       <c r="I375" s="7">
-        <v>0</v>
+        <v>0.39567599999999997</v>
       </c>
       <c r="J375" s="7">
-        <v>0</v>
+        <v>2.678577</v>
       </c>
       <c r="K375" s="7"/>
     </row>
@@ -19523,25 +19523,25 @@
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="7">
-        <v>0.014001999999999999</v>
+        <v>0.013854</v>
       </c>
       <c r="F398" s="7">
-        <v>0.060611</v>
+        <v>0.060456</v>
       </c>
       <c r="G398" s="7">
-        <v>0.209238</v>
+        <v>0.209061</v>
       </c>
       <c r="H398" s="7">
-        <v>0.240465</v>
+        <v>0.24028400000000003</v>
       </c>
       <c r="I398" s="7">
-        <v>0.33587000000000006</v>
+        <v>0.335675</v>
       </c>
       <c r="J398" s="7">
-        <v>1.5739070000000002</v>
+        <v>1.573532</v>
       </c>
       <c r="K398" s="7">
-        <v>6.471244</v>
+        <v>6.470153</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
@@ -19909,10 +19909,10 @@
         <v>6</v>
       </c>
       <c r="E410" s="7">
-        <v>-0.051729000000000004</v>
+        <v>-0.052164999999999996</v>
       </c>
       <c r="F410" s="7">
-        <v>0.022742</v>
+        <v>0.022272</v>
       </c>
       <c r="G410" s="7"/>
       <c r="H410" s="7"/>
@@ -20918,19 +20918,19 @@
         <v>6</v>
       </c>
       <c r="E441" s="7">
-        <v>0.14474</v>
+        <v>0.143467</v>
       </c>
       <c r="F441" s="7">
-        <v>0.19993300000000003</v>
+        <v>0.198599</v>
       </c>
       <c r="G441" s="7">
-        <v>0.426655</v>
+        <v>0.425068</v>
       </c>
       <c r="H441" s="7">
-        <v>0.5782970000000001</v>
+        <v>0.576541</v>
       </c>
       <c r="I441" s="7">
-        <v>0.634589</v>
+        <v>0.632771</v>
       </c>
       <c r="J441" s="7"/>
       <c r="K441" s="7"/>
@@ -21515,25 +21515,25 @@
         <v>6</v>
       </c>
       <c r="E460" s="7">
-        <v>0.053217999999999994</v>
+        <v>0.053214</v>
       </c>
       <c r="F460" s="7">
-        <v>0.074434</v>
+        <v>0.07443</v>
       </c>
       <c r="G460" s="7">
-        <v>0.146427</v>
+        <v>0.146422</v>
       </c>
       <c r="H460" s="7">
-        <v>0.241261</v>
+        <v>0.241256</v>
       </c>
       <c r="I460" s="7">
-        <v>0.34747900000000004</v>
+        <v>0.347474</v>
       </c>
       <c r="J460" s="7">
-        <v>1.3751159999999998</v>
+        <v>1.375107</v>
       </c>
       <c r="K460" s="7">
-        <v>18.781592</v>
+        <v>18.781511000000002</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.25">
@@ -21684,25 +21684,25 @@
         <v>3</v>
       </c>
       <c r="E465" s="7">
-        <v>0</v>
+        <v>0.032687</v>
       </c>
       <c r="F465" s="7">
-        <v>0</v>
+        <v>0.078585</v>
       </c>
       <c r="G465" s="7">
-        <v>0</v>
+        <v>0.150145</v>
       </c>
       <c r="H465" s="7">
-        <v>0</v>
+        <v>0.22750499999999999</v>
       </c>
       <c r="I465" s="7">
-        <v>0</v>
+        <v>0.35340499999999997</v>
       </c>
       <c r="J465" s="7">
-        <v>0</v>
+        <v>2.01516</v>
       </c>
       <c r="K465" s="7">
-        <v>0</v>
+        <v>6.102172</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.25">
@@ -22362,16 +22362,16 @@
         <v>2</v>
       </c>
       <c r="E485" s="7">
-        <v>0.029001000000000002</v>
+        <v>0.028996</v>
       </c>
       <c r="F485" s="7">
-        <v>0.09363099999999999</v>
+        <v>0.093626</v>
       </c>
       <c r="G485" s="7">
-        <v>0.230293</v>
+        <v>0.230288</v>
       </c>
       <c r="H485" s="7">
-        <v>0.32335099999999994</v>
+        <v>0.323345</v>
       </c>
       <c r="I485" s="7"/>
       <c r="J485" s="7"/>
@@ -22391,22 +22391,22 @@
         <v>3</v>
       </c>
       <c r="E486" s="7">
-        <v>0</v>
+        <v>0.034077</v>
       </c>
       <c r="F486" s="7">
-        <v>0</v>
+        <v>0.131009</v>
       </c>
       <c r="G486" s="7">
-        <v>0</v>
+        <v>0.272636</v>
       </c>
       <c r="H486" s="7">
-        <v>0</v>
+        <v>0.375764</v>
       </c>
       <c r="I486" s="7">
-        <v>0</v>
+        <v>0.617996</v>
       </c>
       <c r="J486" s="7">
-        <v>0</v>
+        <v>2.167181</v>
       </c>
       <c r="K486" s="7"/>
     </row>
@@ -22682,22 +22682,22 @@
         <v>5</v>
       </c>
       <c r="E495" s="7">
-        <v>0.018698</v>
+        <v>0.017816000000000002</v>
       </c>
       <c r="F495" s="7">
-        <v>0.055987999999999996</v>
+        <v>0.055073</v>
       </c>
       <c r="G495" s="7">
-        <v>0.412317</v>
+        <v>0.411094</v>
       </c>
       <c r="H495" s="7">
-        <v>0.440395</v>
+        <v>0.439148</v>
       </c>
       <c r="I495" s="7">
-        <v>0.590017</v>
+        <v>0.5886399999999999</v>
       </c>
       <c r="J495" s="7">
-        <v>2.2623249999999997</v>
+        <v>2.2595009999999998</v>
       </c>
       <c r="K495" s="7"/>
     </row>
@@ -22975,19 +22975,19 @@
         <v>6</v>
       </c>
       <c r="E504" s="7">
-        <v>-0.033696000000000004</v>
+        <v>-0.033677</v>
       </c>
       <c r="F504" s="7">
-        <v>0.053471000000000005</v>
+        <v>0.053492</v>
       </c>
       <c r="G504" s="7">
-        <v>0.057123</v>
+        <v>0.057144</v>
       </c>
       <c r="H504" s="7">
-        <v>0.18574100000000002</v>
+        <v>0.18576399999999998</v>
       </c>
       <c r="I504" s="7">
-        <v>0.283373</v>
+        <v>0.283398</v>
       </c>
       <c r="J504" s="7"/>
       <c r="K504" s="7"/>
@@ -25053,25 +25053,25 @@
         <v>6</v>
       </c>
       <c r="E570" s="7">
-        <v>0</v>
+        <v>0.027058</v>
       </c>
       <c r="F570" s="7">
-        <v>0</v>
+        <v>0.07721</v>
       </c>
       <c r="G570" s="7">
-        <v>0</v>
+        <v>0.142658</v>
       </c>
       <c r="H570" s="7">
-        <v>0</v>
+        <v>0.13561299999999998</v>
       </c>
       <c r="I570" s="7">
-        <v>0</v>
+        <v>0.21130500000000002</v>
       </c>
       <c r="J570" s="7">
-        <v>0</v>
+        <v>1.540546</v>
       </c>
       <c r="K570" s="7">
-        <v>0</v>
+        <v>6.740503</v>
       </c>
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.25">
@@ -25809,16 +25809,16 @@
         <v>6</v>
       </c>
       <c r="E594" s="7">
-        <v>0.114635</v>
+        <v>0.115892</v>
       </c>
       <c r="F594" s="7">
-        <v>0.10552099999999999</v>
+        <v>0.106768</v>
       </c>
       <c r="G594" s="7">
-        <v>0.037934999999999997</v>
+        <v>0.039106</v>
       </c>
       <c r="H594" s="7">
-        <v>0.21782900000000002</v>
+        <v>0.219202</v>
       </c>
       <c r="I594" s="7"/>
       <c r="J594" s="7"/>
@@ -25964,22 +25964,22 @@
         <v>6</v>
       </c>
       <c r="E599" s="7">
-        <v>0.031935</v>
+        <v>0.032359</v>
       </c>
       <c r="F599" s="7">
-        <v>0.049814</v>
+        <v>0.050246000000000006</v>
       </c>
       <c r="G599" s="7">
-        <v>0.193679</v>
+        <v>0.19417</v>
       </c>
       <c r="H599" s="7">
-        <v>0.323873</v>
+        <v>0.32441699999999996</v>
       </c>
       <c r="I599" s="7">
-        <v>0.449623</v>
+        <v>0.45021900000000004</v>
       </c>
       <c r="J599" s="7">
-        <v>1.79929</v>
+        <v>1.8004419999999999</v>
       </c>
       <c r="K599" s="7"/>
     </row>
@@ -25997,25 +25997,25 @@
         <v>7</v>
       </c>
       <c r="E600" s="7">
-        <v>0.046416000000000006</v>
+        <v>0.062569</v>
       </c>
       <c r="F600" s="7">
-        <v>0.037259</v>
+        <v>0.053271</v>
       </c>
       <c r="G600" s="7">
-        <v>-0.132056</v>
+        <v>-0.118658</v>
       </c>
       <c r="H600" s="7">
-        <v>-0.013675999999999999</v>
+        <v>0.00155</v>
       </c>
       <c r="I600" s="7">
-        <v>0.7509</v>
+        <v>0.777928</v>
       </c>
       <c r="J600" s="7">
-        <v>3.7121370000000002</v>
+        <v>3.7848770000000003</v>
       </c>
       <c r="K600" s="7">
-        <v>12.002258999999999</v>
+        <v>12.202971</v>
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.25">
@@ -26032,25 +26032,25 @@
         <v>6</v>
       </c>
       <c r="E601" s="7">
-        <v>-0.020892</v>
+        <v>-0.029605000000000003</v>
       </c>
       <c r="F601" s="7">
-        <v>-0.028255</v>
+        <v>-0.036903</v>
       </c>
       <c r="G601" s="7">
-        <v>0.0036009999999999996</v>
+        <v>-0.005331</v>
       </c>
       <c r="H601" s="7">
-        <v>-0.07608100000000001</v>
+        <v>-0.084304</v>
       </c>
       <c r="I601" s="7">
-        <v>-0.065265</v>
+        <v>-0.073584</v>
       </c>
       <c r="J601" s="7">
-        <v>0.359903</v>
+        <v>0.3478</v>
       </c>
       <c r="K601" s="7">
-        <v>3.0572269999999997</v>
+        <v>3.0211200000000002</v>
       </c>
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.25">
@@ -26232,16 +26232,16 @@
         <v>5</v>
       </c>
       <c r="E607" s="7">
-        <v>0.027982</v>
+        <v>0.026399</v>
       </c>
       <c r="F607" s="7">
-        <v>0.052554</v>
+        <v>0.050934</v>
       </c>
       <c r="G607" s="7">
-        <v>0.227053</v>
+        <v>0.225164</v>
       </c>
       <c r="H607" s="7">
-        <v>0.23671199999999998</v>
+        <v>0.234808</v>
       </c>
       <c r="I607" s="7"/>
       <c r="J607" s="7"/>
@@ -26765,22 +26765,22 @@
         <v>5</v>
       </c>
       <c r="E624" s="7">
-        <v>0.054993999999999994</v>
+        <v>0.056063</v>
       </c>
       <c r="F624" s="7">
-        <v>0.080291</v>
+        <v>0.081385</v>
       </c>
       <c r="G624" s="7">
-        <v>0.16559100000000002</v>
+        <v>0.166772</v>
       </c>
       <c r="H624" s="7">
-        <v>0.22348600000000002</v>
+        <v>0.224726</v>
       </c>
       <c r="I624" s="7">
-        <v>0.309986</v>
+        <v>0.311313</v>
       </c>
       <c r="J624" s="7">
-        <v>1.158988</v>
+        <v>1.161175</v>
       </c>
       <c r="K624" s="7"/>
     </row>
@@ -26988,19 +26988,19 @@
         <v>5</v>
       </c>
       <c r="E631" s="7">
-        <v>0</v>
+        <v>0.034205</v>
       </c>
       <c r="F631" s="7">
-        <v>0</v>
+        <v>0.106907</v>
       </c>
       <c r="G631" s="7">
-        <v>0</v>
+        <v>0.23194299999999998</v>
       </c>
       <c r="H631" s="7">
-        <v>0</v>
+        <v>0.333219</v>
       </c>
       <c r="I631" s="7">
-        <v>0</v>
+        <v>0.543065</v>
       </c>
       <c r="J631" s="7"/>
       <c r="K631" s="7"/>
@@ -27085,19 +27085,19 @@
         <v>5</v>
       </c>
       <c r="E634" s="7">
-        <v>0</v>
+        <v>0.029887</v>
       </c>
       <c r="F634" s="7">
-        <v>0</v>
+        <v>0.09102</v>
       </c>
       <c r="G634" s="7">
-        <v>0</v>
+        <v>0.18127500000000002</v>
       </c>
       <c r="H634" s="7">
-        <v>0</v>
+        <v>0.047519</v>
       </c>
       <c r="I634" s="7">
-        <v>0</v>
+        <v>0.125455</v>
       </c>
       <c r="J634" s="7"/>
       <c r="K634" s="7"/>
@@ -27116,22 +27116,22 @@
         <v>3</v>
       </c>
       <c r="E635" s="7">
-        <v>0</v>
+        <v>0.027825000000000003</v>
       </c>
       <c r="F635" s="7">
-        <v>0</v>
+        <v>0.044448999999999995</v>
       </c>
       <c r="G635" s="7">
-        <v>0</v>
+        <v>0.133856</v>
       </c>
       <c r="H635" s="7">
-        <v>0</v>
+        <v>0.176651</v>
       </c>
       <c r="I635" s="7">
-        <v>0</v>
+        <v>0.33635</v>
       </c>
       <c r="J635" s="7">
-        <v>0</v>
+        <v>1.700749</v>
       </c>
       <c r="K635" s="7"/>
     </row>
@@ -28438,22 +28438,22 @@
         <v>6</v>
       </c>
       <c r="E677" s="7">
-        <v>0.032215</v>
+        <v>0.032271</v>
       </c>
       <c r="F677" s="7">
-        <v>0.062237999999999995</v>
+        <v>0.062294999999999996</v>
       </c>
       <c r="G677" s="7">
-        <v>0.376716</v>
+        <v>0.37679</v>
       </c>
       <c r="H677" s="7">
-        <v>0.35782800000000003</v>
+        <v>0.357901</v>
       </c>
       <c r="I677" s="7">
-        <v>0.55255</v>
+        <v>0.552634</v>
       </c>
       <c r="J677" s="7">
-        <v>2.500497</v>
+        <v>2.500686</v>
       </c>
       <c r="K677" s="7"/>
     </row>
@@ -28504,25 +28504,25 @@
         <v>5</v>
       </c>
       <c r="E679" s="7">
-        <v>0</v>
+        <v>0.016094</v>
       </c>
       <c r="F679" s="7">
-        <v>0</v>
+        <v>0.028073</v>
       </c>
       <c r="G679" s="7">
-        <v>0</v>
+        <v>0.052369000000000006</v>
       </c>
       <c r="H679" s="7">
-        <v>0</v>
+        <v>0.155027</v>
       </c>
       <c r="I679" s="7">
-        <v>0</v>
+        <v>0.28989</v>
       </c>
       <c r="J679" s="7">
-        <v>0</v>
+        <v>1.565736</v>
       </c>
       <c r="K679" s="7">
-        <v>0</v>
+        <v>6.612551999999999</v>
       </c>
     </row>
     <row r="680" spans="1:11" x14ac:dyDescent="0.25">
@@ -28549,10 +28549,10 @@
         <v>0.232705</v>
       </c>
       <c r="I680" s="7">
-        <v>0.35748800000000003</v>
+        <v>0.357489</v>
       </c>
       <c r="J680" s="7">
-        <v>1.492752</v>
+        <v>1.4927529999999998</v>
       </c>
       <c r="K680" s="7"/>
     </row>
@@ -28570,25 +28570,25 @@
         <v>4</v>
       </c>
       <c r="E681" s="7">
-        <v>0.049387</v>
+        <v>0.049392</v>
       </c>
       <c r="F681" s="7">
-        <v>0.09729499999999999</v>
+        <v>0.0973</v>
       </c>
       <c r="G681" s="7">
-        <v>0.142478</v>
+        <v>0.142483</v>
       </c>
       <c r="H681" s="7">
-        <v>0.22129000000000001</v>
+        <v>0.221296</v>
       </c>
       <c r="I681" s="7">
-        <v>0.384169</v>
+        <v>0.384176</v>
       </c>
       <c r="J681" s="7">
-        <v>1.758228</v>
+        <v>1.7582419999999999</v>
       </c>
       <c r="K681" s="7">
-        <v>6.5765899999999995</v>
+        <v>6.576626999999999</v>
       </c>
     </row>
     <row r="682" spans="1:11" x14ac:dyDescent="0.25">
@@ -28708,22 +28708,22 @@
         <v>6</v>
       </c>
       <c r="E685" s="7">
-        <v>0.036294</v>
+        <v>0.037785</v>
       </c>
       <c r="F685" s="7">
-        <v>0.063279</v>
+        <v>0.064808</v>
       </c>
       <c r="G685" s="7">
-        <v>0.014996</v>
+        <v>0.016456</v>
       </c>
       <c r="H685" s="7">
-        <v>0.146935</v>
+        <v>0.148584</v>
       </c>
       <c r="I685" s="7">
-        <v>0.250394</v>
+        <v>0.252192</v>
       </c>
       <c r="J685" s="7">
-        <v>0.700856</v>
+        <v>0.7033020000000001</v>
       </c>
       <c r="K685" s="7"/>
     </row>
@@ -28741,22 +28741,22 @@
         <v>3</v>
       </c>
       <c r="E686" s="7">
-        <v>0.029922</v>
+        <v>0.032431999999999996</v>
       </c>
       <c r="F686" s="7">
-        <v>0.078729</v>
+        <v>0.081358</v>
       </c>
       <c r="G686" s="7">
-        <v>0.157876</v>
+        <v>0.160697</v>
       </c>
       <c r="H686" s="7">
-        <v>0.25341400000000003</v>
+        <v>0.256469</v>
       </c>
       <c r="I686" s="7">
-        <v>0.434159</v>
+        <v>0.437654</v>
       </c>
       <c r="J686" s="7">
-        <v>2.200012</v>
+        <v>2.2078100000000003</v>
       </c>
       <c r="K686" s="7"/>
     </row>
@@ -28842,25 +28842,25 @@
         <v>6</v>
       </c>
       <c r="E689" s="7">
-        <v>0.021778</v>
+        <v>0.021428</v>
       </c>
       <c r="F689" s="7">
-        <v>0.051921999999999996</v>
+        <v>0.051562000000000004</v>
       </c>
       <c r="G689" s="7">
-        <v>0.422939</v>
+        <v>0.422453</v>
       </c>
       <c r="H689" s="7">
-        <v>0.42859499999999995</v>
+        <v>0.428106</v>
       </c>
       <c r="I689" s="7">
-        <v>0.589057</v>
+        <v>0.5885130000000001</v>
       </c>
       <c r="J689" s="7">
-        <v>2.657292</v>
+        <v>2.65604</v>
       </c>
       <c r="K689" s="7">
-        <v>10.549763</v>
+        <v>10.545811</v>
       </c>
     </row>
     <row r="690" spans="1:11" x14ac:dyDescent="0.25">
@@ -29013,22 +29013,22 @@
         <v>6</v>
       </c>
       <c r="E694" s="7">
-        <v>-0.024394999999999997</v>
+        <v>-0.024621</v>
       </c>
       <c r="F694" s="7">
-        <v>-0.022551</v>
+        <v>-0.022778</v>
       </c>
       <c r="G694" s="7">
-        <v>0.140545</v>
+        <v>0.14028000000000002</v>
       </c>
       <c r="H694" s="7">
-        <v>0.146177</v>
+        <v>0.145911</v>
       </c>
       <c r="I694" s="7">
-        <v>0.265563</v>
+        <v>0.26526900000000003</v>
       </c>
       <c r="J694" s="7">
-        <v>0.718036</v>
+        <v>0.717637</v>
       </c>
       <c r="K694" s="7"/>
     </row>
@@ -29046,22 +29046,22 @@
         <v>2</v>
       </c>
       <c r="E695" s="7">
-        <v>0.032256</v>
+        <v>0.033375</v>
       </c>
       <c r="F695" s="7">
-        <v>0.10277599999999999</v>
+        <v>0.103972</v>
       </c>
       <c r="G695" s="7">
-        <v>0.222954</v>
+        <v>0.22428</v>
       </c>
       <c r="H695" s="7">
-        <v>0.31068</v>
+        <v>0.312101</v>
       </c>
       <c r="I695" s="7">
-        <v>0.483017</v>
+        <v>0.484625</v>
       </c>
       <c r="J695" s="7">
-        <v>2.520022</v>
+        <v>2.523839</v>
       </c>
       <c r="K695" s="7"/>
     </row>
@@ -29329,19 +29329,19 @@
         <v>5</v>
       </c>
       <c r="E704" s="7">
-        <v>0</v>
+        <v>0.031413</v>
       </c>
       <c r="F704" s="7">
-        <v>0</v>
+        <v>0.06283699999999999</v>
       </c>
       <c r="G704" s="7">
-        <v>0</v>
+        <v>0.34360100000000005</v>
       </c>
       <c r="H704" s="7">
-        <v>0</v>
+        <v>0.40990499999999996</v>
       </c>
       <c r="I704" s="7">
-        <v>0</v>
+        <v>0.60704</v>
       </c>
       <c r="J704" s="7"/>
       <c r="K704" s="7"/>
@@ -29566,22 +29566,22 @@
         <v>6</v>
       </c>
       <c r="E711" s="7">
-        <v>0.058586</v>
+        <v>0.058736</v>
       </c>
       <c r="F711" s="7">
-        <v>0.089932</v>
+        <v>0.09008699999999999</v>
       </c>
       <c r="G711" s="7">
-        <v>-0.066879</v>
+        <v>-0.066747</v>
       </c>
       <c r="H711" s="7">
-        <v>0.073306</v>
+        <v>0.073459</v>
       </c>
       <c r="I711" s="7">
-        <v>0.614493</v>
+        <v>0.614722</v>
       </c>
       <c r="J711" s="7">
-        <v>2.9216390000000003</v>
+        <v>2.922196</v>
       </c>
       <c r="K711" s="7"/>
     </row>
@@ -29696,22 +29696,22 @@
         <v>6</v>
       </c>
       <c r="E715" s="7">
-        <v>0.099865</v>
+        <v>0.100192</v>
       </c>
       <c r="F715" s="7">
-        <v>0.134927</v>
+        <v>0.13526300000000002</v>
       </c>
       <c r="G715" s="7">
-        <v>0.142248</v>
+        <v>0.14258800000000002</v>
       </c>
       <c r="H715" s="7">
-        <v>0.383083</v>
+        <v>0.383493</v>
       </c>
       <c r="I715" s="7">
-        <v>0.606772</v>
+        <v>0.6072489999999999</v>
       </c>
       <c r="J715" s="7">
-        <v>1.6435769999999998</v>
+        <v>1.644362</v>
       </c>
       <c r="K715" s="7"/>
     </row>
@@ -29907,19 +29907,19 @@
         <v>4</v>
       </c>
       <c r="E722" s="7">
-        <v>0.046524</v>
+        <v>0.050452000000000004</v>
       </c>
       <c r="F722" s="7">
-        <v>0.129603</v>
+        <v>0.133842</v>
       </c>
       <c r="G722" s="7">
-        <v>0.30165600000000004</v>
+        <v>0.306541</v>
       </c>
       <c r="H722" s="7">
-        <v>0.46914900000000004</v>
+        <v>0.47466200000000003</v>
       </c>
       <c r="I722" s="7">
-        <v>0.668091</v>
+        <v>0.674351</v>
       </c>
       <c r="J722" s="7"/>
       <c r="K722" s="7"/>
@@ -30167,19 +30167,19 @@
         <v>4</v>
       </c>
       <c r="E730" s="7">
-        <v>0.057358</v>
+        <v>0.060589000000000004</v>
       </c>
       <c r="F730" s="7">
-        <v>0.069387</v>
+        <v>0.072655</v>
       </c>
       <c r="G730" s="7">
-        <v>0.092295</v>
+        <v>0.095633</v>
       </c>
       <c r="H730" s="7">
-        <v>0.217484</v>
+        <v>0.22120499999999998</v>
       </c>
       <c r="I730" s="7">
-        <v>0.40303100000000003</v>
+        <v>0.407318</v>
       </c>
       <c r="J730" s="7"/>
       <c r="K730" s="7"/>
@@ -30198,22 +30198,22 @@
         <v>4</v>
       </c>
       <c r="E731" s="7">
-        <v>-0.011999</v>
+        <v>-0.010682</v>
       </c>
       <c r="F731" s="7">
-        <v>0.026923</v>
+        <v>0.028292</v>
       </c>
       <c r="G731" s="7">
-        <v>0.13772700000000002</v>
+        <v>0.139244</v>
       </c>
       <c r="H731" s="7">
-        <v>0.230166</v>
+        <v>0.23180599999999998</v>
       </c>
       <c r="I731" s="7">
-        <v>0.391227</v>
+        <v>0.393082</v>
       </c>
       <c r="J731" s="7">
-        <v>1.864544</v>
+        <v>1.868363</v>
       </c>
       <c r="K731" s="7"/>
     </row>
@@ -30293,19 +30293,19 @@
         <v>6</v>
       </c>
       <c r="E734" s="7">
-        <v>0</v>
+        <v>-0.729098</v>
       </c>
       <c r="F734" s="7">
-        <v>0</v>
+        <v>-0.6789459999999999</v>
       </c>
       <c r="G734" s="7">
-        <v>0</v>
+        <v>-0.553653</v>
       </c>
       <c r="H734" s="7">
-        <v>0</v>
+        <v>-0.274272</v>
       </c>
       <c r="I734" s="7">
-        <v>0</v>
+        <v>-0.11343</v>
       </c>
       <c r="J734" s="7"/>
       <c r="K734" s="7"/>
@@ -30417,22 +30417,22 @@
         <v>6</v>
       </c>
       <c r="E738" s="7">
-        <v>0.015032</v>
+        <v>0.016041</v>
       </c>
       <c r="F738" s="7">
-        <v>-0.018694</v>
+        <v>-0.017718</v>
       </c>
       <c r="G738" s="7">
-        <v>0.156328</v>
+        <v>0.157477</v>
       </c>
       <c r="H738" s="7">
-        <v>0.280399</v>
+        <v>0.28167200000000003</v>
       </c>
       <c r="I738" s="7">
-        <v>0.704596</v>
+        <v>0.7062909999999999</v>
       </c>
       <c r="J738" s="7">
-        <v>2.018033</v>
+        <v>2.021035</v>
       </c>
       <c r="K738" s="7"/>
     </row>
@@ -30897,10 +30897,10 @@
         <v>2</v>
       </c>
       <c r="E754" s="7">
-        <v>0</v>
+        <v>0.044675</v>
       </c>
       <c r="F754" s="7">
-        <v>0</v>
+        <v>0.131318</v>
       </c>
       <c r="G754" s="7"/>
       <c r="H754" s="7"/>
@@ -31641,19 +31641,19 @@
         <v>2</v>
       </c>
       <c r="E778" s="7">
-        <v>0</v>
+        <v>0.043169000000000006</v>
       </c>
       <c r="F778" s="7">
-        <v>0</v>
+        <v>0.12858</v>
       </c>
       <c r="G778" s="7">
-        <v>0</v>
+        <v>0.27084199999999997</v>
       </c>
       <c r="H778" s="7">
-        <v>0</v>
+        <v>0.382175</v>
       </c>
       <c r="I778" s="7">
-        <v>0</v>
+        <v>0.6017399999999999</v>
       </c>
       <c r="J778" s="7"/>
       <c r="K778" s="7"/>
@@ -32331,19 +32331,19 @@
         <v>6</v>
       </c>
       <c r="E800" s="7">
-        <v>0.069619</v>
+        <v>0.069532</v>
       </c>
       <c r="F800" s="7">
-        <v>0.055081</v>
+        <v>0.054996</v>
       </c>
       <c r="G800" s="7">
-        <v>0.38498699999999997</v>
+        <v>0.38487499999999997</v>
       </c>
       <c r="H800" s="7">
-        <v>0.354378</v>
+        <v>0.354268</v>
       </c>
       <c r="I800" s="7">
-        <v>0.446985</v>
+        <v>0.446868</v>
       </c>
       <c r="J800" s="7"/>
       <c r="K800" s="7"/>
@@ -32457,25 +32457,25 @@
         <v>1</v>
       </c>
       <c r="E804" s="7">
-        <v>-0.157414</v>
+        <v>0.034247</v>
       </c>
       <c r="F804" s="7">
-        <v>-0.09899699999999999</v>
+        <v>0.105952</v>
       </c>
       <c r="G804" s="7">
-        <v>-0.009849</v>
+        <v>0.21537900000000001</v>
       </c>
       <c r="H804" s="7">
-        <v>0.056951999999999996</v>
+        <v>0.297375</v>
       </c>
       <c r="I804" s="7">
-        <v>0.19155</v>
+        <v>0.462589</v>
       </c>
       <c r="J804" s="7">
-        <v>1.6045070000000001</v>
+        <v>2.196948</v>
       </c>
       <c r="K804" s="7">
-        <v>2.735546</v>
+        <v>3.585262</v>
       </c>
     </row>
     <row r="805" spans="1:11" x14ac:dyDescent="0.25">
@@ -32651,7 +32651,7 @@
         <v>6</v>
       </c>
       <c r="E810" s="7">
-        <v>0.100534</v>
+        <v>0.101217</v>
       </c>
       <c r="F810" s="7"/>
       <c r="G810" s="7"/>
@@ -32674,13 +32674,13 @@
         <v>5</v>
       </c>
       <c r="E811" s="7">
-        <v>0.065095</v>
+        <v>0.061829</v>
       </c>
       <c r="F811" s="7">
-        <v>0.09990399999999999</v>
+        <v>0.096531</v>
       </c>
       <c r="G811" s="7">
-        <v>0.13561299999999998</v>
+        <v>0.132131</v>
       </c>
       <c r="H811" s="7"/>
       <c r="I811" s="7"/>
@@ -32701,16 +32701,16 @@
         <v>2</v>
       </c>
       <c r="E812" s="7">
-        <v>0.015224999999999999</v>
+        <v>0.020815999999999998</v>
       </c>
       <c r="F812" s="7">
-        <v>0.045530999999999995</v>
+        <v>0.051289</v>
       </c>
       <c r="G812" s="7">
-        <v>0.103044</v>
+        <v>0.109119</v>
       </c>
       <c r="H812" s="7">
-        <v>0.13695000000000002</v>
+        <v>0.143211</v>
       </c>
       <c r="I812" s="7"/>
       <c r="J812" s="7"/>
@@ -32761,22 +32761,22 @@
         <v>6</v>
       </c>
       <c r="E814" s="7">
-        <v>0.017817</v>
+        <v>0.01781</v>
       </c>
       <c r="F814" s="7">
-        <v>0.034661</v>
+        <v>0.034654</v>
       </c>
       <c r="G814" s="7">
-        <v>0.123651</v>
+        <v>0.123644</v>
       </c>
       <c r="H814" s="7">
-        <v>0.25333</v>
+        <v>0.253322</v>
       </c>
       <c r="I814" s="7">
-        <v>0.459026</v>
+        <v>0.459017</v>
       </c>
       <c r="J814" s="7">
-        <v>1.41552</v>
+        <v>1.415505</v>
       </c>
       <c r="K814" s="7"/>
     </row>
@@ -32858,22 +32858,22 @@
         <v>5</v>
       </c>
       <c r="E817" s="7">
-        <v>0.003725</v>
+        <v>0.0031469999999999996</v>
       </c>
       <c r="F817" s="7">
-        <v>-0.014782</v>
+        <v>-0.015349999999999999</v>
       </c>
       <c r="G817" s="7">
-        <v>0.071421</v>
+        <v>0.070804</v>
       </c>
       <c r="H817" s="7">
-        <v>0.15970800000000002</v>
+        <v>0.15904</v>
       </c>
       <c r="I817" s="7">
-        <v>0.382102</v>
+        <v>0.38130600000000003</v>
       </c>
       <c r="J817" s="7">
-        <v>2.4602690000000003</v>
+        <v>2.458277</v>
       </c>
       <c r="K817" s="7"/>
     </row>
@@ -33141,25 +33141,25 @@
         <v>5</v>
       </c>
       <c r="E826" s="7">
-        <v>0.001095</v>
+        <v>0.001094</v>
       </c>
       <c r="F826" s="7">
         <v>0.074843</v>
       </c>
       <c r="G826" s="7">
-        <v>0.14929399999999998</v>
+        <v>0.149293</v>
       </c>
       <c r="H826" s="7">
-        <v>0.230506</v>
+        <v>0.230505</v>
       </c>
       <c r="I826" s="7">
-        <v>0.378703</v>
+        <v>0.378702</v>
       </c>
       <c r="J826" s="7">
-        <v>2.272291</v>
+        <v>2.2722890000000002</v>
       </c>
       <c r="K826" s="7">
-        <v>12.019641</v>
+        <v>12.019630999999999</v>
       </c>
     </row>
     <row r="827" spans="1:11" x14ac:dyDescent="0.25">
@@ -33240,19 +33240,19 @@
         <v>2</v>
       </c>
       <c r="E829" s="7">
-        <v>0.020626000000000002</v>
+        <v>0.024701</v>
       </c>
       <c r="F829" s="7">
-        <v>0.087628</v>
+        <v>0.09197100000000001</v>
       </c>
       <c r="G829" s="7">
-        <v>0.181225</v>
+        <v>0.185942</v>
       </c>
       <c r="H829" s="7">
-        <v>0.26039100000000004</v>
+        <v>0.265424</v>
       </c>
       <c r="I829" s="7">
-        <v>0.368129</v>
+        <v>0.37359200000000004</v>
       </c>
       <c r="J829" s="7"/>
       <c r="K829" s="7"/>
@@ -33401,22 +33401,22 @@
         <v>1</v>
       </c>
       <c r="E834" s="7">
-        <v>0.02848</v>
+        <v>0.028475</v>
       </c>
       <c r="F834" s="7">
-        <v>0.09685</v>
+        <v>0.096845</v>
       </c>
       <c r="G834" s="7">
-        <v>0.208654</v>
+        <v>0.208648</v>
       </c>
       <c r="H834" s="7">
-        <v>0.292214</v>
+        <v>0.292208</v>
       </c>
       <c r="I834" s="7">
-        <v>0.458275</v>
+        <v>0.45826900000000004</v>
       </c>
       <c r="J834" s="7">
-        <v>2.6277</v>
+        <v>2.627683</v>
       </c>
       <c r="K834" s="7"/>
     </row>
@@ -33465,19 +33465,19 @@
         <v>2</v>
       </c>
       <c r="E836" s="7">
-        <v>0.032408</v>
+        <v>0.032406000000000004</v>
       </c>
       <c r="F836" s="7">
-        <v>0.099615</v>
+        <v>0.099613</v>
       </c>
       <c r="G836" s="7">
-        <v>0.217713</v>
+        <v>0.21771100000000002</v>
       </c>
       <c r="H836" s="7">
-        <v>0.30863399999999996</v>
+        <v>0.308631</v>
       </c>
       <c r="I836" s="7">
-        <v>0.48558999999999997</v>
+        <v>0.485587</v>
       </c>
       <c r="J836" s="7"/>
       <c r="K836" s="7"/>
@@ -33620,22 +33620,22 @@
         <v>6</v>
       </c>
       <c r="E841" s="7">
-        <v>0.03633</v>
+        <v>0.036374</v>
       </c>
       <c r="F841" s="7">
-        <v>0.028498000000000002</v>
+        <v>0.028542</v>
       </c>
       <c r="G841" s="7">
-        <v>0.469786</v>
+        <v>0.469849</v>
       </c>
       <c r="H841" s="7">
-        <v>0.446906</v>
+        <v>0.446967</v>
       </c>
       <c r="I841" s="7">
-        <v>0.619238</v>
+        <v>0.619307</v>
       </c>
       <c r="J841" s="7">
-        <v>2.218156</v>
+        <v>2.218293</v>
       </c>
       <c r="K841" s="7"/>
     </row>
@@ -33814,19 +33814,19 @@
         <v>6</v>
       </c>
       <c r="E847" s="7">
-        <v>0</v>
+        <v>-0.0029170000000000003</v>
       </c>
       <c r="F847" s="7">
-        <v>0</v>
+        <v>-0.014472</v>
       </c>
       <c r="G847" s="7">
-        <v>0</v>
+        <v>0.079379</v>
       </c>
       <c r="H847" s="7">
-        <v>0</v>
+        <v>0.218024</v>
       </c>
       <c r="I847" s="7">
-        <v>0</v>
+        <v>0.483385</v>
       </c>
       <c r="J847" s="7"/>
       <c r="K847" s="7"/>
@@ -33845,7 +33845,7 @@
         <v>5</v>
       </c>
       <c r="E848" s="7">
-        <v>0</v>
+        <v>0.036989</v>
       </c>
       <c r="F848" s="7"/>
       <c r="G848" s="7"/>
@@ -33868,19 +33868,19 @@
         <v>5</v>
       </c>
       <c r="E849" s="7">
-        <v>0.03292</v>
+        <v>0.034992999999999996</v>
       </c>
       <c r="F849" s="7">
-        <v>0.07198500000000001</v>
+        <v>0.074136</v>
       </c>
       <c r="G849" s="7">
-        <v>0.16305399999999998</v>
+        <v>0.16538799999999998</v>
       </c>
       <c r="H849" s="7">
-        <v>0.296564</v>
+        <v>0.299166</v>
       </c>
       <c r="I849" s="7">
-        <v>0.461796</v>
+        <v>0.46473</v>
       </c>
       <c r="J849" s="7"/>
       <c r="K849" s="7"/>
@@ -33920,19 +33920,19 @@
         <v>5</v>
       </c>
       <c r="E851" s="7">
-        <v>0</v>
+        <v>0.014633</v>
       </c>
       <c r="F851" s="7">
-        <v>0</v>
+        <v>0.133293</v>
       </c>
       <c r="G851" s="7">
-        <v>0</v>
+        <v>0.43911</v>
       </c>
       <c r="H851" s="7">
-        <v>0</v>
+        <v>0.462769</v>
       </c>
       <c r="I851" s="7">
-        <v>0</v>
+        <v>0.516977</v>
       </c>
       <c r="J851" s="7"/>
       <c r="K851" s="7"/>
@@ -34007,16 +34007,16 @@
         <v>6</v>
       </c>
       <c r="E854" s="7">
-        <v>0</v>
+        <v>0.06385</v>
       </c>
       <c r="F854" s="7">
-        <v>0</v>
+        <v>0.08174200000000001</v>
       </c>
       <c r="G854" s="7">
-        <v>0</v>
+        <v>0.128095</v>
       </c>
       <c r="H854" s="7">
-        <v>0</v>
+        <v>0.45801400000000003</v>
       </c>
       <c r="I854" s="7"/>
       <c r="J854" s="7"/>
@@ -34317,19 +34317,19 @@
         <v>4</v>
       </c>
       <c r="E864" s="7">
-        <v>0.036952</v>
+        <v>0.042126000000000004</v>
       </c>
       <c r="F864" s="7">
-        <v>0.083443</v>
+        <v>0.088848</v>
       </c>
       <c r="G864" s="7">
-        <v>0.173353</v>
+        <v>0.179207</v>
       </c>
       <c r="H864" s="7">
-        <v>0.28575500000000004</v>
+        <v>0.292169</v>
       </c>
       <c r="I864" s="7">
-        <v>0.521226</v>
+        <v>0.528816</v>
       </c>
       <c r="J864" s="7"/>
       <c r="K864" s="7"/>
@@ -34379,19 +34379,19 @@
         <v>5</v>
       </c>
       <c r="E866" s="7">
-        <v>0.026604000000000003</v>
+        <v>0.026434000000000003</v>
       </c>
       <c r="F866" s="7">
-        <v>0.131628</v>
+        <v>0.131441</v>
       </c>
       <c r="G866" s="7">
-        <v>0.21239799999999998</v>
+        <v>0.212197</v>
       </c>
       <c r="H866" s="7">
-        <v>0.23938099999999998</v>
+        <v>0.239176</v>
       </c>
       <c r="I866" s="7">
-        <v>0.42993499999999996</v>
+        <v>0.42969799999999997</v>
       </c>
       <c r="J866" s="7"/>
       <c r="K866" s="7"/>
@@ -34703,22 +34703,22 @@
         <v>5</v>
       </c>
       <c r="E876" s="7">
-        <v>0.023171</v>
+        <v>0.02338</v>
       </c>
       <c r="F876" s="7">
-        <v>0.120726</v>
+        <v>0.120955</v>
       </c>
       <c r="G876" s="7">
-        <v>0.187253</v>
+        <v>0.18749500000000002</v>
       </c>
       <c r="H876" s="7">
-        <v>0.250713</v>
+        <v>0.250969</v>
       </c>
       <c r="I876" s="7">
-        <v>0.273573</v>
+        <v>0.273833</v>
       </c>
       <c r="J876" s="7">
-        <v>0.651526</v>
+        <v>0.6518640000000001</v>
       </c>
       <c r="K876" s="7"/>
     </row>
@@ -34946,25 +34946,25 @@
         <v>6</v>
       </c>
       <c r="E883" s="7">
-        <v>0</v>
+        <v>0.023003999999999997</v>
       </c>
       <c r="F883" s="7">
-        <v>0</v>
+        <v>0.058594</v>
       </c>
       <c r="G883" s="7">
-        <v>0</v>
+        <v>0.22328199999999998</v>
       </c>
       <c r="H883" s="7">
-        <v>0</v>
+        <v>0.331405</v>
       </c>
       <c r="I883" s="7">
-        <v>0</v>
+        <v>0.432369</v>
       </c>
       <c r="J883" s="7">
-        <v>0</v>
+        <v>0.761358</v>
       </c>
       <c r="K883" s="7">
-        <v>0</v>
+        <v>9.478408</v>
       </c>
     </row>
     <row r="884" spans="1:11" x14ac:dyDescent="0.25">
@@ -34981,22 +34981,22 @@
         <v>3</v>
       </c>
       <c r="E884" s="7">
-        <v>0</v>
+        <v>0.034987</v>
       </c>
       <c r="F884" s="7">
-        <v>0</v>
+        <v>0.098628</v>
       </c>
       <c r="G884" s="7">
-        <v>0</v>
+        <v>0.201578</v>
       </c>
       <c r="H884" s="7">
-        <v>0</v>
+        <v>0.29236799999999996</v>
       </c>
       <c r="I884" s="7">
-        <v>0</v>
+        <v>0.459441</v>
       </c>
       <c r="J884" s="7">
-        <v>0</v>
+        <v>2.357001</v>
       </c>
       <c r="K884" s="7"/>
     </row>
@@ -35117,19 +35117,19 @@
         <v>6</v>
       </c>
       <c r="E888" s="7">
-        <v>0.022644</v>
+        <v>0.022942999999999998</v>
       </c>
       <c r="F888" s="7">
-        <v>0.048459</v>
+        <v>0.048766</v>
       </c>
       <c r="G888" s="7">
-        <v>0.46740000000000004</v>
+        <v>0.467829</v>
       </c>
       <c r="H888" s="7">
-        <v>0.489091</v>
+        <v>0.489527</v>
       </c>
       <c r="I888" s="7">
-        <v>0.662733</v>
+        <v>0.66322</v>
       </c>
       <c r="J888" s="7"/>
       <c r="K888" s="7"/>
@@ -35148,25 +35148,25 @@
         <v>6</v>
       </c>
       <c r="E889" s="7">
-        <v>0.014325000000000001</v>
+        <v>0.014322</v>
       </c>
       <c r="F889" s="7">
-        <v>0.064403</v>
+        <v>0.064399</v>
       </c>
       <c r="G889" s="7">
-        <v>0.44177</v>
+        <v>0.441766</v>
       </c>
       <c r="H889" s="7">
-        <v>0.387223</v>
+        <v>0.387219</v>
       </c>
       <c r="I889" s="7">
-        <v>0.490752</v>
+        <v>0.490747</v>
       </c>
       <c r="J889" s="7">
-        <v>2.239716</v>
+        <v>2.239706</v>
       </c>
       <c r="K889" s="7">
-        <v>7.78171</v>
+        <v>7.781683</v>
       </c>
     </row>
     <row r="890" spans="1:11" x14ac:dyDescent="0.25">
@@ -35410,25 +35410,25 @@
         <v>7</v>
       </c>
       <c r="E897" s="7">
-        <v>0</v>
+        <v>-0.180257</v>
       </c>
       <c r="F897" s="7">
-        <v>0</v>
+        <v>-0.35997100000000004</v>
       </c>
       <c r="G897" s="7">
-        <v>0</v>
+        <v>-0.603726</v>
       </c>
       <c r="H897" s="7">
-        <v>0</v>
+        <v>-0.783612</v>
       </c>
       <c r="I897" s="7">
-        <v>0</v>
+        <v>1.6943139999999999</v>
       </c>
       <c r="J897" s="7">
-        <v>0</v>
+        <v>2.362933</v>
       </c>
       <c r="K897" s="7">
-        <v>0</v>
+        <v>18.76882</v>
       </c>
     </row>
     <row r="898" spans="1:11" x14ac:dyDescent="0.25">
@@ -35686,25 +35686,25 @@
         <v>6</v>
       </c>
       <c r="E905" s="7">
-        <v>0</v>
+        <v>0.032188</v>
       </c>
       <c r="F905" s="7">
-        <v>0</v>
+        <v>0.043045</v>
       </c>
       <c r="G905" s="7">
-        <v>0</v>
+        <v>0.173411</v>
       </c>
       <c r="H905" s="7">
-        <v>0</v>
+        <v>0.255741</v>
       </c>
       <c r="I905" s="7">
-        <v>0</v>
+        <v>0.364234</v>
       </c>
       <c r="J905" s="7">
-        <v>0</v>
+        <v>1.251339</v>
       </c>
       <c r="K905" s="7">
-        <v>0</v>
+        <v>4.49856</v>
       </c>
     </row>
     <row r="906" spans="1:11" x14ac:dyDescent="0.25">
@@ -35721,22 +35721,22 @@
         <v>4</v>
       </c>
       <c r="E906" s="7">
-        <v>0</v>
+        <v>0.053899</v>
       </c>
       <c r="F906" s="7">
-        <v>0</v>
+        <v>0.086005</v>
       </c>
       <c r="G906" s="7">
-        <v>0</v>
+        <v>0.14544</v>
       </c>
       <c r="H906" s="7">
-        <v>0</v>
+        <v>0.249875</v>
       </c>
       <c r="I906" s="7">
-        <v>0</v>
+        <v>0.43719</v>
       </c>
       <c r="J906" s="7">
-        <v>0</v>
+        <v>1.73986</v>
       </c>
       <c r="K906" s="7"/>
     </row>
@@ -36121,19 +36121,19 @@
         <v>2</v>
       </c>
       <c r="E918" s="7">
-        <v>0.032703</v>
+        <v>0.034152999999999996</v>
       </c>
       <c r="F918" s="7">
-        <v>0.082228</v>
+        <v>0.083747</v>
       </c>
       <c r="G918" s="7">
-        <v>0.17685800000000002</v>
+        <v>0.17851</v>
       </c>
       <c r="H918" s="7">
-        <v>0.275076</v>
+        <v>0.276866</v>
       </c>
       <c r="I918" s="7">
-        <v>0.444756</v>
+        <v>0.446784</v>
       </c>
       <c r="J918" s="7"/>
       <c r="K918" s="7"/>
@@ -36280,25 +36280,25 @@
         <v>6</v>
       </c>
       <c r="E923" s="7">
-        <v>0</v>
+        <v>0.053864999999999996</v>
       </c>
       <c r="F923" s="7">
-        <v>0</v>
+        <v>0.08999499999999999</v>
       </c>
       <c r="G923" s="7">
-        <v>0</v>
+        <v>-0.032117</v>
       </c>
       <c r="H923" s="7">
-        <v>0</v>
+        <v>0.094361</v>
       </c>
       <c r="I923" s="7">
-        <v>0</v>
+        <v>0.42681600000000003</v>
       </c>
       <c r="J923" s="7">
-        <v>0</v>
+        <v>1.90594</v>
       </c>
       <c r="K923" s="7">
-        <v>0</v>
+        <v>6.469339</v>
       </c>
     </row>
     <row r="924" spans="1:11" x14ac:dyDescent="0.25">
@@ -36680,25 +36680,25 @@
         <v>7</v>
       </c>
       <c r="E935" s="7">
-        <v>0.029804</v>
+        <v>0.030396999999999997</v>
       </c>
       <c r="F935" s="7">
-        <v>0.053673</v>
+        <v>0.054279</v>
       </c>
       <c r="G935" s="7">
-        <v>0.238813</v>
+        <v>0.23952600000000002</v>
       </c>
       <c r="H935" s="7">
-        <v>0.322927</v>
+        <v>0.323688</v>
       </c>
       <c r="I935" s="7">
-        <v>0.42761299999999997</v>
+        <v>0.42843400000000004</v>
       </c>
       <c r="J935" s="7">
-        <v>3.3443310000000004</v>
+        <v>3.3468310000000003</v>
       </c>
       <c r="K935" s="7">
-        <v>18.404118</v>
+        <v>18.415286000000002</v>
       </c>
     </row>
     <row r="936" spans="1:11" x14ac:dyDescent="0.25">
@@ -36785,16 +36785,16 @@
         <v>6</v>
       </c>
       <c r="E938" s="7">
-        <v>0.028672</v>
+        <v>0.026715</v>
       </c>
       <c r="F938" s="7">
-        <v>-0.001187</v>
+        <v>-0.003088</v>
       </c>
       <c r="G938" s="7">
-        <v>0.073636</v>
+        <v>0.071592</v>
       </c>
       <c r="H938" s="7">
-        <v>0.16580899999999998</v>
+        <v>0.16359</v>
       </c>
       <c r="I938" s="7"/>
       <c r="J938" s="7"/>
@@ -36814,22 +36814,22 @@
         <v>5</v>
       </c>
       <c r="E939" s="7">
-        <v>0.062696</v>
+        <v>0.06558</v>
       </c>
       <c r="F939" s="7">
-        <v>0.15376599999999999</v>
+        <v>0.156897</v>
       </c>
       <c r="G939" s="7">
-        <v>0.269998</v>
+        <v>0.273445</v>
       </c>
       <c r="H939" s="7">
-        <v>0.353643</v>
+        <v>0.35731699999999994</v>
       </c>
       <c r="I939" s="7">
-        <v>0.570236</v>
+        <v>0.5744980000000001</v>
       </c>
       <c r="J939" s="7">
-        <v>1.863989</v>
+        <v>1.871762</v>
       </c>
       <c r="K939" s="7"/>
     </row>
@@ -37187,19 +37187,19 @@
         <v>6</v>
       </c>
       <c r="E950" s="7">
-        <v>0.059633000000000005</v>
+        <v>0.05975</v>
       </c>
       <c r="F950" s="7">
-        <v>0.094068</v>
+        <v>0.09418900000000001</v>
       </c>
       <c r="G950" s="7">
-        <v>0.153035</v>
+        <v>0.153162</v>
       </c>
       <c r="H950" s="7">
-        <v>0.310487</v>
+        <v>0.310631</v>
       </c>
       <c r="I950" s="7">
-        <v>0.48484099999999997</v>
+        <v>0.485005</v>
       </c>
       <c r="J950" s="7"/>
       <c r="K950" s="7"/>
@@ -37352,10 +37352,10 @@
         <v>6</v>
       </c>
       <c r="E955" s="7">
-        <v>0</v>
+        <v>0.033059</v>
       </c>
       <c r="F955" s="7">
-        <v>0</v>
+        <v>0.043032</v>
       </c>
       <c r="G955" s="7"/>
       <c r="H955" s="7"/>
@@ -37731,25 +37731,25 @@
         <v>5</v>
       </c>
       <c r="E970" s="7">
-        <v>0</v>
+        <v>0.049303</v>
       </c>
       <c r="F970" s="7">
-        <v>0</v>
+        <v>0.081225</v>
       </c>
       <c r="G970" s="7">
-        <v>0</v>
+        <v>0.12826</v>
       </c>
       <c r="H970" s="7">
-        <v>0</v>
+        <v>0.20613199999999998</v>
       </c>
       <c r="I970" s="7">
-        <v>0</v>
+        <v>0.359608</v>
       </c>
       <c r="J970" s="7">
-        <v>0</v>
+        <v>1.417057</v>
       </c>
       <c r="K970" s="7">
-        <v>0</v>
+        <v>6.01615</v>
       </c>
     </row>
     <row r="971" spans="1:11" x14ac:dyDescent="0.25">
@@ -37828,25 +37828,25 @@
         <v>4</v>
       </c>
       <c r="E973" s="7">
-        <v>0</v>
+        <v>0.035232</v>
       </c>
       <c r="F973" s="7">
-        <v>0</v>
+        <v>0.09757199999999999</v>
       </c>
       <c r="G973" s="7">
-        <v>0</v>
+        <v>0.17582</v>
       </c>
       <c r="H973" s="7">
-        <v>0</v>
+        <v>0.244006</v>
       </c>
       <c r="I973" s="7">
-        <v>0</v>
+        <v>0.377857</v>
       </c>
       <c r="J973" s="7">
-        <v>0</v>
+        <v>1.231262</v>
       </c>
       <c r="K973" s="7">
-        <v>0</v>
+        <v>4.877548</v>
       </c>
     </row>
     <row r="974" spans="1:11" x14ac:dyDescent="0.25">
@@ -38129,22 +38129,22 @@
         <v>2</v>
       </c>
       <c r="E982" s="7">
-        <v>0</v>
+        <v>0.032959999999999996</v>
       </c>
       <c r="F982" s="7">
-        <v>0</v>
+        <v>0.091236</v>
       </c>
       <c r="G982" s="7">
-        <v>0</v>
+        <v>0.19257000000000002</v>
       </c>
       <c r="H982" s="7">
-        <v>0</v>
+        <v>0.280184</v>
       </c>
       <c r="I982" s="7">
-        <v>0</v>
+        <v>0.42928600000000006</v>
       </c>
       <c r="J982" s="7">
-        <v>0</v>
+        <v>1.8117400000000001</v>
       </c>
       <c r="K982" s="7"/>
     </row>
@@ -38661,22 +38661,22 @@
         <v>5</v>
       </c>
       <c r="E998" s="7">
-        <v>0</v>
+        <v>-0.000443</v>
       </c>
       <c r="F998" s="7">
-        <v>0</v>
+        <v>0.017887</v>
       </c>
       <c r="G998" s="7">
-        <v>0</v>
+        <v>0.431265</v>
       </c>
       <c r="H998" s="7">
-        <v>0</v>
+        <v>0.48637099999999994</v>
       </c>
       <c r="I998" s="7">
-        <v>0</v>
+        <v>0.6986960000000001</v>
       </c>
       <c r="J998" s="7">
-        <v>0</v>
+        <v>2.358741</v>
       </c>
       <c r="K998" s="7"/>
     </row>
@@ -39284,25 +39284,25 @@
         <v>5</v>
       </c>
       <c r="E1017" s="7">
-        <v>0</v>
+        <v>0.060186</v>
       </c>
       <c r="F1017" s="7">
-        <v>0</v>
+        <v>0.080909</v>
       </c>
       <c r="G1017" s="7">
-        <v>0</v>
+        <v>0.126364</v>
       </c>
       <c r="H1017" s="7">
-        <v>0</v>
+        <v>0.211904</v>
       </c>
       <c r="I1017" s="7">
-        <v>0</v>
+        <v>0.288939</v>
       </c>
       <c r="J1017" s="7">
-        <v>0</v>
+        <v>1.116307</v>
       </c>
       <c r="K1017" s="7">
-        <v>0</v>
+        <v>4.731812</v>
       </c>
     </row>
     <row r="1018" spans="1:11" x14ac:dyDescent="0.25">
@@ -39466,25 +39466,25 @@
         <v>6</v>
       </c>
       <c r="E1023" s="7">
-        <v>0</v>
+        <v>0.060354</v>
       </c>
       <c r="F1023" s="7">
-        <v>0</v>
+        <v>0.079028</v>
       </c>
       <c r="G1023" s="7">
-        <v>0</v>
+        <v>0.318245</v>
       </c>
       <c r="H1023" s="7">
-        <v>0</v>
+        <v>0.264432</v>
       </c>
       <c r="I1023" s="7">
-        <v>0</v>
+        <v>0.463048</v>
       </c>
       <c r="J1023" s="7">
-        <v>0</v>
+        <v>2.20272</v>
       </c>
       <c r="K1023" s="7">
-        <v>0</v>
+        <v>8.6577</v>
       </c>
     </row>
     <row r="1024" spans="1:11" x14ac:dyDescent="0.25">
@@ -39753,25 +39753,25 @@
         <v>7</v>
       </c>
       <c r="E1032" s="7">
-        <v>0</v>
+        <v>0.070164</v>
       </c>
       <c r="F1032" s="7">
-        <v>0</v>
+        <v>0.033817</v>
       </c>
       <c r="G1032" s="7">
-        <v>0</v>
+        <v>-0.134832</v>
       </c>
       <c r="H1032" s="7">
-        <v>0</v>
+        <v>0.017861000000000002</v>
       </c>
       <c r="I1032" s="7">
-        <v>0</v>
+        <v>0.823215</v>
       </c>
       <c r="J1032" s="7">
-        <v>0</v>
+        <v>3.7823480000000003</v>
       </c>
       <c r="K1032" s="7">
-        <v>0</v>
+        <v>12.054922999999999</v>
       </c>
     </row>
     <row r="1033" spans="1:11" x14ac:dyDescent="0.25">
@@ -40077,22 +40077,22 @@
         <v>6</v>
       </c>
       <c r="E1042" s="7">
-        <v>0.076048</v>
+        <v>0.076182</v>
       </c>
       <c r="F1042" s="7">
-        <v>0.101798</v>
+        <v>0.101935</v>
       </c>
       <c r="G1042" s="7">
-        <v>0.110555</v>
+        <v>0.110693</v>
       </c>
       <c r="H1042" s="7">
-        <v>0.27235499999999996</v>
+        <v>0.272514</v>
       </c>
       <c r="I1042" s="7">
-        <v>0.479234</v>
+        <v>0.479418</v>
       </c>
       <c r="J1042" s="7">
-        <v>1.808018</v>
+        <v>1.808367</v>
       </c>
       <c r="K1042" s="7"/>
     </row>
@@ -40638,25 +40638,25 @@
         <v>5</v>
       </c>
       <c r="E1059" s="7">
-        <v>0.062196</v>
+        <v>0.062232</v>
       </c>
       <c r="F1059" s="7">
-        <v>0.10213</v>
+        <v>0.102167</v>
       </c>
       <c r="G1059" s="7">
-        <v>0.139829</v>
+        <v>0.13986700000000002</v>
       </c>
       <c r="H1059" s="7">
-        <v>0.191197</v>
+        <v>0.191237</v>
       </c>
       <c r="I1059" s="7">
-        <v>0.28351299999999996</v>
+        <v>0.283555</v>
       </c>
       <c r="J1059" s="7">
-        <v>1.249754</v>
+        <v>1.249829</v>
       </c>
       <c r="K1059" s="7">
-        <v>7.350401000000001</v>
+        <v>7.35068</v>
       </c>
     </row>
     <row r="1060" spans="1:11" x14ac:dyDescent="0.25">
@@ -40863,22 +40863,22 @@
         <v>6</v>
       </c>
       <c r="E1066" s="7">
-        <v>0.039845</v>
+        <v>0.04054700000000001</v>
       </c>
       <c r="F1066" s="7">
-        <v>0.049471999999999995</v>
+        <v>0.050180999999999996</v>
       </c>
       <c r="G1066" s="7">
-        <v>0.20367999999999997</v>
+        <v>0.204492</v>
       </c>
       <c r="H1066" s="7">
-        <v>0.27884</v>
+        <v>0.27970300000000003</v>
       </c>
       <c r="I1066" s="7">
-        <v>0.411559</v>
+        <v>0.412512</v>
       </c>
       <c r="J1066" s="7">
-        <v>1.392329</v>
+        <v>1.3939439999999998</v>
       </c>
       <c r="K1066" s="7"/>
     </row>
@@ -40896,19 +40896,19 @@
         <v>5</v>
       </c>
       <c r="E1067" s="7">
-        <v>0.065607</v>
+        <v>0.064982</v>
       </c>
       <c r="F1067" s="7">
-        <v>0.17762599999999998</v>
+        <v>0.176935</v>
       </c>
       <c r="G1067" s="7">
-        <v>0.21878399999999998</v>
+        <v>0.21806999999999999</v>
       </c>
       <c r="H1067" s="7">
-        <v>0.303336</v>
+        <v>0.30257100000000003</v>
       </c>
       <c r="I1067" s="7">
-        <v>0.345132</v>
+        <v>0.344343</v>
       </c>
       <c r="J1067" s="7"/>
       <c r="K1067" s="7"/>
